--- a/examples/ltd-latest/Fixedassets.xlsx
+++ b/examples/ltd-latest/Fixedassets.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS AT </t>
   </si>
   <si>
-    <t xml:space="preserve">Land &amp; Property</t>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Plant &amp; Machinery</t>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t xml:space="preserve">to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">New Land &amp; Property</t>
@@ -655,7 +658,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -836,10 +839,22 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -860,64 +875,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1285,11 +1292,6 @@
         <row r="5">
           <cell r="G5">
             <v>100</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6">
-            <v>45748</v>
           </cell>
         </row>
         <row r="7">
@@ -1649,13 +1651,13 @@
       <c r="C4" s="20"/>
       <c r="D4" s="21"/>
       <c r="E4" s="22"/>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="26" t="str">
         <f aca="false">D6</f>
-        <v>45748</v>
-      </c>
-      <c r="G4" s="26" t="n">
+        <v>Laptop (0.5 years old)</v>
+      </c>
+      <c r="G4" s="26" t="str">
         <f aca="false">D6</f>
-        <v>45748</v>
+        <v>Laptop (0.5 years old)</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="23"/>
@@ -1670,9 +1672,9 @@
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
       <c r="N4" s="13"/>
-      <c r="O4" s="10" t="n">
+      <c r="O4" s="10" t="str">
         <f aca="false">D6</f>
-        <v>45748</v>
+        <v>Laptop (0.5 years old)</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>100</v>
@@ -1729,65 +1731,44 @@
         <v>20</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="n">
-        <f aca="false">[1]Admin!$L$6</f>
-        <v>45748</v>
-      </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42"/>
-      <c r="B7" s="51" t="s">
+      <c r="D6" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
+      <c r="E6" s="44" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="50"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1797,7 +1778,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="50" t="str">
+      <c r="G8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -1805,39 +1786,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="50" t="str">
+      <c r="I8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="50" t="str">
+      <c r="J8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="50" t="str">
+      <c r="K8" s="53" t="str">
         <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
         <v> </v>
       </c>
-      <c r="L8" s="50"/>
+      <c r="L8" s="53"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="50" t="str">
+      <c r="W8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="50" t="str">
+      <c r="X8" s="53" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1847,7 +1828,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="50" t="str">
+      <c r="G9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -1855,39 +1836,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="50" t="str">
+      <c r="I9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="50" t="str">
+      <c r="J9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="50" t="str">
+      <c r="K9" s="53" t="str">
         <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
         <v> </v>
       </c>
-      <c r="L9" s="50"/>
+      <c r="L9" s="53"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
+      <c r="T9" s="50"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="50" t="str">
+      <c r="W9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="50" t="str">
+      <c r="X9" s="53" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="50"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1897,7 +1878,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="50" t="str">
+      <c r="G10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -1905,39 +1886,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="50" t="str">
+      <c r="I10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="50" t="str">
+      <c r="J10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="50" t="str">
+      <c r="K10" s="53" t="str">
         <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
         <v> </v>
       </c>
-      <c r="L10" s="50"/>
+      <c r="L10" s="53"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="50" t="str">
+      <c r="W10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="50" t="str">
+      <c r="X10" s="53" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
+      <c r="Y10" s="50"/>
+      <c r="Z10" s="50"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1973,9 +1954,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="50"/>
+      <c r="L11" s="53"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="50"/>
+      <c r="N11" s="53"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -1993,8 +1974,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="47"/>
-      <c r="U11" s="49"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="52"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2022,61 +2003,61 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="53"/>
+      <c r="W12" s="53"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="53"/>
+      <c r="Z12" s="53"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="51"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="66" t="n">
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="67" t="n">
         <v>0.1</v>
       </c>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="52"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="53"/>
+      <c r="X13" s="53"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="50"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2086,7 +2067,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="50" t="str">
+      <c r="G14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2094,48 +2075,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="50" t="str">
+      <c r="I14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="50" t="str">
+      <c r="J14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="50" t="str">
+      <c r="K14" s="53" t="str">
         <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
         <v> </v>
       </c>
-      <c r="L14" s="50"/>
+      <c r="L14" s="53"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47" t="str">
+      <c r="N14" s="53"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="47" t="str">
+      <c r="S14" s="50" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="47"/>
+      <c r="T14" s="50"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="50" t="str">
+      <c r="W14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="50" t="str">
+      <c r="X14" s="53" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="47" t="str">
+      <c r="Y14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="47" t="str">
+      <c r="Z14" s="50" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2148,7 +2129,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="50" t="str">
+      <c r="G15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2156,48 +2137,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="50" t="str">
+      <c r="I15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="50" t="str">
+      <c r="J15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="50" t="str">
+      <c r="K15" s="53" t="str">
         <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
         <v> </v>
       </c>
-      <c r="L15" s="50"/>
+      <c r="L15" s="53"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47" t="str">
+      <c r="N15" s="53"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="47" t="str">
+      <c r="S15" s="50" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="47"/>
+      <c r="T15" s="50"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="50" t="str">
+      <c r="W15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="50" t="str">
+      <c r="X15" s="53" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="47" t="str">
+      <c r="Y15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="47" t="str">
+      <c r="Z15" s="50" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2210,7 +2191,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="50" t="str">
+      <c r="G16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2218,48 +2199,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="50" t="str">
+      <c r="I16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="50" t="str">
+      <c r="J16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="50" t="str">
+      <c r="K16" s="53" t="str">
         <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
         <v> </v>
       </c>
-      <c r="L16" s="50"/>
+      <c r="L16" s="53"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47" t="str">
+      <c r="N16" s="53"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="47" t="str">
+      <c r="S16" s="50" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="47"/>
+      <c r="T16" s="50"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="50" t="str">
+      <c r="W16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="50" t="str">
+      <c r="X16" s="53" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="47" t="str">
+      <c r="Y16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="47" t="str">
+      <c r="Z16" s="50" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2272,7 +2253,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="50" t="str">
+      <c r="G17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2280,48 +2261,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="50" t="str">
+      <c r="I17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="50" t="str">
+      <c r="J17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="50" t="str">
+      <c r="K17" s="53" t="str">
         <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
         <v> </v>
       </c>
-      <c r="L17" s="50"/>
+      <c r="L17" s="53"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47" t="str">
+      <c r="N17" s="53"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="47" t="str">
+      <c r="S17" s="50" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="47"/>
+      <c r="T17" s="50"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="50" t="str">
+      <c r="W17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="50" t="str">
+      <c r="X17" s="53" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="47" t="str">
+      <c r="Y17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="47" t="str">
+      <c r="Z17" s="50" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2334,7 +2315,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="50" t="str">
+      <c r="G18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2342,48 +2323,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="50" t="str">
+      <c r="I18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="50" t="str">
+      <c r="J18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="50" t="str">
+      <c r="K18" s="53" t="str">
         <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
         <v> </v>
       </c>
-      <c r="L18" s="50"/>
+      <c r="L18" s="53"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47" t="str">
+      <c r="N18" s="53"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="47" t="str">
+      <c r="S18" s="50" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="47"/>
+      <c r="T18" s="50"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="50" t="str">
+      <c r="W18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="50" t="str">
+      <c r="X18" s="53" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="47" t="str">
+      <c r="Y18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="47" t="str">
+      <c r="Z18" s="50" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2396,7 +2377,7 @@
       <c r="D19" s="56"/>
       <c r="E19" s="57"/>
       <c r="F19" s="57"/>
-      <c r="G19" s="50" t="str">
+      <c r="G19" s="53" t="str">
         <f aca="false">IF(E19&gt;0,E19-F19," ")</f>
         <v> </v>
       </c>
@@ -2404,48 +2385,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I19" s="50" t="str">
+      <c r="I19" s="53" t="str">
         <f aca="false">IF(E19&gt;0,MIN(E19*H19,G19)," ")</f>
         <v> </v>
       </c>
-      <c r="J19" s="50" t="str">
+      <c r="J19" s="53" t="str">
         <f aca="false">IF(E19&gt;0,F19+I19," ")</f>
         <v> </v>
       </c>
-      <c r="K19" s="50" t="str">
+      <c r="K19" s="53" t="str">
         <f aca="false">IF(E19&gt;0,E19-J19," ")</f>
         <v> </v>
       </c>
-      <c r="L19" s="50"/>
+      <c r="L19" s="53"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47" t="str">
+      <c r="N19" s="53"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="50" t="str">
         <f aca="false">IF(O19&gt;0,O19*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S19" s="47" t="str">
+      <c r="S19" s="50" t="str">
         <f aca="false">IF(O19&gt;0,O19-R19," ")</f>
         <v> </v>
       </c>
-      <c r="T19" s="47"/>
+      <c r="T19" s="50"/>
       <c r="U19" s="54"/>
       <c r="V19" s="57"/>
-      <c r="W19" s="50" t="str">
+      <c r="W19" s="53" t="str">
         <f aca="false">IF(V19&gt;0,E19," ")</f>
         <v> </v>
       </c>
-      <c r="X19" s="50" t="str">
+      <c r="X19" s="53" t="str">
         <f aca="false">IF(V19&gt;0,J19," ")</f>
         <v> </v>
       </c>
-      <c r="Y19" s="47" t="str">
+      <c r="Y19" s="50" t="str">
         <f aca="false">IF((U19+V19)&gt;0,IF(V19&lt;S19,S19-V19," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z19" s="47" t="str">
+      <c r="Z19" s="50" t="str">
         <f aca="false">IF((U19+V19)&gt;0,IF(V19&gt;S19,V19-S19," ")," ")</f>
         <v> </v>
       </c>
@@ -2458,7 +2439,7 @@
       <c r="D20" s="56"/>
       <c r="E20" s="57"/>
       <c r="F20" s="57"/>
-      <c r="G20" s="50" t="str">
+      <c r="G20" s="53" t="str">
         <f aca="false">IF(E20&gt;0,E20-F20," ")</f>
         <v> </v>
       </c>
@@ -2466,48 +2447,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I20" s="50" t="str">
+      <c r="I20" s="53" t="str">
         <f aca="false">IF(E20&gt;0,MIN(E20*H20,G20)," ")</f>
         <v> </v>
       </c>
-      <c r="J20" s="50" t="str">
+      <c r="J20" s="53" t="str">
         <f aca="false">IF(E20&gt;0,F20+I20," ")</f>
         <v> </v>
       </c>
-      <c r="K20" s="50" t="str">
+      <c r="K20" s="53" t="str">
         <f aca="false">IF(E20&gt;0,E20-J20," ")</f>
         <v> </v>
       </c>
-      <c r="L20" s="50"/>
+      <c r="L20" s="53"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47" t="str">
+      <c r="N20" s="53"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50" t="str">
         <f aca="false">IF(O20&gt;0,O20*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S20" s="47" t="str">
+      <c r="S20" s="50" t="str">
         <f aca="false">IF(O20&gt;0,O20-R20," ")</f>
         <v> </v>
       </c>
-      <c r="T20" s="47"/>
+      <c r="T20" s="50"/>
       <c r="U20" s="54"/>
       <c r="V20" s="57"/>
-      <c r="W20" s="50" t="str">
+      <c r="W20" s="53" t="str">
         <f aca="false">IF(V20&gt;0,E20," ")</f>
         <v> </v>
       </c>
-      <c r="X20" s="50" t="str">
+      <c r="X20" s="53" t="str">
         <f aca="false">IF(V20&gt;0,J20," ")</f>
         <v> </v>
       </c>
-      <c r="Y20" s="47" t="str">
+      <c r="Y20" s="50" t="str">
         <f aca="false">IF((U20+V20)&gt;0,IF(V20&lt;S20,S20-V20," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z20" s="47" t="str">
+      <c r="Z20" s="50" t="str">
         <f aca="false">IF((U20+V20)&gt;0,IF(V20&gt;S20,V20-S20," ")," ")</f>
         <v> </v>
       </c>
@@ -2520,7 +2501,7 @@
       <c r="D21" s="56"/>
       <c r="E21" s="57"/>
       <c r="F21" s="57"/>
-      <c r="G21" s="50" t="str">
+      <c r="G21" s="53" t="str">
         <f aca="false">IF(E21&gt;0,E21-F21," ")</f>
         <v> </v>
       </c>
@@ -2528,48 +2509,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I21" s="50" t="str">
+      <c r="I21" s="53" t="str">
         <f aca="false">IF(E21&gt;0,MIN(E21*H21,G21)," ")</f>
         <v> </v>
       </c>
-      <c r="J21" s="50" t="str">
+      <c r="J21" s="53" t="str">
         <f aca="false">IF(E21&gt;0,F21+I21," ")</f>
         <v> </v>
       </c>
-      <c r="K21" s="50" t="str">
+      <c r="K21" s="53" t="str">
         <f aca="false">IF(E21&gt;0,E21-J21," ")</f>
         <v> </v>
       </c>
-      <c r="L21" s="50"/>
+      <c r="L21" s="53"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47" t="str">
+      <c r="N21" s="53"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50" t="str">
         <f aca="false">IF(O21&gt;0,O21*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S21" s="47" t="str">
+      <c r="S21" s="50" t="str">
         <f aca="false">IF(O21&gt;0,O21-R21," ")</f>
         <v> </v>
       </c>
-      <c r="T21" s="47"/>
+      <c r="T21" s="50"/>
       <c r="U21" s="54"/>
       <c r="V21" s="57"/>
-      <c r="W21" s="50" t="str">
+      <c r="W21" s="53" t="str">
         <f aca="false">IF(V21&gt;0,E21," ")</f>
         <v> </v>
       </c>
-      <c r="X21" s="50" t="str">
+      <c r="X21" s="53" t="str">
         <f aca="false">IF(V21&gt;0,J21," ")</f>
         <v> </v>
       </c>
-      <c r="Y21" s="47" t="str">
+      <c r="Y21" s="50" t="str">
         <f aca="false">IF((U21+V21)&gt;0,IF(V21&lt;S21,S21-V21," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z21" s="47" t="str">
+      <c r="Z21" s="50" t="str">
         <f aca="false">IF((U21+V21)&gt;0,IF(V21&gt;S21,V21-S21," ")," ")</f>
         <v> </v>
       </c>
@@ -2608,9 +2589,9 @@
         <f aca="false">SUM(K14:K21)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="50"/>
+      <c r="L22" s="53"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="50"/>
+      <c r="N22" s="53"/>
       <c r="O22" s="61" t="n">
         <f aca="false">SUM(O14:O21)</f>
         <v>0</v>
@@ -2628,8 +2609,8 @@
         <f aca="false">SUM(S14:S21)</f>
         <v>0</v>
       </c>
-      <c r="T22" s="47"/>
-      <c r="U22" s="49"/>
+      <c r="T22" s="50"/>
+      <c r="U22" s="52"/>
       <c r="V22" s="60" t="n">
         <f aca="false">SUM(V14:V21)</f>
         <v>0</v>
@@ -2657,61 +2638,61 @@
       <c r="B23" s="63"/>
       <c r="C23" s="64"/>
       <c r="D23" s="65"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
       <c r="H23" s="58"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
       <c r="P23" s="62"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="49"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="50"/>
-      <c r="Y23" s="50"/>
-      <c r="Z23" s="50"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="52"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="53"/>
+      <c r="Y23" s="53"/>
+      <c r="Z23" s="53"/>
       <c r="AA23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="42"/>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="51"/>
+      <c r="C24" s="66"/>
       <c r="D24" s="62"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="66" t="n">
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="67" t="n">
         <v>0.2</v>
       </c>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47"/>
-      <c r="S24" s="47"/>
-      <c r="T24" s="47"/>
-      <c r="U24" s="49"/>
-      <c r="V24" s="50"/>
-      <c r="W24" s="50"/>
-      <c r="X24" s="50"/>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="47"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="50"/>
+      <c r="S24" s="50"/>
+      <c r="T24" s="50"/>
+      <c r="U24" s="52"/>
+      <c r="V24" s="53"/>
+      <c r="W24" s="53"/>
+      <c r="X24" s="53"/>
+      <c r="Y24" s="50"/>
+      <c r="Z24" s="50"/>
       <c r="AA24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2721,7 +2702,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="50" t="str">
+      <c r="G25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2729,48 +2710,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="50" t="str">
+      <c r="I25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="50" t="str">
+      <c r="J25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="50" t="str">
+      <c r="K25" s="53" t="str">
         <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
         <v> </v>
       </c>
-      <c r="L25" s="50"/>
+      <c r="L25" s="53"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47" t="str">
+      <c r="N25" s="53"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="47" t="str">
+      <c r="S25" s="50" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="47"/>
+      <c r="T25" s="50"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="50" t="str">
+      <c r="W25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="50" t="str">
+      <c r="X25" s="53" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="47" t="str">
+      <c r="Y25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="47" t="str">
+      <c r="Z25" s="50" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2783,7 +2764,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="50" t="str">
+      <c r="G26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -2791,48 +2772,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="50" t="str">
+      <c r="I26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="50" t="str">
+      <c r="J26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="50" t="str">
+      <c r="K26" s="53" t="str">
         <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
         <v> </v>
       </c>
-      <c r="L26" s="50"/>
+      <c r="L26" s="53"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47" t="str">
+      <c r="N26" s="53"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="47" t="str">
+      <c r="S26" s="50" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="47"/>
+      <c r="T26" s="50"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="50" t="str">
+      <c r="W26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="50" t="str">
+      <c r="X26" s="53" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="47" t="str">
+      <c r="Y26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="47" t="str">
+      <c r="Z26" s="50" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -2845,7 +2826,7 @@
       <c r="D27" s="56"/>
       <c r="E27" s="57"/>
       <c r="F27" s="57"/>
-      <c r="G27" s="50" t="str">
+      <c r="G27" s="53" t="str">
         <f aca="false">IF(E27&gt;0,E27-F27," ")</f>
         <v> </v>
       </c>
@@ -2853,48 +2834,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I27" s="50" t="str">
+      <c r="I27" s="53" t="str">
         <f aca="false">IF(E27&gt;0,MIN(E27*H27,G27)," ")</f>
         <v> </v>
       </c>
-      <c r="J27" s="50" t="str">
+      <c r="J27" s="53" t="str">
         <f aca="false">IF(E27&gt;0,F27+I27," ")</f>
         <v> </v>
       </c>
-      <c r="K27" s="50" t="str">
+      <c r="K27" s="53" t="str">
         <f aca="false">IF(E27&gt;0,E27-J27," ")</f>
         <v> </v>
       </c>
-      <c r="L27" s="50"/>
+      <c r="L27" s="53"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47" t="str">
+      <c r="N27" s="53"/>
+      <c r="O27" s="68"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50" t="str">
         <f aca="false">IF(O27&gt;0,O27*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S27" s="47" t="str">
+      <c r="S27" s="50" t="str">
         <f aca="false">IF(O27&gt;0,O27-R27," ")</f>
         <v> </v>
       </c>
-      <c r="T27" s="47"/>
+      <c r="T27" s="50"/>
       <c r="U27" s="54"/>
       <c r="V27" s="57"/>
-      <c r="W27" s="50" t="str">
+      <c r="W27" s="53" t="str">
         <f aca="false">IF(V27&gt;0,E27," ")</f>
         <v> </v>
       </c>
-      <c r="X27" s="50" t="str">
+      <c r="X27" s="53" t="str">
         <f aca="false">IF(V27&gt;0,J27," ")</f>
         <v> </v>
       </c>
-      <c r="Y27" s="47" t="str">
+      <c r="Y27" s="50" t="str">
         <f aca="false">IF((U27+V27)&gt;0,IF(V27&lt;S27,S27-V27," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z27" s="47" t="str">
+      <c r="Z27" s="50" t="str">
         <f aca="false">IF((U27+V27)&gt;0,IF(V27&gt;S27,V27-S27," ")," ")</f>
         <v> </v>
       </c>
@@ -2907,7 +2888,7 @@
       <c r="D28" s="56"/>
       <c r="E28" s="57"/>
       <c r="F28" s="57"/>
-      <c r="G28" s="50" t="str">
+      <c r="G28" s="53" t="str">
         <f aca="false">IF(E28&gt;0,E28-F28," ")</f>
         <v> </v>
       </c>
@@ -2915,48 +2896,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I28" s="50" t="str">
+      <c r="I28" s="53" t="str">
         <f aca="false">IF(E28&gt;0,MIN(E28*H28,G28)," ")</f>
         <v> </v>
       </c>
-      <c r="J28" s="50" t="str">
+      <c r="J28" s="53" t="str">
         <f aca="false">IF(E28&gt;0,F28+I28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="50" t="str">
+      <c r="K28" s="53" t="str">
         <f aca="false">IF(E28&gt;0,E28-J28," ")</f>
         <v> </v>
       </c>
-      <c r="L28" s="50"/>
+      <c r="L28" s="53"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="47"/>
-      <c r="R28" s="47" t="str">
+      <c r="N28" s="53"/>
+      <c r="O28" s="68"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50" t="str">
         <f aca="false">IF(O28&gt;0,O28*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S28" s="47" t="str">
+      <c r="S28" s="50" t="str">
         <f aca="false">IF(O28&gt;0,O28-R28," ")</f>
         <v> </v>
       </c>
-      <c r="T28" s="47"/>
+      <c r="T28" s="50"/>
       <c r="U28" s="54"/>
       <c r="V28" s="57"/>
-      <c r="W28" s="50" t="str">
+      <c r="W28" s="53" t="str">
         <f aca="false">IF(V28&gt;0,E28," ")</f>
         <v> </v>
       </c>
-      <c r="X28" s="50" t="str">
+      <c r="X28" s="53" t="str">
         <f aca="false">IF(V28&gt;0,J28," ")</f>
         <v> </v>
       </c>
-      <c r="Y28" s="47" t="str">
+      <c r="Y28" s="50" t="str">
         <f aca="false">IF((U28+V28)&gt;0,IF(V28&lt;S28,S28-V28," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z28" s="47" t="str">
+      <c r="Z28" s="50" t="str">
         <f aca="false">IF((U28+V28)&gt;0,IF(V28&gt;S28,V28-S28," ")," ")</f>
         <v> </v>
       </c>
@@ -2969,7 +2950,7 @@
       <c r="D29" s="56"/>
       <c r="E29" s="57"/>
       <c r="F29" s="57"/>
-      <c r="G29" s="50" t="str">
+      <c r="G29" s="53" t="str">
         <f aca="false">IF(E29&gt;0,E29-F29," ")</f>
         <v> </v>
       </c>
@@ -2977,48 +2958,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I29" s="50" t="str">
+      <c r="I29" s="53" t="str">
         <f aca="false">IF(E29&gt;0,MIN(E29*H29,G29)," ")</f>
         <v> </v>
       </c>
-      <c r="J29" s="50" t="str">
+      <c r="J29" s="53" t="str">
         <f aca="false">IF(E29&gt;0,F29+I29," ")</f>
         <v> </v>
       </c>
-      <c r="K29" s="50" t="str">
+      <c r="K29" s="53" t="str">
         <f aca="false">IF(E29&gt;0,E29-J29," ")</f>
         <v> </v>
       </c>
-      <c r="L29" s="50"/>
+      <c r="L29" s="53"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="67"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47" t="str">
+      <c r="N29" s="53"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50" t="str">
         <f aca="false">IF(O29&gt;0,O29*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S29" s="47" t="str">
+      <c r="S29" s="50" t="str">
         <f aca="false">IF(O29&gt;0,O29-R29," ")</f>
         <v> </v>
       </c>
-      <c r="T29" s="47"/>
+      <c r="T29" s="50"/>
       <c r="U29" s="54"/>
       <c r="V29" s="57"/>
-      <c r="W29" s="50" t="str">
+      <c r="W29" s="53" t="str">
         <f aca="false">IF(V29&gt;0,E29," ")</f>
         <v> </v>
       </c>
-      <c r="X29" s="50" t="str">
+      <c r="X29" s="53" t="str">
         <f aca="false">IF(V29&gt;0,J29," ")</f>
         <v> </v>
       </c>
-      <c r="Y29" s="47" t="str">
+      <c r="Y29" s="50" t="str">
         <f aca="false">IF((U29+V29)&gt;0,IF(V29&lt;S29,S29-V29," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z29" s="47" t="str">
+      <c r="Z29" s="50" t="str">
         <f aca="false">IF((U29+V29)&gt;0,IF(V29&gt;S29,V29-S29," ")," ")</f>
         <v> </v>
       </c>
@@ -3057,9 +3038,9 @@
         <f aca="false">SUM(K25:K29)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="50"/>
+      <c r="L30" s="53"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="50"/>
+      <c r="N30" s="53"/>
       <c r="O30" s="61" t="n">
         <f aca="false">SUM(O25:O29)</f>
         <v>0</v>
@@ -3077,8 +3058,8 @@
         <f aca="false">SUM(S25:S29)</f>
         <v>0</v>
       </c>
-      <c r="T30" s="47"/>
-      <c r="U30" s="49"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="52"/>
       <c r="V30" s="60" t="n">
         <f aca="false">SUM(V25:V29)</f>
         <v>0</v>
@@ -3106,61 +3087,61 @@
       <c r="B31" s="63"/>
       <c r="C31" s="64"/>
       <c r="D31" s="65"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
       <c r="H31" s="58"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
       <c r="P31" s="62"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="47"/>
-      <c r="U31" s="49"/>
-      <c r="V31" s="50"/>
-      <c r="W31" s="50"/>
-      <c r="X31" s="50"/>
-      <c r="Y31" s="50"/>
-      <c r="Z31" s="50"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="53"/>
+      <c r="S31" s="53"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="52"/>
+      <c r="V31" s="53"/>
+      <c r="W31" s="53"/>
+      <c r="X31" s="53"/>
+      <c r="Y31" s="53"/>
+      <c r="Z31" s="53"/>
       <c r="AA31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="42"/>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="66" t="n">
+      <c r="C32" s="66"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="67" t="n">
         <v>0.33</v>
       </c>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="47"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47"/>
-      <c r="S32" s="47"/>
-      <c r="T32" s="47"/>
-      <c r="U32" s="49"/>
-      <c r="V32" s="50"/>
-      <c r="W32" s="50"/>
-      <c r="X32" s="50"/>
-      <c r="Y32" s="47"/>
-      <c r="Z32" s="47"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="53"/>
+      <c r="W32" s="53"/>
+      <c r="X32" s="53"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="50"/>
       <c r="AA32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3170,7 +3151,7 @@
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
       <c r="F33" s="57"/>
-      <c r="G33" s="50" t="str">
+      <c r="G33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
         <v> </v>
       </c>
@@ -3178,48 +3159,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="50" t="str">
+      <c r="I33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="50" t="str">
+      <c r="J33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="50" t="str">
+      <c r="K33" s="53" t="str">
         <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
         <v> </v>
       </c>
-      <c r="L33" s="50"/>
+      <c r="L33" s="53"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47" t="str">
+      <c r="N33" s="53"/>
+      <c r="O33" s="68"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="47" t="str">
+      <c r="S33" s="50" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="47"/>
+      <c r="T33" s="50"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="50" t="str">
+      <c r="W33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="50" t="str">
+      <c r="X33" s="53" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="47" t="str">
+      <c r="Y33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="47" t="str">
+      <c r="Z33" s="50" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3232,7 +3213,7 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="50" t="str">
+      <c r="G34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
         <v> </v>
       </c>
@@ -3240,48 +3221,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="50" t="str">
+      <c r="I34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="50" t="str">
+      <c r="J34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="50" t="str">
+      <c r="K34" s="53" t="str">
         <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
         <v> </v>
       </c>
-      <c r="L34" s="50"/>
+      <c r="L34" s="53"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="67"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47" t="str">
+      <c r="N34" s="53"/>
+      <c r="O34" s="68"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="50"/>
+      <c r="R34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="47" t="str">
+      <c r="S34" s="50" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="47"/>
+      <c r="T34" s="50"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="50" t="str">
+      <c r="W34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="50" t="str">
+      <c r="X34" s="53" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="47" t="str">
+      <c r="Y34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="47" t="str">
+      <c r="Z34" s="50" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3294,7 +3275,7 @@
       <c r="D35" s="56"/>
       <c r="E35" s="57"/>
       <c r="F35" s="57"/>
-      <c r="G35" s="50" t="str">
+      <c r="G35" s="53" t="str">
         <f aca="false">IF(E35&gt;0,E35-F35," ")</f>
         <v> </v>
       </c>
@@ -3302,48 +3283,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I35" s="50" t="str">
+      <c r="I35" s="53" t="str">
         <f aca="false">IF(E35&gt;0,MIN(E35*H35,G35)," ")</f>
         <v> </v>
       </c>
-      <c r="J35" s="50" t="str">
+      <c r="J35" s="53" t="str">
         <f aca="false">IF(E35&gt;0,F35+I35," ")</f>
         <v> </v>
       </c>
-      <c r="K35" s="50" t="str">
+      <c r="K35" s="53" t="str">
         <f aca="false">IF(E35&gt;0,E35-J35," ")</f>
         <v> </v>
       </c>
-      <c r="L35" s="50"/>
+      <c r="L35" s="53"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47" t="str">
+      <c r="N35" s="53"/>
+      <c r="O35" s="68"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="50" t="str">
         <f aca="false">IF(O35&gt;0,O35*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S35" s="47" t="str">
+      <c r="S35" s="50" t="str">
         <f aca="false">IF(O35&gt;0,O35-R35," ")</f>
         <v> </v>
       </c>
-      <c r="T35" s="47"/>
+      <c r="T35" s="50"/>
       <c r="U35" s="54"/>
       <c r="V35" s="57"/>
-      <c r="W35" s="50" t="str">
+      <c r="W35" s="53" t="str">
         <f aca="false">IF(V35&gt;0,E35," ")</f>
         <v> </v>
       </c>
-      <c r="X35" s="50" t="str">
+      <c r="X35" s="53" t="str">
         <f aca="false">IF(V35&gt;0,J35," ")</f>
         <v> </v>
       </c>
-      <c r="Y35" s="47" t="str">
+      <c r="Y35" s="50" t="str">
         <f aca="false">IF((U35+V35)&gt;0,IF(V35&lt;S35,S35-V35," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z35" s="47" t="str">
+      <c r="Z35" s="50" t="str">
         <f aca="false">IF((U35+V35)&gt;0,IF(V35&gt;S35,V35-S35," ")," ")</f>
         <v> </v>
       </c>
@@ -3356,7 +3337,7 @@
       <c r="D36" s="56"/>
       <c r="E36" s="57"/>
       <c r="F36" s="57"/>
-      <c r="G36" s="50" t="str">
+      <c r="G36" s="53" t="str">
         <f aca="false">IF(E36&gt;0,E36-F36," ")</f>
         <v> </v>
       </c>
@@ -3364,48 +3345,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I36" s="50" t="str">
+      <c r="I36" s="53" t="str">
         <f aca="false">IF(E36&gt;0,MIN(E36*H36,G36)," ")</f>
         <v> </v>
       </c>
-      <c r="J36" s="50" t="str">
+      <c r="J36" s="53" t="str">
         <f aca="false">IF(E36&gt;0,F36+I36," ")</f>
         <v> </v>
       </c>
-      <c r="K36" s="50" t="str">
+      <c r="K36" s="53" t="str">
         <f aca="false">IF(E36&gt;0,E36-J36," ")</f>
         <v> </v>
       </c>
-      <c r="L36" s="50"/>
+      <c r="L36" s="53"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="47" t="str">
+      <c r="N36" s="53"/>
+      <c r="O36" s="68"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="50" t="str">
         <f aca="false">IF(O36&gt;0,O36*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S36" s="47" t="str">
+      <c r="S36" s="50" t="str">
         <f aca="false">IF(O36&gt;0,O36-R36," ")</f>
         <v> </v>
       </c>
-      <c r="T36" s="47"/>
+      <c r="T36" s="50"/>
       <c r="U36" s="54"/>
       <c r="V36" s="57"/>
-      <c r="W36" s="50" t="str">
+      <c r="W36" s="53" t="str">
         <f aca="false">IF(V36&gt;0,E36," ")</f>
         <v> </v>
       </c>
-      <c r="X36" s="50" t="str">
+      <c r="X36" s="53" t="str">
         <f aca="false">IF(V36&gt;0,J36," ")</f>
         <v> </v>
       </c>
-      <c r="Y36" s="47" t="str">
+      <c r="Y36" s="50" t="str">
         <f aca="false">IF((U36+V36)&gt;0,IF(V36&lt;S36,S36-V36," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z36" s="47" t="str">
+      <c r="Z36" s="50" t="str">
         <f aca="false">IF((U36+V36)&gt;0,IF(V36&gt;S36,V36-S36," ")," ")</f>
         <v> </v>
       </c>
@@ -3418,7 +3399,7 @@
       <c r="D37" s="56"/>
       <c r="E37" s="57"/>
       <c r="F37" s="57"/>
-      <c r="G37" s="50" t="str">
+      <c r="G37" s="53" t="str">
         <f aca="false">IF(E37&gt;0,E37-F37," ")</f>
         <v> </v>
       </c>
@@ -3426,48 +3407,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I37" s="50" t="str">
+      <c r="I37" s="53" t="str">
         <f aca="false">IF(E37&gt;0,MIN(E37*H37,G37)," ")</f>
         <v> </v>
       </c>
-      <c r="J37" s="50" t="str">
+      <c r="J37" s="53" t="str">
         <f aca="false">IF(E37&gt;0,F37+I37," ")</f>
         <v> </v>
       </c>
-      <c r="K37" s="50" t="str">
+      <c r="K37" s="53" t="str">
         <f aca="false">IF(E37&gt;0,E37-J37," ")</f>
         <v> </v>
       </c>
-      <c r="L37" s="50"/>
+      <c r="L37" s="53"/>
       <c r="M37" s="58"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="47"/>
-      <c r="R37" s="47" t="str">
+      <c r="N37" s="53"/>
+      <c r="O37" s="68"/>
+      <c r="P37" s="51"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="50" t="str">
         <f aca="false">IF(O37&gt;0,O37*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S37" s="47" t="str">
+      <c r="S37" s="50" t="str">
         <f aca="false">IF(O37&gt;0,O37-R37," ")</f>
         <v> </v>
       </c>
-      <c r="T37" s="47"/>
+      <c r="T37" s="50"/>
       <c r="U37" s="54"/>
       <c r="V37" s="57"/>
-      <c r="W37" s="50" t="str">
+      <c r="W37" s="53" t="str">
         <f aca="false">IF(V37&gt;0,E37," ")</f>
         <v> </v>
       </c>
-      <c r="X37" s="50" t="str">
+      <c r="X37" s="53" t="str">
         <f aca="false">IF(V37&gt;0,J37," ")</f>
         <v> </v>
       </c>
-      <c r="Y37" s="47" t="str">
+      <c r="Y37" s="50" t="str">
         <f aca="false">IF((U37+V37)&gt;0,IF(V37&lt;S37,S37-V37," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z37" s="47" t="str">
+      <c r="Z37" s="50" t="str">
         <f aca="false">IF((U37+V37)&gt;0,IF(V37&gt;S37,V37-S37," ")," ")</f>
         <v> </v>
       </c>
@@ -3480,7 +3461,7 @@
       <c r="D38" s="56"/>
       <c r="E38" s="57"/>
       <c r="F38" s="57"/>
-      <c r="G38" s="50" t="str">
+      <c r="G38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
         <v> </v>
       </c>
@@ -3488,48 +3469,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I38" s="50" t="str">
+      <c r="I38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
         <v> </v>
       </c>
-      <c r="J38" s="50" t="str">
+      <c r="J38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
         <v> </v>
       </c>
-      <c r="K38" s="50" t="str">
+      <c r="K38" s="53" t="str">
         <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
         <v> </v>
       </c>
-      <c r="L38" s="50"/>
+      <c r="L38" s="53"/>
       <c r="M38" s="58"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47" t="str">
+      <c r="N38" s="53"/>
+      <c r="O38" s="68"/>
+      <c r="P38" s="51"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,O38*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S38" s="47" t="str">
+      <c r="S38" s="50" t="str">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
         <v> </v>
       </c>
-      <c r="T38" s="47"/>
+      <c r="T38" s="50"/>
       <c r="U38" s="54"/>
       <c r="V38" s="57"/>
-      <c r="W38" s="50" t="str">
+      <c r="W38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
         <v> </v>
       </c>
-      <c r="X38" s="50" t="str">
+      <c r="X38" s="53" t="str">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
         <v> </v>
       </c>
-      <c r="Y38" s="47" t="str">
+      <c r="Y38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,S38-V38," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z38" s="47" t="str">
+      <c r="Z38" s="50" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,V38-S38," ")," ")</f>
         <v> </v>
       </c>
@@ -3542,7 +3523,7 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="50" t="str">
+      <c r="G39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
         <v> </v>
       </c>
@@ -3550,48 +3531,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I39" s="50" t="str">
+      <c r="I39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="50" t="str">
+      <c r="J39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="50" t="str">
+      <c r="K39" s="53" t="str">
         <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
         <v> </v>
       </c>
-      <c r="L39" s="50"/>
+      <c r="L39" s="53"/>
       <c r="M39" s="58"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="47" t="str">
+      <c r="N39" s="53"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,O39*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="47" t="str">
+      <c r="S39" s="50" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="47"/>
+      <c r="T39" s="50"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="50" t="str">
+      <c r="W39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="50" t="str">
+      <c r="X39" s="53" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="47" t="str">
+      <c r="Y39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,S39-V39," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="47" t="str">
+      <c r="Z39" s="50" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,V39-S39," ")," ")</f>
         <v> </v>
       </c>
@@ -3604,7 +3585,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="50" t="str">
+      <c r="G40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
         <v> </v>
       </c>
@@ -3612,48 +3593,48 @@
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I40" s="50" t="str">
+      <c r="I40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="50" t="str">
+      <c r="J40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="50" t="str">
+      <c r="K40" s="53" t="str">
         <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
         <v> </v>
       </c>
-      <c r="L40" s="50"/>
+      <c r="L40" s="53"/>
       <c r="M40" s="58"/>
-      <c r="N40" s="50"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="47"/>
-      <c r="R40" s="47" t="str">
+      <c r="N40" s="53"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,O40*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="47" t="str">
+      <c r="S40" s="50" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="47"/>
+      <c r="T40" s="50"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="50" t="str">
+      <c r="W40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="50" t="str">
+      <c r="X40" s="53" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="47" t="str">
+      <c r="Y40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,S40-V40," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="47" t="str">
+      <c r="Z40" s="50" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,V40-S40," ")," ")</f>
         <v> </v>
       </c>
@@ -3692,9 +3673,9 @@
         <f aca="false">SUM(K33:K40)</f>
         <v>0</v>
       </c>
-      <c r="L41" s="50"/>
+      <c r="L41" s="53"/>
       <c r="M41" s="58"/>
-      <c r="N41" s="50"/>
+      <c r="N41" s="53"/>
       <c r="O41" s="61" t="n">
         <f aca="false">SUM(O33:O40)</f>
         <v>0</v>
@@ -3712,8 +3693,8 @@
         <f aca="false">SUM(S33:S40)</f>
         <v>0</v>
       </c>
-      <c r="T41" s="47"/>
-      <c r="U41" s="49"/>
+      <c r="T41" s="50"/>
+      <c r="U41" s="52"/>
       <c r="V41" s="60" t="n">
         <f aca="false">SUM(V33:V40)</f>
         <v>0</v>
@@ -3741,61 +3722,61 @@
       <c r="B42" s="63"/>
       <c r="C42" s="64"/>
       <c r="D42" s="65"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
       <c r="H42" s="58"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="50"/>
-      <c r="L42" s="50"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="53"/>
       <c r="M42" s="58"/>
-      <c r="N42" s="50"/>
-      <c r="O42" s="50"/>
+      <c r="N42" s="53"/>
+      <c r="O42" s="53"/>
       <c r="P42" s="62"/>
-      <c r="Q42" s="50"/>
-      <c r="R42" s="50"/>
-      <c r="S42" s="50"/>
-      <c r="T42" s="47"/>
-      <c r="U42" s="49"/>
-      <c r="V42" s="50"/>
-      <c r="W42" s="50"/>
-      <c r="X42" s="50"/>
-      <c r="Y42" s="50"/>
-      <c r="Z42" s="50"/>
+      <c r="Q42" s="53"/>
+      <c r="R42" s="53"/>
+      <c r="S42" s="53"/>
+      <c r="T42" s="50"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="53"/>
+      <c r="W42" s="53"/>
+      <c r="X42" s="53"/>
+      <c r="Y42" s="53"/>
+      <c r="Z42" s="53"/>
       <c r="AA42" s="25"/>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="66" t="n">
+      <c r="C43" s="66"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="67" t="n">
         <v>0.25</v>
       </c>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="69"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="70"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="53"/>
       <c r="P43" s="62"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="70"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
+      <c r="Q43" s="53"/>
+      <c r="R43" s="53"/>
+      <c r="S43" s="53"/>
+      <c r="T43" s="71"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="53"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="53"/>
+      <c r="Z43" s="53"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3805,7 +3786,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
-      <c r="G44" s="50" t="str">
+      <c r="G44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
         <v> </v>
       </c>
@@ -3813,50 +3794,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="50" t="str">
+      <c r="I44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="50" t="str">
+      <c r="J44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="50" t="str">
+      <c r="K44" s="53" t="str">
         <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
         <v> </v>
       </c>
-      <c r="L44" s="50"/>
-      <c r="M44" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="50"/>
-      <c r="O44" s="67"/>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="47" t="str">
+      <c r="L44" s="53"/>
+      <c r="M44" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="53"/>
+      <c r="O44" s="68"/>
+      <c r="P44" s="51"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4/100*(1-M44),3000*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="47" t="str">
+      <c r="S44" s="50" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="47"/>
+      <c r="T44" s="50"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="50" t="str">
+      <c r="W44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="50" t="str">
+      <c r="X44" s="53" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="47" t="str">
+      <c r="Y44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="47" t="str">
+      <c r="Z44" s="50" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -3869,7 +3850,7 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="50" t="str">
+      <c r="G45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
         <v> </v>
       </c>
@@ -3877,50 +3858,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="50" t="str">
+      <c r="I45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="50" t="str">
+      <c r="J45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="50" t="str">
+      <c r="K45" s="53" t="str">
         <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
         <v> </v>
       </c>
-      <c r="L45" s="50"/>
-      <c r="M45" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="50"/>
-      <c r="O45" s="67"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47" t="str">
+      <c r="L45" s="53"/>
+      <c r="M45" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="53"/>
+      <c r="O45" s="68"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4/100*(1-M45),3000*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="47" t="str">
+      <c r="S45" s="50" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="47"/>
+      <c r="T45" s="50"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="50" t="str">
+      <c r="W45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="50" t="str">
+      <c r="X45" s="53" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="47" t="str">
+      <c r="Y45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="47" t="str">
+      <c r="Z45" s="50" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -3933,7 +3914,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="50" t="str">
+      <c r="G46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -3941,50 +3922,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="50" t="str">
+      <c r="I46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="50" t="str">
+      <c r="J46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="50" t="str">
+      <c r="K46" s="53" t="str">
         <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
         <v> </v>
       </c>
-      <c r="L46" s="50"/>
-      <c r="M46" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="50"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47" t="str">
+      <c r="L46" s="53"/>
+      <c r="M46" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="53"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="51"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4/100*(1-M46),3000*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="47" t="str">
+      <c r="S46" s="50" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="47"/>
+      <c r="T46" s="50"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="50" t="str">
+      <c r="W46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="50" t="str">
+      <c r="X46" s="53" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="47" t="str">
+      <c r="Y46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="47" t="str">
+      <c r="Z46" s="50" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -3997,7 +3978,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="50" t="str">
+      <c r="G47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -4005,50 +3986,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="50" t="str">
+      <c r="I47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="50" t="str">
+      <c r="J47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="50" t="str">
+      <c r="K47" s="53" t="str">
         <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
         <v> </v>
       </c>
-      <c r="L47" s="50"/>
-      <c r="M47" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="50"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="48"/>
-      <c r="Q47" s="47"/>
-      <c r="R47" s="47" t="str">
+      <c r="L47" s="53"/>
+      <c r="M47" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="53"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="51"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4/100*(1-M47),3000*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="47" t="str">
+      <c r="S47" s="50" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="47"/>
+      <c r="T47" s="50"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="50" t="str">
+      <c r="W47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="50" t="str">
+      <c r="X47" s="53" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="47" t="str">
+      <c r="Y47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="47" t="str">
+      <c r="Z47" s="50" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4061,7 +4042,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="50" t="str">
+      <c r="G48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4069,50 +4050,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="50" t="str">
+      <c r="I48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="50" t="str">
+      <c r="J48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="50" t="str">
+      <c r="K48" s="53" t="str">
         <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
         <v> </v>
       </c>
-      <c r="L48" s="50"/>
-      <c r="M48" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="50"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47" t="str">
+      <c r="L48" s="53"/>
+      <c r="M48" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="53"/>
+      <c r="O48" s="68"/>
+      <c r="P48" s="51"/>
+      <c r="Q48" s="50"/>
+      <c r="R48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4/100*(1-M48),3000*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="47" t="str">
+      <c r="S48" s="50" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="47"/>
+      <c r="T48" s="50"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="50" t="str">
+      <c r="W48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="50" t="str">
+      <c r="X48" s="53" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="47" t="str">
+      <c r="Y48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="47" t="str">
+      <c r="Z48" s="50" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4120,33 +4101,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="51"/>
+      <c r="C49" s="66"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="47"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="47"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="49"/>
-      <c r="V49" s="50"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="50"/>
-      <c r="Y49" s="47"/>
-      <c r="Z49" s="47"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="50"/>
+      <c r="P49" s="51"/>
+      <c r="Q49" s="50"/>
+      <c r="R49" s="50"/>
+      <c r="S49" s="50"/>
+      <c r="T49" s="50"/>
+      <c r="U49" s="52"/>
+      <c r="V49" s="53"/>
+      <c r="W49" s="53"/>
+      <c r="X49" s="53"/>
+      <c r="Y49" s="50"/>
+      <c r="Z49" s="50"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4156,7 +4137,7 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="50" t="str">
+      <c r="G50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
         <v> </v>
       </c>
@@ -4164,50 +4145,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="50" t="str">
+      <c r="I50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="50" t="str">
+      <c r="J50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="50" t="str">
+      <c r="K50" s="53" t="str">
         <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
         <v> </v>
       </c>
-      <c r="L50" s="50"/>
-      <c r="M50" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="50"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47" t="str">
+      <c r="L50" s="53"/>
+      <c r="M50" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="53"/>
+      <c r="O50" s="68"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="50"/>
+      <c r="R50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,IF(O50&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M50),O50*R$4/100)*(1-M50)," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="47" t="str">
+      <c r="S50" s="50" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="47"/>
+      <c r="T50" s="50"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="50" t="str">
+      <c r="W50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="50" t="str">
+      <c r="X50" s="53" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="47" t="str">
+      <c r="Y50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="47" t="str">
+      <c r="Z50" s="50" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4220,7 +4201,7 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="50" t="str">
+      <c r="G51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
         <v> </v>
       </c>
@@ -4228,50 +4209,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="50" t="str">
+      <c r="I51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="50" t="str">
+      <c r="J51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="50" t="str">
+      <c r="K51" s="53" t="str">
         <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
         <v> </v>
       </c>
-      <c r="L51" s="50"/>
-      <c r="M51" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="50"/>
-      <c r="O51" s="67"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47" t="str">
+      <c r="L51" s="53"/>
+      <c r="M51" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="53"/>
+      <c r="O51" s="68"/>
+      <c r="P51" s="51"/>
+      <c r="Q51" s="50"/>
+      <c r="R51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,IF(O51&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M51),O51*R$4/100)*(1-M51)," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="47" t="str">
+      <c r="S51" s="50" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="47"/>
+      <c r="T51" s="50"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="50" t="str">
+      <c r="W51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="50" t="str">
+      <c r="X51" s="53" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="47" t="str">
+      <c r="Y51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="47" t="str">
+      <c r="Z51" s="50" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4284,7 +4265,7 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="50" t="str">
+      <c r="G52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
         <v> </v>
       </c>
@@ -4292,50 +4273,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="50" t="str">
+      <c r="I52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="50" t="str">
+      <c r="J52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="50" t="str">
+      <c r="K52" s="53" t="str">
         <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
         <v> </v>
       </c>
-      <c r="L52" s="50"/>
-      <c r="M52" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="50"/>
-      <c r="O52" s="67"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47" t="str">
+      <c r="L52" s="53"/>
+      <c r="M52" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="53"/>
+      <c r="O52" s="68"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="50"/>
+      <c r="R52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,IF(O52&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M52),O52*R$4/100)*(1-M52)," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="47" t="str">
+      <c r="S52" s="50" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="47"/>
+      <c r="T52" s="50"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="50" t="str">
+      <c r="W52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="50" t="str">
+      <c r="X52" s="53" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="47" t="str">
+      <c r="Y52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="47" t="str">
+      <c r="Z52" s="50" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4348,7 +4329,7 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="50" t="str">
+      <c r="G53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
         <v> </v>
       </c>
@@ -4356,50 +4337,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="50" t="str">
+      <c r="I53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="50" t="str">
+      <c r="J53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="50" t="str">
+      <c r="K53" s="53" t="str">
         <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
         <v> </v>
       </c>
-      <c r="L53" s="50"/>
-      <c r="M53" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="50"/>
-      <c r="O53" s="67"/>
-      <c r="P53" s="48"/>
-      <c r="Q53" s="47"/>
-      <c r="R53" s="47" t="str">
+      <c r="L53" s="53"/>
+      <c r="M53" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="53"/>
+      <c r="O53" s="68"/>
+      <c r="P53" s="51"/>
+      <c r="Q53" s="50"/>
+      <c r="R53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,IF(O53&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M53),O53*R$4/100)*(1-M53)," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="47" t="str">
+      <c r="S53" s="50" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="47"/>
+      <c r="T53" s="50"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="50" t="str">
+      <c r="W53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="50" t="str">
+      <c r="X53" s="53" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="47" t="str">
+      <c r="Y53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="47" t="str">
+      <c r="Z53" s="50" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4412,7 +4393,7 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="50" t="str">
+      <c r="G54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
         <v> </v>
       </c>
@@ -4420,50 +4401,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="50" t="str">
+      <c r="I54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="50" t="str">
+      <c r="J54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="50" t="str">
+      <c r="K54" s="53" t="str">
         <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
         <v> </v>
       </c>
-      <c r="L54" s="50"/>
-      <c r="M54" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="50"/>
-      <c r="O54" s="67"/>
-      <c r="P54" s="48"/>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47" t="str">
+      <c r="L54" s="53"/>
+      <c r="M54" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="53"/>
+      <c r="O54" s="68"/>
+      <c r="P54" s="51"/>
+      <c r="Q54" s="50"/>
+      <c r="R54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,IF(O54&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M54),O54*R$4/100)*(1-M54)," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="47" t="str">
+      <c r="S54" s="50" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="47"/>
+      <c r="T54" s="50"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="50" t="str">
+      <c r="W54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="50" t="str">
+      <c r="X54" s="53" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="47" t="str">
+      <c r="Y54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="47" t="str">
+      <c r="Z54" s="50" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4502,9 +4483,9 @@
         <f aca="false">SUM(K44:K54)</f>
         <v>0</v>
       </c>
-      <c r="L55" s="50"/>
-      <c r="M55" s="69"/>
-      <c r="N55" s="50"/>
+      <c r="L55" s="53"/>
+      <c r="M55" s="70"/>
+      <c r="N55" s="53"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O44:O54)</f>
         <v>0</v>
@@ -4522,8 +4503,8 @@
         <f aca="false">SUM(S44:S54)</f>
         <v>0</v>
       </c>
-      <c r="T55" s="50"/>
-      <c r="U55" s="49"/>
+      <c r="T55" s="53"/>
+      <c r="U55" s="52"/>
       <c r="V55" s="60" t="n">
         <f aca="false">SUM(V44:V54)</f>
         <v>0</v>
@@ -4548,31 +4529,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="71"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="72"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="50"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="47"/>
-      <c r="P56" s="48"/>
-      <c r="Q56" s="47"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47"/>
-      <c r="T56" s="47"/>
-      <c r="U56" s="49"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="47"/>
-      <c r="X56" s="47"/>
-      <c r="Y56" s="47"/>
-      <c r="Z56" s="47"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="50"/>
+      <c r="P56" s="51"/>
+      <c r="Q56" s="50"/>
+      <c r="R56" s="50"/>
+      <c r="S56" s="50"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="52"/>
+      <c r="V56" s="53"/>
+      <c r="W56" s="50"/>
+      <c r="X56" s="50"/>
+      <c r="Y56" s="50"/>
+      <c r="Z56" s="50"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4582,74 +4563,74 @@
         <v>EXISTING FIXED ASSETS AT </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="72" t="n">
+      <c r="D57" s="73" t="str">
         <f aca="false">D6</f>
-        <v>45748</v>
-      </c>
-      <c r="E57" s="73" t="n">
+        <v>Laptop (0.5 years old)</v>
+      </c>
+      <c r="E57" s="74" t="n">
         <f aca="false">E11+E22+E30+E41+E55</f>
         <v>0</v>
       </c>
-      <c r="F57" s="73" t="n">
+      <c r="F57" s="74" t="n">
         <f aca="false">F11+F22+F30+F41+F55</f>
         <v>0</v>
       </c>
-      <c r="G57" s="73" t="n">
+      <c r="G57" s="74" t="n">
         <f aca="false">G11+G22+G30+G41+G55</f>
         <v>0</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="73" t="n">
+      <c r="I57" s="74" t="n">
         <f aca="false">I11+I22+I30+I41+I55</f>
         <v>0</v>
       </c>
-      <c r="J57" s="73" t="n">
+      <c r="J57" s="74" t="n">
         <f aca="false">J11+J22+J30+J41+J55</f>
         <v>0</v>
       </c>
-      <c r="K57" s="73" t="n">
+      <c r="K57" s="74" t="n">
         <f aca="false">K11+K22+K30+K41+K55</f>
         <v>0</v>
       </c>
-      <c r="L57" s="50"/>
+      <c r="L57" s="53"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="50"/>
-      <c r="O57" s="73" t="n">
+      <c r="N57" s="53"/>
+      <c r="O57" s="74" t="n">
         <f aca="false">O11+O22+O30+O41+O55</f>
         <v>0</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="73" t="n">
+      <c r="Q57" s="74" t="n">
         <f aca="false">Q11+Q22+Q30+Q41+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="73" t="n">
+      <c r="R57" s="74" t="n">
         <f aca="false">R11+R22+R30+R41+R55</f>
         <v>0</v>
       </c>
-      <c r="S57" s="73" t="n">
+      <c r="S57" s="74" t="n">
         <f aca="false">S11+S22+S30+S41+S55</f>
         <v>0</v>
       </c>
-      <c r="T57" s="47"/>
-      <c r="U57" s="49"/>
-      <c r="V57" s="73" t="n">
+      <c r="T57" s="50"/>
+      <c r="U57" s="52"/>
+      <c r="V57" s="74" t="n">
         <f aca="false">V11+V22+V30+V41+V55</f>
         <v>0</v>
       </c>
-      <c r="W57" s="73" t="n">
+      <c r="W57" s="74" t="n">
         <f aca="false">W11+W22+W30+W41+W55</f>
         <v>0</v>
       </c>
-      <c r="X57" s="73" t="n">
+      <c r="X57" s="74" t="n">
         <f aca="false">X11+X22+X30+X41+X55</f>
         <v>0</v>
       </c>
-      <c r="Y57" s="73" t="n">
+      <c r="Y57" s="74" t="n">
         <f aca="false">Y11+Y22+Y30+Y41+Y55</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="73" t="n">
+      <c r="Z57" s="74" t="n">
         <f aca="false">Z11+Z22+Z30+Z41+Z55</f>
         <v>0</v>
       </c>
@@ -4657,251 +4638,251 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="74"/>
-      <c r="C58" s="75"/>
-      <c r="D58" s="76"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="50"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="47"/>
-      <c r="P58" s="48"/>
-      <c r="Q58" s="47"/>
-      <c r="R58" s="47"/>
-      <c r="S58" s="47"/>
-      <c r="T58" s="47"/>
-      <c r="U58" s="49"/>
-      <c r="V58" s="50"/>
-      <c r="W58" s="50"/>
-      <c r="X58" s="50"/>
-      <c r="Y58" s="47"/>
-      <c r="Z58" s="47"/>
+      <c r="N58" s="53"/>
+      <c r="O58" s="50"/>
+      <c r="P58" s="51"/>
+      <c r="Q58" s="50"/>
+      <c r="R58" s="50"/>
+      <c r="S58" s="50"/>
+      <c r="T58" s="50"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="53"/>
+      <c r="W58" s="53"/>
+      <c r="X58" s="53"/>
+      <c r="Y58" s="50"/>
+      <c r="Z58" s="50"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
-      <c r="B59" s="77" t="s">
+      <c r="B59" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="77"/>
-      <c r="D59" s="78" t="n">
+      <c r="C59" s="78"/>
+      <c r="D59" s="79" t="str">
         <f aca="false">D57</f>
-        <v>45748</v>
-      </c>
-      <c r="E59" s="79" t="s">
+        <v>Laptop (0.5 years old)</v>
+      </c>
+      <c r="E59" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="F59" s="80" t="n">
+      <c r="F59" s="81" t="n">
         <f aca="false">J4</f>
         <v>46477</v>
       </c>
-      <c r="G59" s="81"/>
+      <c r="G59" s="82"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
-      <c r="L59" s="47"/>
+      <c r="I59" s="50"/>
+      <c r="J59" s="50"/>
+      <c r="K59" s="50"/>
+      <c r="L59" s="50"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="47"/>
-      <c r="O59" s="47"/>
-      <c r="P59" s="48"/>
-      <c r="Q59" s="47"/>
-      <c r="R59" s="47"/>
-      <c r="S59" s="47"/>
-      <c r="T59" s="47"/>
-      <c r="U59" s="49"/>
-      <c r="V59" s="50"/>
-      <c r="W59" s="50"/>
-      <c r="X59" s="50"/>
-      <c r="Y59" s="47"/>
-      <c r="Z59" s="47"/>
+      <c r="N59" s="50"/>
+      <c r="O59" s="50"/>
+      <c r="P59" s="51"/>
+      <c r="Q59" s="50"/>
+      <c r="R59" s="50"/>
+      <c r="S59" s="50"/>
+      <c r="T59" s="50"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="53"/>
+      <c r="W59" s="53"/>
+      <c r="X59" s="53"/>
+      <c r="Y59" s="50"/>
+      <c r="Z59" s="50"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" s="51"/>
-      <c r="D60" s="52"/>
-      <c r="E60" s="45"/>
-      <c r="F60" s="81"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="82" t="n">
+      <c r="B60" s="66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="66"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="82"/>
+      <c r="G60" s="82"/>
+      <c r="H60" s="83" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I60" s="45"/>
-      <c r="J60" s="45"/>
-      <c r="K60" s="45"/>
-      <c r="L60" s="45"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="47"/>
+      <c r="K60" s="47"/>
+      <c r="L60" s="47"/>
       <c r="M60" s="58"/>
-      <c r="N60" s="45"/>
-      <c r="O60" s="47"/>
-      <c r="P60" s="48"/>
-      <c r="Q60" s="47"/>
-      <c r="R60" s="47"/>
-      <c r="S60" s="47"/>
-      <c r="T60" s="47"/>
-      <c r="U60" s="49"/>
-      <c r="V60" s="50"/>
-      <c r="W60" s="50"/>
-      <c r="X60" s="50"/>
-      <c r="Y60" s="47"/>
-      <c r="Z60" s="47"/>
+      <c r="N60" s="47"/>
+      <c r="O60" s="50"/>
+      <c r="P60" s="51"/>
+      <c r="Q60" s="50"/>
+      <c r="R60" s="50"/>
+      <c r="S60" s="50"/>
+      <c r="T60" s="50"/>
+      <c r="U60" s="52"/>
+      <c r="V60" s="53"/>
+      <c r="W60" s="53"/>
+      <c r="X60" s="53"/>
+      <c r="Y60" s="50"/>
+      <c r="Z60" s="50"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="83"/>
+      <c r="D61" s="84"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="50"/>
-      <c r="G61" s="50"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="50" t="str">
+      <c r="I61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="50" t="str">
+      <c r="J61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="50" t="str">
+      <c r="K61" s="53" t="str">
         <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
         <v> </v>
       </c>
-      <c r="L61" s="50"/>
+      <c r="L61" s="53"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="50"/>
-      <c r="O61" s="47"/>
-      <c r="P61" s="48"/>
-      <c r="Q61" s="47"/>
-      <c r="R61" s="47"/>
-      <c r="S61" s="47"/>
-      <c r="T61" s="47"/>
+      <c r="N61" s="53"/>
+      <c r="O61" s="50"/>
+      <c r="P61" s="51"/>
+      <c r="Q61" s="50"/>
+      <c r="R61" s="50"/>
+      <c r="S61" s="50"/>
+      <c r="T61" s="50"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="50" t="str">
+      <c r="W61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="50" t="str">
+      <c r="X61" s="53" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="47"/>
-      <c r="Z61" s="47"/>
+      <c r="Y61" s="50"/>
+      <c r="Z61" s="50"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="83"/>
+      <c r="D62" s="84"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="50"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="50" t="str">
+      <c r="I62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="50" t="str">
+      <c r="J62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="50" t="str">
+      <c r="K62" s="53" t="str">
         <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
         <v> </v>
       </c>
-      <c r="L62" s="50"/>
+      <c r="L62" s="53"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="50"/>
-      <c r="O62" s="47"/>
-      <c r="P62" s="48"/>
-      <c r="Q62" s="47"/>
-      <c r="R62" s="47"/>
-      <c r="S62" s="47"/>
-      <c r="T62" s="47"/>
+      <c r="N62" s="53"/>
+      <c r="O62" s="50"/>
+      <c r="P62" s="51"/>
+      <c r="Q62" s="50"/>
+      <c r="R62" s="50"/>
+      <c r="S62" s="50"/>
+      <c r="T62" s="50"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="50" t="str">
+      <c r="W62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="50" t="str">
+      <c r="X62" s="53" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="47"/>
-      <c r="Z62" s="47"/>
+      <c r="Y62" s="50"/>
+      <c r="Z62" s="50"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="83"/>
+      <c r="D63" s="84"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="50" t="str">
+      <c r="I63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="50" t="str">
+      <c r="J63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="50" t="str">
+      <c r="K63" s="53" t="str">
         <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
         <v> </v>
       </c>
-      <c r="L63" s="50"/>
+      <c r="L63" s="53"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="50"/>
-      <c r="O63" s="47"/>
-      <c r="P63" s="48"/>
-      <c r="Q63" s="47"/>
-      <c r="R63" s="47"/>
-      <c r="S63" s="47"/>
-      <c r="T63" s="47"/>
+      <c r="N63" s="53"/>
+      <c r="O63" s="50"/>
+      <c r="P63" s="51"/>
+      <c r="Q63" s="50"/>
+      <c r="R63" s="50"/>
+      <c r="S63" s="50"/>
+      <c r="T63" s="50"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="50" t="str">
+      <c r="W63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="50" t="str">
+      <c r="X63" s="53" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="47"/>
-      <c r="Z63" s="47"/>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="50"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -4930,14 +4911,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="50"/>
+      <c r="L64" s="53"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="50"/>
+      <c r="N64" s="53"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="84"/>
+      <c r="P64" s="85"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -4950,8 +4931,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="47"/>
-      <c r="U64" s="49"/>
+      <c r="T64" s="50"/>
+      <c r="U64" s="52"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -4979,62 +4960,62 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="50"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="50"/>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="L65" s="50"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="53"/>
+      <c r="K65" s="53"/>
+      <c r="L65" s="53"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="50"/>
-      <c r="O65" s="50"/>
+      <c r="N65" s="53"/>
+      <c r="O65" s="53"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="50"/>
-      <c r="R65" s="50"/>
-      <c r="S65" s="50"/>
-      <c r="T65" s="47"/>
-      <c r="U65" s="49"/>
-      <c r="V65" s="50"/>
-      <c r="W65" s="50"/>
-      <c r="X65" s="50"/>
-      <c r="Y65" s="50"/>
-      <c r="Z65" s="50"/>
+      <c r="Q65" s="53"/>
+      <c r="R65" s="53"/>
+      <c r="S65" s="53"/>
+      <c r="T65" s="50"/>
+      <c r="U65" s="52"/>
+      <c r="V65" s="53"/>
+      <c r="W65" s="53"/>
+      <c r="X65" s="53"/>
+      <c r="Y65" s="53"/>
+      <c r="Z65" s="53"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="51"/>
+      <c r="C66" s="66"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="50"/>
-      <c r="H66" s="85" t="n">
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="86" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="50"/>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="50"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="53"/>
+      <c r="K66" s="53"/>
+      <c r="L66" s="53"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="50"/>
-      <c r="O66" s="47"/>
-      <c r="P66" s="48"/>
-      <c r="Q66" s="47"/>
-      <c r="R66" s="47"/>
-      <c r="S66" s="47"/>
-      <c r="T66" s="47"/>
-      <c r="U66" s="49"/>
-      <c r="V66" s="50"/>
-      <c r="W66" s="50"/>
-      <c r="X66" s="50"/>
-      <c r="Y66" s="47"/>
-      <c r="Z66" s="47"/>
+      <c r="N66" s="53"/>
+      <c r="O66" s="50"/>
+      <c r="P66" s="51"/>
+      <c r="Q66" s="50"/>
+      <c r="R66" s="50"/>
+      <c r="S66" s="50"/>
+      <c r="T66" s="50"/>
+      <c r="U66" s="52"/>
+      <c r="V66" s="53"/>
+      <c r="W66" s="53"/>
+      <c r="X66" s="53"/>
+      <c r="Y66" s="50"/>
+      <c r="Z66" s="50"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5043,57 +5024,57 @@
       <c r="C67" s="55"/>
       <c r="D67" s="56"/>
       <c r="E67" s="57"/>
-      <c r="F67" s="50"/>
-      <c r="G67" s="50"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="50" t="str">
+      <c r="I67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
         <v> </v>
       </c>
-      <c r="J67" s="50" t="str">
+      <c r="J67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
         <v> </v>
       </c>
-      <c r="K67" s="50" t="str">
+      <c r="K67" s="53" t="str">
         <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
         <v> </v>
       </c>
-      <c r="L67" s="50"/>
+      <c r="L67" s="53"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="50"/>
-      <c r="O67" s="47"/>
-      <c r="P67" s="48" t="n">
+      <c r="N67" s="53"/>
+      <c r="O67" s="50"/>
+      <c r="P67" s="51" t="n">
         <f aca="false">IF(B67&gt;0,IF(B67&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q67" s="47" t="str">
+      <c r="Q67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67*P67/100," ")</f>
         <v> </v>
       </c>
-      <c r="R67" s="47"/>
-      <c r="S67" s="47" t="str">
+      <c r="R67" s="50"/>
+      <c r="S67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
         <v> </v>
       </c>
-      <c r="T67" s="47"/>
+      <c r="T67" s="50"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="50" t="str">
+      <c r="W67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="50" t="str">
+      <c r="X67" s="53" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="47" t="str">
+      <c r="Y67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="47" t="str">
+      <c r="Z67" s="50" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5105,57 +5086,57 @@
       <c r="C68" s="55"/>
       <c r="D68" s="56"/>
       <c r="E68" s="57"/>
-      <c r="F68" s="50"/>
-      <c r="G68" s="50"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="50" t="str">
+      <c r="I68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
         <v> </v>
       </c>
-      <c r="J68" s="50" t="str">
+      <c r="J68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
         <v> </v>
       </c>
-      <c r="K68" s="50" t="str">
+      <c r="K68" s="53" t="str">
         <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
         <v> </v>
       </c>
-      <c r="L68" s="50"/>
+      <c r="L68" s="53"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="50"/>
-      <c r="O68" s="47"/>
-      <c r="P68" s="48" t="n">
+      <c r="N68" s="53"/>
+      <c r="O68" s="50"/>
+      <c r="P68" s="51" t="n">
         <f aca="false">IF(B68&gt;0,IF(B68&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q68" s="47" t="str">
+      <c r="Q68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68*P68/100," ")</f>
         <v> </v>
       </c>
-      <c r="R68" s="47"/>
-      <c r="S68" s="47" t="str">
+      <c r="R68" s="50"/>
+      <c r="S68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
         <v> </v>
       </c>
-      <c r="T68" s="47"/>
+      <c r="T68" s="50"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="50" t="str">
+      <c r="W68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="50" t="str">
+      <c r="X68" s="53" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="47" t="str">
+      <c r="Y68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="47" t="str">
+      <c r="Z68" s="50" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5167,57 +5148,57 @@
       <c r="C69" s="55"/>
       <c r="D69" s="56"/>
       <c r="E69" s="57"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="50" t="str">
+      <c r="I69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
         <v> </v>
       </c>
-      <c r="J69" s="50" t="str">
+      <c r="J69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
         <v> </v>
       </c>
-      <c r="K69" s="50" t="str">
+      <c r="K69" s="53" t="str">
         <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
         <v> </v>
       </c>
-      <c r="L69" s="50"/>
+      <c r="L69" s="53"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="50"/>
-      <c r="O69" s="47"/>
-      <c r="P69" s="48" t="n">
+      <c r="N69" s="53"/>
+      <c r="O69" s="50"/>
+      <c r="P69" s="51" t="n">
         <f aca="false">IF(B69&gt;0,IF(B69&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q69" s="47" t="str">
+      <c r="Q69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69*P69/100," ")</f>
         <v> </v>
       </c>
-      <c r="R69" s="47"/>
-      <c r="S69" s="47" t="str">
+      <c r="R69" s="50"/>
+      <c r="S69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
         <v> </v>
       </c>
-      <c r="T69" s="47"/>
+      <c r="T69" s="50"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="50" t="str">
+      <c r="W69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="50" t="str">
+      <c r="X69" s="53" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="47" t="str">
+      <c r="Y69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="47" t="str">
+      <c r="Z69" s="50" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5229,57 +5210,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="50" t="str">
+      <c r="I70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="50" t="str">
+      <c r="J70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="50" t="str">
+      <c r="K70" s="53" t="str">
         <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
         <v> </v>
       </c>
-      <c r="L70" s="50"/>
+      <c r="L70" s="53"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="47"/>
-      <c r="P70" s="48" t="n">
+      <c r="N70" s="53"/>
+      <c r="O70" s="50"/>
+      <c r="P70" s="51" t="n">
         <f aca="false">IF(B70&gt;0,IF(B70&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q70" s="47" t="str">
+      <c r="Q70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70/100," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47" t="str">
+      <c r="R70" s="50"/>
+      <c r="S70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="47"/>
+      <c r="T70" s="50"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="50" t="str">
+      <c r="W70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="50" t="str">
+      <c r="X70" s="53" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="47" t="str">
+      <c r="Y70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="47" t="str">
+      <c r="Z70" s="50" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5291,57 +5272,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="50" t="str">
+      <c r="I71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="50" t="str">
+      <c r="J71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="50" t="str">
+      <c r="K71" s="53" t="str">
         <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
         <v> </v>
       </c>
-      <c r="L71" s="50"/>
+      <c r="L71" s="53"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="50"/>
-      <c r="O71" s="47"/>
-      <c r="P71" s="48" t="n">
+      <c r="N71" s="53"/>
+      <c r="O71" s="50"/>
+      <c r="P71" s="51" t="n">
         <f aca="false">IF(B71&gt;0,IF(B71&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q71" s="47" t="str">
+      <c r="Q71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71/100," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="47"/>
-      <c r="S71" s="47" t="str">
+      <c r="R71" s="50"/>
+      <c r="S71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="47"/>
+      <c r="T71" s="50"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="50" t="str">
+      <c r="W71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="50" t="str">
+      <c r="X71" s="53" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="47" t="str">
+      <c r="Y71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="47" t="str">
+      <c r="Z71" s="50" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5353,57 +5334,57 @@
       <c r="C72" s="55"/>
       <c r="D72" s="56"/>
       <c r="E72" s="57"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53"/>
       <c r="H72" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I72" s="50" t="str">
+      <c r="I72" s="53" t="str">
         <f aca="false">IF(E72&gt;0,MIN(E72*H72,G72)," ")</f>
         <v> </v>
       </c>
-      <c r="J72" s="50" t="str">
+      <c r="J72" s="53" t="str">
         <f aca="false">IF(E72&gt;0,F72+I72," ")</f>
         <v> </v>
       </c>
-      <c r="K72" s="50" t="str">
+      <c r="K72" s="53" t="str">
         <f aca="false">IF(E72&gt;0,E72-J72," ")</f>
         <v> </v>
       </c>
-      <c r="L72" s="50"/>
+      <c r="L72" s="53"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="50"/>
-      <c r="O72" s="47"/>
-      <c r="P72" s="48" t="n">
+      <c r="N72" s="53"/>
+      <c r="O72" s="50"/>
+      <c r="P72" s="51" t="n">
         <f aca="false">IF(B72&gt;0,IF(B72&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q72" s="47" t="str">
+      <c r="Q72" s="50" t="str">
         <f aca="false">IF(E72&gt;0,E72*P72/100," ")</f>
         <v> </v>
       </c>
-      <c r="R72" s="47"/>
-      <c r="S72" s="47" t="str">
+      <c r="R72" s="50"/>
+      <c r="S72" s="50" t="str">
         <f aca="false">IF(E72&gt;0,E72-Q72," ")</f>
         <v> </v>
       </c>
-      <c r="T72" s="47"/>
+      <c r="T72" s="50"/>
       <c r="U72" s="54"/>
       <c r="V72" s="57"/>
-      <c r="W72" s="50" t="str">
+      <c r="W72" s="53" t="str">
         <f aca="false">IF(V72&gt;0,E72," ")</f>
         <v> </v>
       </c>
-      <c r="X72" s="50" t="str">
+      <c r="X72" s="53" t="str">
         <f aca="false">IF(V72&gt;0,J72," ")</f>
         <v> </v>
       </c>
-      <c r="Y72" s="47" t="str">
+      <c r="Y72" s="50" t="str">
         <f aca="false">IF((U72+V72)&gt;0,IF(V72&lt;S72,S72-V72," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z72" s="47" t="str">
+      <c r="Z72" s="50" t="str">
         <f aca="false">IF((U72+V72)&gt;0,IF(V72&gt;S72,V72-S72," ")," ")</f>
         <v> </v>
       </c>
@@ -5415,57 +5396,57 @@
       <c r="C73" s="55"/>
       <c r="D73" s="56"/>
       <c r="E73" s="57"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="50"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="53"/>
       <c r="H73" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I73" s="50" t="str">
+      <c r="I73" s="53" t="str">
         <f aca="false">IF(E73&gt;0,MIN(E73*H73,G73)," ")</f>
         <v> </v>
       </c>
-      <c r="J73" s="50" t="str">
+      <c r="J73" s="53" t="str">
         <f aca="false">IF(E73&gt;0,F73+I73," ")</f>
         <v> </v>
       </c>
-      <c r="K73" s="50" t="str">
+      <c r="K73" s="53" t="str">
         <f aca="false">IF(E73&gt;0,E73-J73," ")</f>
         <v> </v>
       </c>
-      <c r="L73" s="50"/>
+      <c r="L73" s="53"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="50"/>
-      <c r="O73" s="47"/>
-      <c r="P73" s="48" t="n">
+      <c r="N73" s="53"/>
+      <c r="O73" s="50"/>
+      <c r="P73" s="51" t="n">
         <f aca="false">IF(B73&gt;0,IF(B73&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q73" s="47" t="str">
+      <c r="Q73" s="50" t="str">
         <f aca="false">IF(E73&gt;0,E73*P73/100," ")</f>
         <v> </v>
       </c>
-      <c r="R73" s="47"/>
-      <c r="S73" s="47" t="str">
+      <c r="R73" s="50"/>
+      <c r="S73" s="50" t="str">
         <f aca="false">IF(E73&gt;0,E73-Q73," ")</f>
         <v> </v>
       </c>
-      <c r="T73" s="47"/>
+      <c r="T73" s="50"/>
       <c r="U73" s="54"/>
       <c r="V73" s="57"/>
-      <c r="W73" s="50" t="str">
+      <c r="W73" s="53" t="str">
         <f aca="false">IF(V73&gt;0,E73," ")</f>
         <v> </v>
       </c>
-      <c r="X73" s="50" t="str">
+      <c r="X73" s="53" t="str">
         <f aca="false">IF(V73&gt;0,J73," ")</f>
         <v> </v>
       </c>
-      <c r="Y73" s="47" t="str">
+      <c r="Y73" s="50" t="str">
         <f aca="false">IF((U73+V73)&gt;0,IF(V73&lt;S73,S73-V73," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z73" s="47" t="str">
+      <c r="Z73" s="50" t="str">
         <f aca="false">IF((U73+V73)&gt;0,IF(V73&gt;S73,V73-S73," ")," ")</f>
         <v> </v>
       </c>
@@ -5477,57 +5458,57 @@
       <c r="C74" s="55"/>
       <c r="D74" s="56"/>
       <c r="E74" s="57"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="50"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
       <c r="H74" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I74" s="50" t="str">
+      <c r="I74" s="53" t="str">
         <f aca="false">IF(E74&gt;0,MIN(E74*H74,G74)," ")</f>
         <v> </v>
       </c>
-      <c r="J74" s="50" t="str">
+      <c r="J74" s="53" t="str">
         <f aca="false">IF(E74&gt;0,F74+I74," ")</f>
         <v> </v>
       </c>
-      <c r="K74" s="50" t="str">
+      <c r="K74" s="53" t="str">
         <f aca="false">IF(E74&gt;0,E74-J74," ")</f>
         <v> </v>
       </c>
-      <c r="L74" s="50"/>
+      <c r="L74" s="53"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="50"/>
-      <c r="O74" s="47"/>
-      <c r="P74" s="48" t="n">
+      <c r="N74" s="53"/>
+      <c r="O74" s="50"/>
+      <c r="P74" s="51" t="n">
         <f aca="false">IF(B74&gt;0,IF(B74&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q74" s="47" t="str">
+      <c r="Q74" s="50" t="str">
         <f aca="false">IF(E74&gt;0,E74*P74/100," ")</f>
         <v> </v>
       </c>
-      <c r="R74" s="47"/>
-      <c r="S74" s="47" t="str">
+      <c r="R74" s="50"/>
+      <c r="S74" s="50" t="str">
         <f aca="false">IF(E74&gt;0,E74-Q74," ")</f>
         <v> </v>
       </c>
-      <c r="T74" s="47"/>
+      <c r="T74" s="50"/>
       <c r="U74" s="54"/>
       <c r="V74" s="57"/>
-      <c r="W74" s="50" t="str">
+      <c r="W74" s="53" t="str">
         <f aca="false">IF(V74&gt;0,E74," ")</f>
         <v> </v>
       </c>
-      <c r="X74" s="50" t="str">
+      <c r="X74" s="53" t="str">
         <f aca="false">IF(V74&gt;0,J74," ")</f>
         <v> </v>
       </c>
-      <c r="Y74" s="47" t="str">
+      <c r="Y74" s="50" t="str">
         <f aca="false">IF((U74+V74)&gt;0,IF(V74&lt;S74,S74-V74," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z74" s="47" t="str">
+      <c r="Z74" s="50" t="str">
         <f aca="false">IF((U74+V74)&gt;0,IF(V74&gt;S74,V74-S74," ")," ")</f>
         <v> </v>
       </c>
@@ -5536,7 +5517,7 @@
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C75" s="59"/>
       <c r="D75" s="59"/>
@@ -5565,9 +5546,9 @@
         <f aca="false">SUM(K67:K74)</f>
         <v>0</v>
       </c>
-      <c r="L75" s="50"/>
+      <c r="L75" s="53"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="50"/>
+      <c r="N75" s="53"/>
       <c r="O75" s="61" t="n">
         <f aca="false">SUM(O67:O74)</f>
         <v>0</v>
@@ -5585,8 +5566,8 @@
         <f aca="false">SUM(S67:S74)</f>
         <v>0</v>
       </c>
-      <c r="T75" s="47"/>
-      <c r="U75" s="49"/>
+      <c r="T75" s="50"/>
+      <c r="U75" s="52"/>
       <c r="V75" s="60" t="n">
         <f aca="false">SUM(V67:V74)</f>
         <v>0</v>
@@ -5614,121 +5595,121 @@
       <c r="B76" s="63"/>
       <c r="C76" s="64"/>
       <c r="D76" s="65"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
       <c r="H76" s="58"/>
-      <c r="I76" s="50"/>
-      <c r="J76" s="50"/>
-      <c r="K76" s="50"/>
-      <c r="L76" s="50"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
+      <c r="L76" s="53"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="50"/>
-      <c r="O76" s="50"/>
+      <c r="N76" s="53"/>
+      <c r="O76" s="53"/>
       <c r="P76" s="62"/>
-      <c r="Q76" s="50"/>
-      <c r="R76" s="50"/>
-      <c r="S76" s="50"/>
-      <c r="T76" s="47"/>
-      <c r="U76" s="49"/>
-      <c r="V76" s="50"/>
-      <c r="W76" s="50"/>
-      <c r="X76" s="50"/>
-      <c r="Y76" s="50"/>
-      <c r="Z76" s="50"/>
+      <c r="Q76" s="53"/>
+      <c r="R76" s="53"/>
+      <c r="S76" s="53"/>
+      <c r="T76" s="50"/>
+      <c r="U76" s="52"/>
+      <c r="V76" s="53"/>
+      <c r="W76" s="53"/>
+      <c r="X76" s="53"/>
+      <c r="Y76" s="53"/>
+      <c r="Z76" s="53"/>
       <c r="AA76" s="25"/>
     </row>
     <row r="77" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="42"/>
-      <c r="B77" s="51" t="s">
+      <c r="B77" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="C77" s="51"/>
+      <c r="C77" s="66"/>
       <c r="D77" s="62"/>
-      <c r="E77" s="50"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
-      <c r="H77" s="85" t="n">
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="86" t="n">
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="50"/>
-      <c r="J77" s="50"/>
-      <c r="K77" s="50"/>
-      <c r="L77" s="50"/>
+      <c r="I77" s="53"/>
+      <c r="J77" s="53"/>
+      <c r="K77" s="53"/>
+      <c r="L77" s="53"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="50"/>
-      <c r="O77" s="47"/>
-      <c r="P77" s="48"/>
-      <c r="Q77" s="47"/>
-      <c r="R77" s="47"/>
-      <c r="S77" s="47"/>
-      <c r="T77" s="47"/>
-      <c r="U77" s="49"/>
-      <c r="V77" s="50"/>
-      <c r="W77" s="50"/>
-      <c r="X77" s="50"/>
-      <c r="Y77" s="47"/>
-      <c r="Z77" s="47"/>
+      <c r="N77" s="53"/>
+      <c r="O77" s="50"/>
+      <c r="P77" s="51"/>
+      <c r="Q77" s="50"/>
+      <c r="R77" s="50"/>
+      <c r="S77" s="50"/>
+      <c r="T77" s="50"/>
+      <c r="U77" s="52"/>
+      <c r="V77" s="53"/>
+      <c r="W77" s="53"/>
+      <c r="X77" s="53"/>
+      <c r="Y77" s="50"/>
+      <c r="Z77" s="50"/>
       <c r="AA77" s="25"/>
     </row>
     <row r="78" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="83"/>
+      <c r="D78" s="84"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="50" t="str">
+      <c r="I78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="50" t="str">
+      <c r="J78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="50" t="str">
+      <c r="K78" s="53" t="str">
         <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
         <v> </v>
       </c>
-      <c r="L78" s="50"/>
+      <c r="L78" s="53"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="50"/>
-      <c r="O78" s="47"/>
-      <c r="P78" s="48" t="n">
+      <c r="N78" s="53"/>
+      <c r="O78" s="50"/>
+      <c r="P78" s="51" t="n">
         <f aca="false">IF(B78&gt;0,IF(B78&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q78" s="47" t="str">
+      <c r="Q78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78/100," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="47"/>
-      <c r="S78" s="47" t="str">
+      <c r="R78" s="50"/>
+      <c r="S78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="47"/>
+      <c r="T78" s="50"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="50" t="str">
+      <c r="W78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="50" t="str">
+      <c r="X78" s="53" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="47" t="str">
+      <c r="Y78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="47" t="str">
+      <c r="Z78" s="50" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5738,59 +5719,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="83"/>
+      <c r="D79" s="84"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="50" t="str">
+      <c r="I79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="50" t="str">
+      <c r="J79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="50" t="str">
+      <c r="K79" s="53" t="str">
         <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
         <v> </v>
       </c>
-      <c r="L79" s="50"/>
+      <c r="L79" s="53"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="50"/>
-      <c r="O79" s="47"/>
-      <c r="P79" s="48" t="n">
+      <c r="N79" s="53"/>
+      <c r="O79" s="50"/>
+      <c r="P79" s="51" t="n">
         <f aca="false">IF(B79&gt;0,IF(B79&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q79" s="47" t="str">
+      <c r="Q79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79/100," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="47"/>
-      <c r="S79" s="47" t="str">
+      <c r="R79" s="50"/>
+      <c r="S79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="47"/>
+      <c r="T79" s="50"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="50" t="str">
+      <c r="W79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="50" t="str">
+      <c r="X79" s="53" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="47" t="str">
+      <c r="Y79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="47" t="str">
+      <c r="Z79" s="50" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -5800,59 +5781,59 @@
       <c r="A80" s="42"/>
       <c r="B80" s="54"/>
       <c r="C80" s="55"/>
-      <c r="D80" s="83"/>
+      <c r="D80" s="84"/>
       <c r="E80" s="57"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
       <c r="H80" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I80" s="50" t="str">
+      <c r="I80" s="53" t="str">
         <f aca="false">IF(E80&gt;0,MIN(E80*H80,G80)," ")</f>
         <v> </v>
       </c>
-      <c r="J80" s="50" t="str">
+      <c r="J80" s="53" t="str">
         <f aca="false">IF(E80&gt;0,F80+I80," ")</f>
         <v> </v>
       </c>
-      <c r="K80" s="50" t="str">
+      <c r="K80" s="53" t="str">
         <f aca="false">IF(E80&gt;0,E80-J80," ")</f>
         <v> </v>
       </c>
-      <c r="L80" s="50"/>
+      <c r="L80" s="53"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="50"/>
-      <c r="O80" s="47"/>
-      <c r="P80" s="48" t="n">
+      <c r="N80" s="53"/>
+      <c r="O80" s="50"/>
+      <c r="P80" s="51" t="n">
         <f aca="false">IF(B80&gt;0,IF(B80&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q80" s="47" t="str">
+      <c r="Q80" s="50" t="str">
         <f aca="false">IF(E80&gt;0,E80*P80/100," ")</f>
         <v> </v>
       </c>
-      <c r="R80" s="47"/>
-      <c r="S80" s="47" t="str">
+      <c r="R80" s="50"/>
+      <c r="S80" s="50" t="str">
         <f aca="false">IF(E80&gt;0,E80-Q80," ")</f>
         <v> </v>
       </c>
-      <c r="T80" s="47"/>
+      <c r="T80" s="50"/>
       <c r="U80" s="54"/>
       <c r="V80" s="57"/>
-      <c r="W80" s="50" t="str">
+      <c r="W80" s="53" t="str">
         <f aca="false">IF(V80&gt;0,E80," ")</f>
         <v> </v>
       </c>
-      <c r="X80" s="50" t="str">
+      <c r="X80" s="53" t="str">
         <f aca="false">IF(V80&gt;0,J80," ")</f>
         <v> </v>
       </c>
-      <c r="Y80" s="47" t="str">
+      <c r="Y80" s="50" t="str">
         <f aca="false">IF((U80+V80)&gt;0,IF(V80&lt;S80,S80-V80," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z80" s="47" t="str">
+      <c r="Z80" s="50" t="str">
         <f aca="false">IF((U80+V80)&gt;0,IF(V80&gt;S80,V80-S80," ")," ")</f>
         <v> </v>
       </c>
@@ -5862,59 +5843,59 @@
       <c r="A81" s="42"/>
       <c r="B81" s="54"/>
       <c r="C81" s="55"/>
-      <c r="D81" s="83"/>
+      <c r="D81" s="84"/>
       <c r="E81" s="57"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
       <c r="H81" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I81" s="50" t="str">
+      <c r="I81" s="53" t="str">
         <f aca="false">IF(E81&gt;0,MIN(E81*H81,G81)," ")</f>
         <v> </v>
       </c>
-      <c r="J81" s="50" t="str">
+      <c r="J81" s="53" t="str">
         <f aca="false">IF(E81&gt;0,F81+I81," ")</f>
         <v> </v>
       </c>
-      <c r="K81" s="50" t="str">
+      <c r="K81" s="53" t="str">
         <f aca="false">IF(E81&gt;0,E81-J81," ")</f>
         <v> </v>
       </c>
-      <c r="L81" s="50"/>
+      <c r="L81" s="53"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="50"/>
-      <c r="O81" s="47"/>
-      <c r="P81" s="48" t="n">
+      <c r="N81" s="53"/>
+      <c r="O81" s="50"/>
+      <c r="P81" s="51" t="n">
         <f aca="false">IF(B81&gt;0,IF(B81&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q81" s="47" t="str">
+      <c r="Q81" s="50" t="str">
         <f aca="false">IF(E81&gt;0,E81*P81/100," ")</f>
         <v> </v>
       </c>
-      <c r="R81" s="47"/>
-      <c r="S81" s="47" t="str">
+      <c r="R81" s="50"/>
+      <c r="S81" s="50" t="str">
         <f aca="false">IF(E81&gt;0,E81-Q81," ")</f>
         <v> </v>
       </c>
-      <c r="T81" s="47"/>
+      <c r="T81" s="50"/>
       <c r="U81" s="54"/>
       <c r="V81" s="57"/>
-      <c r="W81" s="50" t="str">
+      <c r="W81" s="53" t="str">
         <f aca="false">IF(V81&gt;0,E81," ")</f>
         <v> </v>
       </c>
-      <c r="X81" s="50" t="str">
+      <c r="X81" s="53" t="str">
         <f aca="false">IF(V81&gt;0,J81," ")</f>
         <v> </v>
       </c>
-      <c r="Y81" s="47" t="str">
+      <c r="Y81" s="50" t="str">
         <f aca="false">IF((U81+V81)&gt;0,IF(V81&lt;S81,S81-V81," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z81" s="47" t="str">
+      <c r="Z81" s="50" t="str">
         <f aca="false">IF((U81+V81)&gt;0,IF(V81&gt;S81,V81-S81," ")," ")</f>
         <v> </v>
       </c>
@@ -5924,59 +5905,59 @@
       <c r="A82" s="42"/>
       <c r="B82" s="54"/>
       <c r="C82" s="55"/>
-      <c r="D82" s="83"/>
+      <c r="D82" s="84"/>
       <c r="E82" s="57"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="53"/>
       <c r="H82" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I82" s="50" t="str">
+      <c r="I82" s="53" t="str">
         <f aca="false">IF(E82&gt;0,MIN(E82*H82,G82)," ")</f>
         <v> </v>
       </c>
-      <c r="J82" s="50" t="str">
+      <c r="J82" s="53" t="str">
         <f aca="false">IF(E82&gt;0,F82+I82," ")</f>
         <v> </v>
       </c>
-      <c r="K82" s="50" t="str">
+      <c r="K82" s="53" t="str">
         <f aca="false">IF(E82&gt;0,E82-J82," ")</f>
         <v> </v>
       </c>
-      <c r="L82" s="50"/>
+      <c r="L82" s="53"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="50"/>
-      <c r="O82" s="47"/>
-      <c r="P82" s="48" t="n">
+      <c r="N82" s="53"/>
+      <c r="O82" s="50"/>
+      <c r="P82" s="51" t="n">
         <f aca="false">IF(B82&gt;0,IF(B82&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q82" s="47" t="str">
+      <c r="Q82" s="50" t="str">
         <f aca="false">IF(E82&gt;0,E82*P82/100," ")</f>
         <v> </v>
       </c>
-      <c r="R82" s="47"/>
-      <c r="S82" s="47" t="str">
+      <c r="R82" s="50"/>
+      <c r="S82" s="50" t="str">
         <f aca="false">IF(E82&gt;0,E82-Q82," ")</f>
         <v> </v>
       </c>
-      <c r="T82" s="47"/>
+      <c r="T82" s="50"/>
       <c r="U82" s="54"/>
       <c r="V82" s="57"/>
-      <c r="W82" s="50" t="str">
+      <c r="W82" s="53" t="str">
         <f aca="false">IF(V82&gt;0,E82," ")</f>
         <v> </v>
       </c>
-      <c r="X82" s="50" t="str">
+      <c r="X82" s="53" t="str">
         <f aca="false">IF(V82&gt;0,J82," ")</f>
         <v> </v>
       </c>
-      <c r="Y82" s="47" t="str">
+      <c r="Y82" s="50" t="str">
         <f aca="false">IF((U82+V82)&gt;0,IF(V82&lt;S82,S82-V82," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z82" s="47" t="str">
+      <c r="Z82" s="50" t="str">
         <f aca="false">IF((U82+V82)&gt;0,IF(V82&gt;S82,V82-S82," ")," ")</f>
         <v> </v>
       </c>
@@ -5985,7 +5966,7 @@
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C83" s="59"/>
       <c r="D83" s="59"/>
@@ -6014,9 +5995,9 @@
         <f aca="false">SUM(K78:K82)</f>
         <v>0</v>
       </c>
-      <c r="L83" s="50"/>
+      <c r="L83" s="53"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="50"/>
+      <c r="N83" s="53"/>
       <c r="O83" s="61" t="n">
         <f aca="false">SUM(O78:O82)</f>
         <v>0</v>
@@ -6034,8 +6015,8 @@
         <f aca="false">SUM(S78:S82)</f>
         <v>0</v>
       </c>
-      <c r="T83" s="47"/>
-      <c r="U83" s="49"/>
+      <c r="T83" s="50"/>
+      <c r="U83" s="52"/>
       <c r="V83" s="60" t="n">
         <f aca="false">SUM(V78:V82)</f>
         <v>0</v>
@@ -6063,121 +6044,121 @@
       <c r="B84" s="63"/>
       <c r="C84" s="64"/>
       <c r="D84" s="65"/>
-      <c r="E84" s="50"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
       <c r="H84" s="58"/>
-      <c r="I84" s="50"/>
-      <c r="J84" s="50"/>
-      <c r="K84" s="50"/>
-      <c r="L84" s="50"/>
+      <c r="I84" s="53"/>
+      <c r="J84" s="53"/>
+      <c r="K84" s="53"/>
+      <c r="L84" s="53"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="50"/>
-      <c r="O84" s="50"/>
+      <c r="N84" s="53"/>
+      <c r="O84" s="53"/>
       <c r="P84" s="62"/>
-      <c r="Q84" s="50"/>
-      <c r="R84" s="50"/>
-      <c r="S84" s="50"/>
-      <c r="T84" s="47"/>
-      <c r="U84" s="49"/>
-      <c r="V84" s="50"/>
-      <c r="W84" s="50"/>
-      <c r="X84" s="50"/>
-      <c r="Y84" s="50"/>
-      <c r="Z84" s="50"/>
+      <c r="Q84" s="53"/>
+      <c r="R84" s="53"/>
+      <c r="S84" s="53"/>
+      <c r="T84" s="50"/>
+      <c r="U84" s="52"/>
+      <c r="V84" s="53"/>
+      <c r="W84" s="53"/>
+      <c r="X84" s="53"/>
+      <c r="Y84" s="53"/>
+      <c r="Z84" s="53"/>
       <c r="AA84" s="25"/>
     </row>
     <row r="85" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="42"/>
-      <c r="B85" s="51" t="s">
+      <c r="B85" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="C85" s="51"/>
-      <c r="D85" s="68"/>
-      <c r="E85" s="50"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
-      <c r="H85" s="85" t="n">
+      <c r="C85" s="66"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="86" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="50"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="50"/>
-      <c r="L85" s="50"/>
+      <c r="I85" s="53"/>
+      <c r="J85" s="53"/>
+      <c r="K85" s="53"/>
+      <c r="L85" s="53"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="50"/>
-      <c r="O85" s="47"/>
-      <c r="P85" s="48"/>
-      <c r="Q85" s="47"/>
-      <c r="R85" s="47"/>
-      <c r="S85" s="47"/>
-      <c r="T85" s="47"/>
-      <c r="U85" s="49"/>
-      <c r="V85" s="50"/>
-      <c r="W85" s="50"/>
-      <c r="X85" s="50"/>
-      <c r="Y85" s="47"/>
-      <c r="Z85" s="47"/>
+      <c r="N85" s="53"/>
+      <c r="O85" s="50"/>
+      <c r="P85" s="51"/>
+      <c r="Q85" s="50"/>
+      <c r="R85" s="50"/>
+      <c r="S85" s="50"/>
+      <c r="T85" s="50"/>
+      <c r="U85" s="52"/>
+      <c r="V85" s="53"/>
+      <c r="W85" s="53"/>
+      <c r="X85" s="53"/>
+      <c r="Y85" s="50"/>
+      <c r="Z85" s="50"/>
       <c r="AA85" s="25"/>
     </row>
     <row r="86" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="83"/>
+      <c r="D86" s="84"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="50" t="str">
+      <c r="I86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="50" t="str">
+      <c r="J86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="50" t="str">
+      <c r="K86" s="53" t="str">
         <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
         <v> </v>
       </c>
-      <c r="L86" s="50"/>
+      <c r="L86" s="53"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="50"/>
-      <c r="O86" s="47"/>
-      <c r="P86" s="48" t="n">
+      <c r="N86" s="53"/>
+      <c r="O86" s="50"/>
+      <c r="P86" s="51" t="n">
         <f aca="false">IF(B86&gt;0,IF(B86&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q86" s="47" t="str">
+      <c r="Q86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86/100," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="47"/>
-      <c r="S86" s="47" t="str">
+      <c r="R86" s="50"/>
+      <c r="S86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="47"/>
+      <c r="T86" s="50"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="50" t="str">
+      <c r="W86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="50" t="str">
+      <c r="X86" s="53" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="47" t="str">
+      <c r="Y86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="47" t="str">
+      <c r="Z86" s="50" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6187,59 +6168,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="83"/>
+      <c r="D87" s="84"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="50" t="str">
+      <c r="I87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="50" t="str">
+      <c r="J87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="50" t="str">
+      <c r="K87" s="53" t="str">
         <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
         <v> </v>
       </c>
-      <c r="L87" s="50"/>
+      <c r="L87" s="53"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="50"/>
-      <c r="O87" s="47"/>
-      <c r="P87" s="48" t="n">
+      <c r="N87" s="53"/>
+      <c r="O87" s="50"/>
+      <c r="P87" s="51" t="n">
         <f aca="false">IF(B87&gt;0,IF(B87&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q87" s="47" t="str">
+      <c r="Q87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87/100," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="47"/>
-      <c r="S87" s="47" t="str">
+      <c r="R87" s="50"/>
+      <c r="S87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="47"/>
+      <c r="T87" s="50"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="50" t="str">
+      <c r="W87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="50" t="str">
+      <c r="X87" s="53" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="47" t="str">
+      <c r="Y87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="47" t="str">
+      <c r="Z87" s="50" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6249,59 +6230,59 @@
       <c r="A88" s="42"/>
       <c r="B88" s="54"/>
       <c r="C88" s="55"/>
-      <c r="D88" s="83"/>
+      <c r="D88" s="84"/>
       <c r="E88" s="57"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
       <c r="H88" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I88" s="50" t="str">
+      <c r="I88" s="53" t="str">
         <f aca="false">IF(E88&gt;0,MIN(E88*H88,G88)," ")</f>
         <v> </v>
       </c>
-      <c r="J88" s="50" t="str">
+      <c r="J88" s="53" t="str">
         <f aca="false">IF(E88&gt;0,F88+I88," ")</f>
         <v> </v>
       </c>
-      <c r="K88" s="50" t="str">
+      <c r="K88" s="53" t="str">
         <f aca="false">IF(E88&gt;0,E88-J88," ")</f>
         <v> </v>
       </c>
-      <c r="L88" s="50"/>
+      <c r="L88" s="53"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="50"/>
-      <c r="O88" s="47"/>
-      <c r="P88" s="48" t="n">
+      <c r="N88" s="53"/>
+      <c r="O88" s="50"/>
+      <c r="P88" s="51" t="n">
         <f aca="false">IF(B88&gt;0,IF(B88&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q88" s="47" t="str">
+      <c r="Q88" s="50" t="str">
         <f aca="false">IF(E88&gt;0,E88*P88/100," ")</f>
         <v> </v>
       </c>
-      <c r="R88" s="47"/>
-      <c r="S88" s="47" t="str">
+      <c r="R88" s="50"/>
+      <c r="S88" s="50" t="str">
         <f aca="false">IF(E88&gt;0,E88-Q88," ")</f>
         <v> </v>
       </c>
-      <c r="T88" s="47"/>
+      <c r="T88" s="50"/>
       <c r="U88" s="54"/>
       <c r="V88" s="57"/>
-      <c r="W88" s="50" t="str">
+      <c r="W88" s="53" t="str">
         <f aca="false">IF(V88&gt;0,E88," ")</f>
         <v> </v>
       </c>
-      <c r="X88" s="50" t="str">
+      <c r="X88" s="53" t="str">
         <f aca="false">IF(V88&gt;0,J88," ")</f>
         <v> </v>
       </c>
-      <c r="Y88" s="47" t="str">
+      <c r="Y88" s="50" t="str">
         <f aca="false">IF((U88+V88)&gt;0,IF(V88&lt;S88,S88-V88," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z88" s="47" t="str">
+      <c r="Z88" s="50" t="str">
         <f aca="false">IF((U88+V88)&gt;0,IF(V88&gt;S88,V88-S88," ")," ")</f>
         <v> </v>
       </c>
@@ -6311,59 +6292,59 @@
       <c r="A89" s="42"/>
       <c r="B89" s="54"/>
       <c r="C89" s="55"/>
-      <c r="D89" s="83"/>
+      <c r="D89" s="84"/>
       <c r="E89" s="57"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
       <c r="H89" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I89" s="50" t="str">
+      <c r="I89" s="53" t="str">
         <f aca="false">IF(E89&gt;0,MIN(E89*H89,G89)," ")</f>
         <v> </v>
       </c>
-      <c r="J89" s="50" t="str">
+      <c r="J89" s="53" t="str">
         <f aca="false">IF(E89&gt;0,F89+I89," ")</f>
         <v> </v>
       </c>
-      <c r="K89" s="50" t="str">
+      <c r="K89" s="53" t="str">
         <f aca="false">IF(E89&gt;0,E89-J89," ")</f>
         <v> </v>
       </c>
-      <c r="L89" s="50"/>
+      <c r="L89" s="53"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="50"/>
-      <c r="O89" s="47"/>
-      <c r="P89" s="48" t="n">
+      <c r="N89" s="53"/>
+      <c r="O89" s="50"/>
+      <c r="P89" s="51" t="n">
         <f aca="false">IF(B89&gt;0,IF(B89&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q89" s="47" t="str">
+      <c r="Q89" s="50" t="str">
         <f aca="false">IF(E89&gt;0,E89*P89/100," ")</f>
         <v> </v>
       </c>
-      <c r="R89" s="47"/>
-      <c r="S89" s="47" t="str">
+      <c r="R89" s="50"/>
+      <c r="S89" s="50" t="str">
         <f aca="false">IF(E89&gt;0,E89-Q89," ")</f>
         <v> </v>
       </c>
-      <c r="T89" s="47"/>
+      <c r="T89" s="50"/>
       <c r="U89" s="54"/>
       <c r="V89" s="57"/>
-      <c r="W89" s="50" t="str">
+      <c r="W89" s="53" t="str">
         <f aca="false">IF(V89&gt;0,E89," ")</f>
         <v> </v>
       </c>
-      <c r="X89" s="50" t="str">
+      <c r="X89" s="53" t="str">
         <f aca="false">IF(V89&gt;0,J89," ")</f>
         <v> </v>
       </c>
-      <c r="Y89" s="47" t="str">
+      <c r="Y89" s="50" t="str">
         <f aca="false">IF((U89+V89)&gt;0,IF(V89&lt;S89,S89-V89," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z89" s="47" t="str">
+      <c r="Z89" s="50" t="str">
         <f aca="false">IF((U89+V89)&gt;0,IF(V89&gt;S89,V89-S89," ")," ")</f>
         <v> </v>
       </c>
@@ -6373,59 +6354,59 @@
       <c r="A90" s="42"/>
       <c r="B90" s="54"/>
       <c r="C90" s="55"/>
-      <c r="D90" s="83"/>
+      <c r="D90" s="84"/>
       <c r="E90" s="57"/>
-      <c r="F90" s="50"/>
-      <c r="G90" s="50"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
       <c r="H90" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I90" s="50" t="str">
+      <c r="I90" s="53" t="str">
         <f aca="false">IF(E90&gt;0,MIN(E90*H90,G90)," ")</f>
         <v> </v>
       </c>
-      <c r="J90" s="50" t="str">
+      <c r="J90" s="53" t="str">
         <f aca="false">IF(E90&gt;0,F90+I90," ")</f>
         <v> </v>
       </c>
-      <c r="K90" s="50" t="str">
+      <c r="K90" s="53" t="str">
         <f aca="false">IF(E90&gt;0,E90-J90," ")</f>
         <v> </v>
       </c>
-      <c r="L90" s="50"/>
+      <c r="L90" s="53"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="50"/>
-      <c r="O90" s="47"/>
-      <c r="P90" s="48" t="n">
+      <c r="N90" s="53"/>
+      <c r="O90" s="50"/>
+      <c r="P90" s="51" t="n">
         <f aca="false">IF(B90&gt;0,IF(B90&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q90" s="47" t="str">
+      <c r="Q90" s="50" t="str">
         <f aca="false">IF(E90&gt;0,E90*P90/100," ")</f>
         <v> </v>
       </c>
-      <c r="R90" s="47"/>
-      <c r="S90" s="47" t="str">
+      <c r="R90" s="50"/>
+      <c r="S90" s="50" t="str">
         <f aca="false">IF(E90&gt;0,E90-Q90," ")</f>
         <v> </v>
       </c>
-      <c r="T90" s="47"/>
+      <c r="T90" s="50"/>
       <c r="U90" s="54"/>
       <c r="V90" s="57"/>
-      <c r="W90" s="50" t="str">
+      <c r="W90" s="53" t="str">
         <f aca="false">IF(V90&gt;0,E90," ")</f>
         <v> </v>
       </c>
-      <c r="X90" s="50" t="str">
+      <c r="X90" s="53" t="str">
         <f aca="false">IF(V90&gt;0,J90," ")</f>
         <v> </v>
       </c>
-      <c r="Y90" s="47" t="str">
+      <c r="Y90" s="50" t="str">
         <f aca="false">IF((U90+V90)&gt;0,IF(V90&lt;S90,S90-V90," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z90" s="47" t="str">
+      <c r="Z90" s="50" t="str">
         <f aca="false">IF((U90+V90)&gt;0,IF(V90&gt;S90,V90-S90," ")," ")</f>
         <v> </v>
       </c>
@@ -6435,59 +6416,59 @@
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="83"/>
+      <c r="D91" s="84"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I91" s="50" t="str">
+      <c r="I91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="50" t="str">
+      <c r="J91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="50" t="str">
+      <c r="K91" s="53" t="str">
         <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
         <v> </v>
       </c>
-      <c r="L91" s="50"/>
+      <c r="L91" s="53"/>
       <c r="M91" s="58"/>
-      <c r="N91" s="50"/>
-      <c r="O91" s="47"/>
-      <c r="P91" s="48" t="n">
+      <c r="N91" s="53"/>
+      <c r="O91" s="50"/>
+      <c r="P91" s="51" t="n">
         <f aca="false">IF(B91&gt;0,IF(B91&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q91" s="47" t="str">
+      <c r="Q91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91*P91/100," ")</f>
         <v> </v>
       </c>
-      <c r="R91" s="47"/>
-      <c r="S91" s="47" t="str">
+      <c r="R91" s="50"/>
+      <c r="S91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91-Q91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="47"/>
+      <c r="T91" s="50"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="50" t="str">
+      <c r="W91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="50" t="str">
+      <c r="X91" s="53" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="47" t="str">
+      <c r="Y91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,S91-V91," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="47" t="str">
+      <c r="Z91" s="50" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,V91-S91," ")," ")</f>
         <v> </v>
       </c>
@@ -6497,59 +6478,59 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="83"/>
+      <c r="D92" s="84"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="50"/>
+      <c r="F92" s="53"/>
+      <c r="G92" s="53"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I92" s="50" t="str">
+      <c r="I92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="50" t="str">
+      <c r="J92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="50" t="str">
+      <c r="K92" s="53" t="str">
         <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
         <v> </v>
       </c>
-      <c r="L92" s="50"/>
+      <c r="L92" s="53"/>
       <c r="M92" s="58"/>
-      <c r="N92" s="50"/>
-      <c r="O92" s="47"/>
-      <c r="P92" s="48" t="n">
+      <c r="N92" s="53"/>
+      <c r="O92" s="50"/>
+      <c r="P92" s="51" t="n">
         <f aca="false">IF(B92&gt;0,IF(B92&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q92" s="47" t="str">
+      <c r="Q92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92*P92/100," ")</f>
         <v> </v>
       </c>
-      <c r="R92" s="47"/>
-      <c r="S92" s="47" t="str">
+      <c r="R92" s="50"/>
+      <c r="S92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92-Q92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="47"/>
+      <c r="T92" s="50"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="50" t="str">
+      <c r="W92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="50" t="str">
+      <c r="X92" s="53" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="47" t="str">
+      <c r="Y92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,S92-V92," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="47" t="str">
+      <c r="Z92" s="50" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,V92-S92," ")," ")</f>
         <v> </v>
       </c>
@@ -6559,59 +6540,59 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="83"/>
+      <c r="D93" s="84"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
+      <c r="F93" s="53"/>
+      <c r="G93" s="53"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I93" s="50" t="str">
+      <c r="I93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="50" t="str">
+      <c r="J93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="50" t="str">
+      <c r="K93" s="53" t="str">
         <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
         <v> </v>
       </c>
-      <c r="L93" s="50"/>
+      <c r="L93" s="53"/>
       <c r="M93" s="58"/>
-      <c r="N93" s="50"/>
-      <c r="O93" s="47"/>
-      <c r="P93" s="48" t="n">
+      <c r="N93" s="53"/>
+      <c r="O93" s="50"/>
+      <c r="P93" s="51" t="n">
         <f aca="false">IF(B93&gt;0,IF(B93&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q93" s="47" t="str">
+      <c r="Q93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93*P93/100," ")</f>
         <v> </v>
       </c>
-      <c r="R93" s="47"/>
-      <c r="S93" s="47" t="str">
+      <c r="R93" s="50"/>
+      <c r="S93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93-Q93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="47"/>
+      <c r="T93" s="50"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="50" t="str">
+      <c r="W93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="50" t="str">
+      <c r="X93" s="53" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="47" t="str">
+      <c r="Y93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,S93-V93," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="47" t="str">
+      <c r="Z93" s="50" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,V93-S93," ")," ")</f>
         <v> </v>
       </c>
@@ -6620,7 +6601,7 @@
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="42"/>
       <c r="B94" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="59"/>
@@ -6649,9 +6630,9 @@
         <f aca="false">SUM(K86:K93)</f>
         <v>0</v>
       </c>
-      <c r="L94" s="50"/>
+      <c r="L94" s="53"/>
       <c r="M94" s="58"/>
-      <c r="N94" s="50"/>
+      <c r="N94" s="53"/>
       <c r="O94" s="61" t="n">
         <f aca="false">SUM(O86:O93)</f>
         <v>0</v>
@@ -6669,8 +6650,8 @@
         <f aca="false">SUM(S86:S93)</f>
         <v>0</v>
       </c>
-      <c r="T94" s="47"/>
-      <c r="U94" s="49"/>
+      <c r="T94" s="50"/>
+      <c r="U94" s="52"/>
       <c r="V94" s="60" t="n">
         <f aca="false">SUM(V86:V93)</f>
         <v>0</v>
@@ -6698,120 +6679,120 @@
       <c r="B95" s="63"/>
       <c r="C95" s="64"/>
       <c r="D95" s="65"/>
-      <c r="E95" s="50"/>
-      <c r="F95" s="50"/>
-      <c r="G95" s="50"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="53"/>
       <c r="H95" s="58"/>
-      <c r="I95" s="50"/>
-      <c r="J95" s="50"/>
-      <c r="K95" s="50"/>
-      <c r="L95" s="50"/>
+      <c r="I95" s="53"/>
+      <c r="J95" s="53"/>
+      <c r="K95" s="53"/>
+      <c r="L95" s="53"/>
       <c r="M95" s="58"/>
-      <c r="N95" s="50"/>
-      <c r="O95" s="50"/>
+      <c r="N95" s="53"/>
+      <c r="O95" s="53"/>
       <c r="P95" s="62"/>
-      <c r="Q95" s="50"/>
-      <c r="R95" s="50"/>
-      <c r="S95" s="50"/>
-      <c r="T95" s="47"/>
-      <c r="U95" s="49"/>
-      <c r="V95" s="50"/>
-      <c r="W95" s="50"/>
-      <c r="X95" s="50"/>
-      <c r="Y95" s="50"/>
-      <c r="Z95" s="50"/>
+      <c r="Q95" s="53"/>
+      <c r="R95" s="53"/>
+      <c r="S95" s="53"/>
+      <c r="T95" s="50"/>
+      <c r="U95" s="52"/>
+      <c r="V95" s="53"/>
+      <c r="W95" s="53"/>
+      <c r="X95" s="53"/>
+      <c r="Y95" s="53"/>
+      <c r="Z95" s="53"/>
       <c r="AA95" s="25"/>
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="51" t="s">
+      <c r="B96" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C96" s="51"/>
-      <c r="D96" s="68"/>
-      <c r="E96" s="50"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50"/>
-      <c r="H96" s="85" t="n">
+      <c r="C96" s="66"/>
+      <c r="D96" s="69"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53"/>
+      <c r="H96" s="86" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I96" s="50"/>
-      <c r="J96" s="50"/>
-      <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="50"/>
-      <c r="O96" s="47"/>
+      <c r="N96" s="53"/>
+      <c r="O96" s="50"/>
       <c r="P96" s="62"/>
-      <c r="Q96" s="47"/>
-      <c r="R96" s="47"/>
-      <c r="S96" s="47"/>
-      <c r="T96" s="47"/>
-      <c r="U96" s="49"/>
-      <c r="V96" s="50"/>
-      <c r="W96" s="50"/>
-      <c r="X96" s="50"/>
-      <c r="Y96" s="47"/>
-      <c r="Z96" s="47"/>
+      <c r="Q96" s="50"/>
+      <c r="R96" s="50"/>
+      <c r="S96" s="50"/>
+      <c r="T96" s="50"/>
+      <c r="U96" s="52"/>
+      <c r="V96" s="53"/>
+      <c r="W96" s="53"/>
+      <c r="X96" s="53"/>
+      <c r="Y96" s="50"/>
+      <c r="Z96" s="50"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="83"/>
+      <c r="D97" s="84"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
+      <c r="F97" s="53"/>
+      <c r="G97" s="53"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="50" t="str">
+      <c r="I97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="50" t="str">
+      <c r="J97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="50" t="str">
+      <c r="K97" s="53" t="str">
         <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
         <v> </v>
       </c>
-      <c r="L97" s="50"/>
-      <c r="M97" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="50"/>
-      <c r="O97" s="47"/>
-      <c r="P97" s="48"/>
-      <c r="Q97" s="47"/>
-      <c r="R97" s="47" t="str">
+      <c r="L97" s="53"/>
+      <c r="M97" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="53"/>
+      <c r="O97" s="50"/>
+      <c r="P97" s="51"/>
+      <c r="Q97" s="50"/>
+      <c r="R97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,IF(E97&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M97),E97*R$4/100)*(1-M97)," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="47" t="str">
+      <c r="S97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="47"/>
+      <c r="T97" s="50"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="50" t="str">
+      <c r="W97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="50" t="str">
+      <c r="X97" s="53" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="47" t="str">
+      <c r="Y97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="47" t="str">
+      <c r="Z97" s="50" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -6821,58 +6802,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="83"/>
+      <c r="D98" s="84"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="50"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="50" t="str">
+      <c r="I98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="50" t="str">
+      <c r="J98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="50" t="str">
+      <c r="K98" s="53" t="str">
         <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
         <v> </v>
       </c>
-      <c r="L98" s="50"/>
-      <c r="M98" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="50"/>
-      <c r="O98" s="47"/>
-      <c r="P98" s="48"/>
-      <c r="Q98" s="47"/>
-      <c r="R98" s="47" t="str">
+      <c r="L98" s="53"/>
+      <c r="M98" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="53"/>
+      <c r="O98" s="50"/>
+      <c r="P98" s="51"/>
+      <c r="Q98" s="50"/>
+      <c r="R98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,IF(E98&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M98),E98*R$4/100)*(1-M98)," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="47" t="str">
+      <c r="S98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="47"/>
+      <c r="T98" s="50"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="50" t="str">
+      <c r="W98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="50" t="str">
+      <c r="X98" s="53" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="47" t="str">
+      <c r="Y98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="47" t="str">
+      <c r="Z98" s="50" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -6882,58 +6863,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="83"/>
+      <c r="D99" s="84"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
+      <c r="F99" s="53"/>
+      <c r="G99" s="53"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="50" t="str">
+      <c r="I99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="50" t="str">
+      <c r="J99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="50" t="str">
+      <c r="K99" s="53" t="str">
         <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
         <v> </v>
       </c>
-      <c r="L99" s="50"/>
-      <c r="M99" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="50"/>
-      <c r="O99" s="47"/>
-      <c r="P99" s="48"/>
-      <c r="Q99" s="47"/>
-      <c r="R99" s="47" t="str">
+      <c r="L99" s="53"/>
+      <c r="M99" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="53"/>
+      <c r="O99" s="50"/>
+      <c r="P99" s="51"/>
+      <c r="Q99" s="50"/>
+      <c r="R99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,IF(E99&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M99),E99*R$4/100)*(1-M99)," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="47" t="str">
+      <c r="S99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="47"/>
+      <c r="T99" s="50"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="50" t="str">
+      <c r="W99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="50" t="str">
+      <c r="X99" s="53" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="47" t="str">
+      <c r="Y99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="47" t="str">
+      <c r="Z99" s="50" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -6943,58 +6924,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="83"/>
+      <c r="D100" s="84"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="53"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="50" t="str">
+      <c r="I100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="50" t="str">
+      <c r="J100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="50" t="str">
+      <c r="K100" s="53" t="str">
         <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
         <v> </v>
       </c>
-      <c r="L100" s="50"/>
-      <c r="M100" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="50"/>
-      <c r="O100" s="47"/>
-      <c r="P100" s="48"/>
-      <c r="Q100" s="47"/>
-      <c r="R100" s="47" t="str">
+      <c r="L100" s="53"/>
+      <c r="M100" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="53"/>
+      <c r="O100" s="50"/>
+      <c r="P100" s="51"/>
+      <c r="Q100" s="50"/>
+      <c r="R100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,IF(E100&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M100),E100*R$4/100)*(1-M100)," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="47" t="str">
+      <c r="S100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="47"/>
+      <c r="T100" s="50"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="50" t="str">
+      <c r="W100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="50" t="str">
+      <c r="X100" s="53" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="47" t="str">
+      <c r="Y100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="47" t="str">
+      <c r="Z100" s="50" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -7004,58 +6985,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="83"/>
+      <c r="D101" s="84"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
+      <c r="F101" s="53"/>
+      <c r="G101" s="53"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="50" t="str">
+      <c r="I101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="50" t="str">
+      <c r="J101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="50" t="str">
+      <c r="K101" s="53" t="str">
         <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
         <v> </v>
       </c>
-      <c r="L101" s="50"/>
-      <c r="M101" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="50"/>
-      <c r="O101" s="47"/>
-      <c r="P101" s="48"/>
-      <c r="Q101" s="47"/>
-      <c r="R101" s="47" t="str">
+      <c r="L101" s="53"/>
+      <c r="M101" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="53"/>
+      <c r="O101" s="50"/>
+      <c r="P101" s="51"/>
+      <c r="Q101" s="50"/>
+      <c r="R101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,IF(E101&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M101),E101*R$4/100)*(1-M101)," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="47" t="str">
+      <c r="S101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="47"/>
+      <c r="T101" s="50"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="50" t="str">
+      <c r="W101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="50" t="str">
+      <c r="X101" s="53" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="47" t="str">
+      <c r="Y101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="47" t="str">
+      <c r="Z101" s="50" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7063,94 +7044,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="51" t="s">
+      <c r="B102" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="51"/>
-      <c r="D102" s="68"/>
-      <c r="E102" s="50"/>
-      <c r="F102" s="50"/>
-      <c r="G102" s="50"/>
+      <c r="C102" s="66"/>
+      <c r="D102" s="69"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="50"/>
-      <c r="J102" s="50"/>
-      <c r="K102" s="50"/>
-      <c r="L102" s="50"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="53"/>
+      <c r="L102" s="53"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="50"/>
-      <c r="O102" s="47"/>
-      <c r="P102" s="48"/>
-      <c r="Q102" s="47"/>
-      <c r="R102" s="47"/>
-      <c r="S102" s="47"/>
-      <c r="T102" s="47"/>
-      <c r="U102" s="49"/>
-      <c r="V102" s="50"/>
-      <c r="W102" s="50"/>
-      <c r="X102" s="50"/>
-      <c r="Y102" s="47"/>
-      <c r="Z102" s="47"/>
+      <c r="N102" s="53"/>
+      <c r="O102" s="50"/>
+      <c r="P102" s="51"/>
+      <c r="Q102" s="50"/>
+      <c r="R102" s="50"/>
+      <c r="S102" s="50"/>
+      <c r="T102" s="50"/>
+      <c r="U102" s="52"/>
+      <c r="V102" s="53"/>
+      <c r="W102" s="53"/>
+      <c r="X102" s="53"/>
+      <c r="Y102" s="50"/>
+      <c r="Z102" s="50"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="83"/>
+      <c r="D103" s="84"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="50"/>
-      <c r="G103" s="50"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="53"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="50" t="str">
+      <c r="I103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="50" t="str">
+      <c r="J103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="50" t="str">
+      <c r="K103" s="53" t="str">
         <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
         <v> </v>
       </c>
-      <c r="L103" s="50"/>
-      <c r="M103" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="50"/>
-      <c r="O103" s="47"/>
-      <c r="P103" s="48" t="n">
+      <c r="L103" s="53"/>
+      <c r="M103" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="53"/>
+      <c r="O103" s="50"/>
+      <c r="P103" s="51" t="n">
         <f aca="false">IF(B103&gt;0,IF(B103&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q103" s="47" t="str">
+      <c r="Q103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103/100," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="47"/>
-      <c r="S103" s="47" t="str">
+      <c r="R103" s="50"/>
+      <c r="S103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="47"/>
+      <c r="T103" s="50"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="50" t="str">
+      <c r="W103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="50" t="str">
+      <c r="X103" s="53" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="47" t="str">
+      <c r="Y103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="47" t="str">
+      <c r="Z103" s="50" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7160,61 +7141,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="83"/>
+      <c r="D104" s="84"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="50"/>
-      <c r="G104" s="50"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="50" t="str">
+      <c r="I104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="50" t="str">
+      <c r="J104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="50" t="str">
+      <c r="K104" s="53" t="str">
         <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
         <v> </v>
       </c>
-      <c r="L104" s="50"/>
-      <c r="M104" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="50"/>
-      <c r="O104" s="47"/>
-      <c r="P104" s="48" t="n">
+      <c r="L104" s="53"/>
+      <c r="M104" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="53"/>
+      <c r="O104" s="50"/>
+      <c r="P104" s="51" t="n">
         <f aca="false">IF(B104&gt;0,IF(B104&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q104" s="47" t="str">
+      <c r="Q104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104/100," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="47"/>
-      <c r="S104" s="47" t="str">
+      <c r="R104" s="50"/>
+      <c r="S104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="47"/>
+      <c r="T104" s="50"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="50" t="str">
+      <c r="W104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="50" t="str">
+      <c r="X104" s="53" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="47" t="str">
+      <c r="Y104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="47" t="str">
+      <c r="Z104" s="50" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7224,61 +7205,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="83"/>
+      <c r="D105" s="84"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="50"/>
-      <c r="G105" s="50"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="53"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="50" t="str">
+      <c r="I105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="50" t="str">
+      <c r="J105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="50" t="str">
+      <c r="K105" s="53" t="str">
         <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
         <v> </v>
       </c>
-      <c r="L105" s="50"/>
-      <c r="M105" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="50"/>
-      <c r="O105" s="47"/>
-      <c r="P105" s="48" t="n">
+      <c r="L105" s="53"/>
+      <c r="M105" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="53"/>
+      <c r="O105" s="50"/>
+      <c r="P105" s="51" t="n">
         <f aca="false">IF(B105&gt;0,IF(B105&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q105" s="47" t="str">
+      <c r="Q105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105/100," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="47"/>
-      <c r="S105" s="47" t="str">
+      <c r="R105" s="50"/>
+      <c r="S105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="47"/>
+      <c r="T105" s="50"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="50" t="str">
+      <c r="W105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="50" t="str">
+      <c r="X105" s="53" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="47" t="str">
+      <c r="Y105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="47" t="str">
+      <c r="Z105" s="50" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7288,61 +7269,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="83"/>
+      <c r="D106" s="84"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="50"/>
-      <c r="G106" s="50"/>
+      <c r="F106" s="53"/>
+      <c r="G106" s="53"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="50" t="str">
+      <c r="I106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="50" t="str">
+      <c r="J106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="50" t="str">
+      <c r="K106" s="53" t="str">
         <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
         <v> </v>
       </c>
-      <c r="L106" s="50"/>
-      <c r="M106" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="50"/>
-      <c r="O106" s="47"/>
-      <c r="P106" s="48" t="n">
+      <c r="L106" s="53"/>
+      <c r="M106" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="53"/>
+      <c r="O106" s="50"/>
+      <c r="P106" s="51" t="n">
         <f aca="false">IF(B106&gt;0,IF(B106&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q106" s="47" t="str">
+      <c r="Q106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106/100," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="47"/>
-      <c r="S106" s="47" t="str">
+      <c r="R106" s="50"/>
+      <c r="S106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="47"/>
+      <c r="T106" s="50"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="50" t="str">
+      <c r="W106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="50" t="str">
+      <c r="X106" s="53" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="47" t="str">
+      <c r="Y106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="47" t="str">
+      <c r="Z106" s="50" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7352,61 +7333,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="83"/>
+      <c r="D107" s="84"/>
       <c r="E107" s="57"/>
-      <c r="F107" s="50"/>
-      <c r="G107" s="50"/>
+      <c r="F107" s="53"/>
+      <c r="G107" s="53"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="50" t="str">
+      <c r="I107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="50" t="str">
+      <c r="J107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="50" t="str">
+      <c r="K107" s="53" t="str">
         <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
         <v> </v>
       </c>
-      <c r="L107" s="50"/>
-      <c r="M107" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="50"/>
-      <c r="O107" s="47"/>
-      <c r="P107" s="48" t="n">
+      <c r="L107" s="53"/>
+      <c r="M107" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="53"/>
+      <c r="O107" s="50"/>
+      <c r="P107" s="51" t="n">
         <f aca="false">IF(B107&gt;0,IF(B107&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q107" s="47" t="str">
+      <c r="Q107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107/100," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="47"/>
-      <c r="S107" s="47" t="str">
+      <c r="R107" s="50"/>
+      <c r="S107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="47"/>
+      <c r="T107" s="50"/>
       <c r="U107" s="54"/>
       <c r="V107" s="57"/>
-      <c r="W107" s="50" t="str">
+      <c r="W107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="50" t="str">
+      <c r="X107" s="53" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="47" t="str">
+      <c r="Y107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="47" t="str">
+      <c r="Z107" s="50" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7415,7 +7396,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7444,9 +7425,9 @@
         <f aca="false">SUM(K97:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="50"/>
+      <c r="L108" s="53"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="50"/>
+      <c r="N108" s="53"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O97:O107)</f>
         <v>0</v>
@@ -7464,8 +7445,8 @@
         <f aca="false">SUM(S97:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="47"/>
-      <c r="U108" s="49"/>
+      <c r="T108" s="50"/>
+      <c r="U108" s="52"/>
       <c r="V108" s="60" t="n">
         <f aca="false">SUM(V97:V107)</f>
         <v>0</v>
@@ -7490,140 +7471,140 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="71"/>
-      <c r="D109" s="68"/>
-      <c r="E109" s="50"/>
-      <c r="F109" s="50"/>
-      <c r="G109" s="50"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="72"/>
+      <c r="D109" s="69"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="53"/>
+      <c r="G109" s="53"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="50"/>
-      <c r="J109" s="50"/>
-      <c r="K109" s="50"/>
-      <c r="L109" s="50"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="53"/>
+      <c r="K109" s="53"/>
+      <c r="L109" s="53"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="50"/>
-      <c r="O109" s="47"/>
-      <c r="P109" s="48"/>
-      <c r="Q109" s="47"/>
-      <c r="R109" s="47"/>
-      <c r="S109" s="47"/>
-      <c r="T109" s="47"/>
-      <c r="U109" s="49"/>
-      <c r="V109" s="50"/>
-      <c r="W109" s="47"/>
-      <c r="X109" s="47"/>
-      <c r="Y109" s="47"/>
-      <c r="Z109" s="47"/>
+      <c r="N109" s="53"/>
+      <c r="O109" s="50"/>
+      <c r="P109" s="51"/>
+      <c r="Q109" s="50"/>
+      <c r="R109" s="50"/>
+      <c r="S109" s="50"/>
+      <c r="T109" s="50"/>
+      <c r="U109" s="52"/>
+      <c r="V109" s="53"/>
+      <c r="W109" s="50"/>
+      <c r="X109" s="50"/>
+      <c r="Y109" s="50"/>
+      <c r="Z109" s="50"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="42"/>
       <c r="B110" s="43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C110" s="43"/>
-      <c r="D110" s="86" t="n">
+      <c r="D110" s="87" t="n">
         <f aca="false">F59</f>
         <v>46477</v>
       </c>
-      <c r="E110" s="73" t="n">
+      <c r="E110" s="74" t="n">
         <f aca="false">E64+E75+E83+E94+E108</f>
         <v>0</v>
       </c>
-      <c r="F110" s="73" t="n">
+      <c r="F110" s="74" t="n">
         <f aca="false">F64+F75+F83+F94+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="73" t="n">
+      <c r="G110" s="74" t="n">
         <f aca="false">G64+G75+G83+G94+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="73" t="n">
+      <c r="I110" s="74" t="n">
         <f aca="false">I64+I75+I83+I94+I108</f>
         <v>0</v>
       </c>
-      <c r="J110" s="73" t="n">
+      <c r="J110" s="74" t="n">
         <f aca="false">J64+J75+J83+J94+J108</f>
         <v>0</v>
       </c>
-      <c r="K110" s="73" t="n">
+      <c r="K110" s="74" t="n">
         <f aca="false">K64+K75+K83+K94+K108</f>
         <v>0</v>
       </c>
-      <c r="L110" s="50"/>
+      <c r="L110" s="53"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="50"/>
-      <c r="O110" s="73" t="n">
+      <c r="N110" s="53"/>
+      <c r="O110" s="74" t="n">
         <f aca="false">O64+O75+O83+O94+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="73" t="n">
+      <c r="Q110" s="74" t="n">
         <f aca="false">Q64+Q75+Q83+Q94+Q108</f>
         <v>0</v>
       </c>
-      <c r="R110" s="73" t="n">
+      <c r="R110" s="74" t="n">
         <f aca="false">R64+R75+R83+R94+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="73" t="n">
+      <c r="S110" s="74" t="n">
         <f aca="false">S64+S75+S83+S94+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="47"/>
-      <c r="U110" s="49"/>
-      <c r="V110" s="73" t="n">
+      <c r="T110" s="50"/>
+      <c r="U110" s="52"/>
+      <c r="V110" s="74" t="n">
         <f aca="false">V64+V75+V83+V94+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="73" t="n">
+      <c r="W110" s="74" t="n">
         <f aca="false">W64+W75+W83+W94+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="73" t="n">
+      <c r="X110" s="74" t="n">
         <f aca="false">X64+X75+X83+X94+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="73" t="n">
+      <c r="Y110" s="74" t="n">
         <f aca="false">Y64+Y75+Y83+Y94+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="73" t="n">
+      <c r="Z110" s="74" t="n">
         <f aca="false">Z64+Z75+Z83+Z94+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="87"/>
-      <c r="B111" s="88"/>
-      <c r="C111" s="89"/>
-      <c r="D111" s="90"/>
-      <c r="E111" s="91"/>
-      <c r="F111" s="91"/>
-      <c r="G111" s="91"/>
-      <c r="H111" s="92"/>
-      <c r="I111" s="91"/>
-      <c r="J111" s="91"/>
-      <c r="K111" s="91"/>
-      <c r="L111" s="91"/>
-      <c r="M111" s="92"/>
-      <c r="N111" s="91"/>
-      <c r="O111" s="93"/>
-      <c r="P111" s="94"/>
-      <c r="Q111" s="93"/>
-      <c r="R111" s="93"/>
-      <c r="S111" s="93"/>
-      <c r="T111" s="93"/>
-      <c r="U111" s="88"/>
-      <c r="V111" s="91"/>
-      <c r="W111" s="91"/>
-      <c r="X111" s="91"/>
-      <c r="Y111" s="93"/>
-      <c r="Z111" s="93"/>
-      <c r="AA111" s="95"/>
+      <c r="A111" s="88"/>
+      <c r="B111" s="89"/>
+      <c r="C111" s="90"/>
+      <c r="D111" s="91"/>
+      <c r="E111" s="92"/>
+      <c r="F111" s="92"/>
+      <c r="G111" s="92"/>
+      <c r="H111" s="93"/>
+      <c r="I111" s="92"/>
+      <c r="J111" s="92"/>
+      <c r="K111" s="92"/>
+      <c r="L111" s="92"/>
+      <c r="M111" s="93"/>
+      <c r="N111" s="92"/>
+      <c r="O111" s="94"/>
+      <c r="P111" s="95"/>
+      <c r="Q111" s="94"/>
+      <c r="R111" s="94"/>
+      <c r="S111" s="94"/>
+      <c r="T111" s="94"/>
+      <c r="U111" s="89"/>
+      <c r="V111" s="92"/>
+      <c r="W111" s="92"/>
+      <c r="X111" s="92"/>
+      <c r="Y111" s="94"/>
+      <c r="Z111" s="94"/>
+      <c r="AA111" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="54">
@@ -7707,37 +7688,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="96" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="96" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="96" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="96" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="96" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="96" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="96" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="96" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="96" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="96" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="97" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="97" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="97" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="97" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="97" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="97" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="97" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="97" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="97" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="97" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="97" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="97" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="97" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="97"/>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="98"/>
+      <c r="A1" s="98"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="99"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7749,23 +7730,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="99"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="103" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="104"/>
-      <c r="O2" s="106"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="104" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="107"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7777,21 +7758,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="99"/>
-      <c r="B3" s="100"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="106"/>
+      <c r="A3" s="100"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="107"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -7803,31 +7784,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="99"/>
-      <c r="B4" s="109" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="110" t="s">
+      <c r="A4" s="100"/>
+      <c r="B4" s="110" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="102"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="104"/>
-      <c r="G4" s="111" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="110" t="s">
+      <c r="F4" s="105"/>
+      <c r="G4" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="104"/>
-      <c r="M4" s="112" t="s">
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="112"/>
-      <c r="O4" s="106"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="113" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="113"/>
+      <c r="O4" s="107"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -7839,25 +7820,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="99"/>
-      <c r="B5" s="100" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="100" t="s">
+      <c r="A5" s="100"/>
+      <c r="B5" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="101"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="112"/>
-      <c r="N5" s="112"/>
-      <c r="O5" s="106"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="101" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="102"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="107"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -7869,31 +7850,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="99"/>
-      <c r="B6" s="113" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="114" t="n">
+      <c r="A6" s="100"/>
+      <c r="B6" s="114" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="115" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="104"/>
-      <c r="G6" s="113" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="114" t="n">
+      <c r="F6" s="105"/>
+      <c r="G6" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="114"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="115" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="104"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="106"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="107"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -7905,31 +7886,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="99"/>
-      <c r="B7" s="113" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="113"/>
-      <c r="D7" s="113"/>
-      <c r="E7" s="114" t="n">
+      <c r="A7" s="100"/>
+      <c r="B7" s="114" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115" t="n">
         <f aca="false">Schedule!E75</f>
         <v>0</v>
       </c>
-      <c r="F7" s="104"/>
-      <c r="G7" s="113" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="114" t="n">
+      <c r="F7" s="105"/>
+      <c r="G7" s="114" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="115" t="n">
         <f aca="false">Schedule!V22+Schedule!V75</f>
         <v>0</v>
       </c>
-      <c r="L7" s="104"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="106"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="113"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="107"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -7941,31 +7922,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="99"/>
-      <c r="B8" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="113"/>
-      <c r="D8" s="113"/>
-      <c r="E8" s="114" t="n">
+      <c r="A8" s="100"/>
+      <c r="B8" s="114" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="114"/>
+      <c r="D8" s="114"/>
+      <c r="E8" s="115" t="n">
         <f aca="false">Schedule!E83</f>
         <v>0</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="113" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="114" t="n">
+      <c r="F8" s="105"/>
+      <c r="G8" s="114" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="115" t="n">
         <f aca="false">Schedule!V30+Schedule!V83</f>
         <v>0</v>
       </c>
-      <c r="L8" s="104"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="112"/>
-      <c r="O8" s="106"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="107"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -7977,31 +7958,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="99"/>
-      <c r="B9" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="113"/>
-      <c r="E9" s="114" t="n">
+      <c r="A9" s="100"/>
+      <c r="B9" s="114" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="114"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115" t="n">
         <f aca="false">Schedule!E94</f>
         <v>0</v>
       </c>
-      <c r="F9" s="104"/>
-      <c r="G9" s="113" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="114" t="n">
+      <c r="F9" s="105"/>
+      <c r="G9" s="114" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="115" t="n">
         <f aca="false">Schedule!V41+Schedule!V94</f>
         <v>0</v>
       </c>
-      <c r="L9" s="104"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="106"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="107"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -8013,31 +7994,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="99"/>
-      <c r="B10" s="113" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="113"/>
-      <c r="E10" s="114" t="n">
+      <c r="A10" s="100"/>
+      <c r="B10" s="114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="115" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="113" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="114" t="n">
+      <c r="F10" s="105"/>
+      <c r="G10" s="114" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="115" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
         <v>0</v>
       </c>
-      <c r="L10" s="104"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
-      <c r="O10" s="106"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="113"/>
+      <c r="N10" s="113"/>
+      <c r="O10" s="107"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8049,31 +8030,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="99"/>
-      <c r="B11" s="115" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="116" t="n">
+      <c r="A11" s="100"/>
+      <c r="B11" s="116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="117" t="n">
         <f aca="false">SUM(E6:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="104"/>
-      <c r="G11" s="117" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="117"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="117"/>
-      <c r="K11" s="116" t="n">
+      <c r="F11" s="105"/>
+      <c r="G11" s="118" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="118"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="118"/>
+      <c r="K11" s="117" t="n">
         <f aca="false">SUM(K6:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="104"/>
-      <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
-      <c r="O11" s="106"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="113"/>
+      <c r="O11" s="107"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8085,21 +8066,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="112"/>
-      <c r="N12" s="112"/>
-      <c r="O12" s="106"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
+      <c r="O12" s="107"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8111,31 +8092,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="99"/>
-      <c r="B13" s="115" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="116" t="e">
+      <c r="A13" s="100"/>
+      <c r="B13" s="116" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="117" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="F13" s="104"/>
-      <c r="G13" s="117" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
-      <c r="K13" s="116" t="e">
+      <c r="F13" s="105"/>
+      <c r="G13" s="118" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="117" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="L13" s="104"/>
-      <c r="M13" s="112"/>
-      <c r="N13" s="112"/>
-      <c r="O13" s="106"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="113"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="107"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8147,21 +8128,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="100"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="106"/>
+      <c r="A14" s="100"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="105"/>
+      <c r="M14" s="113"/>
+      <c r="N14" s="113"/>
+      <c r="O14" s="107"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8173,33 +8154,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="99"/>
-      <c r="B15" s="118" t="e">
+      <c r="A15" s="100"/>
+      <c r="B15" s="119" t="e">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>#N/A</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119" t="e">
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="120" t="e">
         <f aca="false">E13-E11</f>
         <v>#N/A</v>
       </c>
-      <c r="F15" s="104"/>
-      <c r="G15" s="118" t="e">
+      <c r="F15" s="105"/>
+      <c r="G15" s="119" t="e">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>#N/A</v>
       </c>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="119" t="e">
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="120" t="e">
         <f aca="false">K13-K11</f>
         <v>#N/A</v>
       </c>
-      <c r="L15" s="104"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="106"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="113"/>
+      <c r="N15" s="113"/>
+      <c r="O15" s="107"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8211,21 +8192,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="120"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="125"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="126"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="125"/>
+      <c r="K16" s="125"/>
+      <c r="L16" s="125"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="125"/>
+      <c r="O16" s="127"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8277,122 +8258,122 @@
   <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="128" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="128" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="128" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="129" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="128" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="128" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="129"/>
-      <c r="B1" s="100"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="129"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="130"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="129"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="133" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="n">
+      <c r="A2" s="130"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="134" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="134"/>
+      <c r="E2" s="135" t="n">
         <f aca="false">SUM(E8:E26)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="129"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="137" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="130"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="129"/>
-      <c r="B3" s="137" t="s">
-        <v>52</v>
+      <c r="A3" s="130"/>
+      <c r="B3" s="138" t="s">
+        <v>53</v>
       </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="129"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="130"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="129"/>
-      <c r="B4" s="49"/>
+      <c r="A4" s="130"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="129"/>
-    </row>
-    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="140"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="130"/>
+    </row>
+    <row r="5" s="143" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="141"/>
       <c r="B5" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="141" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="141" t="s">
+      <c r="E5" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="141" t="s">
+      <c r="F5" s="142" t="s">
         <v>58</v>
       </c>
+      <c r="G5" s="142" t="s">
+        <v>59</v>
+      </c>
       <c r="H5" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
+      <c r="I5" s="142" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
       <c r="L5" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="140"/>
-    </row>
-    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="140"/>
+        <v>62</v>
+      </c>
+      <c r="M5" s="141"/>
+    </row>
+    <row r="6" s="143" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="141"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8400,507 +8381,507 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="141" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="141" t="s">
+      <c r="I6" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="141" t="s">
+      <c r="J6" s="142" t="s">
         <v>64</v>
       </c>
+      <c r="K6" s="142" t="s">
+        <v>65</v>
+      </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="140"/>
+      <c r="M6" s="141"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="129"/>
-      <c r="B7" s="49"/>
+      <c r="A7" s="130"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="129"/>
+      <c r="M7" s="130"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="129"/>
+      <c r="A8" s="130"/>
       <c r="B8" s="54"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="135" t="str">
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="136" t="str">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="135" t="str">
+      <c r="J8" s="136" t="str">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="135" t="str">
+      <c r="K8" s="136" t="str">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="129"/>
+      <c r="M8" s="130"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="129"/>
-      <c r="B9" s="49"/>
+      <c r="A9" s="130"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="136"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="136"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="129"/>
+      <c r="M9" s="130"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="129"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="54"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="143"/>
-      <c r="I10" s="135" t="e">
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="135" t="str">
+      <c r="J10" s="136" t="str">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="135" t="str">
+      <c r="K10" s="136" t="str">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="129"/>
+      <c r="M10" s="130"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="129"/>
-      <c r="B11" s="49"/>
+      <c r="A11" s="130"/>
+      <c r="B11" s="52"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="129"/>
+      <c r="M11" s="130"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="129"/>
+      <c r="A12" s="130"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="135" t="e">
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="135" t="str">
+      <c r="J12" s="136" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="135" t="str">
+      <c r="K12" s="136" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="129"/>
+      <c r="M12" s="130"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="129"/>
-      <c r="B13" s="49"/>
+      <c r="A13" s="130"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="136"/>
+      <c r="J13" s="136"/>
+      <c r="K13" s="136"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="129"/>
+      <c r="M13" s="130"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="129"/>
+      <c r="A14" s="130"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="135" t="e">
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="135" t="str">
+      <c r="J14" s="136" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="135" t="str">
+      <c r="K14" s="136" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="129"/>
+      <c r="M14" s="130"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="129"/>
-      <c r="B15" s="49"/>
+      <c r="A15" s="130"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="136"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="129"/>
+      <c r="M15" s="130"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="129"/>
+      <c r="A16" s="130"/>
       <c r="B16" s="54"/>
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="143"/>
-      <c r="I16" s="135" t="e">
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J16" s="135" t="str">
+      <c r="J16" s="136" t="str">
         <f aca="false">IF(H16&gt;0,I16-K16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="135" t="str">
+      <c r="K16" s="136" t="str">
         <f aca="false">IF(H16&gt;0,G16/H16," ")</f>
         <v> </v>
       </c>
       <c r="L16" s="56"/>
-      <c r="M16" s="129"/>
+      <c r="M16" s="130"/>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="129"/>
-      <c r="B17" s="49"/>
+      <c r="A17" s="130"/>
+      <c r="B17" s="52"/>
       <c r="C17" s="62"/>
       <c r="D17" s="62"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="135"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="129"/>
+      <c r="M17" s="130"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="129"/>
+      <c r="A18" s="130"/>
       <c r="B18" s="54"/>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="143"/>
-      <c r="I18" s="135" t="e">
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="144"/>
+      <c r="I18" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J18" s="135" t="str">
+      <c r="J18" s="136" t="str">
         <f aca="false">IF(H18&gt;0,I18-K18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="135" t="str">
+      <c r="K18" s="136" t="str">
         <f aca="false">IF(H18&gt;0,G18/H18," ")</f>
         <v> </v>
       </c>
       <c r="L18" s="56"/>
-      <c r="M18" s="129"/>
+      <c r="M18" s="130"/>
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="129"/>
-      <c r="B19" s="49"/>
+      <c r="A19" s="130"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="62"/>
       <c r="D19" s="62"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="135"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="136"/>
       <c r="L19" s="62"/>
-      <c r="M19" s="129"/>
+      <c r="M19" s="130"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="129"/>
+      <c r="A20" s="130"/>
       <c r="B20" s="54"/>
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
-      <c r="E20" s="134"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="143"/>
-      <c r="I20" s="135" t="e">
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="144"/>
+      <c r="I20" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J20" s="135" t="str">
+      <c r="J20" s="136" t="str">
         <f aca="false">IF(H20&gt;0,I20-K20," ")</f>
         <v> </v>
       </c>
-      <c r="K20" s="135" t="str">
+      <c r="K20" s="136" t="str">
         <f aca="false">IF(H20&gt;0,G20/H20," ")</f>
         <v> </v>
       </c>
       <c r="L20" s="56"/>
-      <c r="M20" s="129"/>
+      <c r="M20" s="130"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="129"/>
-      <c r="B21" s="49"/>
+      <c r="A21" s="130"/>
+      <c r="B21" s="52"/>
       <c r="C21" s="62"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="135"/>
-      <c r="J21" s="135"/>
-      <c r="K21" s="135"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="136"/>
       <c r="L21" s="62"/>
-      <c r="M21" s="129"/>
+      <c r="M21" s="130"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="129"/>
+      <c r="A22" s="130"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="143"/>
-      <c r="I22" s="135" t="e">
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J22" s="135" t="str">
+      <c r="J22" s="136" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="135" t="str">
+      <c r="K22" s="136" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="129"/>
+      <c r="M22" s="130"/>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="129"/>
-      <c r="B23" s="49"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="135"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="136"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="129"/>
+      <c r="M23" s="130"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="129"/>
+      <c r="A24" s="130"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="135" t="e">
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="135" t="str">
+      <c r="J24" s="136" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="135" t="str">
+      <c r="K24" s="136" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="129"/>
+      <c r="M24" s="130"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="129"/>
-      <c r="B25" s="49"/>
+      <c r="A25" s="130"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="135"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="136"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="129"/>
+      <c r="M25" s="130"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="129"/>
+      <c r="A26" s="130"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="135" t="e">
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="144"/>
+      <c r="I26" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="135" t="str">
+      <c r="J26" s="136" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="135" t="str">
+      <c r="K26" s="136" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="129"/>
+      <c r="M26" s="130"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="129"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="130"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="136"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="129"/>
+      <c r="M27" s="130"/>
     </row>
     <row r="28" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="129"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="102"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="131"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="131"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="129"/>
+      <c r="A28" s="130"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="103"/>
+      <c r="M28" s="130"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="129"/>
-      <c r="B29" s="137" t="s">
-        <v>65</v>
+      <c r="A29" s="130"/>
+      <c r="B29" s="138" t="s">
+        <v>66</v>
       </c>
       <c r="C29" s="62"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
       <c r="H29" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="I29" s="132"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="132"/>
+        <v>67</v>
+      </c>
+      <c r="I29" s="133"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="133"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="129"/>
+      <c r="M29" s="130"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="129"/>
-      <c r="B30" s="49"/>
+      <c r="A30" s="130"/>
+      <c r="B30" s="52"/>
       <c r="C30" s="62"/>
       <c r="D30" s="62"/>
-      <c r="E30" s="132"/>
-      <c r="F30" s="132"/>
-      <c r="G30" s="132"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="135"/>
-      <c r="J30" s="135"/>
-      <c r="K30" s="135"/>
+      <c r="E30" s="133"/>
+      <c r="F30" s="133"/>
+      <c r="G30" s="133"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="136"/>
       <c r="L30" s="62"/>
-      <c r="M30" s="129"/>
-    </row>
-    <row r="31" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="140"/>
+      <c r="M30" s="130"/>
+    </row>
+    <row r="31" s="143" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="141"/>
       <c r="B31" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="141" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="141" t="s">
+      <c r="E31" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="G31" s="141" t="s">
+      <c r="F31" s="142" t="s">
         <v>58</v>
       </c>
+      <c r="G31" s="142" t="s">
+        <v>59</v>
+      </c>
       <c r="H31" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="J31" s="141"/>
-      <c r="K31" s="141"/>
+      <c r="I31" s="142" t="s">
+        <v>61</v>
+      </c>
+      <c r="J31" s="142"/>
+      <c r="K31" s="142"/>
       <c r="L31" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="140"/>
-    </row>
-    <row r="32" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="140"/>
+        <v>62</v>
+      </c>
+      <c r="M31" s="141"/>
+    </row>
+    <row r="32" s="143" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="141"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -8908,437 +8889,437 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
-      <c r="I32" s="141" t="s">
-        <v>62</v>
-      </c>
-      <c r="J32" s="141" t="s">
+      <c r="I32" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="K32" s="141" t="s">
+      <c r="J32" s="142" t="s">
         <v>64</v>
       </c>
+      <c r="K32" s="142" t="s">
+        <v>65</v>
+      </c>
       <c r="L32" s="21"/>
-      <c r="M32" s="140"/>
-    </row>
-    <row r="33" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="140"/>
-      <c r="B33" s="144"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="144"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="144"/>
-      <c r="I33" s="145"/>
-      <c r="J33" s="145"/>
-      <c r="K33" s="145"/>
-      <c r="L33" s="144"/>
-      <c r="M33" s="140"/>
+      <c r="M32" s="141"/>
+    </row>
+    <row r="33" s="143" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="141"/>
+      <c r="B33" s="145"/>
+      <c r="C33" s="145"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="145"/>
+      <c r="H33" s="145"/>
+      <c r="I33" s="146"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="146"/>
+      <c r="L33" s="145"/>
+      <c r="M33" s="141"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="129"/>
+      <c r="A34" s="130"/>
       <c r="B34" s="54"/>
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
-      <c r="E34" s="134"/>
-      <c r="F34" s="134"/>
-      <c r="G34" s="134"/>
-      <c r="H34" s="143"/>
-      <c r="I34" s="135" t="str">
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="144"/>
+      <c r="I34" s="136" t="str">
         <f aca="false">IF(E34&gt;0,(E34+F34+G34)/H34," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="135" t="str">
+      <c r="J34" s="136" t="str">
         <f aca="false">IF(H34&gt;0,I34-K34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="135" t="str">
+      <c r="K34" s="136" t="str">
         <f aca="false">IF(H34&gt;0,G34/H34," ")</f>
         <v> </v>
       </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="129"/>
+      <c r="M34" s="130"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="129"/>
-      <c r="B35" s="49"/>
+      <c r="A35" s="130"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="62"/>
       <c r="D35" s="62"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="132"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="135"/>
-      <c r="J35" s="135"/>
-      <c r="K35" s="135"/>
+      <c r="E35" s="133"/>
+      <c r="F35" s="133"/>
+      <c r="G35" s="133"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="136"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="136"/>
       <c r="L35" s="62"/>
-      <c r="M35" s="129"/>
+      <c r="M35" s="130"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="129"/>
+      <c r="A36" s="130"/>
       <c r="B36" s="54"/>
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="134"/>
-      <c r="G36" s="134"/>
-      <c r="H36" s="143"/>
-      <c r="I36" s="135" t="e">
+      <c r="E36" s="135"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="144"/>
+      <c r="I36" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J36" s="135" t="str">
+      <c r="J36" s="136" t="str">
         <f aca="false">IF(H36&gt;0,I36-K36," ")</f>
         <v> </v>
       </c>
-      <c r="K36" s="135" t="str">
+      <c r="K36" s="136" t="str">
         <f aca="false">IF(H36&gt;0,G36/H36," ")</f>
         <v> </v>
       </c>
       <c r="L36" s="56"/>
-      <c r="M36" s="129"/>
+      <c r="M36" s="130"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="129"/>
-      <c r="B37" s="49"/>
+      <c r="A37" s="130"/>
+      <c r="B37" s="52"/>
       <c r="C37" s="62"/>
       <c r="D37" s="62"/>
-      <c r="E37" s="132"/>
-      <c r="F37" s="132"/>
-      <c r="G37" s="132"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="135"/>
-      <c r="J37" s="135"/>
-      <c r="K37" s="135"/>
+      <c r="E37" s="133"/>
+      <c r="F37" s="133"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="136"/>
+      <c r="J37" s="136"/>
+      <c r="K37" s="136"/>
       <c r="L37" s="62"/>
-      <c r="M37" s="129"/>
+      <c r="M37" s="130"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="129"/>
+      <c r="A38" s="130"/>
       <c r="B38" s="54"/>
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="134"/>
-      <c r="G38" s="134"/>
-      <c r="H38" s="143"/>
-      <c r="I38" s="135" t="e">
+      <c r="E38" s="135"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="135"/>
+      <c r="H38" s="144"/>
+      <c r="I38" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J38" s="135" t="str">
+      <c r="J38" s="136" t="str">
         <f aca="false">IF(H38&gt;0,I38-K38," ")</f>
         <v> </v>
       </c>
-      <c r="K38" s="135" t="str">
+      <c r="K38" s="136" t="str">
         <f aca="false">IF(H38&gt;0,G38/H38," ")</f>
         <v> </v>
       </c>
       <c r="L38" s="56"/>
-      <c r="M38" s="129"/>
+      <c r="M38" s="130"/>
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="129"/>
-      <c r="B39" s="49"/>
+      <c r="A39" s="130"/>
+      <c r="B39" s="52"/>
       <c r="C39" s="62"/>
       <c r="D39" s="62"/>
-      <c r="E39" s="132"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="132"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="135"/>
-      <c r="J39" s="135"/>
-      <c r="K39" s="135"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="136"/>
       <c r="L39" s="62"/>
-      <c r="M39" s="129"/>
+      <c r="M39" s="130"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="129"/>
+      <c r="A40" s="130"/>
       <c r="B40" s="54"/>
       <c r="C40" s="56"/>
       <c r="D40" s="56"/>
-      <c r="E40" s="134"/>
-      <c r="F40" s="134"/>
-      <c r="G40" s="134"/>
-      <c r="H40" s="143"/>
-      <c r="I40" s="135" t="e">
+      <c r="E40" s="135"/>
+      <c r="F40" s="135"/>
+      <c r="G40" s="135"/>
+      <c r="H40" s="144"/>
+      <c r="I40" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J40" s="135" t="str">
+      <c r="J40" s="136" t="str">
         <f aca="false">IF(H40&gt;0,I40-K40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="135" t="str">
+      <c r="K40" s="136" t="str">
         <f aca="false">IF(H40&gt;0,G40/H40," ")</f>
         <v> </v>
       </c>
       <c r="L40" s="56"/>
-      <c r="M40" s="129"/>
+      <c r="M40" s="130"/>
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="129"/>
-      <c r="B41" s="49"/>
+      <c r="A41" s="130"/>
+      <c r="B41" s="52"/>
       <c r="C41" s="62"/>
       <c r="D41" s="62"/>
-      <c r="E41" s="132"/>
-      <c r="F41" s="132"/>
-      <c r="G41" s="132"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="135"/>
-      <c r="J41" s="135"/>
-      <c r="K41" s="135"/>
+      <c r="E41" s="133"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="136"/>
+      <c r="J41" s="136"/>
+      <c r="K41" s="136"/>
       <c r="L41" s="62"/>
-      <c r="M41" s="129"/>
+      <c r="M41" s="130"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="129"/>
+      <c r="A42" s="130"/>
       <c r="B42" s="54"/>
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="134"/>
-      <c r="G42" s="134"/>
-      <c r="H42" s="143"/>
-      <c r="I42" s="135" t="e">
+      <c r="E42" s="135"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="135"/>
+      <c r="H42" s="144"/>
+      <c r="I42" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J42" s="135" t="str">
+      <c r="J42" s="136" t="str">
         <f aca="false">IF(H42&gt;0,I42-K42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="135" t="str">
+      <c r="K42" s="136" t="str">
         <f aca="false">IF(H42&gt;0,G42/H42," ")</f>
         <v> </v>
       </c>
       <c r="L42" s="56"/>
-      <c r="M42" s="129"/>
+      <c r="M42" s="130"/>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="129"/>
-      <c r="B43" s="49"/>
+      <c r="A43" s="130"/>
+      <c r="B43" s="52"/>
       <c r="C43" s="62"/>
       <c r="D43" s="62"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="135"/>
-      <c r="J43" s="135"/>
-      <c r="K43" s="135"/>
+      <c r="E43" s="133"/>
+      <c r="F43" s="133"/>
+      <c r="G43" s="133"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="136"/>
+      <c r="K43" s="136"/>
       <c r="L43" s="62"/>
-      <c r="M43" s="129"/>
+      <c r="M43" s="130"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="129"/>
+      <c r="A44" s="130"/>
       <c r="B44" s="54"/>
       <c r="C44" s="56"/>
       <c r="D44" s="56"/>
-      <c r="E44" s="134"/>
-      <c r="F44" s="134"/>
-      <c r="G44" s="134"/>
-      <c r="H44" s="143"/>
-      <c r="I44" s="135" t="e">
+      <c r="E44" s="135"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="135"/>
+      <c r="H44" s="144"/>
+      <c r="I44" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J44" s="135" t="str">
+      <c r="J44" s="136" t="str">
         <f aca="false">IF(H44&gt;0,I44-K44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="135" t="str">
+      <c r="K44" s="136" t="str">
         <f aca="false">IF(H44&gt;0,G44/H44," ")</f>
         <v> </v>
       </c>
       <c r="L44" s="56"/>
-      <c r="M44" s="129"/>
+      <c r="M44" s="130"/>
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="129"/>
-      <c r="B45" s="49"/>
+      <c r="A45" s="130"/>
+      <c r="B45" s="52"/>
       <c r="C45" s="62"/>
       <c r="D45" s="62"/>
-      <c r="E45" s="132"/>
-      <c r="F45" s="132"/>
-      <c r="G45" s="132"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="135"/>
-      <c r="J45" s="135"/>
-      <c r="K45" s="135"/>
+      <c r="E45" s="133"/>
+      <c r="F45" s="133"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="136"/>
+      <c r="J45" s="136"/>
+      <c r="K45" s="136"/>
       <c r="L45" s="62"/>
-      <c r="M45" s="129"/>
+      <c r="M45" s="130"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="129"/>
+      <c r="A46" s="130"/>
       <c r="B46" s="54"/>
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
-      <c r="E46" s="134"/>
-      <c r="F46" s="134"/>
-      <c r="G46" s="134"/>
-      <c r="H46" s="143"/>
-      <c r="I46" s="135" t="e">
+      <c r="E46" s="135"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="135"/>
+      <c r="H46" s="144"/>
+      <c r="I46" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J46" s="135" t="str">
+      <c r="J46" s="136" t="str">
         <f aca="false">IF(H46&gt;0,I46-K46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="135" t="str">
+      <c r="K46" s="136" t="str">
         <f aca="false">IF(H46&gt;0,G46/H46," ")</f>
         <v> </v>
       </c>
       <c r="L46" s="56"/>
-      <c r="M46" s="129"/>
+      <c r="M46" s="130"/>
     </row>
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="129"/>
-      <c r="B47" s="49"/>
+      <c r="A47" s="130"/>
+      <c r="B47" s="52"/>
       <c r="C47" s="62"/>
       <c r="D47" s="62"/>
-      <c r="E47" s="132"/>
-      <c r="F47" s="132"/>
-      <c r="G47" s="132"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="135"/>
-      <c r="J47" s="135"/>
-      <c r="K47" s="135"/>
+      <c r="E47" s="133"/>
+      <c r="F47" s="133"/>
+      <c r="G47" s="133"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="136"/>
       <c r="L47" s="62"/>
-      <c r="M47" s="129"/>
+      <c r="M47" s="130"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="129"/>
+      <c r="A48" s="130"/>
       <c r="B48" s="54"/>
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
-      <c r="E48" s="134"/>
-      <c r="F48" s="134"/>
-      <c r="G48" s="134"/>
-      <c r="H48" s="143"/>
-      <c r="I48" s="135" t="e">
+      <c r="E48" s="135"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="135"/>
+      <c r="H48" s="144"/>
+      <c r="I48" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J48" s="135" t="str">
+      <c r="J48" s="136" t="str">
         <f aca="false">IF(H48&gt;0,I48-K48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="135" t="str">
+      <c r="K48" s="136" t="str">
         <f aca="false">IF(H48&gt;0,G48/H48," ")</f>
         <v> </v>
       </c>
       <c r="L48" s="56"/>
-      <c r="M48" s="129"/>
+      <c r="M48" s="130"/>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="129"/>
-      <c r="B49" s="49"/>
+      <c r="A49" s="130"/>
+      <c r="B49" s="52"/>
       <c r="C49" s="62"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="132"/>
-      <c r="F49" s="132"/>
-      <c r="G49" s="132"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="135"/>
-      <c r="J49" s="135"/>
-      <c r="K49" s="135"/>
+      <c r="E49" s="133"/>
+      <c r="F49" s="133"/>
+      <c r="G49" s="133"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="136"/>
+      <c r="J49" s="136"/>
+      <c r="K49" s="136"/>
       <c r="L49" s="62"/>
-      <c r="M49" s="129"/>
+      <c r="M49" s="130"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="129"/>
+      <c r="A50" s="130"/>
       <c r="B50" s="54"/>
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
-      <c r="E50" s="134"/>
-      <c r="F50" s="134"/>
-      <c r="G50" s="134"/>
-      <c r="H50" s="143"/>
-      <c r="I50" s="135" t="e">
+      <c r="E50" s="135"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="135"/>
+      <c r="H50" s="144"/>
+      <c r="I50" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J50" s="135" t="str">
+      <c r="J50" s="136" t="str">
         <f aca="false">IF(H50&gt;0,I50-K50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="135" t="str">
+      <c r="K50" s="136" t="str">
         <f aca="false">IF(H50&gt;0,G50/H50," ")</f>
         <v> </v>
       </c>
       <c r="L50" s="56"/>
-      <c r="M50" s="129"/>
+      <c r="M50" s="130"/>
     </row>
     <row r="51" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="129"/>
-      <c r="B51" s="49"/>
+      <c r="A51" s="130"/>
+      <c r="B51" s="52"/>
       <c r="C51" s="62"/>
       <c r="D51" s="62"/>
-      <c r="E51" s="132"/>
-      <c r="F51" s="132"/>
-      <c r="G51" s="132"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="135"/>
-      <c r="J51" s="135"/>
-      <c r="K51" s="135"/>
+      <c r="E51" s="133"/>
+      <c r="F51" s="133"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="136"/>
+      <c r="J51" s="136"/>
+      <c r="K51" s="136"/>
       <c r="L51" s="62"/>
-      <c r="M51" s="129"/>
+      <c r="M51" s="130"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="129"/>
+      <c r="A52" s="130"/>
       <c r="B52" s="54"/>
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
-      <c r="E52" s="134"/>
-      <c r="F52" s="134"/>
-      <c r="G52" s="134"/>
-      <c r="H52" s="143"/>
-      <c r="I52" s="135" t="e">
+      <c r="E52" s="135"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="144"/>
+      <c r="I52" s="136" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J52" s="135" t="str">
+      <c r="J52" s="136" t="str">
         <f aca="false">IF(H52&gt;0,I52-K52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="135" t="str">
+      <c r="K52" s="136" t="str">
         <f aca="false">IF(H52&gt;0,G52/H52," ")</f>
         <v> </v>
       </c>
       <c r="L52" s="56"/>
-      <c r="M52" s="129"/>
+      <c r="M52" s="130"/>
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="129"/>
-      <c r="B53" s="49"/>
+      <c r="A53" s="130"/>
+      <c r="B53" s="52"/>
       <c r="C53" s="62"/>
       <c r="D53" s="62"/>
-      <c r="E53" s="132"/>
-      <c r="F53" s="132"/>
-      <c r="G53" s="132"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="135"/>
-      <c r="J53" s="135"/>
-      <c r="K53" s="135"/>
+      <c r="E53" s="133"/>
+      <c r="F53" s="133"/>
+      <c r="G53" s="133"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="136"/>
+      <c r="J53" s="136"/>
+      <c r="K53" s="136"/>
       <c r="L53" s="62"/>
-      <c r="M53" s="129"/>
+      <c r="M53" s="130"/>
     </row>
     <row r="54" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="129"/>
-      <c r="B54" s="100"/>
-      <c r="C54" s="102"/>
-      <c r="D54" s="102"/>
-      <c r="E54" s="129"/>
-      <c r="F54" s="129"/>
-      <c r="G54" s="129"/>
-      <c r="H54" s="130"/>
-      <c r="I54" s="131"/>
-      <c r="J54" s="131"/>
-      <c r="K54" s="131"/>
-      <c r="L54" s="102"/>
-      <c r="M54" s="129"/>
+      <c r="A54" s="130"/>
+      <c r="B54" s="101"/>
+      <c r="C54" s="103"/>
+      <c r="D54" s="103"/>
+      <c r="E54" s="130"/>
+      <c r="F54" s="130"/>
+      <c r="G54" s="130"/>
+      <c r="H54" s="131"/>
+      <c r="I54" s="132"/>
+      <c r="J54" s="132"/>
+      <c r="K54" s="132"/>
+      <c r="L54" s="103"/>
+      <c r="M54" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/ltd-latest/Fixedassets.xlsx
+++ b/examples/ltd-latest/Fixedassets.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">EXISTING FIXED ASSETS AT </t>
   </si>
   <si>
-    <t xml:space="preserve">Laptop (0.5 years old)</t>
+    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">Plant &amp; Machinery</t>
@@ -215,7 +215,13 @@
     <t xml:space="preserve">Computers</t>
   </si>
   <si>
+    <t xml:space="preserve">Laptop (0.5 years old)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Motor Vehicles - Cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van (2.5 years old)</t>
   </si>
   <si>
     <t xml:space="preserve">Motor Vehicles - Vans &amp; Lorries</t>
@@ -225,9 +231,6 @@
   </si>
   <si>
     <t xml:space="preserve">to</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land &amp; Property</t>
   </si>
   <si>
     <t xml:space="preserve">New Land &amp; Property</t>
@@ -658,7 +661,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="146">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -839,42 +842,42 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -921,10 +924,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1292,6 +1291,11 @@
         <row r="5">
           <cell r="G5">
             <v>100</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>45748</v>
           </cell>
         </row>
         <row r="7">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>0</v>
+        <v>10098</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
@@ -1651,13 +1655,13 @@
       <c r="C4" s="20"/>
       <c r="D4" s="21"/>
       <c r="E4" s="22"/>
-      <c r="F4" s="26" t="str">
+      <c r="F4" s="26" t="n">
         <f aca="false">D6</f>
-        <v>Laptop (0.5 years old)</v>
-      </c>
-      <c r="G4" s="26" t="str">
+        <v>45748</v>
+      </c>
+      <c r="G4" s="26" t="n">
         <f aca="false">D6</f>
-        <v>Laptop (0.5 years old)</v>
+        <v>45748</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="23"/>
@@ -1672,9 +1676,9 @@
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
       <c r="N4" s="13"/>
-      <c r="O4" s="10" t="str">
+      <c r="O4" s="10" t="n">
         <f aca="false">D6</f>
-        <v>Laptop (0.5 years old)</v>
+        <v>45748</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>100</v>
@@ -1731,44 +1735,65 @@
         <v>20</v>
       </c>
       <c r="C6" s="43"/>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="44" t="n">
+        <f aca="false">[1]Admin!$L$6</f>
+        <v>45748</v>
+      </c>
+      <c r="E6" s="44"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="50"/>
+      <c r="W6" s="50"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42"/>
+      <c r="B7" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y6" s="7" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="50"/>
-      <c r="Z7" s="50"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
       <c r="AA7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1778,7 +1803,7 @@
       <c r="D8" s="56"/>
       <c r="E8" s="57"/>
       <c r="F8" s="57"/>
-      <c r="G8" s="53" t="str">
+      <c r="G8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
         <v> </v>
       </c>
@@ -1786,39 +1811,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="53" t="str">
+      <c r="I8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="53" t="str">
+      <c r="J8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="53" t="str">
+      <c r="K8" s="50" t="str">
         <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
         <v> </v>
       </c>
-      <c r="L8" s="53"/>
+      <c r="L8" s="50"/>
       <c r="M8" s="58"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
       <c r="U8" s="54"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="53" t="str">
+      <c r="W8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,E8," ")</f>
         <v> </v>
       </c>
-      <c r="X8" s="53" t="str">
+      <c r="X8" s="50" t="str">
         <f aca="false">IF(V8&gt;0,J8," ")</f>
         <v> </v>
       </c>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
       <c r="AA8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1828,7 +1853,7 @@
       <c r="D9" s="56"/>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
-      <c r="G9" s="53" t="str">
+      <c r="G9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,E9-F9," ")</f>
         <v> </v>
       </c>
@@ -1836,39 +1861,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I9" s="53" t="str">
+      <c r="I9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,MIN(E9*H9,G9)," ")</f>
         <v> </v>
       </c>
-      <c r="J9" s="53" t="str">
+      <c r="J9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,F9+I9," ")</f>
         <v> </v>
       </c>
-      <c r="K9" s="53" t="str">
+      <c r="K9" s="50" t="str">
         <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
         <v> </v>
       </c>
-      <c r="L9" s="53"/>
+      <c r="L9" s="50"/>
       <c r="M9" s="58"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
       <c r="U9" s="54"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="53" t="str">
+      <c r="W9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,E9," ")</f>
         <v> </v>
       </c>
-      <c r="X9" s="53" t="str">
+      <c r="X9" s="50" t="str">
         <f aca="false">IF(V9&gt;0,J9," ")</f>
         <v> </v>
       </c>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="50"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
       <c r="AA9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1878,7 +1903,7 @@
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
-      <c r="G10" s="53" t="str">
+      <c r="G10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,E10-F10," ")</f>
         <v> </v>
       </c>
@@ -1886,39 +1911,39 @@
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I10" s="53" t="str">
+      <c r="I10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,MIN(E10*H10,G10)," ")</f>
         <v> </v>
       </c>
-      <c r="J10" s="53" t="str">
+      <c r="J10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,F10+I10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="53" t="str">
+      <c r="K10" s="50" t="str">
         <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
         <v> </v>
       </c>
-      <c r="L10" s="53"/>
+      <c r="L10" s="50"/>
       <c r="M10" s="58"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
       <c r="U10" s="54"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="53" t="str">
+      <c r="W10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,E10," ")</f>
         <v> </v>
       </c>
-      <c r="X10" s="53" t="str">
+      <c r="X10" s="50" t="str">
         <f aca="false">IF(V10&gt;0,J10," ")</f>
         <v> </v>
       </c>
-      <c r="Y10" s="50"/>
-      <c r="Z10" s="50"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="47"/>
       <c r="AA10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1954,9 +1979,9 @@
         <f aca="false">SUM(K8:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="53"/>
+      <c r="L11" s="50"/>
       <c r="M11" s="58"/>
-      <c r="N11" s="53"/>
+      <c r="N11" s="50"/>
       <c r="O11" s="61" t="n">
         <f aca="false">SUM(O8:O10)</f>
         <v>0</v>
@@ -1974,8 +1999,8 @@
         <f aca="false">SUM(S8:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="50"/>
-      <c r="U11" s="52"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="49"/>
       <c r="V11" s="60" t="n">
         <f aca="false">SUM(V8:V10)</f>
         <v>0</v>
@@ -2003,61 +2028,61 @@
       <c r="B12" s="63"/>
       <c r="C12" s="64"/>
       <c r="D12" s="65"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="58"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
       <c r="M12" s="58"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
       <c r="P12" s="62"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="53"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="53"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
       <c r="AA12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="66"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="67" t="n">
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="66" t="n">
         <v>0.1</v>
       </c>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
       <c r="M13" s="58"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="50"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
       <c r="AA13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2067,7 +2092,7 @@
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,E14-F14," ")</f>
         <v> </v>
       </c>
@@ -2075,48 +2100,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,MIN(E14*H14,G14)," ")</f>
         <v> </v>
       </c>
-      <c r="J14" s="53" t="str">
+      <c r="J14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,F14+I14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="53" t="str">
+      <c r="K14" s="50" t="str">
         <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
         <v> </v>
       </c>
-      <c r="L14" s="53"/>
+      <c r="L14" s="50"/>
       <c r="M14" s="58"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50" t="str">
+      <c r="N14" s="50"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S14" s="50" t="str">
+      <c r="S14" s="47" t="str">
         <f aca="false">IF(O14&gt;0,O14-R14," ")</f>
         <v> </v>
       </c>
-      <c r="T14" s="50"/>
+      <c r="T14" s="47"/>
       <c r="U14" s="54"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="53" t="str">
+      <c r="W14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,E14," ")</f>
         <v> </v>
       </c>
-      <c r="X14" s="53" t="str">
+      <c r="X14" s="50" t="str">
         <f aca="false">IF(V14&gt;0,J14," ")</f>
         <v> </v>
       </c>
-      <c r="Y14" s="50" t="str">
+      <c r="Y14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&lt;S14,S14-V14," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z14" s="50" t="str">
+      <c r="Z14" s="47" t="str">
         <f aca="false">IF((U14+V14)&gt;0,IF(V14&gt;S14,V14-S14," ")," ")</f>
         <v> </v>
       </c>
@@ -2129,7 +2154,7 @@
       <c r="D15" s="56"/>
       <c r="E15" s="57"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="53" t="str">
+      <c r="G15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,E15-F15," ")</f>
         <v> </v>
       </c>
@@ -2137,48 +2162,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I15" s="53" t="str">
+      <c r="I15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,MIN(E15*H15,G15)," ")</f>
         <v> </v>
       </c>
-      <c r="J15" s="53" t="str">
+      <c r="J15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,F15+I15," ")</f>
         <v> </v>
       </c>
-      <c r="K15" s="53" t="str">
+      <c r="K15" s="50" t="str">
         <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
         <v> </v>
       </c>
-      <c r="L15" s="53"/>
+      <c r="L15" s="50"/>
       <c r="M15" s="58"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50" t="str">
+      <c r="N15" s="50"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S15" s="50" t="str">
+      <c r="S15" s="47" t="str">
         <f aca="false">IF(O15&gt;0,O15-R15," ")</f>
         <v> </v>
       </c>
-      <c r="T15" s="50"/>
+      <c r="T15" s="47"/>
       <c r="U15" s="54"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="53" t="str">
+      <c r="W15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,E15," ")</f>
         <v> </v>
       </c>
-      <c r="X15" s="53" t="str">
+      <c r="X15" s="50" t="str">
         <f aca="false">IF(V15&gt;0,J15," ")</f>
         <v> </v>
       </c>
-      <c r="Y15" s="50" t="str">
+      <c r="Y15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&lt;S15,S15-V15," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z15" s="50" t="str">
+      <c r="Z15" s="47" t="str">
         <f aca="false">IF((U15+V15)&gt;0,IF(V15&gt;S15,V15-S15," ")," ")</f>
         <v> </v>
       </c>
@@ -2191,7 +2216,7 @@
       <c r="D16" s="56"/>
       <c r="E16" s="57"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,E16-F16," ")</f>
         <v> </v>
       </c>
@@ -2199,48 +2224,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,MIN(E16*H16,G16)," ")</f>
         <v> </v>
       </c>
-      <c r="J16" s="53" t="str">
+      <c r="J16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,F16+I16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="53" t="str">
+      <c r="K16" s="50" t="str">
         <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
         <v> </v>
       </c>
-      <c r="L16" s="53"/>
+      <c r="L16" s="50"/>
       <c r="M16" s="58"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50" t="str">
+      <c r="N16" s="50"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S16" s="50" t="str">
+      <c r="S16" s="47" t="str">
         <f aca="false">IF(O16&gt;0,O16-R16," ")</f>
         <v> </v>
       </c>
-      <c r="T16" s="50"/>
+      <c r="T16" s="47"/>
       <c r="U16" s="54"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="53" t="str">
+      <c r="W16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,E16," ")</f>
         <v> </v>
       </c>
-      <c r="X16" s="53" t="str">
+      <c r="X16" s="50" t="str">
         <f aca="false">IF(V16&gt;0,J16," ")</f>
         <v> </v>
       </c>
-      <c r="Y16" s="50" t="str">
+      <c r="Y16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&lt;S16,S16-V16," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z16" s="50" t="str">
+      <c r="Z16" s="47" t="str">
         <f aca="false">IF((U16+V16)&gt;0,IF(V16&gt;S16,V16-S16," ")," ")</f>
         <v> </v>
       </c>
@@ -2253,7 +2278,7 @@
       <c r="D17" s="56"/>
       <c r="E17" s="57"/>
       <c r="F17" s="57"/>
-      <c r="G17" s="53" t="str">
+      <c r="G17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,E17-F17," ")</f>
         <v> </v>
       </c>
@@ -2261,48 +2286,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I17" s="53" t="str">
+      <c r="I17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,MIN(E17*H17,G17)," ")</f>
         <v> </v>
       </c>
-      <c r="J17" s="53" t="str">
+      <c r="J17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,F17+I17," ")</f>
         <v> </v>
       </c>
-      <c r="K17" s="53" t="str">
+      <c r="K17" s="50" t="str">
         <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
         <v> </v>
       </c>
-      <c r="L17" s="53"/>
+      <c r="L17" s="50"/>
       <c r="M17" s="58"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50" t="str">
+      <c r="N17" s="50"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S17" s="50" t="str">
+      <c r="S17" s="47" t="str">
         <f aca="false">IF(O17&gt;0,O17-R17," ")</f>
         <v> </v>
       </c>
-      <c r="T17" s="50"/>
+      <c r="T17" s="47"/>
       <c r="U17" s="54"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="53" t="str">
+      <c r="W17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,E17," ")</f>
         <v> </v>
       </c>
-      <c r="X17" s="53" t="str">
+      <c r="X17" s="50" t="str">
         <f aca="false">IF(V17&gt;0,J17," ")</f>
         <v> </v>
       </c>
-      <c r="Y17" s="50" t="str">
+      <c r="Y17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&lt;S17,S17-V17," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z17" s="50" t="str">
+      <c r="Z17" s="47" t="str">
         <f aca="false">IF((U17+V17)&gt;0,IF(V17&gt;S17,V17-S17," ")," ")</f>
         <v> </v>
       </c>
@@ -2315,7 +2340,7 @@
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
-      <c r="G18" s="53" t="str">
+      <c r="G18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,E18-F18," ")</f>
         <v> </v>
       </c>
@@ -2323,48 +2348,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,MIN(E18*H18,G18)," ")</f>
         <v> </v>
       </c>
-      <c r="J18" s="53" t="str">
+      <c r="J18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,F18+I18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="53" t="str">
+      <c r="K18" s="50" t="str">
         <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
         <v> </v>
       </c>
-      <c r="L18" s="53"/>
+      <c r="L18" s="50"/>
       <c r="M18" s="58"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50" t="str">
+      <c r="N18" s="50"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S18" s="50" t="str">
+      <c r="S18" s="47" t="str">
         <f aca="false">IF(O18&gt;0,O18-R18," ")</f>
         <v> </v>
       </c>
-      <c r="T18" s="50"/>
+      <c r="T18" s="47"/>
       <c r="U18" s="54"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="53" t="str">
+      <c r="W18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,E18," ")</f>
         <v> </v>
       </c>
-      <c r="X18" s="53" t="str">
+      <c r="X18" s="50" t="str">
         <f aca="false">IF(V18&gt;0,J18," ")</f>
         <v> </v>
       </c>
-      <c r="Y18" s="50" t="str">
+      <c r="Y18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&lt;S18,S18-V18," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z18" s="50" t="str">
+      <c r="Z18" s="47" t="str">
         <f aca="false">IF((U18+V18)&gt;0,IF(V18&gt;S18,V18-S18," ")," ")</f>
         <v> </v>
       </c>
@@ -2377,7 +2402,7 @@
       <c r="D19" s="56"/>
       <c r="E19" s="57"/>
       <c r="F19" s="57"/>
-      <c r="G19" s="53" t="str">
+      <c r="G19" s="50" t="str">
         <f aca="false">IF(E19&gt;0,E19-F19," ")</f>
         <v> </v>
       </c>
@@ -2385,48 +2410,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I19" s="53" t="str">
+      <c r="I19" s="50" t="str">
         <f aca="false">IF(E19&gt;0,MIN(E19*H19,G19)," ")</f>
         <v> </v>
       </c>
-      <c r="J19" s="53" t="str">
+      <c r="J19" s="50" t="str">
         <f aca="false">IF(E19&gt;0,F19+I19," ")</f>
         <v> </v>
       </c>
-      <c r="K19" s="53" t="str">
+      <c r="K19" s="50" t="str">
         <f aca="false">IF(E19&gt;0,E19-J19," ")</f>
         <v> </v>
       </c>
-      <c r="L19" s="53"/>
+      <c r="L19" s="50"/>
       <c r="M19" s="58"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50" t="str">
+      <c r="N19" s="50"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47" t="str">
         <f aca="false">IF(O19&gt;0,O19*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S19" s="50" t="str">
+      <c r="S19" s="47" t="str">
         <f aca="false">IF(O19&gt;0,O19-R19," ")</f>
         <v> </v>
       </c>
-      <c r="T19" s="50"/>
+      <c r="T19" s="47"/>
       <c r="U19" s="54"/>
       <c r="V19" s="57"/>
-      <c r="W19" s="53" t="str">
+      <c r="W19" s="50" t="str">
         <f aca="false">IF(V19&gt;0,E19," ")</f>
         <v> </v>
       </c>
-      <c r="X19" s="53" t="str">
+      <c r="X19" s="50" t="str">
         <f aca="false">IF(V19&gt;0,J19," ")</f>
         <v> </v>
       </c>
-      <c r="Y19" s="50" t="str">
+      <c r="Y19" s="47" t="str">
         <f aca="false">IF((U19+V19)&gt;0,IF(V19&lt;S19,S19-V19," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z19" s="50" t="str">
+      <c r="Z19" s="47" t="str">
         <f aca="false">IF((U19+V19)&gt;0,IF(V19&gt;S19,V19-S19," ")," ")</f>
         <v> </v>
       </c>
@@ -2439,7 +2464,7 @@
       <c r="D20" s="56"/>
       <c r="E20" s="57"/>
       <c r="F20" s="57"/>
-      <c r="G20" s="53" t="str">
+      <c r="G20" s="50" t="str">
         <f aca="false">IF(E20&gt;0,E20-F20," ")</f>
         <v> </v>
       </c>
@@ -2447,48 +2472,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I20" s="53" t="str">
+      <c r="I20" s="50" t="str">
         <f aca="false">IF(E20&gt;0,MIN(E20*H20,G20)," ")</f>
         <v> </v>
       </c>
-      <c r="J20" s="53" t="str">
+      <c r="J20" s="50" t="str">
         <f aca="false">IF(E20&gt;0,F20+I20," ")</f>
         <v> </v>
       </c>
-      <c r="K20" s="53" t="str">
+      <c r="K20" s="50" t="str">
         <f aca="false">IF(E20&gt;0,E20-J20," ")</f>
         <v> </v>
       </c>
-      <c r="L20" s="53"/>
+      <c r="L20" s="50"/>
       <c r="M20" s="58"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="68"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50" t="str">
+      <c r="N20" s="50"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47" t="str">
         <f aca="false">IF(O20&gt;0,O20*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S20" s="50" t="str">
+      <c r="S20" s="47" t="str">
         <f aca="false">IF(O20&gt;0,O20-R20," ")</f>
         <v> </v>
       </c>
-      <c r="T20" s="50"/>
+      <c r="T20" s="47"/>
       <c r="U20" s="54"/>
       <c r="V20" s="57"/>
-      <c r="W20" s="53" t="str">
+      <c r="W20" s="50" t="str">
         <f aca="false">IF(V20&gt;0,E20," ")</f>
         <v> </v>
       </c>
-      <c r="X20" s="53" t="str">
+      <c r="X20" s="50" t="str">
         <f aca="false">IF(V20&gt;0,J20," ")</f>
         <v> </v>
       </c>
-      <c r="Y20" s="50" t="str">
+      <c r="Y20" s="47" t="str">
         <f aca="false">IF((U20+V20)&gt;0,IF(V20&lt;S20,S20-V20," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z20" s="50" t="str">
+      <c r="Z20" s="47" t="str">
         <f aca="false">IF((U20+V20)&gt;0,IF(V20&gt;S20,V20-S20," ")," ")</f>
         <v> </v>
       </c>
@@ -2501,7 +2526,7 @@
       <c r="D21" s="56"/>
       <c r="E21" s="57"/>
       <c r="F21" s="57"/>
-      <c r="G21" s="53" t="str">
+      <c r="G21" s="50" t="str">
         <f aca="false">IF(E21&gt;0,E21-F21," ")</f>
         <v> </v>
       </c>
@@ -2509,48 +2534,48 @@
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I21" s="53" t="str">
+      <c r="I21" s="50" t="str">
         <f aca="false">IF(E21&gt;0,MIN(E21*H21,G21)," ")</f>
         <v> </v>
       </c>
-      <c r="J21" s="53" t="str">
+      <c r="J21" s="50" t="str">
         <f aca="false">IF(E21&gt;0,F21+I21," ")</f>
         <v> </v>
       </c>
-      <c r="K21" s="53" t="str">
+      <c r="K21" s="50" t="str">
         <f aca="false">IF(E21&gt;0,E21-J21," ")</f>
         <v> </v>
       </c>
-      <c r="L21" s="53"/>
+      <c r="L21" s="50"/>
       <c r="M21" s="58"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50" t="str">
+      <c r="N21" s="50"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47" t="str">
         <f aca="false">IF(O21&gt;0,O21*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S21" s="50" t="str">
+      <c r="S21" s="47" t="str">
         <f aca="false">IF(O21&gt;0,O21-R21," ")</f>
         <v> </v>
       </c>
-      <c r="T21" s="50"/>
+      <c r="T21" s="47"/>
       <c r="U21" s="54"/>
       <c r="V21" s="57"/>
-      <c r="W21" s="53" t="str">
+      <c r="W21" s="50" t="str">
         <f aca="false">IF(V21&gt;0,E21," ")</f>
         <v> </v>
       </c>
-      <c r="X21" s="53" t="str">
+      <c r="X21" s="50" t="str">
         <f aca="false">IF(V21&gt;0,J21," ")</f>
         <v> </v>
       </c>
-      <c r="Y21" s="50" t="str">
+      <c r="Y21" s="47" t="str">
         <f aca="false">IF((U21+V21)&gt;0,IF(V21&lt;S21,S21-V21," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z21" s="50" t="str">
+      <c r="Z21" s="47" t="str">
         <f aca="false">IF((U21+V21)&gt;0,IF(V21&gt;S21,V21-S21," ")," ")</f>
         <v> </v>
       </c>
@@ -2589,9 +2614,9 @@
         <f aca="false">SUM(K14:K21)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="53"/>
+      <c r="L22" s="50"/>
       <c r="M22" s="58"/>
-      <c r="N22" s="53"/>
+      <c r="N22" s="50"/>
       <c r="O22" s="61" t="n">
         <f aca="false">SUM(O14:O21)</f>
         <v>0</v>
@@ -2609,8 +2634,8 @@
         <f aca="false">SUM(S14:S21)</f>
         <v>0</v>
       </c>
-      <c r="T22" s="50"/>
-      <c r="U22" s="52"/>
+      <c r="T22" s="47"/>
+      <c r="U22" s="49"/>
       <c r="V22" s="60" t="n">
         <f aca="false">SUM(V14:V21)</f>
         <v>0</v>
@@ -2638,61 +2663,61 @@
       <c r="B23" s="63"/>
       <c r="C23" s="64"/>
       <c r="D23" s="65"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
       <c r="H23" s="58"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
       <c r="M23" s="58"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
       <c r="P23" s="62"/>
-      <c r="Q23" s="53"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="53"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="52"/>
-      <c r="V23" s="53"/>
-      <c r="W23" s="53"/>
-      <c r="X23" s="53"/>
-      <c r="Y23" s="53"/>
-      <c r="Z23" s="53"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="50"/>
+      <c r="T23" s="47"/>
+      <c r="U23" s="49"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="50"/>
+      <c r="Y23" s="50"/>
+      <c r="Z23" s="50"/>
       <c r="AA23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="42"/>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="66"/>
+      <c r="C24" s="51"/>
       <c r="D24" s="62"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="67" t="n">
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="66" t="n">
         <v>0.2</v>
       </c>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
       <c r="M24" s="58"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50"/>
-      <c r="S24" s="50"/>
-      <c r="T24" s="50"/>
-      <c r="U24" s="52"/>
-      <c r="V24" s="53"/>
-      <c r="W24" s="53"/>
-      <c r="X24" s="53"/>
-      <c r="Y24" s="50"/>
-      <c r="Z24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47"/>
+      <c r="S24" s="47"/>
+      <c r="T24" s="47"/>
+      <c r="U24" s="49"/>
+      <c r="V24" s="50"/>
+      <c r="W24" s="50"/>
+      <c r="X24" s="50"/>
+      <c r="Y24" s="47"/>
+      <c r="Z24" s="47"/>
       <c r="AA24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2702,7 +2727,7 @@
       <c r="D25" s="56"/>
       <c r="E25" s="57"/>
       <c r="F25" s="57"/>
-      <c r="G25" s="53" t="str">
+      <c r="G25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,E25-F25," ")</f>
         <v> </v>
       </c>
@@ -2710,48 +2735,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="53" t="str">
+      <c r="I25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,MIN(E25*H25,G25)," ")</f>
         <v> </v>
       </c>
-      <c r="J25" s="53" t="str">
+      <c r="J25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,F25+I25," ")</f>
         <v> </v>
       </c>
-      <c r="K25" s="53" t="str">
+      <c r="K25" s="50" t="str">
         <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
         <v> </v>
       </c>
-      <c r="L25" s="53"/>
+      <c r="L25" s="50"/>
       <c r="M25" s="58"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50" t="str">
+      <c r="N25" s="50"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S25" s="50" t="str">
+      <c r="S25" s="47" t="str">
         <f aca="false">IF(O25&gt;0,O25-R25," ")</f>
         <v> </v>
       </c>
-      <c r="T25" s="50"/>
+      <c r="T25" s="47"/>
       <c r="U25" s="54"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="53" t="str">
+      <c r="W25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,E25," ")</f>
         <v> </v>
       </c>
-      <c r="X25" s="53" t="str">
+      <c r="X25" s="50" t="str">
         <f aca="false">IF(V25&gt;0,J25," ")</f>
         <v> </v>
       </c>
-      <c r="Y25" s="50" t="str">
+      <c r="Y25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&lt;S25,S25-V25," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z25" s="50" t="str">
+      <c r="Z25" s="47" t="str">
         <f aca="false">IF((U25+V25)&gt;0,IF(V25&gt;S25,V25-S25," ")," ")</f>
         <v> </v>
       </c>
@@ -2764,7 +2789,7 @@
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
       <c r="F26" s="57"/>
-      <c r="G26" s="53" t="str">
+      <c r="G26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,E26-F26," ")</f>
         <v> </v>
       </c>
@@ -2772,48 +2797,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I26" s="53" t="str">
+      <c r="I26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,MIN(E26*H26,G26)," ")</f>
         <v> </v>
       </c>
-      <c r="J26" s="53" t="str">
+      <c r="J26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,F26+I26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="53" t="str">
+      <c r="K26" s="50" t="str">
         <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
         <v> </v>
       </c>
-      <c r="L26" s="53"/>
+      <c r="L26" s="50"/>
       <c r="M26" s="58"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50" t="str">
+      <c r="N26" s="50"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S26" s="50" t="str">
+      <c r="S26" s="47" t="str">
         <f aca="false">IF(O26&gt;0,O26-R26," ")</f>
         <v> </v>
       </c>
-      <c r="T26" s="50"/>
+      <c r="T26" s="47"/>
       <c r="U26" s="54"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="53" t="str">
+      <c r="W26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,E26," ")</f>
         <v> </v>
       </c>
-      <c r="X26" s="53" t="str">
+      <c r="X26" s="50" t="str">
         <f aca="false">IF(V26&gt;0,J26," ")</f>
         <v> </v>
       </c>
-      <c r="Y26" s="50" t="str">
+      <c r="Y26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&lt;S26,S26-V26," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z26" s="50" t="str">
+      <c r="Z26" s="47" t="str">
         <f aca="false">IF((U26+V26)&gt;0,IF(V26&gt;S26,V26-S26," ")," ")</f>
         <v> </v>
       </c>
@@ -2826,7 +2851,7 @@
       <c r="D27" s="56"/>
       <c r="E27" s="57"/>
       <c r="F27" s="57"/>
-      <c r="G27" s="53" t="str">
+      <c r="G27" s="50" t="str">
         <f aca="false">IF(E27&gt;0,E27-F27," ")</f>
         <v> </v>
       </c>
@@ -2834,48 +2859,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I27" s="53" t="str">
+      <c r="I27" s="50" t="str">
         <f aca="false">IF(E27&gt;0,MIN(E27*H27,G27)," ")</f>
         <v> </v>
       </c>
-      <c r="J27" s="53" t="str">
+      <c r="J27" s="50" t="str">
         <f aca="false">IF(E27&gt;0,F27+I27," ")</f>
         <v> </v>
       </c>
-      <c r="K27" s="53" t="str">
+      <c r="K27" s="50" t="str">
         <f aca="false">IF(E27&gt;0,E27-J27," ")</f>
         <v> </v>
       </c>
-      <c r="L27" s="53"/>
+      <c r="L27" s="50"/>
       <c r="M27" s="58"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="68"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50" t="str">
+      <c r="N27" s="50"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47" t="str">
         <f aca="false">IF(O27&gt;0,O27*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S27" s="50" t="str">
+      <c r="S27" s="47" t="str">
         <f aca="false">IF(O27&gt;0,O27-R27," ")</f>
         <v> </v>
       </c>
-      <c r="T27" s="50"/>
+      <c r="T27" s="47"/>
       <c r="U27" s="54"/>
       <c r="V27" s="57"/>
-      <c r="W27" s="53" t="str">
+      <c r="W27" s="50" t="str">
         <f aca="false">IF(V27&gt;0,E27," ")</f>
         <v> </v>
       </c>
-      <c r="X27" s="53" t="str">
+      <c r="X27" s="50" t="str">
         <f aca="false">IF(V27&gt;0,J27," ")</f>
         <v> </v>
       </c>
-      <c r="Y27" s="50" t="str">
+      <c r="Y27" s="47" t="str">
         <f aca="false">IF((U27+V27)&gt;0,IF(V27&lt;S27,S27-V27," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z27" s="50" t="str">
+      <c r="Z27" s="47" t="str">
         <f aca="false">IF((U27+V27)&gt;0,IF(V27&gt;S27,V27-S27," ")," ")</f>
         <v> </v>
       </c>
@@ -2888,7 +2913,7 @@
       <c r="D28" s="56"/>
       <c r="E28" s="57"/>
       <c r="F28" s="57"/>
-      <c r="G28" s="53" t="str">
+      <c r="G28" s="50" t="str">
         <f aca="false">IF(E28&gt;0,E28-F28," ")</f>
         <v> </v>
       </c>
@@ -2896,48 +2921,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I28" s="53" t="str">
+      <c r="I28" s="50" t="str">
         <f aca="false">IF(E28&gt;0,MIN(E28*H28,G28)," ")</f>
         <v> </v>
       </c>
-      <c r="J28" s="53" t="str">
+      <c r="J28" s="50" t="str">
         <f aca="false">IF(E28&gt;0,F28+I28," ")</f>
         <v> </v>
       </c>
-      <c r="K28" s="53" t="str">
+      <c r="K28" s="50" t="str">
         <f aca="false">IF(E28&gt;0,E28-J28," ")</f>
         <v> </v>
       </c>
-      <c r="L28" s="53"/>
+      <c r="L28" s="50"/>
       <c r="M28" s="58"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="68"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50" t="str">
+      <c r="N28" s="50"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="47"/>
+      <c r="R28" s="47" t="str">
         <f aca="false">IF(O28&gt;0,O28*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S28" s="50" t="str">
+      <c r="S28" s="47" t="str">
         <f aca="false">IF(O28&gt;0,O28-R28," ")</f>
         <v> </v>
       </c>
-      <c r="T28" s="50"/>
+      <c r="T28" s="47"/>
       <c r="U28" s="54"/>
       <c r="V28" s="57"/>
-      <c r="W28" s="53" t="str">
+      <c r="W28" s="50" t="str">
         <f aca="false">IF(V28&gt;0,E28," ")</f>
         <v> </v>
       </c>
-      <c r="X28" s="53" t="str">
+      <c r="X28" s="50" t="str">
         <f aca="false">IF(V28&gt;0,J28," ")</f>
         <v> </v>
       </c>
-      <c r="Y28" s="50" t="str">
+      <c r="Y28" s="47" t="str">
         <f aca="false">IF((U28+V28)&gt;0,IF(V28&lt;S28,S28-V28," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z28" s="50" t="str">
+      <c r="Z28" s="47" t="str">
         <f aca="false">IF((U28+V28)&gt;0,IF(V28&gt;S28,V28-S28," ")," ")</f>
         <v> </v>
       </c>
@@ -2950,7 +2975,7 @@
       <c r="D29" s="56"/>
       <c r="E29" s="57"/>
       <c r="F29" s="57"/>
-      <c r="G29" s="53" t="str">
+      <c r="G29" s="50" t="str">
         <f aca="false">IF(E29&gt;0,E29-F29," ")</f>
         <v> </v>
       </c>
@@ -2958,48 +2983,48 @@
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I29" s="53" t="str">
+      <c r="I29" s="50" t="str">
         <f aca="false">IF(E29&gt;0,MIN(E29*H29,G29)," ")</f>
         <v> </v>
       </c>
-      <c r="J29" s="53" t="str">
+      <c r="J29" s="50" t="str">
         <f aca="false">IF(E29&gt;0,F29+I29," ")</f>
         <v> </v>
       </c>
-      <c r="K29" s="53" t="str">
+      <c r="K29" s="50" t="str">
         <f aca="false">IF(E29&gt;0,E29-J29," ")</f>
         <v> </v>
       </c>
-      <c r="L29" s="53"/>
+      <c r="L29" s="50"/>
       <c r="M29" s="58"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="68"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50" t="str">
+      <c r="N29" s="50"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="47" t="str">
         <f aca="false">IF(O29&gt;0,O29*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S29" s="50" t="str">
+      <c r="S29" s="47" t="str">
         <f aca="false">IF(O29&gt;0,O29-R29," ")</f>
         <v> </v>
       </c>
-      <c r="T29" s="50"/>
+      <c r="T29" s="47"/>
       <c r="U29" s="54"/>
       <c r="V29" s="57"/>
-      <c r="W29" s="53" t="str">
+      <c r="W29" s="50" t="str">
         <f aca="false">IF(V29&gt;0,E29," ")</f>
         <v> </v>
       </c>
-      <c r="X29" s="53" t="str">
+      <c r="X29" s="50" t="str">
         <f aca="false">IF(V29&gt;0,J29," ")</f>
         <v> </v>
       </c>
-      <c r="Y29" s="50" t="str">
+      <c r="Y29" s="47" t="str">
         <f aca="false">IF((U29+V29)&gt;0,IF(V29&lt;S29,S29-V29," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z29" s="50" t="str">
+      <c r="Z29" s="47" t="str">
         <f aca="false">IF((U29+V29)&gt;0,IF(V29&gt;S29,V29-S29," ")," ")</f>
         <v> </v>
       </c>
@@ -3038,9 +3063,9 @@
         <f aca="false">SUM(K25:K29)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="53"/>
+      <c r="L30" s="50"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="53"/>
+      <c r="N30" s="50"/>
       <c r="O30" s="61" t="n">
         <f aca="false">SUM(O25:O29)</f>
         <v>0</v>
@@ -3058,8 +3083,8 @@
         <f aca="false">SUM(S25:S29)</f>
         <v>0</v>
       </c>
-      <c r="T30" s="50"/>
-      <c r="U30" s="52"/>
+      <c r="T30" s="47"/>
+      <c r="U30" s="49"/>
       <c r="V30" s="60" t="n">
         <f aca="false">SUM(V25:V29)</f>
         <v>0</v>
@@ -3087,120 +3112,119 @@
       <c r="B31" s="63"/>
       <c r="C31" s="64"/>
       <c r="D31" s="65"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
       <c r="H31" s="58"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
       <c r="M31" s="58"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="53"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
       <c r="P31" s="62"/>
-      <c r="Q31" s="53"/>
-      <c r="R31" s="53"/>
-      <c r="S31" s="53"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="52"/>
-      <c r="V31" s="53"/>
-      <c r="W31" s="53"/>
-      <c r="X31" s="53"/>
-      <c r="Y31" s="53"/>
-      <c r="Z31" s="53"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="47"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="50"/>
+      <c r="W31" s="50"/>
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="50"/>
       <c r="AA31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="42"/>
-      <c r="B32" s="66" t="s">
+      <c r="B32" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="67" t="n">
+      <c r="C32" s="51"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="66" t="n">
         <v>0.33</v>
       </c>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
       <c r="M32" s="58"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="53"/>
-      <c r="W32" s="53"/>
-      <c r="X32" s="53"/>
-      <c r="Y32" s="50"/>
-      <c r="Z32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="47"/>
+      <c r="R32" s="47"/>
+      <c r="S32" s="47"/>
+      <c r="T32" s="47"/>
+      <c r="U32" s="49"/>
+      <c r="V32" s="50"/>
+      <c r="W32" s="50"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="47"/>
+      <c r="Z32" s="47"/>
       <c r="AA32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="42"/>
       <c r="B33" s="54"/>
       <c r="C33" s="55"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="53" t="str">
-        <f aca="false">IF(E33&gt;0,E33-F33," ")</f>
-        <v> </v>
+      <c r="D33" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>270</v>
       </c>
       <c r="H33" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I33" s="53" t="str">
+      <c r="I33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,MIN(E33*H33,G33)," ")</f>
         <v> </v>
       </c>
-      <c r="J33" s="53" t="str">
+      <c r="J33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,F33+I33," ")</f>
         <v> </v>
       </c>
-      <c r="K33" s="53" t="str">
+      <c r="K33" s="50" t="str">
         <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
         <v> </v>
       </c>
-      <c r="L33" s="53"/>
+      <c r="L33" s="50"/>
       <c r="M33" s="58"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="68"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50" t="str">
+      <c r="N33" s="50"/>
+      <c r="O33" s="67"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="47"/>
+      <c r="R33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S33" s="50" t="str">
+      <c r="S33" s="47" t="str">
         <f aca="false">IF(O33&gt;0,O33-R33," ")</f>
         <v> </v>
       </c>
-      <c r="T33" s="50"/>
+      <c r="T33" s="47"/>
       <c r="U33" s="54"/>
       <c r="V33" s="57"/>
-      <c r="W33" s="53" t="str">
+      <c r="W33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,E33," ")</f>
         <v> </v>
       </c>
-      <c r="X33" s="53" t="str">
+      <c r="X33" s="50" t="str">
         <f aca="false">IF(V33&gt;0,J33," ")</f>
         <v> </v>
       </c>
-      <c r="Y33" s="50" t="str">
+      <c r="Y33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&lt;S33,S33-V33," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z33" s="50" t="str">
+      <c r="Z33" s="47" t="str">
         <f aca="false">IF((U33+V33)&gt;0,IF(V33&gt;S33,V33-S33," ")," ")</f>
         <v> </v>
       </c>
@@ -3213,56 +3237,53 @@
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
       <c r="F34" s="57"/>
-      <c r="G34" s="53" t="str">
-        <f aca="false">IF(E34&gt;0,E34-F34," ")</f>
-        <v> </v>
-      </c>
+      <c r="G34" s="50"/>
       <c r="H34" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I34" s="53" t="str">
+      <c r="I34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,MIN(E34*H34,G34)," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="53" t="str">
+      <c r="J34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,F34+I34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="53" t="str">
+      <c r="K34" s="50" t="str">
         <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
         <v> </v>
       </c>
-      <c r="L34" s="53"/>
+      <c r="L34" s="50"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="68"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="50" t="str">
+      <c r="N34" s="50"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="47"/>
+      <c r="R34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S34" s="50" t="str">
+      <c r="S34" s="47" t="str">
         <f aca="false">IF(O34&gt;0,O34-R34," ")</f>
         <v> </v>
       </c>
-      <c r="T34" s="50"/>
+      <c r="T34" s="47"/>
       <c r="U34" s="54"/>
       <c r="V34" s="57"/>
-      <c r="W34" s="53" t="str">
+      <c r="W34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,E34," ")</f>
         <v> </v>
       </c>
-      <c r="X34" s="53" t="str">
+      <c r="X34" s="50" t="str">
         <f aca="false">IF(V34&gt;0,J34," ")</f>
         <v> </v>
       </c>
-      <c r="Y34" s="50" t="str">
+      <c r="Y34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&lt;S34,S34-V34," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z34" s="50" t="str">
+      <c r="Z34" s="47" t="str">
         <f aca="false">IF((U34+V34)&gt;0,IF(V34&gt;S34,V34-S34," ")," ")</f>
         <v> </v>
       </c>
@@ -3275,56 +3296,53 @@
       <c r="D35" s="56"/>
       <c r="E35" s="57"/>
       <c r="F35" s="57"/>
-      <c r="G35" s="53" t="str">
-        <f aca="false">IF(E35&gt;0,E35-F35," ")</f>
-        <v> </v>
-      </c>
+      <c r="G35" s="50"/>
       <c r="H35" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I35" s="53" t="str">
+      <c r="I35" s="50" t="str">
         <f aca="false">IF(E35&gt;0,MIN(E35*H35,G35)," ")</f>
         <v> </v>
       </c>
-      <c r="J35" s="53" t="str">
+      <c r="J35" s="50" t="str">
         <f aca="false">IF(E35&gt;0,F35+I35," ")</f>
         <v> </v>
       </c>
-      <c r="K35" s="53" t="str">
+      <c r="K35" s="50" t="str">
         <f aca="false">IF(E35&gt;0,E35-J35," ")</f>
         <v> </v>
       </c>
-      <c r="L35" s="53"/>
+      <c r="L35" s="50"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="68"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50" t="str">
+      <c r="N35" s="50"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="47"/>
+      <c r="R35" s="47" t="str">
         <f aca="false">IF(O35&gt;0,O35*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S35" s="50" t="str">
+      <c r="S35" s="47" t="str">
         <f aca="false">IF(O35&gt;0,O35-R35," ")</f>
         <v> </v>
       </c>
-      <c r="T35" s="50"/>
+      <c r="T35" s="47"/>
       <c r="U35" s="54"/>
       <c r="V35" s="57"/>
-      <c r="W35" s="53" t="str">
+      <c r="W35" s="50" t="str">
         <f aca="false">IF(V35&gt;0,E35," ")</f>
         <v> </v>
       </c>
-      <c r="X35" s="53" t="str">
+      <c r="X35" s="50" t="str">
         <f aca="false">IF(V35&gt;0,J35," ")</f>
         <v> </v>
       </c>
-      <c r="Y35" s="50" t="str">
+      <c r="Y35" s="47" t="str">
         <f aca="false">IF((U35+V35)&gt;0,IF(V35&lt;S35,S35-V35," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z35" s="50" t="str">
+      <c r="Z35" s="47" t="str">
         <f aca="false">IF((U35+V35)&gt;0,IF(V35&gt;S35,V35-S35," ")," ")</f>
         <v> </v>
       </c>
@@ -3337,56 +3355,53 @@
       <c r="D36" s="56"/>
       <c r="E36" s="57"/>
       <c r="F36" s="57"/>
-      <c r="G36" s="53" t="str">
-        <f aca="false">IF(E36&gt;0,E36-F36," ")</f>
-        <v> </v>
-      </c>
+      <c r="G36" s="50"/>
       <c r="H36" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I36" s="53" t="str">
+      <c r="I36" s="50" t="str">
         <f aca="false">IF(E36&gt;0,MIN(E36*H36,G36)," ")</f>
         <v> </v>
       </c>
-      <c r="J36" s="53" t="str">
+      <c r="J36" s="50" t="str">
         <f aca="false">IF(E36&gt;0,F36+I36," ")</f>
         <v> </v>
       </c>
-      <c r="K36" s="53" t="str">
+      <c r="K36" s="50" t="str">
         <f aca="false">IF(E36&gt;0,E36-J36," ")</f>
         <v> </v>
       </c>
-      <c r="L36" s="53"/>
+      <c r="L36" s="50"/>
       <c r="M36" s="58"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="68"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50" t="str">
+      <c r="N36" s="50"/>
+      <c r="O36" s="67"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="47"/>
+      <c r="R36" s="47" t="str">
         <f aca="false">IF(O36&gt;0,O36*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S36" s="50" t="str">
+      <c r="S36" s="47" t="str">
         <f aca="false">IF(O36&gt;0,O36-R36," ")</f>
         <v> </v>
       </c>
-      <c r="T36" s="50"/>
+      <c r="T36" s="47"/>
       <c r="U36" s="54"/>
       <c r="V36" s="57"/>
-      <c r="W36" s="53" t="str">
+      <c r="W36" s="50" t="str">
         <f aca="false">IF(V36&gt;0,E36," ")</f>
         <v> </v>
       </c>
-      <c r="X36" s="53" t="str">
+      <c r="X36" s="50" t="str">
         <f aca="false">IF(V36&gt;0,J36," ")</f>
         <v> </v>
       </c>
-      <c r="Y36" s="50" t="str">
+      <c r="Y36" s="47" t="str">
         <f aca="false">IF((U36+V36)&gt;0,IF(V36&lt;S36,S36-V36," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z36" s="50" t="str">
+      <c r="Z36" s="47" t="str">
         <f aca="false">IF((U36+V36)&gt;0,IF(V36&gt;S36,V36-S36," ")," ")</f>
         <v> </v>
       </c>
@@ -3399,56 +3414,53 @@
       <c r="D37" s="56"/>
       <c r="E37" s="57"/>
       <c r="F37" s="57"/>
-      <c r="G37" s="53" t="str">
-        <f aca="false">IF(E37&gt;0,E37-F37," ")</f>
-        <v> </v>
-      </c>
+      <c r="G37" s="50"/>
       <c r="H37" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I37" s="53" t="str">
+      <c r="I37" s="50" t="str">
         <f aca="false">IF(E37&gt;0,MIN(E37*H37,G37)," ")</f>
         <v> </v>
       </c>
-      <c r="J37" s="53" t="str">
+      <c r="J37" s="50" t="str">
         <f aca="false">IF(E37&gt;0,F37+I37," ")</f>
         <v> </v>
       </c>
-      <c r="K37" s="53" t="str">
+      <c r="K37" s="50" t="str">
         <f aca="false">IF(E37&gt;0,E37-J37," ")</f>
         <v> </v>
       </c>
-      <c r="L37" s="53"/>
+      <c r="L37" s="50"/>
       <c r="M37" s="58"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50" t="str">
+      <c r="N37" s="50"/>
+      <c r="O37" s="67"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="47"/>
+      <c r="R37" s="47" t="str">
         <f aca="false">IF(O37&gt;0,O37*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S37" s="50" t="str">
+      <c r="S37" s="47" t="str">
         <f aca="false">IF(O37&gt;0,O37-R37," ")</f>
         <v> </v>
       </c>
-      <c r="T37" s="50"/>
+      <c r="T37" s="47"/>
       <c r="U37" s="54"/>
       <c r="V37" s="57"/>
-      <c r="W37" s="53" t="str">
+      <c r="W37" s="50" t="str">
         <f aca="false">IF(V37&gt;0,E37," ")</f>
         <v> </v>
       </c>
-      <c r="X37" s="53" t="str">
+      <c r="X37" s="50" t="str">
         <f aca="false">IF(V37&gt;0,J37," ")</f>
         <v> </v>
       </c>
-      <c r="Y37" s="50" t="str">
+      <c r="Y37" s="47" t="str">
         <f aca="false">IF((U37+V37)&gt;0,IF(V37&lt;S37,S37-V37," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z37" s="50" t="str">
+      <c r="Z37" s="47" t="str">
         <f aca="false">IF((U37+V37)&gt;0,IF(V37&gt;S37,V37-S37," ")," ")</f>
         <v> </v>
       </c>
@@ -3461,56 +3473,53 @@
       <c r="D38" s="56"/>
       <c r="E38" s="57"/>
       <c r="F38" s="57"/>
-      <c r="G38" s="53" t="str">
-        <f aca="false">IF(E38&gt;0,E38-F38," ")</f>
-        <v> </v>
-      </c>
+      <c r="G38" s="50"/>
       <c r="H38" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I38" s="53" t="str">
+      <c r="I38" s="50" t="str">
         <f aca="false">IF(E38&gt;0,MIN(E38*H38,G38)," ")</f>
         <v> </v>
       </c>
-      <c r="J38" s="53" t="str">
+      <c r="J38" s="50" t="str">
         <f aca="false">IF(E38&gt;0,F38+I38," ")</f>
         <v> </v>
       </c>
-      <c r="K38" s="53" t="str">
+      <c r="K38" s="50" t="str">
         <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
         <v> </v>
       </c>
-      <c r="L38" s="53"/>
+      <c r="L38" s="50"/>
       <c r="M38" s="58"/>
-      <c r="N38" s="53"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50" t="str">
+      <c r="N38" s="50"/>
+      <c r="O38" s="67"/>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47" t="str">
         <f aca="false">IF(O38&gt;0,O38*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S38" s="50" t="str">
+      <c r="S38" s="47" t="str">
         <f aca="false">IF(O38&gt;0,O38-R38," ")</f>
         <v> </v>
       </c>
-      <c r="T38" s="50"/>
+      <c r="T38" s="47"/>
       <c r="U38" s="54"/>
       <c r="V38" s="57"/>
-      <c r="W38" s="53" t="str">
+      <c r="W38" s="50" t="str">
         <f aca="false">IF(V38&gt;0,E38," ")</f>
         <v> </v>
       </c>
-      <c r="X38" s="53" t="str">
+      <c r="X38" s="50" t="str">
         <f aca="false">IF(V38&gt;0,J38," ")</f>
         <v> </v>
       </c>
-      <c r="Y38" s="50" t="str">
+      <c r="Y38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&lt;S38,S38-V38," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z38" s="50" t="str">
+      <c r="Z38" s="47" t="str">
         <f aca="false">IF((U38+V38)&gt;0,IF(V38&gt;S38,V38-S38," ")," ")</f>
         <v> </v>
       </c>
@@ -3523,56 +3532,53 @@
       <c r="D39" s="56"/>
       <c r="E39" s="57"/>
       <c r="F39" s="57"/>
-      <c r="G39" s="53" t="str">
-        <f aca="false">IF(E39&gt;0,E39-F39," ")</f>
-        <v> </v>
-      </c>
+      <c r="G39" s="50"/>
       <c r="H39" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I39" s="53" t="str">
+      <c r="I39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,MIN(E39*H39,G39)," ")</f>
         <v> </v>
       </c>
-      <c r="J39" s="53" t="str">
+      <c r="J39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,F39+I39," ")</f>
         <v> </v>
       </c>
-      <c r="K39" s="53" t="str">
+      <c r="K39" s="50" t="str">
         <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
         <v> </v>
       </c>
-      <c r="L39" s="53"/>
+      <c r="L39" s="50"/>
       <c r="M39" s="58"/>
-      <c r="N39" s="53"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50" t="str">
+      <c r="N39" s="50"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="47"/>
+      <c r="R39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,O39*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S39" s="50" t="str">
+      <c r="S39" s="47" t="str">
         <f aca="false">IF(O39&gt;0,O39-R39," ")</f>
         <v> </v>
       </c>
-      <c r="T39" s="50"/>
+      <c r="T39" s="47"/>
       <c r="U39" s="54"/>
       <c r="V39" s="57"/>
-      <c r="W39" s="53" t="str">
+      <c r="W39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,E39," ")</f>
         <v> </v>
       </c>
-      <c r="X39" s="53" t="str">
+      <c r="X39" s="50" t="str">
         <f aca="false">IF(V39&gt;0,J39," ")</f>
         <v> </v>
       </c>
-      <c r="Y39" s="50" t="str">
+      <c r="Y39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&lt;S39,S39-V39," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z39" s="50" t="str">
+      <c r="Z39" s="47" t="str">
         <f aca="false">IF((U39+V39)&gt;0,IF(V39&gt;S39,V39-S39," ")," ")</f>
         <v> </v>
       </c>
@@ -3585,56 +3591,53 @@
       <c r="D40" s="56"/>
       <c r="E40" s="57"/>
       <c r="F40" s="57"/>
-      <c r="G40" s="53" t="str">
-        <f aca="false">IF(E40&gt;0,E40-F40," ")</f>
-        <v> </v>
-      </c>
+      <c r="G40" s="50"/>
       <c r="H40" s="58" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I40" s="53" t="str">
+      <c r="I40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,MIN(E40*H40,G40)," ")</f>
         <v> </v>
       </c>
-      <c r="J40" s="53" t="str">
+      <c r="J40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,F40+I40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="53" t="str">
+      <c r="K40" s="50" t="str">
         <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
         <v> </v>
       </c>
-      <c r="L40" s="53"/>
+      <c r="L40" s="50"/>
       <c r="M40" s="58"/>
-      <c r="N40" s="53"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50" t="str">
+      <c r="N40" s="50"/>
+      <c r="O40" s="67"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="47"/>
+      <c r="R40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,O40*R$4/100," ")</f>
         <v> </v>
       </c>
-      <c r="S40" s="50" t="str">
+      <c r="S40" s="47" t="str">
         <f aca="false">IF(O40&gt;0,O40-R40," ")</f>
         <v> </v>
       </c>
-      <c r="T40" s="50"/>
+      <c r="T40" s="47"/>
       <c r="U40" s="54"/>
       <c r="V40" s="57"/>
-      <c r="W40" s="53" t="str">
+      <c r="W40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,E40," ")</f>
         <v> </v>
       </c>
-      <c r="X40" s="53" t="str">
+      <c r="X40" s="50" t="str">
         <f aca="false">IF(V40&gt;0,J40," ")</f>
         <v> </v>
       </c>
-      <c r="Y40" s="50" t="str">
+      <c r="Y40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&lt;S40,S40-V40," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z40" s="50" t="str">
+      <c r="Z40" s="47" t="str">
         <f aca="false">IF((U40+V40)&gt;0,IF(V40&gt;S40,V40-S40," ")," ")</f>
         <v> </v>
       </c>
@@ -3644,7 +3647,7 @@
       <c r="A41" s="42"/>
       <c r="B41" s="59" t="str">
         <f aca="false">IF((E41-F41)=([1]OpenAccounts!$J$13-[1]OpenAccounts!$P$13),"Existing Computers","Check Opening Balkance Sheet figures agree")</f>
-        <v>Existing Computers</v>
+        <v>Check Opening Balkance Sheet figures agree</v>
       </c>
       <c r="C41" s="59"/>
       <c r="D41" s="59"/>
@@ -3654,7 +3657,7 @@
       </c>
       <c r="F41" s="60" t="n">
         <f aca="false">SUM(F33:F40)</f>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="G41" s="61" t="n">
         <f aca="false">SUM(G33:G40)</f>
@@ -3673,9 +3676,9 @@
         <f aca="false">SUM(K33:K40)</f>
         <v>0</v>
       </c>
-      <c r="L41" s="53"/>
+      <c r="L41" s="50"/>
       <c r="M41" s="58"/>
-      <c r="N41" s="53"/>
+      <c r="N41" s="50"/>
       <c r="O41" s="61" t="n">
         <f aca="false">SUM(O33:O40)</f>
         <v>0</v>
@@ -3693,8 +3696,8 @@
         <f aca="false">SUM(S33:S40)</f>
         <v>0</v>
       </c>
-      <c r="T41" s="50"/>
-      <c r="U41" s="52"/>
+      <c r="T41" s="47"/>
+      <c r="U41" s="49"/>
       <c r="V41" s="60" t="n">
         <f aca="false">SUM(V33:V40)</f>
         <v>0</v>
@@ -3722,122 +3725,121 @@
       <c r="B42" s="63"/>
       <c r="C42" s="64"/>
       <c r="D42" s="65"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
       <c r="H42" s="58"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="50"/>
+      <c r="L42" s="50"/>
       <c r="M42" s="58"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="53"/>
+      <c r="N42" s="50"/>
+      <c r="O42" s="50"/>
       <c r="P42" s="62"/>
-      <c r="Q42" s="53"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="53"/>
-      <c r="T42" s="50"/>
-      <c r="U42" s="52"/>
-      <c r="V42" s="53"/>
-      <c r="W42" s="53"/>
-      <c r="X42" s="53"/>
-      <c r="Y42" s="53"/>
-      <c r="Z42" s="53"/>
+      <c r="Q42" s="50"/>
+      <c r="R42" s="50"/>
+      <c r="S42" s="50"/>
+      <c r="T42" s="47"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="50"/>
+      <c r="W42" s="50"/>
+      <c r="X42" s="50"/>
+      <c r="Y42" s="50"/>
+      <c r="Z42" s="50"/>
       <c r="AA42" s="25"/>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
-      <c r="B43" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="67" t="n">
+      <c r="B43" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="51"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="66" t="n">
         <v>0.25</v>
       </c>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="70"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="53"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
+      <c r="M43" s="69"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
       <c r="P43" s="62"/>
-      <c r="Q43" s="53"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="53"/>
-      <c r="T43" s="71"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="53"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="53"/>
-      <c r="Z43" s="53"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="70"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="50"/>
+      <c r="W43" s="50"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="50"/>
       <c r="AA43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="55"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="53" t="str">
-        <f aca="false">IF(E44&gt;0,E44-F44," ")</f>
-        <v> </v>
+      <c r="D44" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>9828</v>
       </c>
       <c r="H44" s="58" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="53" t="str">
+      <c r="I44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,MIN(E44*H44,G44)," ")</f>
         <v> </v>
       </c>
-      <c r="J44" s="53" t="str">
+      <c r="J44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,F44+I44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="53" t="str">
+      <c r="K44" s="50" t="str">
         <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
         <v> </v>
       </c>
-      <c r="L44" s="53"/>
-      <c r="M44" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="53"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50" t="str">
+      <c r="L44" s="50"/>
+      <c r="M44" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="50"/>
+      <c r="O44" s="67"/>
+      <c r="P44" s="48"/>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,MIN(O44*R$4/100*(1-M44),3000*(1-M44))," ")</f>
         <v> </v>
       </c>
-      <c r="S44" s="50" t="str">
+      <c r="S44" s="47" t="str">
         <f aca="false">IF(O44&gt;0,O44-R44," ")</f>
         <v> </v>
       </c>
-      <c r="T44" s="50"/>
+      <c r="T44" s="47"/>
       <c r="U44" s="54"/>
       <c r="V44" s="57"/>
-      <c r="W44" s="53" t="str">
+      <c r="W44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,E44," ")</f>
         <v> </v>
       </c>
-      <c r="X44" s="53" t="str">
+      <c r="X44" s="50" t="str">
         <f aca="false">IF(V44&gt;0,J44," ")</f>
         <v> </v>
       </c>
-      <c r="Y44" s="50" t="str">
+      <c r="Y44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&lt;S44,(S44-V44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z44" s="50" t="str">
+      <c r="Z44" s="47" t="str">
         <f aca="false">IF((U44+V44)&gt;0,IF(V44&gt;S44,(V44-S44)*(1-M44)," ")," ")</f>
         <v> </v>
       </c>
@@ -3850,58 +3852,55 @@
       <c r="D45" s="56"/>
       <c r="E45" s="57"/>
       <c r="F45" s="57"/>
-      <c r="G45" s="53" t="str">
-        <f aca="false">IF(E45&gt;0,E45-F45," ")</f>
-        <v> </v>
-      </c>
+      <c r="G45" s="50"/>
       <c r="H45" s="58" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I45" s="53" t="str">
+      <c r="I45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,MIN(E45*H45,G45)," ")</f>
         <v> </v>
       </c>
-      <c r="J45" s="53" t="str">
+      <c r="J45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,F45+I45," ")</f>
         <v> </v>
       </c>
-      <c r="K45" s="53" t="str">
+      <c r="K45" s="50" t="str">
         <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
         <v> </v>
       </c>
-      <c r="L45" s="53"/>
-      <c r="M45" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="53"/>
-      <c r="O45" s="68"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50" t="str">
+      <c r="L45" s="50"/>
+      <c r="M45" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="50"/>
+      <c r="O45" s="67"/>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,MIN(O45*R$4/100*(1-M45),3000*(1-M45))," ")</f>
         <v> </v>
       </c>
-      <c r="S45" s="50" t="str">
+      <c r="S45" s="47" t="str">
         <f aca="false">IF(O45&gt;0,O45-R45," ")</f>
         <v> </v>
       </c>
-      <c r="T45" s="50"/>
+      <c r="T45" s="47"/>
       <c r="U45" s="54"/>
       <c r="V45" s="57"/>
-      <c r="W45" s="53" t="str">
+      <c r="W45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,E45," ")</f>
         <v> </v>
       </c>
-      <c r="X45" s="53" t="str">
+      <c r="X45" s="50" t="str">
         <f aca="false">IF(V45&gt;0,J45," ")</f>
         <v> </v>
       </c>
-      <c r="Y45" s="50" t="str">
+      <c r="Y45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&lt;S45,(S45-V45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z45" s="50" t="str">
+      <c r="Z45" s="47" t="str">
         <f aca="false">IF((U45+V45)&gt;0,IF(V45&gt;S45,(V45-S45)*(1-M45)," ")," ")</f>
         <v> </v>
       </c>
@@ -3914,7 +3913,7 @@
       <c r="D46" s="56"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
-      <c r="G46" s="53" t="str">
+      <c r="G46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,E46-F46," ")</f>
         <v> </v>
       </c>
@@ -3922,50 +3921,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I46" s="53" t="str">
+      <c r="I46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,MIN(E46*H46,G46)," ")</f>
         <v> </v>
       </c>
-      <c r="J46" s="53" t="str">
+      <c r="J46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,F46+I46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="53" t="str">
+      <c r="K46" s="50" t="str">
         <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
         <v> </v>
       </c>
-      <c r="L46" s="53"/>
-      <c r="M46" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="53"/>
-      <c r="O46" s="68"/>
-      <c r="P46" s="51"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50" t="str">
+      <c r="L46" s="50"/>
+      <c r="M46" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="50"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="47"/>
+      <c r="R46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,MIN(O46*R$4/100*(1-M46),3000*(1-M46))," ")</f>
         <v> </v>
       </c>
-      <c r="S46" s="50" t="str">
+      <c r="S46" s="47" t="str">
         <f aca="false">IF(O46&gt;0,O46-R46," ")</f>
         <v> </v>
       </c>
-      <c r="T46" s="50"/>
+      <c r="T46" s="47"/>
       <c r="U46" s="54"/>
       <c r="V46" s="57"/>
-      <c r="W46" s="53" t="str">
+      <c r="W46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,E46," ")</f>
         <v> </v>
       </c>
-      <c r="X46" s="53" t="str">
+      <c r="X46" s="50" t="str">
         <f aca="false">IF(V46&gt;0,J46," ")</f>
         <v> </v>
       </c>
-      <c r="Y46" s="50" t="str">
+      <c r="Y46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&lt;S46,(S46-V46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z46" s="50" t="str">
+      <c r="Z46" s="47" t="str">
         <f aca="false">IF((U46+V46)&gt;0,IF(V46&gt;S46,(V46-S46)*(1-M46)," ")," ")</f>
         <v> </v>
       </c>
@@ -3978,7 +3977,7 @@
       <c r="D47" s="56"/>
       <c r="E47" s="57"/>
       <c r="F47" s="57"/>
-      <c r="G47" s="53" t="str">
+      <c r="G47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,E47-F47," ")</f>
         <v> </v>
       </c>
@@ -3986,50 +3985,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I47" s="53" t="str">
+      <c r="I47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,MIN(E47*H47,G47)," ")</f>
         <v> </v>
       </c>
-      <c r="J47" s="53" t="str">
+      <c r="J47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,F47+I47," ")</f>
         <v> </v>
       </c>
-      <c r="K47" s="53" t="str">
+      <c r="K47" s="50" t="str">
         <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
         <v> </v>
       </c>
-      <c r="L47" s="53"/>
-      <c r="M47" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="53"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="51"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50" t="str">
+      <c r="L47" s="50"/>
+      <c r="M47" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="50"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="48"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,MIN(O47*R$4/100*(1-M47),3000*(1-M47))," ")</f>
         <v> </v>
       </c>
-      <c r="S47" s="50" t="str">
+      <c r="S47" s="47" t="str">
         <f aca="false">IF(O47&gt;0,O47-R47," ")</f>
         <v> </v>
       </c>
-      <c r="T47" s="50"/>
+      <c r="T47" s="47"/>
       <c r="U47" s="54"/>
       <c r="V47" s="57"/>
-      <c r="W47" s="53" t="str">
+      <c r="W47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,E47," ")</f>
         <v> </v>
       </c>
-      <c r="X47" s="53" t="str">
+      <c r="X47" s="50" t="str">
         <f aca="false">IF(V47&gt;0,J47," ")</f>
         <v> </v>
       </c>
-      <c r="Y47" s="50" t="str">
+      <c r="Y47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&lt;S47,(S47-V47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z47" s="50" t="str">
+      <c r="Z47" s="47" t="str">
         <f aca="false">IF((U47+V47)&gt;0,IF(V47&gt;S47,(V47-S47)*(1-M47)," ")," ")</f>
         <v> </v>
       </c>
@@ -4042,7 +4041,7 @@
       <c r="D48" s="56"/>
       <c r="E48" s="57"/>
       <c r="F48" s="57"/>
-      <c r="G48" s="53" t="str">
+      <c r="G48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,E48-F48," ")</f>
         <v> </v>
       </c>
@@ -4050,50 +4049,50 @@
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I48" s="53" t="str">
+      <c r="I48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,MIN(E48*H48,G48)," ")</f>
         <v> </v>
       </c>
-      <c r="J48" s="53" t="str">
+      <c r="J48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,F48+I48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="53" t="str">
+      <c r="K48" s="50" t="str">
         <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
         <v> </v>
       </c>
-      <c r="L48" s="53"/>
-      <c r="M48" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="53"/>
-      <c r="O48" s="68"/>
-      <c r="P48" s="51"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50" t="str">
+      <c r="L48" s="50"/>
+      <c r="M48" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="50"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="48"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,MIN(O48*R$4/100*(1-M48),3000*(1-M48))," ")</f>
         <v> </v>
       </c>
-      <c r="S48" s="50" t="str">
+      <c r="S48" s="47" t="str">
         <f aca="false">IF(O48&gt;0,O48-R48," ")</f>
         <v> </v>
       </c>
-      <c r="T48" s="50"/>
+      <c r="T48" s="47"/>
       <c r="U48" s="54"/>
       <c r="V48" s="57"/>
-      <c r="W48" s="53" t="str">
+      <c r="W48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,E48," ")</f>
         <v> </v>
       </c>
-      <c r="X48" s="53" t="str">
+      <c r="X48" s="50" t="str">
         <f aca="false">IF(V48&gt;0,J48," ")</f>
         <v> </v>
       </c>
-      <c r="Y48" s="50" t="str">
+      <c r="Y48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&lt;S48,(S48-V48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z48" s="50" t="str">
+      <c r="Z48" s="47" t="str">
         <f aca="false">IF((U48+V48)&gt;0,IF(V48&gt;S48,(V48-S48)*(1-M48)," ")," ")</f>
         <v> </v>
       </c>
@@ -4101,33 +4100,33 @@
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
-      <c r="B49" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="C49" s="66"/>
+      <c r="B49" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="51"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
       <c r="H49" s="58"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="50"/>
+      <c r="L49" s="50"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="51"/>
-      <c r="Q49" s="50"/>
-      <c r="R49" s="50"/>
-      <c r="S49" s="50"/>
-      <c r="T49" s="50"/>
-      <c r="U49" s="52"/>
-      <c r="V49" s="53"/>
-      <c r="W49" s="53"/>
-      <c r="X49" s="53"/>
-      <c r="Y49" s="50"/>
-      <c r="Z49" s="50"/>
+      <c r="N49" s="50"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="47"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="47"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="50"/>
+      <c r="W49" s="50"/>
+      <c r="X49" s="50"/>
+      <c r="Y49" s="47"/>
+      <c r="Z49" s="47"/>
       <c r="AA49" s="25"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4137,58 +4136,55 @@
       <c r="D50" s="56"/>
       <c r="E50" s="57"/>
       <c r="F50" s="57"/>
-      <c r="G50" s="53" t="str">
-        <f aca="false">IF(E50&gt;0,E50-F50," ")</f>
-        <v> </v>
-      </c>
+      <c r="G50" s="50"/>
       <c r="H50" s="58" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I50" s="53" t="str">
+      <c r="I50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,MIN(E50*H50,G50)," ")</f>
         <v> </v>
       </c>
-      <c r="J50" s="53" t="str">
+      <c r="J50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,F50+I50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="53" t="str">
+      <c r="K50" s="50" t="str">
         <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
         <v> </v>
       </c>
-      <c r="L50" s="53"/>
-      <c r="M50" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="53"/>
-      <c r="O50" s="68"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="50"/>
-      <c r="R50" s="50" t="str">
+      <c r="L50" s="50"/>
+      <c r="M50" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="50"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,IF(O50&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M50),O50*R$4/100)*(1-M50)," ")</f>
         <v> </v>
       </c>
-      <c r="S50" s="50" t="str">
+      <c r="S50" s="47" t="str">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
         <v> </v>
       </c>
-      <c r="T50" s="50"/>
+      <c r="T50" s="47"/>
       <c r="U50" s="54"/>
       <c r="V50" s="57"/>
-      <c r="W50" s="53" t="str">
+      <c r="W50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,E50," ")</f>
         <v> </v>
       </c>
-      <c r="X50" s="53" t="str">
+      <c r="X50" s="50" t="str">
         <f aca="false">IF(V50&gt;0,J50," ")</f>
         <v> </v>
       </c>
-      <c r="Y50" s="50" t="str">
+      <c r="Y50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z50" s="50" t="str">
+      <c r="Z50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
         <v> </v>
       </c>
@@ -4201,58 +4197,55 @@
       <c r="D51" s="56"/>
       <c r="E51" s="57"/>
       <c r="F51" s="57"/>
-      <c r="G51" s="53" t="str">
-        <f aca="false">IF(E51&gt;0,E51-F51," ")</f>
-        <v> </v>
-      </c>
+      <c r="G51" s="50"/>
       <c r="H51" s="58" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I51" s="53" t="str">
+      <c r="I51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,MIN(E51*H51,G51)," ")</f>
         <v> </v>
       </c>
-      <c r="J51" s="53" t="str">
+      <c r="J51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,F51+I51," ")</f>
         <v> </v>
       </c>
-      <c r="K51" s="53" t="str">
+      <c r="K51" s="50" t="str">
         <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
         <v> </v>
       </c>
-      <c r="L51" s="53"/>
-      <c r="M51" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="53"/>
-      <c r="O51" s="68"/>
-      <c r="P51" s="51"/>
-      <c r="Q51" s="50"/>
-      <c r="R51" s="50" t="str">
+      <c r="L51" s="50"/>
+      <c r="M51" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="50"/>
+      <c r="O51" s="67"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,IF(O51&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M51),O51*R$4/100)*(1-M51)," ")</f>
         <v> </v>
       </c>
-      <c r="S51" s="50" t="str">
+      <c r="S51" s="47" t="str">
         <f aca="false">IF(O51&gt;0,O51-R51," ")</f>
         <v> </v>
       </c>
-      <c r="T51" s="50"/>
+      <c r="T51" s="47"/>
       <c r="U51" s="54"/>
       <c r="V51" s="57"/>
-      <c r="W51" s="53" t="str">
+      <c r="W51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,E51," ")</f>
         <v> </v>
       </c>
-      <c r="X51" s="53" t="str">
+      <c r="X51" s="50" t="str">
         <f aca="false">IF(V51&gt;0,J51," ")</f>
         <v> </v>
       </c>
-      <c r="Y51" s="50" t="str">
+      <c r="Y51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&lt;S51,(S51-V51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z51" s="50" t="str">
+      <c r="Z51" s="47" t="str">
         <f aca="false">IF((U51+V51)&gt;0,IF(V51&gt;S51,(V51-S51)*(1-M51)," ")," ")</f>
         <v> </v>
       </c>
@@ -4265,58 +4258,55 @@
       <c r="D52" s="56"/>
       <c r="E52" s="57"/>
       <c r="F52" s="57"/>
-      <c r="G52" s="53" t="str">
-        <f aca="false">IF(E52&gt;0,E52-F52," ")</f>
-        <v> </v>
-      </c>
+      <c r="G52" s="50"/>
       <c r="H52" s="58" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I52" s="53" t="str">
+      <c r="I52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,MIN(E52*H52,G52)," ")</f>
         <v> </v>
       </c>
-      <c r="J52" s="53" t="str">
+      <c r="J52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,F52+I52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="53" t="str">
+      <c r="K52" s="50" t="str">
         <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
         <v> </v>
       </c>
-      <c r="L52" s="53"/>
-      <c r="M52" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="53"/>
-      <c r="O52" s="68"/>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="50"/>
-      <c r="R52" s="50" t="str">
+      <c r="L52" s="50"/>
+      <c r="M52" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="50"/>
+      <c r="O52" s="67"/>
+      <c r="P52" s="48"/>
+      <c r="Q52" s="47"/>
+      <c r="R52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,IF(O52&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M52),O52*R$4/100)*(1-M52)," ")</f>
         <v> </v>
       </c>
-      <c r="S52" s="50" t="str">
+      <c r="S52" s="47" t="str">
         <f aca="false">IF(O52&gt;0,O52-R52," ")</f>
         <v> </v>
       </c>
-      <c r="T52" s="50"/>
+      <c r="T52" s="47"/>
       <c r="U52" s="54"/>
       <c r="V52" s="57"/>
-      <c r="W52" s="53" t="str">
+      <c r="W52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,E52," ")</f>
         <v> </v>
       </c>
-      <c r="X52" s="53" t="str">
+      <c r="X52" s="50" t="str">
         <f aca="false">IF(V52&gt;0,J52," ")</f>
         <v> </v>
       </c>
-      <c r="Y52" s="50" t="str">
+      <c r="Y52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&lt;S52,(S52-V52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z52" s="50" t="str">
+      <c r="Z52" s="47" t="str">
         <f aca="false">IF((U52+V52)&gt;0,IF(V52&gt;S52,(V52-S52)*(1-M52)," ")," ")</f>
         <v> </v>
       </c>
@@ -4329,58 +4319,55 @@
       <c r="D53" s="56"/>
       <c r="E53" s="57"/>
       <c r="F53" s="57"/>
-      <c r="G53" s="53" t="str">
-        <f aca="false">IF(E53&gt;0,E53-F53," ")</f>
-        <v> </v>
-      </c>
+      <c r="G53" s="50"/>
       <c r="H53" s="58" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I53" s="53" t="str">
+      <c r="I53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,MIN(E53*H53,G53)," ")</f>
         <v> </v>
       </c>
-      <c r="J53" s="53" t="str">
+      <c r="J53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,F53+I53," ")</f>
         <v> </v>
       </c>
-      <c r="K53" s="53" t="str">
+      <c r="K53" s="50" t="str">
         <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
         <v> </v>
       </c>
-      <c r="L53" s="53"/>
-      <c r="M53" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="53"/>
-      <c r="O53" s="68"/>
-      <c r="P53" s="51"/>
-      <c r="Q53" s="50"/>
-      <c r="R53" s="50" t="str">
+      <c r="L53" s="50"/>
+      <c r="M53" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="50"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="47"/>
+      <c r="R53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,IF(O53&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M53),O53*R$4/100)*(1-M53)," ")</f>
         <v> </v>
       </c>
-      <c r="S53" s="50" t="str">
+      <c r="S53" s="47" t="str">
         <f aca="false">IF(O53&gt;0,O53-R53," ")</f>
         <v> </v>
       </c>
-      <c r="T53" s="50"/>
+      <c r="T53" s="47"/>
       <c r="U53" s="54"/>
       <c r="V53" s="57"/>
-      <c r="W53" s="53" t="str">
+      <c r="W53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,E53," ")</f>
         <v> </v>
       </c>
-      <c r="X53" s="53" t="str">
+      <c r="X53" s="50" t="str">
         <f aca="false">IF(V53&gt;0,J53," ")</f>
         <v> </v>
       </c>
-      <c r="Y53" s="50" t="str">
+      <c r="Y53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&lt;S53,(S53-V53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z53" s="50" t="str">
+      <c r="Z53" s="47" t="str">
         <f aca="false">IF((U53+V53)&gt;0,IF(V53&gt;S53,(V53-S53)*(1-M53)," ")," ")</f>
         <v> </v>
       </c>
@@ -4393,58 +4380,55 @@
       <c r="D54" s="56"/>
       <c r="E54" s="57"/>
       <c r="F54" s="57"/>
-      <c r="G54" s="53" t="str">
-        <f aca="false">IF(E54&gt;0,E54-F54," ")</f>
-        <v> </v>
-      </c>
+      <c r="G54" s="50"/>
       <c r="H54" s="58" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I54" s="53" t="str">
+      <c r="I54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,MIN(E54*H54,G54)," ")</f>
         <v> </v>
       </c>
-      <c r="J54" s="53" t="str">
+      <c r="J54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,F54+I54," ")</f>
         <v> </v>
       </c>
-      <c r="K54" s="53" t="str">
+      <c r="K54" s="50" t="str">
         <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
         <v> </v>
       </c>
-      <c r="L54" s="53"/>
-      <c r="M54" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="53"/>
-      <c r="O54" s="68"/>
-      <c r="P54" s="51"/>
-      <c r="Q54" s="50"/>
-      <c r="R54" s="50" t="str">
+      <c r="L54" s="50"/>
+      <c r="M54" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="50"/>
+      <c r="O54" s="67"/>
+      <c r="P54" s="48"/>
+      <c r="Q54" s="47"/>
+      <c r="R54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,IF(O54&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M54),O54*R$4/100)*(1-M54)," ")</f>
         <v> </v>
       </c>
-      <c r="S54" s="50" t="str">
+      <c r="S54" s="47" t="str">
         <f aca="false">IF(O54&gt;0,O54-R54," ")</f>
         <v> </v>
       </c>
-      <c r="T54" s="50"/>
+      <c r="T54" s="47"/>
       <c r="U54" s="54"/>
       <c r="V54" s="57"/>
-      <c r="W54" s="53" t="str">
+      <c r="W54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,E54," ")</f>
         <v> </v>
       </c>
-      <c r="X54" s="53" t="str">
+      <c r="X54" s="50" t="str">
         <f aca="false">IF(V54&gt;0,J54," ")</f>
         <v> </v>
       </c>
-      <c r="Y54" s="50" t="str">
+      <c r="Y54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&lt;S54,(S54-V54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z54" s="50" t="str">
+      <c r="Z54" s="47" t="str">
         <f aca="false">IF((U54+V54)&gt;0,IF(V54&gt;S54,(V54-S54)*(1-M54)," ")," ")</f>
         <v> </v>
       </c>
@@ -4454,7 +4438,7 @@
       <c r="A55" s="42"/>
       <c r="B55" s="59" t="str">
         <f aca="false">IF((E55-F55)=([1]OpenAccounts!$K$13-[1]OpenAccounts!$Q$13),"Existing Motor Vehicles","Check Opening Balance Sheet figures agree")</f>
-        <v>Existing Motor Vehicles</v>
+        <v>Check Opening Balance Sheet figures agree</v>
       </c>
       <c r="C55" s="59"/>
       <c r="D55" s="59"/>
@@ -4464,7 +4448,7 @@
       </c>
       <c r="F55" s="60" t="n">
         <f aca="false">SUM(F44:F54)</f>
-        <v>0</v>
+        <v>9828</v>
       </c>
       <c r="G55" s="61" t="n">
         <f aca="false">SUM(G44:G54)</f>
@@ -4483,9 +4467,9 @@
         <f aca="false">SUM(K44:K54)</f>
         <v>0</v>
       </c>
-      <c r="L55" s="53"/>
-      <c r="M55" s="70"/>
-      <c r="N55" s="53"/>
+      <c r="L55" s="50"/>
+      <c r="M55" s="69"/>
+      <c r="N55" s="50"/>
       <c r="O55" s="61" t="n">
         <f aca="false">SUM(O44:O54)</f>
         <v>0</v>
@@ -4503,8 +4487,8 @@
         <f aca="false">SUM(S44:S54)</f>
         <v>0</v>
       </c>
-      <c r="T55" s="53"/>
-      <c r="U55" s="52"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="49"/>
       <c r="V55" s="60" t="n">
         <f aca="false">SUM(V44:V54)</f>
         <v>0</v>
@@ -4529,31 +4513,31 @@
     </row>
     <row r="56" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="42"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="72"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="71"/>
       <c r="D56" s="62"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
       <c r="H56" s="58"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="50"/>
+      <c r="K56" s="50"/>
+      <c r="L56" s="50"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="50"/>
-      <c r="P56" s="51"/>
-      <c r="Q56" s="50"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="50"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="52"/>
-      <c r="V56" s="53"/>
-      <c r="W56" s="50"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="50"/>
-      <c r="Z56" s="50"/>
+      <c r="N56" s="50"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="48"/>
+      <c r="Q56" s="47"/>
+      <c r="R56" s="47"/>
+      <c r="S56" s="47"/>
+      <c r="T56" s="47"/>
+      <c r="U56" s="49"/>
+      <c r="V56" s="50"/>
+      <c r="W56" s="47"/>
+      <c r="X56" s="47"/>
+      <c r="Y56" s="47"/>
+      <c r="Z56" s="47"/>
       <c r="AA56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4563,74 +4547,74 @@
         <v>EXISTING FIXED ASSETS AT </v>
       </c>
       <c r="C57" s="43"/>
-      <c r="D57" s="73" t="str">
+      <c r="D57" s="72" t="n">
         <f aca="false">D6</f>
-        <v>Laptop (0.5 years old)</v>
-      </c>
-      <c r="E57" s="74" t="n">
+        <v>45748</v>
+      </c>
+      <c r="E57" s="73" t="n">
         <f aca="false">E11+E22+E30+E41+E55</f>
         <v>0</v>
       </c>
-      <c r="F57" s="74" t="n">
+      <c r="F57" s="73" t="n">
         <f aca="false">F11+F22+F30+F41+F55</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="74" t="n">
+        <v>10098</v>
+      </c>
+      <c r="G57" s="73" t="n">
         <f aca="false">G11+G22+G30+G41+G55</f>
         <v>0</v>
       </c>
       <c r="H57" s="58"/>
-      <c r="I57" s="74" t="n">
+      <c r="I57" s="73" t="n">
         <f aca="false">I11+I22+I30+I41+I55</f>
         <v>0</v>
       </c>
-      <c r="J57" s="74" t="n">
+      <c r="J57" s="73" t="n">
         <f aca="false">J11+J22+J30+J41+J55</f>
         <v>0</v>
       </c>
-      <c r="K57" s="74" t="n">
+      <c r="K57" s="73" t="n">
         <f aca="false">K11+K22+K30+K41+K55</f>
         <v>0</v>
       </c>
-      <c r="L57" s="53"/>
+      <c r="L57" s="50"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="74" t="n">
+      <c r="N57" s="50"/>
+      <c r="O57" s="73" t="n">
         <f aca="false">O11+O22+O30+O41+O55</f>
         <v>0</v>
       </c>
       <c r="P57" s="62"/>
-      <c r="Q57" s="74" t="n">
+      <c r="Q57" s="73" t="n">
         <f aca="false">Q11+Q22+Q30+Q41+Q55</f>
         <v>0</v>
       </c>
-      <c r="R57" s="74" t="n">
+      <c r="R57" s="73" t="n">
         <f aca="false">R11+R22+R30+R41+R55</f>
         <v>0</v>
       </c>
-      <c r="S57" s="74" t="n">
+      <c r="S57" s="73" t="n">
         <f aca="false">S11+S22+S30+S41+S55</f>
         <v>0</v>
       </c>
-      <c r="T57" s="50"/>
-      <c r="U57" s="52"/>
-      <c r="V57" s="74" t="n">
+      <c r="T57" s="47"/>
+      <c r="U57" s="49"/>
+      <c r="V57" s="73" t="n">
         <f aca="false">V11+V22+V30+V41+V55</f>
         <v>0</v>
       </c>
-      <c r="W57" s="74" t="n">
+      <c r="W57" s="73" t="n">
         <f aca="false">W11+W22+W30+W41+W55</f>
         <v>0</v>
       </c>
-      <c r="X57" s="74" t="n">
+      <c r="X57" s="73" t="n">
         <f aca="false">X11+X22+X30+X41+X55</f>
         <v>0</v>
       </c>
-      <c r="Y57" s="74" t="n">
+      <c r="Y57" s="73" t="n">
         <f aca="false">Y11+Y22+Y30+Y41+Y55</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="74" t="n">
+      <c r="Z57" s="73" t="n">
         <f aca="false">Z11+Z22+Z30+Z41+Z55</f>
         <v>0</v>
       </c>
@@ -4638,251 +4622,251 @@
     </row>
     <row r="58" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="42"/>
-      <c r="B58" s="75"/>
-      <c r="C58" s="76"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="58"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="53"/>
-      <c r="K58" s="53"/>
-      <c r="L58" s="53"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="50"/>
+      <c r="K58" s="50"/>
+      <c r="L58" s="50"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="53"/>
-      <c r="O58" s="50"/>
-      <c r="P58" s="51"/>
-      <c r="Q58" s="50"/>
-      <c r="R58" s="50"/>
-      <c r="S58" s="50"/>
-      <c r="T58" s="50"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="53"/>
-      <c r="W58" s="53"/>
-      <c r="X58" s="53"/>
-      <c r="Y58" s="50"/>
-      <c r="Z58" s="50"/>
+      <c r="N58" s="50"/>
+      <c r="O58" s="47"/>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="47"/>
+      <c r="R58" s="47"/>
+      <c r="S58" s="47"/>
+      <c r="T58" s="47"/>
+      <c r="U58" s="49"/>
+      <c r="V58" s="50"/>
+      <c r="W58" s="50"/>
+      <c r="X58" s="50"/>
+      <c r="Y58" s="47"/>
+      <c r="Z58" s="47"/>
       <c r="AA58" s="25"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
-      <c r="B59" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" s="78"/>
-      <c r="D59" s="79" t="str">
+      <c r="B59" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="77"/>
+      <c r="D59" s="78" t="n">
         <f aca="false">D57</f>
-        <v>Laptop (0.5 years old)</v>
-      </c>
-      <c r="E59" s="80" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" s="81" t="n">
+        <v>45748</v>
+      </c>
+      <c r="E59" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="F59" s="80" t="n">
         <f aca="false">J4</f>
         <v>46477</v>
       </c>
-      <c r="G59" s="82"/>
+      <c r="G59" s="81"/>
       <c r="H59" s="58"/>
-      <c r="I59" s="50"/>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="50"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="47"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="50"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="51"/>
-      <c r="Q59" s="50"/>
-      <c r="R59" s="50"/>
-      <c r="S59" s="50"/>
-      <c r="T59" s="50"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="53"/>
-      <c r="W59" s="53"/>
-      <c r="X59" s="53"/>
-      <c r="Y59" s="50"/>
-      <c r="Z59" s="50"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="47"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="47"/>
+      <c r="R59" s="47"/>
+      <c r="S59" s="47"/>
+      <c r="T59" s="47"/>
+      <c r="U59" s="49"/>
+      <c r="V59" s="50"/>
+      <c r="W59" s="50"/>
+      <c r="X59" s="50"/>
+      <c r="Y59" s="47"/>
+      <c r="Z59" s="47"/>
       <c r="AA59" s="25"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="42"/>
-      <c r="B60" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="C60" s="66"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="82"/>
-      <c r="G60" s="82"/>
-      <c r="H60" s="83" t="n">
+      <c r="B60" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="51"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="45"/>
+      <c r="F60" s="81"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="82" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I60" s="47"/>
-      <c r="J60" s="47"/>
-      <c r="K60" s="47"/>
-      <c r="L60" s="47"/>
+      <c r="I60" s="45"/>
+      <c r="J60" s="45"/>
+      <c r="K60" s="45"/>
+      <c r="L60" s="45"/>
       <c r="M60" s="58"/>
-      <c r="N60" s="47"/>
-      <c r="O60" s="50"/>
-      <c r="P60" s="51"/>
-      <c r="Q60" s="50"/>
-      <c r="R60" s="50"/>
-      <c r="S60" s="50"/>
-      <c r="T60" s="50"/>
-      <c r="U60" s="52"/>
-      <c r="V60" s="53"/>
-      <c r="W60" s="53"/>
-      <c r="X60" s="53"/>
-      <c r="Y60" s="50"/>
-      <c r="Z60" s="50"/>
+      <c r="N60" s="45"/>
+      <c r="O60" s="47"/>
+      <c r="P60" s="48"/>
+      <c r="Q60" s="47"/>
+      <c r="R60" s="47"/>
+      <c r="S60" s="47"/>
+      <c r="T60" s="47"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="50"/>
+      <c r="W60" s="50"/>
+      <c r="X60" s="50"/>
+      <c r="Y60" s="47"/>
+      <c r="Z60" s="47"/>
       <c r="AA60" s="25"/>
     </row>
     <row r="61" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="42"/>
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
-      <c r="D61" s="84"/>
+      <c r="D61" s="83"/>
       <c r="E61" s="57"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
+      <c r="F61" s="50"/>
+      <c r="G61" s="50"/>
       <c r="H61" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I61" s="53" t="str">
+      <c r="I61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,MIN(E61*H61,G61)," ")</f>
         <v> </v>
       </c>
-      <c r="J61" s="53" t="str">
+      <c r="J61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,F61+I61," ")</f>
         <v> </v>
       </c>
-      <c r="K61" s="53" t="str">
+      <c r="K61" s="50" t="str">
         <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
         <v> </v>
       </c>
-      <c r="L61" s="53"/>
+      <c r="L61" s="50"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="53"/>
-      <c r="O61" s="50"/>
-      <c r="P61" s="51"/>
-      <c r="Q61" s="50"/>
-      <c r="R61" s="50"/>
-      <c r="S61" s="50"/>
-      <c r="T61" s="50"/>
+      <c r="N61" s="50"/>
+      <c r="O61" s="47"/>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="47"/>
+      <c r="R61" s="47"/>
+      <c r="S61" s="47"/>
+      <c r="T61" s="47"/>
       <c r="U61" s="54"/>
       <c r="V61" s="57"/>
-      <c r="W61" s="53" t="str">
+      <c r="W61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,E61," ")</f>
         <v> </v>
       </c>
-      <c r="X61" s="53" t="str">
+      <c r="X61" s="50" t="str">
         <f aca="false">IF(V61&gt;0,J61," ")</f>
         <v> </v>
       </c>
-      <c r="Y61" s="50"/>
-      <c r="Z61" s="50"/>
+      <c r="Y61" s="47"/>
+      <c r="Z61" s="47"/>
       <c r="AA61" s="25"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
-      <c r="D62" s="84"/>
+      <c r="D62" s="83"/>
       <c r="E62" s="57"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="53"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="50"/>
       <c r="H62" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I62" s="53" t="str">
+      <c r="I62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,MIN(E62*H62,G62)," ")</f>
         <v> </v>
       </c>
-      <c r="J62" s="53" t="str">
+      <c r="J62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,F62+I62," ")</f>
         <v> </v>
       </c>
-      <c r="K62" s="53" t="str">
+      <c r="K62" s="50" t="str">
         <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
         <v> </v>
       </c>
-      <c r="L62" s="53"/>
+      <c r="L62" s="50"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="53"/>
-      <c r="O62" s="50"/>
-      <c r="P62" s="51"/>
-      <c r="Q62" s="50"/>
-      <c r="R62" s="50"/>
-      <c r="S62" s="50"/>
-      <c r="T62" s="50"/>
+      <c r="N62" s="50"/>
+      <c r="O62" s="47"/>
+      <c r="P62" s="48"/>
+      <c r="Q62" s="47"/>
+      <c r="R62" s="47"/>
+      <c r="S62" s="47"/>
+      <c r="T62" s="47"/>
       <c r="U62" s="54"/>
       <c r="V62" s="57"/>
-      <c r="W62" s="53" t="str">
+      <c r="W62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,E62," ")</f>
         <v> </v>
       </c>
-      <c r="X62" s="53" t="str">
+      <c r="X62" s="50" t="str">
         <f aca="false">IF(V62&gt;0,J62," ")</f>
         <v> </v>
       </c>
-      <c r="Y62" s="50"/>
-      <c r="Z62" s="50"/>
+      <c r="Y62" s="47"/>
+      <c r="Z62" s="47"/>
       <c r="AA62" s="25"/>
     </row>
     <row r="63" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="42"/>
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
-      <c r="D63" s="84"/>
+      <c r="D63" s="83"/>
       <c r="E63" s="57"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
       <c r="H63" s="58" t="n">
         <f aca="false">H$60</f>
         <v>0</v>
       </c>
-      <c r="I63" s="53" t="str">
+      <c r="I63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,MIN(E63*H63,G63)," ")</f>
         <v> </v>
       </c>
-      <c r="J63" s="53" t="str">
+      <c r="J63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,F63+I63," ")</f>
         <v> </v>
       </c>
-      <c r="K63" s="53" t="str">
+      <c r="K63" s="50" t="str">
         <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
         <v> </v>
       </c>
-      <c r="L63" s="53"/>
+      <c r="L63" s="50"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="53"/>
-      <c r="O63" s="50"/>
-      <c r="P63" s="51"/>
-      <c r="Q63" s="50"/>
-      <c r="R63" s="50"/>
-      <c r="S63" s="50"/>
-      <c r="T63" s="50"/>
+      <c r="N63" s="50"/>
+      <c r="O63" s="47"/>
+      <c r="P63" s="48"/>
+      <c r="Q63" s="47"/>
+      <c r="R63" s="47"/>
+      <c r="S63" s="47"/>
+      <c r="T63" s="47"/>
       <c r="U63" s="54"/>
       <c r="V63" s="57"/>
-      <c r="W63" s="53" t="str">
+      <c r="W63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,E63," ")</f>
         <v> </v>
       </c>
-      <c r="X63" s="53" t="str">
+      <c r="X63" s="50" t="str">
         <f aca="false">IF(V63&gt;0,J63," ")</f>
         <v> </v>
       </c>
-      <c r="Y63" s="50"/>
-      <c r="Z63" s="50"/>
+      <c r="Y63" s="47"/>
+      <c r="Z63" s="47"/>
       <c r="AA63" s="25"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -4911,14 +4895,14 @@
         <f aca="false">SUM(K61:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="53"/>
+      <c r="L64" s="50"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="53"/>
+      <c r="N64" s="50"/>
       <c r="O64" s="61" t="n">
         <f aca="false">SUM(O61:O63)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="85"/>
+      <c r="P64" s="84"/>
       <c r="Q64" s="61" t="n">
         <f aca="false">SUM(Q61:Q63)</f>
         <v>0</v>
@@ -4931,8 +4915,8 @@
         <f aca="false">SUM(S61:S63)</f>
         <v>0</v>
       </c>
-      <c r="T64" s="50"/>
-      <c r="U64" s="52"/>
+      <c r="T64" s="47"/>
+      <c r="U64" s="49"/>
       <c r="V64" s="60" t="n">
         <f aca="false">SUM(V61:V63)</f>
         <v>0</v>
@@ -4960,62 +4944,62 @@
       <c r="B65" s="63"/>
       <c r="C65" s="64"/>
       <c r="D65" s="65"/>
-      <c r="E65" s="53"/>
-      <c r="F65" s="53"/>
-      <c r="G65" s="53"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
       <c r="H65" s="58"/>
-      <c r="I65" s="53"/>
-      <c r="J65" s="53"/>
-      <c r="K65" s="53"/>
-      <c r="L65" s="53"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="50"/>
+      <c r="K65" s="50"/>
+      <c r="L65" s="50"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="53"/>
-      <c r="O65" s="53"/>
+      <c r="N65" s="50"/>
+      <c r="O65" s="50"/>
       <c r="P65" s="62"/>
-      <c r="Q65" s="53"/>
-      <c r="R65" s="53"/>
-      <c r="S65" s="53"/>
-      <c r="T65" s="50"/>
-      <c r="U65" s="52"/>
-      <c r="V65" s="53"/>
-      <c r="W65" s="53"/>
-      <c r="X65" s="53"/>
-      <c r="Y65" s="53"/>
-      <c r="Z65" s="53"/>
+      <c r="Q65" s="50"/>
+      <c r="R65" s="50"/>
+      <c r="S65" s="50"/>
+      <c r="T65" s="47"/>
+      <c r="U65" s="49"/>
+      <c r="V65" s="50"/>
+      <c r="W65" s="50"/>
+      <c r="X65" s="50"/>
+      <c r="Y65" s="50"/>
+      <c r="Z65" s="50"/>
       <c r="AA65" s="25"/>
     </row>
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
-      <c r="B66" s="66" t="s">
+      <c r="B66" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="66"/>
+      <c r="C66" s="51"/>
       <c r="D66" s="62"/>
-      <c r="E66" s="53"/>
-      <c r="F66" s="53"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="86" t="n">
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="85" t="n">
         <f aca="false">H$13</f>
         <v>0.1</v>
       </c>
-      <c r="I66" s="53"/>
-      <c r="J66" s="53"/>
-      <c r="K66" s="53"/>
-      <c r="L66" s="53"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="50"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="50"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="53"/>
-      <c r="O66" s="50"/>
-      <c r="P66" s="51"/>
-      <c r="Q66" s="50"/>
-      <c r="R66" s="50"/>
-      <c r="S66" s="50"/>
-      <c r="T66" s="50"/>
-      <c r="U66" s="52"/>
-      <c r="V66" s="53"/>
-      <c r="W66" s="53"/>
-      <c r="X66" s="53"/>
-      <c r="Y66" s="50"/>
-      <c r="Z66" s="50"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="47"/>
+      <c r="S66" s="47"/>
+      <c r="T66" s="47"/>
+      <c r="U66" s="49"/>
+      <c r="V66" s="50"/>
+      <c r="W66" s="50"/>
+      <c r="X66" s="50"/>
+      <c r="Y66" s="47"/>
+      <c r="Z66" s="47"/>
       <c r="AA66" s="25"/>
     </row>
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5024,57 +5008,57 @@
       <c r="C67" s="55"/>
       <c r="D67" s="56"/>
       <c r="E67" s="57"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
       <c r="H67" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I67" s="53" t="str">
+      <c r="I67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,MIN(E67*H67,G67)," ")</f>
         <v> </v>
       </c>
-      <c r="J67" s="53" t="str">
+      <c r="J67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,F67+I67," ")</f>
         <v> </v>
       </c>
-      <c r="K67" s="53" t="str">
+      <c r="K67" s="50" t="str">
         <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
         <v> </v>
       </c>
-      <c r="L67" s="53"/>
+      <c r="L67" s="50"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="53"/>
-      <c r="O67" s="50"/>
-      <c r="P67" s="51" t="n">
+      <c r="N67" s="50"/>
+      <c r="O67" s="47"/>
+      <c r="P67" s="48" t="n">
         <f aca="false">IF(B67&gt;0,IF(B67&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q67" s="50" t="str">
+      <c r="Q67" s="47" t="str">
         <f aca="false">IF(E67&gt;0,E67*P67/100," ")</f>
         <v> </v>
       </c>
-      <c r="R67" s="50"/>
-      <c r="S67" s="50" t="str">
+      <c r="R67" s="47"/>
+      <c r="S67" s="47" t="str">
         <f aca="false">IF(E67&gt;0,E67-Q67," ")</f>
         <v> </v>
       </c>
-      <c r="T67" s="50"/>
+      <c r="T67" s="47"/>
       <c r="U67" s="54"/>
       <c r="V67" s="57"/>
-      <c r="W67" s="53" t="str">
+      <c r="W67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,E67," ")</f>
         <v> </v>
       </c>
-      <c r="X67" s="53" t="str">
+      <c r="X67" s="50" t="str">
         <f aca="false">IF(V67&gt;0,J67," ")</f>
         <v> </v>
       </c>
-      <c r="Y67" s="50" t="str">
+      <c r="Y67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&lt;S67,S67-V67," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z67" s="50" t="str">
+      <c r="Z67" s="47" t="str">
         <f aca="false">IF((U67+V67)&gt;0,IF(V67&gt;S67,V67-S67," ")," ")</f>
         <v> </v>
       </c>
@@ -5086,57 +5070,57 @@
       <c r="C68" s="55"/>
       <c r="D68" s="56"/>
       <c r="E68" s="57"/>
-      <c r="F68" s="53"/>
-      <c r="G68" s="53"/>
+      <c r="F68" s="50"/>
+      <c r="G68" s="50"/>
       <c r="H68" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I68" s="53" t="str">
+      <c r="I68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
         <v> </v>
       </c>
-      <c r="J68" s="53" t="str">
+      <c r="J68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
         <v> </v>
       </c>
-      <c r="K68" s="53" t="str">
+      <c r="K68" s="50" t="str">
         <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
         <v> </v>
       </c>
-      <c r="L68" s="53"/>
+      <c r="L68" s="50"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="53"/>
-      <c r="O68" s="50"/>
-      <c r="P68" s="51" t="n">
+      <c r="N68" s="50"/>
+      <c r="O68" s="47"/>
+      <c r="P68" s="48" t="n">
         <f aca="false">IF(B68&gt;0,IF(B68&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q68" s="50" t="str">
+      <c r="Q68" s="47" t="str">
         <f aca="false">IF(E68&gt;0,E68*P68/100," ")</f>
         <v> </v>
       </c>
-      <c r="R68" s="50"/>
-      <c r="S68" s="50" t="str">
+      <c r="R68" s="47"/>
+      <c r="S68" s="47" t="str">
         <f aca="false">IF(E68&gt;0,E68-Q68," ")</f>
         <v> </v>
       </c>
-      <c r="T68" s="50"/>
+      <c r="T68" s="47"/>
       <c r="U68" s="54"/>
       <c r="V68" s="57"/>
-      <c r="W68" s="53" t="str">
+      <c r="W68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,E68," ")</f>
         <v> </v>
       </c>
-      <c r="X68" s="53" t="str">
+      <c r="X68" s="50" t="str">
         <f aca="false">IF(V68&gt;0,J68," ")</f>
         <v> </v>
       </c>
-      <c r="Y68" s="50" t="str">
+      <c r="Y68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&lt;S68,S68-V68," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z68" s="50" t="str">
+      <c r="Z68" s="47" t="str">
         <f aca="false">IF((U68+V68)&gt;0,IF(V68&gt;S68,V68-S68," ")," ")</f>
         <v> </v>
       </c>
@@ -5148,57 +5132,57 @@
       <c r="C69" s="55"/>
       <c r="D69" s="56"/>
       <c r="E69" s="57"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
       <c r="H69" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I69" s="53" t="str">
+      <c r="I69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
         <v> </v>
       </c>
-      <c r="J69" s="53" t="str">
+      <c r="J69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
         <v> </v>
       </c>
-      <c r="K69" s="53" t="str">
+      <c r="K69" s="50" t="str">
         <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
         <v> </v>
       </c>
-      <c r="L69" s="53"/>
+      <c r="L69" s="50"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="53"/>
-      <c r="O69" s="50"/>
-      <c r="P69" s="51" t="n">
+      <c r="N69" s="50"/>
+      <c r="O69" s="47"/>
+      <c r="P69" s="48" t="n">
         <f aca="false">IF(B69&gt;0,IF(B69&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q69" s="50" t="str">
+      <c r="Q69" s="47" t="str">
         <f aca="false">IF(E69&gt;0,E69*P69/100," ")</f>
         <v> </v>
       </c>
-      <c r="R69" s="50"/>
-      <c r="S69" s="50" t="str">
+      <c r="R69" s="47"/>
+      <c r="S69" s="47" t="str">
         <f aca="false">IF(E69&gt;0,E69-Q69," ")</f>
         <v> </v>
       </c>
-      <c r="T69" s="50"/>
+      <c r="T69" s="47"/>
       <c r="U69" s="54"/>
       <c r="V69" s="57"/>
-      <c r="W69" s="53" t="str">
+      <c r="W69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,E69," ")</f>
         <v> </v>
       </c>
-      <c r="X69" s="53" t="str">
+      <c r="X69" s="50" t="str">
         <f aca="false">IF(V69&gt;0,J69," ")</f>
         <v> </v>
       </c>
-      <c r="Y69" s="50" t="str">
+      <c r="Y69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&lt;S69,S69-V69," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z69" s="50" t="str">
+      <c r="Z69" s="47" t="str">
         <f aca="false">IF((U69+V69)&gt;0,IF(V69&gt;S69,V69-S69," ")," ")</f>
         <v> </v>
       </c>
@@ -5210,57 +5194,57 @@
       <c r="C70" s="55"/>
       <c r="D70" s="56"/>
       <c r="E70" s="57"/>
-      <c r="F70" s="53"/>
-      <c r="G70" s="53"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="53" t="str">
+      <c r="I70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
         <v> </v>
       </c>
-      <c r="J70" s="53" t="str">
+      <c r="J70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
         <v> </v>
       </c>
-      <c r="K70" s="53" t="str">
+      <c r="K70" s="50" t="str">
         <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
         <v> </v>
       </c>
-      <c r="L70" s="53"/>
+      <c r="L70" s="50"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="53"/>
-      <c r="O70" s="50"/>
-      <c r="P70" s="51" t="n">
+      <c r="N70" s="50"/>
+      <c r="O70" s="47"/>
+      <c r="P70" s="48" t="n">
         <f aca="false">IF(B70&gt;0,IF(B70&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q70" s="50" t="str">
+      <c r="Q70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70*P70/100," ")</f>
         <v> </v>
       </c>
-      <c r="R70" s="50"/>
-      <c r="S70" s="50" t="str">
+      <c r="R70" s="47"/>
+      <c r="S70" s="47" t="str">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
         <v> </v>
       </c>
-      <c r="T70" s="50"/>
+      <c r="T70" s="47"/>
       <c r="U70" s="54"/>
       <c r="V70" s="57"/>
-      <c r="W70" s="53" t="str">
+      <c r="W70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,E70," ")</f>
         <v> </v>
       </c>
-      <c r="X70" s="53" t="str">
+      <c r="X70" s="50" t="str">
         <f aca="false">IF(V70&gt;0,J70," ")</f>
         <v> </v>
       </c>
-      <c r="Y70" s="50" t="str">
+      <c r="Y70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&lt;S70,S70-V70," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z70" s="50" t="str">
+      <c r="Z70" s="47" t="str">
         <f aca="false">IF((U70+V70)&gt;0,IF(V70&gt;S70,V70-S70," ")," ")</f>
         <v> </v>
       </c>
@@ -5272,57 +5256,57 @@
       <c r="C71" s="55"/>
       <c r="D71" s="56"/>
       <c r="E71" s="57"/>
-      <c r="F71" s="53"/>
-      <c r="G71" s="53"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="53" t="str">
+      <c r="I71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
         <v> </v>
       </c>
-      <c r="J71" s="53" t="str">
+      <c r="J71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
         <v> </v>
       </c>
-      <c r="K71" s="53" t="str">
+      <c r="K71" s="50" t="str">
         <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
         <v> </v>
       </c>
-      <c r="L71" s="53"/>
+      <c r="L71" s="50"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="53"/>
-      <c r="O71" s="50"/>
-      <c r="P71" s="51" t="n">
+      <c r="N71" s="50"/>
+      <c r="O71" s="47"/>
+      <c r="P71" s="48" t="n">
         <f aca="false">IF(B71&gt;0,IF(B71&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q71" s="50" t="str">
+      <c r="Q71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71*P71/100," ")</f>
         <v> </v>
       </c>
-      <c r="R71" s="50"/>
-      <c r="S71" s="50" t="str">
+      <c r="R71" s="47"/>
+      <c r="S71" s="47" t="str">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
         <v> </v>
       </c>
-      <c r="T71" s="50"/>
+      <c r="T71" s="47"/>
       <c r="U71" s="54"/>
       <c r="V71" s="57"/>
-      <c r="W71" s="53" t="str">
+      <c r="W71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,E71," ")</f>
         <v> </v>
       </c>
-      <c r="X71" s="53" t="str">
+      <c r="X71" s="50" t="str">
         <f aca="false">IF(V71&gt;0,J71," ")</f>
         <v> </v>
       </c>
-      <c r="Y71" s="50" t="str">
+      <c r="Y71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&lt;S71,S71-V71," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z71" s="50" t="str">
+      <c r="Z71" s="47" t="str">
         <f aca="false">IF((U71+V71)&gt;0,IF(V71&gt;S71,V71-S71," ")," ")</f>
         <v> </v>
       </c>
@@ -5334,57 +5318,57 @@
       <c r="C72" s="55"/>
       <c r="D72" s="56"/>
       <c r="E72" s="57"/>
-      <c r="F72" s="53"/>
-      <c r="G72" s="53"/>
+      <c r="F72" s="50"/>
+      <c r="G72" s="50"/>
       <c r="H72" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I72" s="53" t="str">
+      <c r="I72" s="50" t="str">
         <f aca="false">IF(E72&gt;0,MIN(E72*H72,G72)," ")</f>
         <v> </v>
       </c>
-      <c r="J72" s="53" t="str">
+      <c r="J72" s="50" t="str">
         <f aca="false">IF(E72&gt;0,F72+I72," ")</f>
         <v> </v>
       </c>
-      <c r="K72" s="53" t="str">
+      <c r="K72" s="50" t="str">
         <f aca="false">IF(E72&gt;0,E72-J72," ")</f>
         <v> </v>
       </c>
-      <c r="L72" s="53"/>
+      <c r="L72" s="50"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="53"/>
-      <c r="O72" s="50"/>
-      <c r="P72" s="51" t="n">
+      <c r="N72" s="50"/>
+      <c r="O72" s="47"/>
+      <c r="P72" s="48" t="n">
         <f aca="false">IF(B72&gt;0,IF(B72&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q72" s="50" t="str">
+      <c r="Q72" s="47" t="str">
         <f aca="false">IF(E72&gt;0,E72*P72/100," ")</f>
         <v> </v>
       </c>
-      <c r="R72" s="50"/>
-      <c r="S72" s="50" t="str">
+      <c r="R72" s="47"/>
+      <c r="S72" s="47" t="str">
         <f aca="false">IF(E72&gt;0,E72-Q72," ")</f>
         <v> </v>
       </c>
-      <c r="T72" s="50"/>
+      <c r="T72" s="47"/>
       <c r="U72" s="54"/>
       <c r="V72" s="57"/>
-      <c r="W72" s="53" t="str">
+      <c r="W72" s="50" t="str">
         <f aca="false">IF(V72&gt;0,E72," ")</f>
         <v> </v>
       </c>
-      <c r="X72" s="53" t="str">
+      <c r="X72" s="50" t="str">
         <f aca="false">IF(V72&gt;0,J72," ")</f>
         <v> </v>
       </c>
-      <c r="Y72" s="50" t="str">
+      <c r="Y72" s="47" t="str">
         <f aca="false">IF((U72+V72)&gt;0,IF(V72&lt;S72,S72-V72," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z72" s="50" t="str">
+      <c r="Z72" s="47" t="str">
         <f aca="false">IF((U72+V72)&gt;0,IF(V72&gt;S72,V72-S72," ")," ")</f>
         <v> </v>
       </c>
@@ -5396,57 +5380,57 @@
       <c r="C73" s="55"/>
       <c r="D73" s="56"/>
       <c r="E73" s="57"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
       <c r="H73" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I73" s="53" t="str">
+      <c r="I73" s="50" t="str">
         <f aca="false">IF(E73&gt;0,MIN(E73*H73,G73)," ")</f>
         <v> </v>
       </c>
-      <c r="J73" s="53" t="str">
+      <c r="J73" s="50" t="str">
         <f aca="false">IF(E73&gt;0,F73+I73," ")</f>
         <v> </v>
       </c>
-      <c r="K73" s="53" t="str">
+      <c r="K73" s="50" t="str">
         <f aca="false">IF(E73&gt;0,E73-J73," ")</f>
         <v> </v>
       </c>
-      <c r="L73" s="53"/>
+      <c r="L73" s="50"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="53"/>
-      <c r="O73" s="50"/>
-      <c r="P73" s="51" t="n">
+      <c r="N73" s="50"/>
+      <c r="O73" s="47"/>
+      <c r="P73" s="48" t="n">
         <f aca="false">IF(B73&gt;0,IF(B73&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q73" s="50" t="str">
+      <c r="Q73" s="47" t="str">
         <f aca="false">IF(E73&gt;0,E73*P73/100," ")</f>
         <v> </v>
       </c>
-      <c r="R73" s="50"/>
-      <c r="S73" s="50" t="str">
+      <c r="R73" s="47"/>
+      <c r="S73" s="47" t="str">
         <f aca="false">IF(E73&gt;0,E73-Q73," ")</f>
         <v> </v>
       </c>
-      <c r="T73" s="50"/>
+      <c r="T73" s="47"/>
       <c r="U73" s="54"/>
       <c r="V73" s="57"/>
-      <c r="W73" s="53" t="str">
+      <c r="W73" s="50" t="str">
         <f aca="false">IF(V73&gt;0,E73," ")</f>
         <v> </v>
       </c>
-      <c r="X73" s="53" t="str">
+      <c r="X73" s="50" t="str">
         <f aca="false">IF(V73&gt;0,J73," ")</f>
         <v> </v>
       </c>
-      <c r="Y73" s="50" t="str">
+      <c r="Y73" s="47" t="str">
         <f aca="false">IF((U73+V73)&gt;0,IF(V73&lt;S73,S73-V73," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z73" s="50" t="str">
+      <c r="Z73" s="47" t="str">
         <f aca="false">IF((U73+V73)&gt;0,IF(V73&gt;S73,V73-S73," ")," ")</f>
         <v> </v>
       </c>
@@ -5458,57 +5442,57 @@
       <c r="C74" s="55"/>
       <c r="D74" s="56"/>
       <c r="E74" s="57"/>
-      <c r="F74" s="53"/>
-      <c r="G74" s="53"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
       <c r="H74" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I74" s="53" t="str">
+      <c r="I74" s="50" t="str">
         <f aca="false">IF(E74&gt;0,MIN(E74*H74,G74)," ")</f>
         <v> </v>
       </c>
-      <c r="J74" s="53" t="str">
+      <c r="J74" s="50" t="str">
         <f aca="false">IF(E74&gt;0,F74+I74," ")</f>
         <v> </v>
       </c>
-      <c r="K74" s="53" t="str">
+      <c r="K74" s="50" t="str">
         <f aca="false">IF(E74&gt;0,E74-J74," ")</f>
         <v> </v>
       </c>
-      <c r="L74" s="53"/>
+      <c r="L74" s="50"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="53"/>
-      <c r="O74" s="50"/>
-      <c r="P74" s="51" t="n">
+      <c r="N74" s="50"/>
+      <c r="O74" s="47"/>
+      <c r="P74" s="48" t="n">
         <f aca="false">IF(B74&gt;0,IF(B74&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q74" s="50" t="str">
+      <c r="Q74" s="47" t="str">
         <f aca="false">IF(E74&gt;0,E74*P74/100," ")</f>
         <v> </v>
       </c>
-      <c r="R74" s="50"/>
-      <c r="S74" s="50" t="str">
+      <c r="R74" s="47"/>
+      <c r="S74" s="47" t="str">
         <f aca="false">IF(E74&gt;0,E74-Q74," ")</f>
         <v> </v>
       </c>
-      <c r="T74" s="50"/>
+      <c r="T74" s="47"/>
       <c r="U74" s="54"/>
       <c r="V74" s="57"/>
-      <c r="W74" s="53" t="str">
+      <c r="W74" s="50" t="str">
         <f aca="false">IF(V74&gt;0,E74," ")</f>
         <v> </v>
       </c>
-      <c r="X74" s="53" t="str">
+      <c r="X74" s="50" t="str">
         <f aca="false">IF(V74&gt;0,J74," ")</f>
         <v> </v>
       </c>
-      <c r="Y74" s="50" t="str">
+      <c r="Y74" s="47" t="str">
         <f aca="false">IF((U74+V74)&gt;0,IF(V74&lt;S74,S74-V74," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z74" s="50" t="str">
+      <c r="Z74" s="47" t="str">
         <f aca="false">IF((U74+V74)&gt;0,IF(V74&gt;S74,V74-S74," ")," ")</f>
         <v> </v>
       </c>
@@ -5517,7 +5501,7 @@
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C75" s="59"/>
       <c r="D75" s="59"/>
@@ -5546,9 +5530,9 @@
         <f aca="false">SUM(K67:K74)</f>
         <v>0</v>
       </c>
-      <c r="L75" s="53"/>
+      <c r="L75" s="50"/>
       <c r="M75" s="58"/>
-      <c r="N75" s="53"/>
+      <c r="N75" s="50"/>
       <c r="O75" s="61" t="n">
         <f aca="false">SUM(O67:O74)</f>
         <v>0</v>
@@ -5566,8 +5550,8 @@
         <f aca="false">SUM(S67:S74)</f>
         <v>0</v>
       </c>
-      <c r="T75" s="50"/>
-      <c r="U75" s="52"/>
+      <c r="T75" s="47"/>
+      <c r="U75" s="49"/>
       <c r="V75" s="60" t="n">
         <f aca="false">SUM(V67:V74)</f>
         <v>0</v>
@@ -5595,121 +5579,121 @@
       <c r="B76" s="63"/>
       <c r="C76" s="64"/>
       <c r="D76" s="65"/>
-      <c r="E76" s="53"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
       <c r="H76" s="58"/>
-      <c r="I76" s="53"/>
-      <c r="J76" s="53"/>
-      <c r="K76" s="53"/>
-      <c r="L76" s="53"/>
+      <c r="I76" s="50"/>
+      <c r="J76" s="50"/>
+      <c r="K76" s="50"/>
+      <c r="L76" s="50"/>
       <c r="M76" s="58"/>
-      <c r="N76" s="53"/>
-      <c r="O76" s="53"/>
+      <c r="N76" s="50"/>
+      <c r="O76" s="50"/>
       <c r="P76" s="62"/>
-      <c r="Q76" s="53"/>
-      <c r="R76" s="53"/>
-      <c r="S76" s="53"/>
-      <c r="T76" s="50"/>
-      <c r="U76" s="52"/>
-      <c r="V76" s="53"/>
-      <c r="W76" s="53"/>
-      <c r="X76" s="53"/>
-      <c r="Y76" s="53"/>
-      <c r="Z76" s="53"/>
+      <c r="Q76" s="50"/>
+      <c r="R76" s="50"/>
+      <c r="S76" s="50"/>
+      <c r="T76" s="47"/>
+      <c r="U76" s="49"/>
+      <c r="V76" s="50"/>
+      <c r="W76" s="50"/>
+      <c r="X76" s="50"/>
+      <c r="Y76" s="50"/>
+      <c r="Z76" s="50"/>
       <c r="AA76" s="25"/>
     </row>
     <row r="77" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="42"/>
-      <c r="B77" s="66" t="s">
+      <c r="B77" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C77" s="66"/>
+      <c r="C77" s="51"/>
       <c r="D77" s="62"/>
-      <c r="E77" s="53"/>
-      <c r="F77" s="53"/>
-      <c r="G77" s="53"/>
-      <c r="H77" s="86" t="n">
+      <c r="E77" s="50"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50"/>
+      <c r="H77" s="85" t="n">
         <f aca="false">H$24</f>
         <v>0.2</v>
       </c>
-      <c r="I77" s="53"/>
-      <c r="J77" s="53"/>
-      <c r="K77" s="53"/>
-      <c r="L77" s="53"/>
+      <c r="I77" s="50"/>
+      <c r="J77" s="50"/>
+      <c r="K77" s="50"/>
+      <c r="L77" s="50"/>
       <c r="M77" s="58"/>
-      <c r="N77" s="53"/>
-      <c r="O77" s="50"/>
-      <c r="P77" s="51"/>
-      <c r="Q77" s="50"/>
-      <c r="R77" s="50"/>
-      <c r="S77" s="50"/>
-      <c r="T77" s="50"/>
-      <c r="U77" s="52"/>
-      <c r="V77" s="53"/>
-      <c r="W77" s="53"/>
-      <c r="X77" s="53"/>
-      <c r="Y77" s="50"/>
-      <c r="Z77" s="50"/>
+      <c r="N77" s="50"/>
+      <c r="O77" s="47"/>
+      <c r="P77" s="48"/>
+      <c r="Q77" s="47"/>
+      <c r="R77" s="47"/>
+      <c r="S77" s="47"/>
+      <c r="T77" s="47"/>
+      <c r="U77" s="49"/>
+      <c r="V77" s="50"/>
+      <c r="W77" s="50"/>
+      <c r="X77" s="50"/>
+      <c r="Y77" s="47"/>
+      <c r="Z77" s="47"/>
       <c r="AA77" s="25"/>
     </row>
     <row r="78" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="42"/>
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
-      <c r="D78" s="84"/>
+      <c r="D78" s="83"/>
       <c r="E78" s="57"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
       <c r="H78" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I78" s="53" t="str">
+      <c r="I78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,MIN(E78*H78,G78)," ")</f>
         <v> </v>
       </c>
-      <c r="J78" s="53" t="str">
+      <c r="J78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,F78+I78," ")</f>
         <v> </v>
       </c>
-      <c r="K78" s="53" t="str">
+      <c r="K78" s="50" t="str">
         <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
         <v> </v>
       </c>
-      <c r="L78" s="53"/>
+      <c r="L78" s="50"/>
       <c r="M78" s="58"/>
-      <c r="N78" s="53"/>
-      <c r="O78" s="50"/>
-      <c r="P78" s="51" t="n">
+      <c r="N78" s="50"/>
+      <c r="O78" s="47"/>
+      <c r="P78" s="48" t="n">
         <f aca="false">IF(B78&gt;0,IF(B78&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q78" s="50" t="str">
+      <c r="Q78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78*P78/100," ")</f>
         <v> </v>
       </c>
-      <c r="R78" s="50"/>
-      <c r="S78" s="50" t="str">
+      <c r="R78" s="47"/>
+      <c r="S78" s="47" t="str">
         <f aca="false">IF(E78&gt;0,E78-Q78," ")</f>
         <v> </v>
       </c>
-      <c r="T78" s="50"/>
+      <c r="T78" s="47"/>
       <c r="U78" s="54"/>
       <c r="V78" s="57"/>
-      <c r="W78" s="53" t="str">
+      <c r="W78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,E78," ")</f>
         <v> </v>
       </c>
-      <c r="X78" s="53" t="str">
+      <c r="X78" s="50" t="str">
         <f aca="false">IF(V78&gt;0,J78," ")</f>
         <v> </v>
       </c>
-      <c r="Y78" s="50" t="str">
+      <c r="Y78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&lt;S78,S78-V78," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z78" s="50" t="str">
+      <c r="Z78" s="47" t="str">
         <f aca="false">IF((U78+V78)&gt;0,IF(V78&gt;S78,V78-S78," ")," ")</f>
         <v> </v>
       </c>
@@ -5719,59 +5703,59 @@
       <c r="A79" s="42"/>
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
-      <c r="D79" s="84"/>
+      <c r="D79" s="83"/>
       <c r="E79" s="57"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
       <c r="H79" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I79" s="53" t="str">
+      <c r="I79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,MIN(E79*H79,G79)," ")</f>
         <v> </v>
       </c>
-      <c r="J79" s="53" t="str">
+      <c r="J79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,F79+I79," ")</f>
         <v> </v>
       </c>
-      <c r="K79" s="53" t="str">
+      <c r="K79" s="50" t="str">
         <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
         <v> </v>
       </c>
-      <c r="L79" s="53"/>
+      <c r="L79" s="50"/>
       <c r="M79" s="58"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="50"/>
-      <c r="P79" s="51" t="n">
+      <c r="N79" s="50"/>
+      <c r="O79" s="47"/>
+      <c r="P79" s="48" t="n">
         <f aca="false">IF(B79&gt;0,IF(B79&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q79" s="50" t="str">
+      <c r="Q79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79*P79/100," ")</f>
         <v> </v>
       </c>
-      <c r="R79" s="50"/>
-      <c r="S79" s="50" t="str">
+      <c r="R79" s="47"/>
+      <c r="S79" s="47" t="str">
         <f aca="false">IF(E79&gt;0,E79-Q79," ")</f>
         <v> </v>
       </c>
-      <c r="T79" s="50"/>
+      <c r="T79" s="47"/>
       <c r="U79" s="54"/>
       <c r="V79" s="57"/>
-      <c r="W79" s="53" t="str">
+      <c r="W79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,E79," ")</f>
         <v> </v>
       </c>
-      <c r="X79" s="53" t="str">
+      <c r="X79" s="50" t="str">
         <f aca="false">IF(V79&gt;0,J79," ")</f>
         <v> </v>
       </c>
-      <c r="Y79" s="50" t="str">
+      <c r="Y79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&lt;S79,S79-V79," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z79" s="50" t="str">
+      <c r="Z79" s="47" t="str">
         <f aca="false">IF((U79+V79)&gt;0,IF(V79&gt;S79,V79-S79," ")," ")</f>
         <v> </v>
       </c>
@@ -5781,59 +5765,59 @@
       <c r="A80" s="42"/>
       <c r="B80" s="54"/>
       <c r="C80" s="55"/>
-      <c r="D80" s="84"/>
+      <c r="D80" s="83"/>
       <c r="E80" s="57"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
       <c r="H80" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I80" s="53" t="str">
+      <c r="I80" s="50" t="str">
         <f aca="false">IF(E80&gt;0,MIN(E80*H80,G80)," ")</f>
         <v> </v>
       </c>
-      <c r="J80" s="53" t="str">
+      <c r="J80" s="50" t="str">
         <f aca="false">IF(E80&gt;0,F80+I80," ")</f>
         <v> </v>
       </c>
-      <c r="K80" s="53" t="str">
+      <c r="K80" s="50" t="str">
         <f aca="false">IF(E80&gt;0,E80-J80," ")</f>
         <v> </v>
       </c>
-      <c r="L80" s="53"/>
+      <c r="L80" s="50"/>
       <c r="M80" s="58"/>
-      <c r="N80" s="53"/>
-      <c r="O80" s="50"/>
-      <c r="P80" s="51" t="n">
+      <c r="N80" s="50"/>
+      <c r="O80" s="47"/>
+      <c r="P80" s="48" t="n">
         <f aca="false">IF(B80&gt;0,IF(B80&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q80" s="50" t="str">
+      <c r="Q80" s="47" t="str">
         <f aca="false">IF(E80&gt;0,E80*P80/100," ")</f>
         <v> </v>
       </c>
-      <c r="R80" s="50"/>
-      <c r="S80" s="50" t="str">
+      <c r="R80" s="47"/>
+      <c r="S80" s="47" t="str">
         <f aca="false">IF(E80&gt;0,E80-Q80," ")</f>
         <v> </v>
       </c>
-      <c r="T80" s="50"/>
+      <c r="T80" s="47"/>
       <c r="U80" s="54"/>
       <c r="V80" s="57"/>
-      <c r="W80" s="53" t="str">
+      <c r="W80" s="50" t="str">
         <f aca="false">IF(V80&gt;0,E80," ")</f>
         <v> </v>
       </c>
-      <c r="X80" s="53" t="str">
+      <c r="X80" s="50" t="str">
         <f aca="false">IF(V80&gt;0,J80," ")</f>
         <v> </v>
       </c>
-      <c r="Y80" s="50" t="str">
+      <c r="Y80" s="47" t="str">
         <f aca="false">IF((U80+V80)&gt;0,IF(V80&lt;S80,S80-V80," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z80" s="50" t="str">
+      <c r="Z80" s="47" t="str">
         <f aca="false">IF((U80+V80)&gt;0,IF(V80&gt;S80,V80-S80," ")," ")</f>
         <v> </v>
       </c>
@@ -5843,59 +5827,59 @@
       <c r="A81" s="42"/>
       <c r="B81" s="54"/>
       <c r="C81" s="55"/>
-      <c r="D81" s="84"/>
+      <c r="D81" s="83"/>
       <c r="E81" s="57"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
       <c r="H81" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I81" s="53" t="str">
+      <c r="I81" s="50" t="str">
         <f aca="false">IF(E81&gt;0,MIN(E81*H81,G81)," ")</f>
         <v> </v>
       </c>
-      <c r="J81" s="53" t="str">
+      <c r="J81" s="50" t="str">
         <f aca="false">IF(E81&gt;0,F81+I81," ")</f>
         <v> </v>
       </c>
-      <c r="K81" s="53" t="str">
+      <c r="K81" s="50" t="str">
         <f aca="false">IF(E81&gt;0,E81-J81," ")</f>
         <v> </v>
       </c>
-      <c r="L81" s="53"/>
+      <c r="L81" s="50"/>
       <c r="M81" s="58"/>
-      <c r="N81" s="53"/>
-      <c r="O81" s="50"/>
-      <c r="P81" s="51" t="n">
+      <c r="N81" s="50"/>
+      <c r="O81" s="47"/>
+      <c r="P81" s="48" t="n">
         <f aca="false">IF(B81&gt;0,IF(B81&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q81" s="50" t="str">
+      <c r="Q81" s="47" t="str">
         <f aca="false">IF(E81&gt;0,E81*P81/100," ")</f>
         <v> </v>
       </c>
-      <c r="R81" s="50"/>
-      <c r="S81" s="50" t="str">
+      <c r="R81" s="47"/>
+      <c r="S81" s="47" t="str">
         <f aca="false">IF(E81&gt;0,E81-Q81," ")</f>
         <v> </v>
       </c>
-      <c r="T81" s="50"/>
+      <c r="T81" s="47"/>
       <c r="U81" s="54"/>
       <c r="V81" s="57"/>
-      <c r="W81" s="53" t="str">
+      <c r="W81" s="50" t="str">
         <f aca="false">IF(V81&gt;0,E81," ")</f>
         <v> </v>
       </c>
-      <c r="X81" s="53" t="str">
+      <c r="X81" s="50" t="str">
         <f aca="false">IF(V81&gt;0,J81," ")</f>
         <v> </v>
       </c>
-      <c r="Y81" s="50" t="str">
+      <c r="Y81" s="47" t="str">
         <f aca="false">IF((U81+V81)&gt;0,IF(V81&lt;S81,S81-V81," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z81" s="50" t="str">
+      <c r="Z81" s="47" t="str">
         <f aca="false">IF((U81+V81)&gt;0,IF(V81&gt;S81,V81-S81," ")," ")</f>
         <v> </v>
       </c>
@@ -5905,59 +5889,59 @@
       <c r="A82" s="42"/>
       <c r="B82" s="54"/>
       <c r="C82" s="55"/>
-      <c r="D82" s="84"/>
+      <c r="D82" s="83"/>
       <c r="E82" s="57"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="53"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
       <c r="H82" s="58" t="n">
         <f aca="false">H$77</f>
         <v>0.2</v>
       </c>
-      <c r="I82" s="53" t="str">
+      <c r="I82" s="50" t="str">
         <f aca="false">IF(E82&gt;0,MIN(E82*H82,G82)," ")</f>
         <v> </v>
       </c>
-      <c r="J82" s="53" t="str">
+      <c r="J82" s="50" t="str">
         <f aca="false">IF(E82&gt;0,F82+I82," ")</f>
         <v> </v>
       </c>
-      <c r="K82" s="53" t="str">
+      <c r="K82" s="50" t="str">
         <f aca="false">IF(E82&gt;0,E82-J82," ")</f>
         <v> </v>
       </c>
-      <c r="L82" s="53"/>
+      <c r="L82" s="50"/>
       <c r="M82" s="58"/>
-      <c r="N82" s="53"/>
-      <c r="O82" s="50"/>
-      <c r="P82" s="51" t="n">
+      <c r="N82" s="50"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="48" t="n">
         <f aca="false">IF(B82&gt;0,IF(B82&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q82" s="50" t="str">
+      <c r="Q82" s="47" t="str">
         <f aca="false">IF(E82&gt;0,E82*P82/100," ")</f>
         <v> </v>
       </c>
-      <c r="R82" s="50"/>
-      <c r="S82" s="50" t="str">
+      <c r="R82" s="47"/>
+      <c r="S82" s="47" t="str">
         <f aca="false">IF(E82&gt;0,E82-Q82," ")</f>
         <v> </v>
       </c>
-      <c r="T82" s="50"/>
+      <c r="T82" s="47"/>
       <c r="U82" s="54"/>
       <c r="V82" s="57"/>
-      <c r="W82" s="53" t="str">
+      <c r="W82" s="50" t="str">
         <f aca="false">IF(V82&gt;0,E82," ")</f>
         <v> </v>
       </c>
-      <c r="X82" s="53" t="str">
+      <c r="X82" s="50" t="str">
         <f aca="false">IF(V82&gt;0,J82," ")</f>
         <v> </v>
       </c>
-      <c r="Y82" s="50" t="str">
+      <c r="Y82" s="47" t="str">
         <f aca="false">IF((U82+V82)&gt;0,IF(V82&lt;S82,S82-V82," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z82" s="50" t="str">
+      <c r="Z82" s="47" t="str">
         <f aca="false">IF((U82+V82)&gt;0,IF(V82&gt;S82,V82-S82," ")," ")</f>
         <v> </v>
       </c>
@@ -5966,7 +5950,7 @@
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C83" s="59"/>
       <c r="D83" s="59"/>
@@ -5995,9 +5979,9 @@
         <f aca="false">SUM(K78:K82)</f>
         <v>0</v>
       </c>
-      <c r="L83" s="53"/>
+      <c r="L83" s="50"/>
       <c r="M83" s="58"/>
-      <c r="N83" s="53"/>
+      <c r="N83" s="50"/>
       <c r="O83" s="61" t="n">
         <f aca="false">SUM(O78:O82)</f>
         <v>0</v>
@@ -6015,8 +5999,8 @@
         <f aca="false">SUM(S78:S82)</f>
         <v>0</v>
       </c>
-      <c r="T83" s="50"/>
-      <c r="U83" s="52"/>
+      <c r="T83" s="47"/>
+      <c r="U83" s="49"/>
       <c r="V83" s="60" t="n">
         <f aca="false">SUM(V78:V82)</f>
         <v>0</v>
@@ -6044,121 +6028,121 @@
       <c r="B84" s="63"/>
       <c r="C84" s="64"/>
       <c r="D84" s="65"/>
-      <c r="E84" s="53"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
       <c r="H84" s="58"/>
-      <c r="I84" s="53"/>
-      <c r="J84" s="53"/>
-      <c r="K84" s="53"/>
-      <c r="L84" s="53"/>
+      <c r="I84" s="50"/>
+      <c r="J84" s="50"/>
+      <c r="K84" s="50"/>
+      <c r="L84" s="50"/>
       <c r="M84" s="58"/>
-      <c r="N84" s="53"/>
-      <c r="O84" s="53"/>
+      <c r="N84" s="50"/>
+      <c r="O84" s="50"/>
       <c r="P84" s="62"/>
-      <c r="Q84" s="53"/>
-      <c r="R84" s="53"/>
-      <c r="S84" s="53"/>
-      <c r="T84" s="50"/>
-      <c r="U84" s="52"/>
-      <c r="V84" s="53"/>
-      <c r="W84" s="53"/>
-      <c r="X84" s="53"/>
-      <c r="Y84" s="53"/>
-      <c r="Z84" s="53"/>
+      <c r="Q84" s="50"/>
+      <c r="R84" s="50"/>
+      <c r="S84" s="50"/>
+      <c r="T84" s="47"/>
+      <c r="U84" s="49"/>
+      <c r="V84" s="50"/>
+      <c r="W84" s="50"/>
+      <c r="X84" s="50"/>
+      <c r="Y84" s="50"/>
+      <c r="Z84" s="50"/>
       <c r="AA84" s="25"/>
     </row>
     <row r="85" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="42"/>
-      <c r="B85" s="66" t="s">
+      <c r="B85" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C85" s="66"/>
-      <c r="D85" s="69"/>
-      <c r="E85" s="53"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="86" t="n">
+      <c r="C85" s="51"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="85" t="n">
         <f aca="false">H$32</f>
         <v>0.33</v>
       </c>
-      <c r="I85" s="53"/>
-      <c r="J85" s="53"/>
-      <c r="K85" s="53"/>
-      <c r="L85" s="53"/>
+      <c r="I85" s="50"/>
+      <c r="J85" s="50"/>
+      <c r="K85" s="50"/>
+      <c r="L85" s="50"/>
       <c r="M85" s="58"/>
-      <c r="N85" s="53"/>
-      <c r="O85" s="50"/>
-      <c r="P85" s="51"/>
-      <c r="Q85" s="50"/>
-      <c r="R85" s="50"/>
-      <c r="S85" s="50"/>
-      <c r="T85" s="50"/>
-      <c r="U85" s="52"/>
-      <c r="V85" s="53"/>
-      <c r="W85" s="53"/>
-      <c r="X85" s="53"/>
-      <c r="Y85" s="50"/>
-      <c r="Z85" s="50"/>
+      <c r="N85" s="50"/>
+      <c r="O85" s="47"/>
+      <c r="P85" s="48"/>
+      <c r="Q85" s="47"/>
+      <c r="R85" s="47"/>
+      <c r="S85" s="47"/>
+      <c r="T85" s="47"/>
+      <c r="U85" s="49"/>
+      <c r="V85" s="50"/>
+      <c r="W85" s="50"/>
+      <c r="X85" s="50"/>
+      <c r="Y85" s="47"/>
+      <c r="Z85" s="47"/>
       <c r="AA85" s="25"/>
     </row>
     <row r="86" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="42"/>
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
-      <c r="D86" s="84"/>
+      <c r="D86" s="83"/>
       <c r="E86" s="57"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
       <c r="H86" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I86" s="53" t="str">
+      <c r="I86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,MIN(E86*H86,G86)," ")</f>
         <v> </v>
       </c>
-      <c r="J86" s="53" t="str">
+      <c r="J86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,F86+I86," ")</f>
         <v> </v>
       </c>
-      <c r="K86" s="53" t="str">
+      <c r="K86" s="50" t="str">
         <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
         <v> </v>
       </c>
-      <c r="L86" s="53"/>
+      <c r="L86" s="50"/>
       <c r="M86" s="58"/>
-      <c r="N86" s="53"/>
-      <c r="O86" s="50"/>
-      <c r="P86" s="51" t="n">
+      <c r="N86" s="50"/>
+      <c r="O86" s="47"/>
+      <c r="P86" s="48" t="n">
         <f aca="false">IF(B86&gt;0,IF(B86&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q86" s="50" t="str">
+      <c r="Q86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86*P86/100," ")</f>
         <v> </v>
       </c>
-      <c r="R86" s="50"/>
-      <c r="S86" s="50" t="str">
+      <c r="R86" s="47"/>
+      <c r="S86" s="47" t="str">
         <f aca="false">IF(E86&gt;0,E86-Q86," ")</f>
         <v> </v>
       </c>
-      <c r="T86" s="50"/>
+      <c r="T86" s="47"/>
       <c r="U86" s="54"/>
       <c r="V86" s="57"/>
-      <c r="W86" s="53" t="str">
+      <c r="W86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,E86," ")</f>
         <v> </v>
       </c>
-      <c r="X86" s="53" t="str">
+      <c r="X86" s="50" t="str">
         <f aca="false">IF(V86&gt;0,J86," ")</f>
         <v> </v>
       </c>
-      <c r="Y86" s="50" t="str">
+      <c r="Y86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&lt;S86,S86-V86," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z86" s="50" t="str">
+      <c r="Z86" s="47" t="str">
         <f aca="false">IF((U86+V86)&gt;0,IF(V86&gt;S86,V86-S86," ")," ")</f>
         <v> </v>
       </c>
@@ -6168,59 +6152,59 @@
       <c r="A87" s="42"/>
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
-      <c r="D87" s="84"/>
+      <c r="D87" s="83"/>
       <c r="E87" s="57"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
       <c r="H87" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I87" s="53" t="str">
+      <c r="I87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,MIN(E87*H87,G87)," ")</f>
         <v> </v>
       </c>
-      <c r="J87" s="53" t="str">
+      <c r="J87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,F87+I87," ")</f>
         <v> </v>
       </c>
-      <c r="K87" s="53" t="str">
+      <c r="K87" s="50" t="str">
         <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
         <v> </v>
       </c>
-      <c r="L87" s="53"/>
+      <c r="L87" s="50"/>
       <c r="M87" s="58"/>
-      <c r="N87" s="53"/>
-      <c r="O87" s="50"/>
-      <c r="P87" s="51" t="n">
+      <c r="N87" s="50"/>
+      <c r="O87" s="47"/>
+      <c r="P87" s="48" t="n">
         <f aca="false">IF(B87&gt;0,IF(B87&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q87" s="50" t="str">
+      <c r="Q87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87*P87/100," ")</f>
         <v> </v>
       </c>
-      <c r="R87" s="50"/>
-      <c r="S87" s="50" t="str">
+      <c r="R87" s="47"/>
+      <c r="S87" s="47" t="str">
         <f aca="false">IF(E87&gt;0,E87-Q87," ")</f>
         <v> </v>
       </c>
-      <c r="T87" s="50"/>
+      <c r="T87" s="47"/>
       <c r="U87" s="54"/>
       <c r="V87" s="57"/>
-      <c r="W87" s="53" t="str">
+      <c r="W87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,E87," ")</f>
         <v> </v>
       </c>
-      <c r="X87" s="53" t="str">
+      <c r="X87" s="50" t="str">
         <f aca="false">IF(V87&gt;0,J87," ")</f>
         <v> </v>
       </c>
-      <c r="Y87" s="50" t="str">
+      <c r="Y87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&lt;S87,S87-V87," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z87" s="50" t="str">
+      <c r="Z87" s="47" t="str">
         <f aca="false">IF((U87+V87)&gt;0,IF(V87&gt;S87,V87-S87," ")," ")</f>
         <v> </v>
       </c>
@@ -6230,59 +6214,59 @@
       <c r="A88" s="42"/>
       <c r="B88" s="54"/>
       <c r="C88" s="55"/>
-      <c r="D88" s="84"/>
+      <c r="D88" s="83"/>
       <c r="E88" s="57"/>
-      <c r="F88" s="53"/>
-      <c r="G88" s="53"/>
+      <c r="F88" s="50"/>
+      <c r="G88" s="50"/>
       <c r="H88" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I88" s="53" t="str">
+      <c r="I88" s="50" t="str">
         <f aca="false">IF(E88&gt;0,MIN(E88*H88,G88)," ")</f>
         <v> </v>
       </c>
-      <c r="J88" s="53" t="str">
+      <c r="J88" s="50" t="str">
         <f aca="false">IF(E88&gt;0,F88+I88," ")</f>
         <v> </v>
       </c>
-      <c r="K88" s="53" t="str">
+      <c r="K88" s="50" t="str">
         <f aca="false">IF(E88&gt;0,E88-J88," ")</f>
         <v> </v>
       </c>
-      <c r="L88" s="53"/>
+      <c r="L88" s="50"/>
       <c r="M88" s="58"/>
-      <c r="N88" s="53"/>
-      <c r="O88" s="50"/>
-      <c r="P88" s="51" t="n">
+      <c r="N88" s="50"/>
+      <c r="O88" s="47"/>
+      <c r="P88" s="48" t="n">
         <f aca="false">IF(B88&gt;0,IF(B88&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q88" s="50" t="str">
+      <c r="Q88" s="47" t="str">
         <f aca="false">IF(E88&gt;0,E88*P88/100," ")</f>
         <v> </v>
       </c>
-      <c r="R88" s="50"/>
-      <c r="S88" s="50" t="str">
+      <c r="R88" s="47"/>
+      <c r="S88" s="47" t="str">
         <f aca="false">IF(E88&gt;0,E88-Q88," ")</f>
         <v> </v>
       </c>
-      <c r="T88" s="50"/>
+      <c r="T88" s="47"/>
       <c r="U88" s="54"/>
       <c r="V88" s="57"/>
-      <c r="W88" s="53" t="str">
+      <c r="W88" s="50" t="str">
         <f aca="false">IF(V88&gt;0,E88," ")</f>
         <v> </v>
       </c>
-      <c r="X88" s="53" t="str">
+      <c r="X88" s="50" t="str">
         <f aca="false">IF(V88&gt;0,J88," ")</f>
         <v> </v>
       </c>
-      <c r="Y88" s="50" t="str">
+      <c r="Y88" s="47" t="str">
         <f aca="false">IF((U88+V88)&gt;0,IF(V88&lt;S88,S88-V88," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z88" s="50" t="str">
+      <c r="Z88" s="47" t="str">
         <f aca="false">IF((U88+V88)&gt;0,IF(V88&gt;S88,V88-S88," ")," ")</f>
         <v> </v>
       </c>
@@ -6292,59 +6276,59 @@
       <c r="A89" s="42"/>
       <c r="B89" s="54"/>
       <c r="C89" s="55"/>
-      <c r="D89" s="84"/>
+      <c r="D89" s="83"/>
       <c r="E89" s="57"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
       <c r="H89" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I89" s="53" t="str">
+      <c r="I89" s="50" t="str">
         <f aca="false">IF(E89&gt;0,MIN(E89*H89,G89)," ")</f>
         <v> </v>
       </c>
-      <c r="J89" s="53" t="str">
+      <c r="J89" s="50" t="str">
         <f aca="false">IF(E89&gt;0,F89+I89," ")</f>
         <v> </v>
       </c>
-      <c r="K89" s="53" t="str">
+      <c r="K89" s="50" t="str">
         <f aca="false">IF(E89&gt;0,E89-J89," ")</f>
         <v> </v>
       </c>
-      <c r="L89" s="53"/>
+      <c r="L89" s="50"/>
       <c r="M89" s="58"/>
-      <c r="N89" s="53"/>
-      <c r="O89" s="50"/>
-      <c r="P89" s="51" t="n">
+      <c r="N89" s="50"/>
+      <c r="O89" s="47"/>
+      <c r="P89" s="48" t="n">
         <f aca="false">IF(B89&gt;0,IF(B89&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q89" s="50" t="str">
+      <c r="Q89" s="47" t="str">
         <f aca="false">IF(E89&gt;0,E89*P89/100," ")</f>
         <v> </v>
       </c>
-      <c r="R89" s="50"/>
-      <c r="S89" s="50" t="str">
+      <c r="R89" s="47"/>
+      <c r="S89" s="47" t="str">
         <f aca="false">IF(E89&gt;0,E89-Q89," ")</f>
         <v> </v>
       </c>
-      <c r="T89" s="50"/>
+      <c r="T89" s="47"/>
       <c r="U89" s="54"/>
       <c r="V89" s="57"/>
-      <c r="W89" s="53" t="str">
+      <c r="W89" s="50" t="str">
         <f aca="false">IF(V89&gt;0,E89," ")</f>
         <v> </v>
       </c>
-      <c r="X89" s="53" t="str">
+      <c r="X89" s="50" t="str">
         <f aca="false">IF(V89&gt;0,J89," ")</f>
         <v> </v>
       </c>
-      <c r="Y89" s="50" t="str">
+      <c r="Y89" s="47" t="str">
         <f aca="false">IF((U89+V89)&gt;0,IF(V89&lt;S89,S89-V89," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z89" s="50" t="str">
+      <c r="Z89" s="47" t="str">
         <f aca="false">IF((U89+V89)&gt;0,IF(V89&gt;S89,V89-S89," ")," ")</f>
         <v> </v>
       </c>
@@ -6354,59 +6338,59 @@
       <c r="A90" s="42"/>
       <c r="B90" s="54"/>
       <c r="C90" s="55"/>
-      <c r="D90" s="84"/>
+      <c r="D90" s="83"/>
       <c r="E90" s="57"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
       <c r="H90" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I90" s="53" t="str">
+      <c r="I90" s="50" t="str">
         <f aca="false">IF(E90&gt;0,MIN(E90*H90,G90)," ")</f>
         <v> </v>
       </c>
-      <c r="J90" s="53" t="str">
+      <c r="J90" s="50" t="str">
         <f aca="false">IF(E90&gt;0,F90+I90," ")</f>
         <v> </v>
       </c>
-      <c r="K90" s="53" t="str">
+      <c r="K90" s="50" t="str">
         <f aca="false">IF(E90&gt;0,E90-J90," ")</f>
         <v> </v>
       </c>
-      <c r="L90" s="53"/>
+      <c r="L90" s="50"/>
       <c r="M90" s="58"/>
-      <c r="N90" s="53"/>
-      <c r="O90" s="50"/>
-      <c r="P90" s="51" t="n">
+      <c r="N90" s="50"/>
+      <c r="O90" s="47"/>
+      <c r="P90" s="48" t="n">
         <f aca="false">IF(B90&gt;0,IF(B90&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q90" s="50" t="str">
+      <c r="Q90" s="47" t="str">
         <f aca="false">IF(E90&gt;0,E90*P90/100," ")</f>
         <v> </v>
       </c>
-      <c r="R90" s="50"/>
-      <c r="S90" s="50" t="str">
+      <c r="R90" s="47"/>
+      <c r="S90" s="47" t="str">
         <f aca="false">IF(E90&gt;0,E90-Q90," ")</f>
         <v> </v>
       </c>
-      <c r="T90" s="50"/>
+      <c r="T90" s="47"/>
       <c r="U90" s="54"/>
       <c r="V90" s="57"/>
-      <c r="W90" s="53" t="str">
+      <c r="W90" s="50" t="str">
         <f aca="false">IF(V90&gt;0,E90," ")</f>
         <v> </v>
       </c>
-      <c r="X90" s="53" t="str">
+      <c r="X90" s="50" t="str">
         <f aca="false">IF(V90&gt;0,J90," ")</f>
         <v> </v>
       </c>
-      <c r="Y90" s="50" t="str">
+      <c r="Y90" s="47" t="str">
         <f aca="false">IF((U90+V90)&gt;0,IF(V90&lt;S90,S90-V90," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z90" s="50" t="str">
+      <c r="Z90" s="47" t="str">
         <f aca="false">IF((U90+V90)&gt;0,IF(V90&gt;S90,V90-S90," ")," ")</f>
         <v> </v>
       </c>
@@ -6416,59 +6400,59 @@
       <c r="A91" s="42"/>
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
-      <c r="D91" s="84"/>
+      <c r="D91" s="83"/>
       <c r="E91" s="57"/>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
       <c r="H91" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I91" s="53" t="str">
+      <c r="I91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,MIN(E91*H91,G91)," ")</f>
         <v> </v>
       </c>
-      <c r="J91" s="53" t="str">
+      <c r="J91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,F91+I91," ")</f>
         <v> </v>
       </c>
-      <c r="K91" s="53" t="str">
+      <c r="K91" s="50" t="str">
         <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
         <v> </v>
       </c>
-      <c r="L91" s="53"/>
+      <c r="L91" s="50"/>
       <c r="M91" s="58"/>
-      <c r="N91" s="53"/>
-      <c r="O91" s="50"/>
-      <c r="P91" s="51" t="n">
+      <c r="N91" s="50"/>
+      <c r="O91" s="47"/>
+      <c r="P91" s="48" t="n">
         <f aca="false">IF(B91&gt;0,IF(B91&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q91" s="50" t="str">
+      <c r="Q91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,E91*P91/100," ")</f>
         <v> </v>
       </c>
-      <c r="R91" s="50"/>
-      <c r="S91" s="50" t="str">
+      <c r="R91" s="47"/>
+      <c r="S91" s="47" t="str">
         <f aca="false">IF(E91&gt;0,E91-Q91," ")</f>
         <v> </v>
       </c>
-      <c r="T91" s="50"/>
+      <c r="T91" s="47"/>
       <c r="U91" s="54"/>
       <c r="V91" s="57"/>
-      <c r="W91" s="53" t="str">
+      <c r="W91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,E91," ")</f>
         <v> </v>
       </c>
-      <c r="X91" s="53" t="str">
+      <c r="X91" s="50" t="str">
         <f aca="false">IF(V91&gt;0,J91," ")</f>
         <v> </v>
       </c>
-      <c r="Y91" s="50" t="str">
+      <c r="Y91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&lt;S91,S91-V91," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z91" s="50" t="str">
+      <c r="Z91" s="47" t="str">
         <f aca="false">IF((U91+V91)&gt;0,IF(V91&gt;S91,V91-S91," ")," ")</f>
         <v> </v>
       </c>
@@ -6478,59 +6462,59 @@
       <c r="A92" s="42"/>
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
-      <c r="D92" s="84"/>
+      <c r="D92" s="83"/>
       <c r="E92" s="57"/>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
       <c r="H92" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I92" s="53" t="str">
+      <c r="I92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,MIN(E92*H92,G92)," ")</f>
         <v> </v>
       </c>
-      <c r="J92" s="53" t="str">
+      <c r="J92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,F92+I92," ")</f>
         <v> </v>
       </c>
-      <c r="K92" s="53" t="str">
+      <c r="K92" s="50" t="str">
         <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
         <v> </v>
       </c>
-      <c r="L92" s="53"/>
+      <c r="L92" s="50"/>
       <c r="M92" s="58"/>
-      <c r="N92" s="53"/>
-      <c r="O92" s="50"/>
-      <c r="P92" s="51" t="n">
+      <c r="N92" s="50"/>
+      <c r="O92" s="47"/>
+      <c r="P92" s="48" t="n">
         <f aca="false">IF(B92&gt;0,IF(B92&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q92" s="50" t="str">
+      <c r="Q92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,E92*P92/100," ")</f>
         <v> </v>
       </c>
-      <c r="R92" s="50"/>
-      <c r="S92" s="50" t="str">
+      <c r="R92" s="47"/>
+      <c r="S92" s="47" t="str">
         <f aca="false">IF(E92&gt;0,E92-Q92," ")</f>
         <v> </v>
       </c>
-      <c r="T92" s="50"/>
+      <c r="T92" s="47"/>
       <c r="U92" s="54"/>
       <c r="V92" s="57"/>
-      <c r="W92" s="53" t="str">
+      <c r="W92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,E92," ")</f>
         <v> </v>
       </c>
-      <c r="X92" s="53" t="str">
+      <c r="X92" s="50" t="str">
         <f aca="false">IF(V92&gt;0,J92," ")</f>
         <v> </v>
       </c>
-      <c r="Y92" s="50" t="str">
+      <c r="Y92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&lt;S92,S92-V92," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z92" s="50" t="str">
+      <c r="Z92" s="47" t="str">
         <f aca="false">IF((U92+V92)&gt;0,IF(V92&gt;S92,V92-S92," ")," ")</f>
         <v> </v>
       </c>
@@ -6540,59 +6524,59 @@
       <c r="A93" s="42"/>
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
-      <c r="D93" s="84"/>
+      <c r="D93" s="83"/>
       <c r="E93" s="57"/>
-      <c r="F93" s="53"/>
-      <c r="G93" s="53"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
       <c r="H93" s="58" t="n">
         <f aca="false">H$85</f>
         <v>0.33</v>
       </c>
-      <c r="I93" s="53" t="str">
+      <c r="I93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,MIN(E93*H93,G93)," ")</f>
         <v> </v>
       </c>
-      <c r="J93" s="53" t="str">
+      <c r="J93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,F93+I93," ")</f>
         <v> </v>
       </c>
-      <c r="K93" s="53" t="str">
+      <c r="K93" s="50" t="str">
         <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
         <v> </v>
       </c>
-      <c r="L93" s="53"/>
+      <c r="L93" s="50"/>
       <c r="M93" s="58"/>
-      <c r="N93" s="53"/>
-      <c r="O93" s="50"/>
-      <c r="P93" s="51" t="n">
+      <c r="N93" s="50"/>
+      <c r="O93" s="47"/>
+      <c r="P93" s="48" t="n">
         <f aca="false">IF(B93&gt;0,IF(B93&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q93" s="50" t="str">
+      <c r="Q93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,E93*P93/100," ")</f>
         <v> </v>
       </c>
-      <c r="R93" s="50"/>
-      <c r="S93" s="50" t="str">
+      <c r="R93" s="47"/>
+      <c r="S93" s="47" t="str">
         <f aca="false">IF(E93&gt;0,E93-Q93," ")</f>
         <v> </v>
       </c>
-      <c r="T93" s="50"/>
+      <c r="T93" s="47"/>
       <c r="U93" s="54"/>
       <c r="V93" s="57"/>
-      <c r="W93" s="53" t="str">
+      <c r="W93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,E93," ")</f>
         <v> </v>
       </c>
-      <c r="X93" s="53" t="str">
+      <c r="X93" s="50" t="str">
         <f aca="false">IF(V93&gt;0,J93," ")</f>
         <v> </v>
       </c>
-      <c r="Y93" s="50" t="str">
+      <c r="Y93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&lt;S93,S93-V93," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z93" s="50" t="str">
+      <c r="Z93" s="47" t="str">
         <f aca="false">IF((U93+V93)&gt;0,IF(V93&gt;S93,V93-S93," ")," ")</f>
         <v> </v>
       </c>
@@ -6601,7 +6585,7 @@
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="42"/>
       <c r="B94" s="59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="59"/>
@@ -6630,9 +6614,9 @@
         <f aca="false">SUM(K86:K93)</f>
         <v>0</v>
       </c>
-      <c r="L94" s="53"/>
+      <c r="L94" s="50"/>
       <c r="M94" s="58"/>
-      <c r="N94" s="53"/>
+      <c r="N94" s="50"/>
       <c r="O94" s="61" t="n">
         <f aca="false">SUM(O86:O93)</f>
         <v>0</v>
@@ -6650,8 +6634,8 @@
         <f aca="false">SUM(S86:S93)</f>
         <v>0</v>
       </c>
-      <c r="T94" s="50"/>
-      <c r="U94" s="52"/>
+      <c r="T94" s="47"/>
+      <c r="U94" s="49"/>
       <c r="V94" s="60" t="n">
         <f aca="false">SUM(V86:V93)</f>
         <v>0</v>
@@ -6679,120 +6663,120 @@
       <c r="B95" s="63"/>
       <c r="C95" s="64"/>
       <c r="D95" s="65"/>
-      <c r="E95" s="53"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
+      <c r="E95" s="50"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50"/>
       <c r="H95" s="58"/>
-      <c r="I95" s="53"/>
-      <c r="J95" s="53"/>
-      <c r="K95" s="53"/>
-      <c r="L95" s="53"/>
+      <c r="I95" s="50"/>
+      <c r="J95" s="50"/>
+      <c r="K95" s="50"/>
+      <c r="L95" s="50"/>
       <c r="M95" s="58"/>
-      <c r="N95" s="53"/>
-      <c r="O95" s="53"/>
+      <c r="N95" s="50"/>
+      <c r="O95" s="50"/>
       <c r="P95" s="62"/>
-      <c r="Q95" s="53"/>
-      <c r="R95" s="53"/>
-      <c r="S95" s="53"/>
-      <c r="T95" s="50"/>
-      <c r="U95" s="52"/>
-      <c r="V95" s="53"/>
-      <c r="W95" s="53"/>
-      <c r="X95" s="53"/>
-      <c r="Y95" s="53"/>
-      <c r="Z95" s="53"/>
+      <c r="Q95" s="50"/>
+      <c r="R95" s="50"/>
+      <c r="S95" s="50"/>
+      <c r="T95" s="47"/>
+      <c r="U95" s="49"/>
+      <c r="V95" s="50"/>
+      <c r="W95" s="50"/>
+      <c r="X95" s="50"/>
+      <c r="Y95" s="50"/>
+      <c r="Z95" s="50"/>
       <c r="AA95" s="25"/>
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
-      <c r="B96" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="C96" s="66"/>
-      <c r="D96" s="69"/>
-      <c r="E96" s="53"/>
-      <c r="F96" s="53"/>
-      <c r="G96" s="53"/>
-      <c r="H96" s="86" t="n">
+      <c r="B96" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="51"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
+      <c r="H96" s="85" t="n">
         <f aca="false">H$43</f>
         <v>0.25</v>
       </c>
-      <c r="I96" s="53"/>
-      <c r="J96" s="53"/>
-      <c r="K96" s="53"/>
-      <c r="L96" s="53"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+      <c r="L96" s="50"/>
       <c r="M96" s="58"/>
-      <c r="N96" s="53"/>
-      <c r="O96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="47"/>
       <c r="P96" s="62"/>
-      <c r="Q96" s="50"/>
-      <c r="R96" s="50"/>
-      <c r="S96" s="50"/>
-      <c r="T96" s="50"/>
-      <c r="U96" s="52"/>
-      <c r="V96" s="53"/>
-      <c r="W96" s="53"/>
-      <c r="X96" s="53"/>
-      <c r="Y96" s="50"/>
-      <c r="Z96" s="50"/>
+      <c r="Q96" s="47"/>
+      <c r="R96" s="47"/>
+      <c r="S96" s="47"/>
+      <c r="T96" s="47"/>
+      <c r="U96" s="49"/>
+      <c r="V96" s="50"/>
+      <c r="W96" s="50"/>
+      <c r="X96" s="50"/>
+      <c r="Y96" s="47"/>
+      <c r="Z96" s="47"/>
       <c r="AA96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="42"/>
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
-      <c r="D97" s="84"/>
+      <c r="D97" s="83"/>
       <c r="E97" s="57"/>
-      <c r="F97" s="53"/>
-      <c r="G97" s="53"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
       <c r="H97" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I97" s="53" t="str">
+      <c r="I97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,MIN(E97*H97,G97)," ")</f>
         <v> </v>
       </c>
-      <c r="J97" s="53" t="str">
+      <c r="J97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,F97+I97," ")</f>
         <v> </v>
       </c>
-      <c r="K97" s="53" t="str">
+      <c r="K97" s="50" t="str">
         <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
         <v> </v>
       </c>
-      <c r="L97" s="53"/>
-      <c r="M97" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="53"/>
-      <c r="O97" s="50"/>
-      <c r="P97" s="51"/>
-      <c r="Q97" s="50"/>
-      <c r="R97" s="50" t="str">
+      <c r="L97" s="50"/>
+      <c r="M97" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="50"/>
+      <c r="O97" s="47"/>
+      <c r="P97" s="48"/>
+      <c r="Q97" s="47"/>
+      <c r="R97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,IF(E97&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M97),E97*R$4/100)*(1-M97)," ")</f>
         <v> </v>
       </c>
-      <c r="S97" s="50" t="str">
+      <c r="S97" s="47" t="str">
         <f aca="false">IF(E97&gt;0,E97-R97," ")</f>
         <v> </v>
       </c>
-      <c r="T97" s="50"/>
+      <c r="T97" s="47"/>
       <c r="U97" s="54"/>
       <c r="V97" s="57"/>
-      <c r="W97" s="53" t="str">
+      <c r="W97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,E97," ")</f>
         <v> </v>
       </c>
-      <c r="X97" s="53" t="str">
+      <c r="X97" s="50" t="str">
         <f aca="false">IF(V97&gt;0,J97," ")</f>
         <v> </v>
       </c>
-      <c r="Y97" s="50" t="str">
+      <c r="Y97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&lt;S97,(S97-V97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z97" s="50" t="str">
+      <c r="Z97" s="47" t="str">
         <f aca="false">IF((U97+V97)&gt;0,IF(V97&gt;S97,(V97-S97)*(1-M97)," ")," ")</f>
         <v> </v>
       </c>
@@ -6802,58 +6786,58 @@
       <c r="A98" s="42"/>
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
-      <c r="D98" s="84"/>
+      <c r="D98" s="83"/>
       <c r="E98" s="57"/>
-      <c r="F98" s="53"/>
-      <c r="G98" s="53"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
       <c r="H98" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I98" s="53" t="str">
+      <c r="I98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,MIN(E98*H98,G98)," ")</f>
         <v> </v>
       </c>
-      <c r="J98" s="53" t="str">
+      <c r="J98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,F98+I98," ")</f>
         <v> </v>
       </c>
-      <c r="K98" s="53" t="str">
+      <c r="K98" s="50" t="str">
         <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
         <v> </v>
       </c>
-      <c r="L98" s="53"/>
-      <c r="M98" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="53"/>
-      <c r="O98" s="50"/>
-      <c r="P98" s="51"/>
-      <c r="Q98" s="50"/>
-      <c r="R98" s="50" t="str">
+      <c r="L98" s="50"/>
+      <c r="M98" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="50"/>
+      <c r="O98" s="47"/>
+      <c r="P98" s="48"/>
+      <c r="Q98" s="47"/>
+      <c r="R98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,IF(E98&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M98),E98*R$4/100)*(1-M98)," ")</f>
         <v> </v>
       </c>
-      <c r="S98" s="50" t="str">
+      <c r="S98" s="47" t="str">
         <f aca="false">IF(E98&gt;0,E98-R98," ")</f>
         <v> </v>
       </c>
-      <c r="T98" s="50"/>
+      <c r="T98" s="47"/>
       <c r="U98" s="54"/>
       <c r="V98" s="57"/>
-      <c r="W98" s="53" t="str">
+      <c r="W98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,E98," ")</f>
         <v> </v>
       </c>
-      <c r="X98" s="53" t="str">
+      <c r="X98" s="50" t="str">
         <f aca="false">IF(V98&gt;0,J98," ")</f>
         <v> </v>
       </c>
-      <c r="Y98" s="50" t="str">
+      <c r="Y98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&lt;S98,(S98-V98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z98" s="50" t="str">
+      <c r="Z98" s="47" t="str">
         <f aca="false">IF((U98+V98)&gt;0,IF(V98&gt;S98,(V98-S98)*(1-M98)," ")," ")</f>
         <v> </v>
       </c>
@@ -6863,58 +6847,58 @@
       <c r="A99" s="42"/>
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
-      <c r="D99" s="84"/>
+      <c r="D99" s="83"/>
       <c r="E99" s="57"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="53"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
       <c r="H99" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I99" s="53" t="str">
+      <c r="I99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,MIN(E99*H99,G99)," ")</f>
         <v> </v>
       </c>
-      <c r="J99" s="53" t="str">
+      <c r="J99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,F99+I99," ")</f>
         <v> </v>
       </c>
-      <c r="K99" s="53" t="str">
+      <c r="K99" s="50" t="str">
         <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
         <v> </v>
       </c>
-      <c r="L99" s="53"/>
-      <c r="M99" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="53"/>
-      <c r="O99" s="50"/>
-      <c r="P99" s="51"/>
-      <c r="Q99" s="50"/>
-      <c r="R99" s="50" t="str">
+      <c r="L99" s="50"/>
+      <c r="M99" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="50"/>
+      <c r="O99" s="47"/>
+      <c r="P99" s="48"/>
+      <c r="Q99" s="47"/>
+      <c r="R99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,IF(E99&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M99),E99*R$4/100)*(1-M99)," ")</f>
         <v> </v>
       </c>
-      <c r="S99" s="50" t="str">
+      <c r="S99" s="47" t="str">
         <f aca="false">IF(E99&gt;0,E99-R99," ")</f>
         <v> </v>
       </c>
-      <c r="T99" s="50"/>
+      <c r="T99" s="47"/>
       <c r="U99" s="54"/>
       <c r="V99" s="57"/>
-      <c r="W99" s="53" t="str">
+      <c r="W99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,E99," ")</f>
         <v> </v>
       </c>
-      <c r="X99" s="53" t="str">
+      <c r="X99" s="50" t="str">
         <f aca="false">IF(V99&gt;0,J99," ")</f>
         <v> </v>
       </c>
-      <c r="Y99" s="50" t="str">
+      <c r="Y99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&lt;S99,(S99-V99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z99" s="50" t="str">
+      <c r="Z99" s="47" t="str">
         <f aca="false">IF((U99+V99)&gt;0,IF(V99&gt;S99,(V99-S99)*(1-M99)," ")," ")</f>
         <v> </v>
       </c>
@@ -6924,58 +6908,58 @@
       <c r="A100" s="42"/>
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
-      <c r="D100" s="84"/>
+      <c r="D100" s="83"/>
       <c r="E100" s="57"/>
-      <c r="F100" s="53"/>
-      <c r="G100" s="53"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
       <c r="H100" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I100" s="53" t="str">
+      <c r="I100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,MIN(E100*H100,G100)," ")</f>
         <v> </v>
       </c>
-      <c r="J100" s="53" t="str">
+      <c r="J100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,F100+I100," ")</f>
         <v> </v>
       </c>
-      <c r="K100" s="53" t="str">
+      <c r="K100" s="50" t="str">
         <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
         <v> </v>
       </c>
-      <c r="L100" s="53"/>
-      <c r="M100" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="53"/>
-      <c r="O100" s="50"/>
-      <c r="P100" s="51"/>
-      <c r="Q100" s="50"/>
-      <c r="R100" s="50" t="str">
+      <c r="L100" s="50"/>
+      <c r="M100" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="50"/>
+      <c r="O100" s="47"/>
+      <c r="P100" s="48"/>
+      <c r="Q100" s="47"/>
+      <c r="R100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,IF(E100&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M100),E100*R$4/100)*(1-M100)," ")</f>
         <v> </v>
       </c>
-      <c r="S100" s="50" t="str">
+      <c r="S100" s="47" t="str">
         <f aca="false">IF(E100&gt;0,E100-R100," ")</f>
         <v> </v>
       </c>
-      <c r="T100" s="50"/>
+      <c r="T100" s="47"/>
       <c r="U100" s="54"/>
       <c r="V100" s="57"/>
-      <c r="W100" s="53" t="str">
+      <c r="W100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,E100," ")</f>
         <v> </v>
       </c>
-      <c r="X100" s="53" t="str">
+      <c r="X100" s="50" t="str">
         <f aca="false">IF(V100&gt;0,J100," ")</f>
         <v> </v>
       </c>
-      <c r="Y100" s="50" t="str">
+      <c r="Y100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&lt;S100,(S100-V100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z100" s="50" t="str">
+      <c r="Z100" s="47" t="str">
         <f aca="false">IF((U100+V100)&gt;0,IF(V100&gt;S100,(V100-S100)*(1-M100)," ")," ")</f>
         <v> </v>
       </c>
@@ -6985,58 +6969,58 @@
       <c r="A101" s="42"/>
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
-      <c r="D101" s="84"/>
+      <c r="D101" s="83"/>
       <c r="E101" s="57"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="53"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
       <c r="H101" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I101" s="53" t="str">
+      <c r="I101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,MIN(E101*H101,G101)," ")</f>
         <v> </v>
       </c>
-      <c r="J101" s="53" t="str">
+      <c r="J101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,F101+I101," ")</f>
         <v> </v>
       </c>
-      <c r="K101" s="53" t="str">
+      <c r="K101" s="50" t="str">
         <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
         <v> </v>
       </c>
-      <c r="L101" s="53"/>
-      <c r="M101" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="53"/>
-      <c r="O101" s="50"/>
-      <c r="P101" s="51"/>
-      <c r="Q101" s="50"/>
-      <c r="R101" s="50" t="str">
+      <c r="L101" s="50"/>
+      <c r="M101" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="50"/>
+      <c r="O101" s="47"/>
+      <c r="P101" s="48"/>
+      <c r="Q101" s="47"/>
+      <c r="R101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,IF(E101&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M101),E101*R$4/100)*(1-M101)," ")</f>
         <v> </v>
       </c>
-      <c r="S101" s="50" t="str">
+      <c r="S101" s="47" t="str">
         <f aca="false">IF(E101&gt;0,E101-R101," ")</f>
         <v> </v>
       </c>
-      <c r="T101" s="50"/>
+      <c r="T101" s="47"/>
       <c r="U101" s="54"/>
       <c r="V101" s="57"/>
-      <c r="W101" s="53" t="str">
+      <c r="W101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,E101," ")</f>
         <v> </v>
       </c>
-      <c r="X101" s="53" t="str">
+      <c r="X101" s="50" t="str">
         <f aca="false">IF(V101&gt;0,J101," ")</f>
         <v> </v>
       </c>
-      <c r="Y101" s="50" t="str">
+      <c r="Y101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&lt;S101,(S101-V101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z101" s="50" t="str">
+      <c r="Z101" s="47" t="str">
         <f aca="false">IF((U101+V101)&gt;0,IF(V101&gt;S101,(V101-S101)*(1-M101)," ")," ")</f>
         <v> </v>
       </c>
@@ -7044,94 +7028,94 @@
     </row>
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
-      <c r="B102" s="66" t="s">
-        <v>26</v>
-      </c>
-      <c r="C102" s="66"/>
-      <c r="D102" s="69"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
+      <c r="B102" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" s="51"/>
+      <c r="D102" s="68"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
-      <c r="L102" s="53"/>
+      <c r="I102" s="50"/>
+      <c r="J102" s="50"/>
+      <c r="K102" s="50"/>
+      <c r="L102" s="50"/>
       <c r="M102" s="58"/>
-      <c r="N102" s="53"/>
-      <c r="O102" s="50"/>
-      <c r="P102" s="51"/>
-      <c r="Q102" s="50"/>
-      <c r="R102" s="50"/>
-      <c r="S102" s="50"/>
-      <c r="T102" s="50"/>
-      <c r="U102" s="52"/>
-      <c r="V102" s="53"/>
-      <c r="W102" s="53"/>
-      <c r="X102" s="53"/>
-      <c r="Y102" s="50"/>
-      <c r="Z102" s="50"/>
+      <c r="N102" s="50"/>
+      <c r="O102" s="47"/>
+      <c r="P102" s="48"/>
+      <c r="Q102" s="47"/>
+      <c r="R102" s="47"/>
+      <c r="S102" s="47"/>
+      <c r="T102" s="47"/>
+      <c r="U102" s="49"/>
+      <c r="V102" s="50"/>
+      <c r="W102" s="50"/>
+      <c r="X102" s="50"/>
+      <c r="Y102" s="47"/>
+      <c r="Z102" s="47"/>
       <c r="AA102" s="25"/>
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="42"/>
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
-      <c r="D103" s="84"/>
+      <c r="D103" s="83"/>
       <c r="E103" s="57"/>
-      <c r="F103" s="53"/>
-      <c r="G103" s="53"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50"/>
       <c r="H103" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I103" s="53" t="str">
+      <c r="I103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,MIN(E103*H103,G103)," ")</f>
         <v> </v>
       </c>
-      <c r="J103" s="53" t="str">
+      <c r="J103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,F103+I103," ")</f>
         <v> </v>
       </c>
-      <c r="K103" s="53" t="str">
+      <c r="K103" s="50" t="str">
         <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
         <v> </v>
       </c>
-      <c r="L103" s="53"/>
-      <c r="M103" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="53"/>
-      <c r="O103" s="50"/>
-      <c r="P103" s="51" t="n">
+      <c r="L103" s="50"/>
+      <c r="M103" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="50"/>
+      <c r="O103" s="47"/>
+      <c r="P103" s="48" t="n">
         <f aca="false">IF(B103&gt;0,IF(B103&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q103" s="50" t="str">
+      <c r="Q103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103*P103/100," ")</f>
         <v> </v>
       </c>
-      <c r="R103" s="50"/>
-      <c r="S103" s="50" t="str">
+      <c r="R103" s="47"/>
+      <c r="S103" s="47" t="str">
         <f aca="false">IF(E103&gt;0,E103-Q103," ")</f>
         <v> </v>
       </c>
-      <c r="T103" s="50"/>
+      <c r="T103" s="47"/>
       <c r="U103" s="54"/>
       <c r="V103" s="57"/>
-      <c r="W103" s="53" t="str">
+      <c r="W103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,E103," ")</f>
         <v> </v>
       </c>
-      <c r="X103" s="53" t="str">
+      <c r="X103" s="50" t="str">
         <f aca="false">IF(V103&gt;0,J103," ")</f>
         <v> </v>
       </c>
-      <c r="Y103" s="50" t="str">
+      <c r="Y103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&lt;S103,(S103-V103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z103" s="50" t="str">
+      <c r="Z103" s="47" t="str">
         <f aca="false">IF((U103+V103)&gt;0,IF(V103&gt;S103,(V103-S103)*(1-M103)," ")," ")</f>
         <v> </v>
       </c>
@@ -7141,61 +7125,61 @@
       <c r="A104" s="42"/>
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
-      <c r="D104" s="84"/>
+      <c r="D104" s="83"/>
       <c r="E104" s="57"/>
-      <c r="F104" s="53"/>
-      <c r="G104" s="53"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50"/>
       <c r="H104" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I104" s="53" t="str">
+      <c r="I104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,MIN(E104*H104,G104)," ")</f>
         <v> </v>
       </c>
-      <c r="J104" s="53" t="str">
+      <c r="J104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,F104+I104," ")</f>
         <v> </v>
       </c>
-      <c r="K104" s="53" t="str">
+      <c r="K104" s="50" t="str">
         <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
         <v> </v>
       </c>
-      <c r="L104" s="53"/>
-      <c r="M104" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="53"/>
-      <c r="O104" s="50"/>
-      <c r="P104" s="51" t="n">
+      <c r="L104" s="50"/>
+      <c r="M104" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="50"/>
+      <c r="O104" s="47"/>
+      <c r="P104" s="48" t="n">
         <f aca="false">IF(B104&gt;0,IF(B104&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q104" s="50" t="str">
+      <c r="Q104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104*P104/100," ")</f>
         <v> </v>
       </c>
-      <c r="R104" s="50"/>
-      <c r="S104" s="50" t="str">
+      <c r="R104" s="47"/>
+      <c r="S104" s="47" t="str">
         <f aca="false">IF(E104&gt;0,E104-Q104," ")</f>
         <v> </v>
       </c>
-      <c r="T104" s="50"/>
+      <c r="T104" s="47"/>
       <c r="U104" s="54"/>
       <c r="V104" s="57"/>
-      <c r="W104" s="53" t="str">
+      <c r="W104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,E104," ")</f>
         <v> </v>
       </c>
-      <c r="X104" s="53" t="str">
+      <c r="X104" s="50" t="str">
         <f aca="false">IF(V104&gt;0,J104," ")</f>
         <v> </v>
       </c>
-      <c r="Y104" s="50" t="str">
+      <c r="Y104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&lt;S104,(S104-V104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z104" s="50" t="str">
+      <c r="Z104" s="47" t="str">
         <f aca="false">IF((U104+V104)&gt;0,IF(V104&gt;S104,(V104-S104)*(1-M104)," ")," ")</f>
         <v> </v>
       </c>
@@ -7205,61 +7189,61 @@
       <c r="A105" s="42"/>
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
-      <c r="D105" s="84"/>
+      <c r="D105" s="83"/>
       <c r="E105" s="57"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50"/>
       <c r="H105" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I105" s="53" t="str">
+      <c r="I105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,MIN(E105*H105,G105)," ")</f>
         <v> </v>
       </c>
-      <c r="J105" s="53" t="str">
+      <c r="J105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,F105+I105," ")</f>
         <v> </v>
       </c>
-      <c r="K105" s="53" t="str">
+      <c r="K105" s="50" t="str">
         <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
         <v> </v>
       </c>
-      <c r="L105" s="53"/>
-      <c r="M105" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="53"/>
-      <c r="O105" s="50"/>
-      <c r="P105" s="51" t="n">
+      <c r="L105" s="50"/>
+      <c r="M105" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="50"/>
+      <c r="O105" s="47"/>
+      <c r="P105" s="48" t="n">
         <f aca="false">IF(B105&gt;0,IF(B105&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q105" s="50" t="str">
+      <c r="Q105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105*P105/100," ")</f>
         <v> </v>
       </c>
-      <c r="R105" s="50"/>
-      <c r="S105" s="50" t="str">
+      <c r="R105" s="47"/>
+      <c r="S105" s="47" t="str">
         <f aca="false">IF(E105&gt;0,E105-Q105," ")</f>
         <v> </v>
       </c>
-      <c r="T105" s="50"/>
+      <c r="T105" s="47"/>
       <c r="U105" s="54"/>
       <c r="V105" s="57"/>
-      <c r="W105" s="53" t="str">
+      <c r="W105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,E105," ")</f>
         <v> </v>
       </c>
-      <c r="X105" s="53" t="str">
+      <c r="X105" s="50" t="str">
         <f aca="false">IF(V105&gt;0,J105," ")</f>
         <v> </v>
       </c>
-      <c r="Y105" s="50" t="str">
+      <c r="Y105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&lt;S105,(S105-V105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z105" s="50" t="str">
+      <c r="Z105" s="47" t="str">
         <f aca="false">IF((U105+V105)&gt;0,IF(V105&gt;S105,(V105-S105)*(1-M105)," ")," ")</f>
         <v> </v>
       </c>
@@ -7269,61 +7253,61 @@
       <c r="A106" s="42"/>
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
-      <c r="D106" s="84"/>
+      <c r="D106" s="83"/>
       <c r="E106" s="57"/>
-      <c r="F106" s="53"/>
-      <c r="G106" s="53"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50"/>
       <c r="H106" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I106" s="53" t="str">
+      <c r="I106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,MIN(E106*H106,G106)," ")</f>
         <v> </v>
       </c>
-      <c r="J106" s="53" t="str">
+      <c r="J106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,F106+I106," ")</f>
         <v> </v>
       </c>
-      <c r="K106" s="53" t="str">
+      <c r="K106" s="50" t="str">
         <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
         <v> </v>
       </c>
-      <c r="L106" s="53"/>
-      <c r="M106" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="53"/>
-      <c r="O106" s="50"/>
-      <c r="P106" s="51" t="n">
+      <c r="L106" s="50"/>
+      <c r="M106" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="50"/>
+      <c r="O106" s="47"/>
+      <c r="P106" s="48" t="n">
         <f aca="false">IF(B106&gt;0,IF(B106&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q106" s="50" t="str">
+      <c r="Q106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106*P106/100," ")</f>
         <v> </v>
       </c>
-      <c r="R106" s="50"/>
-      <c r="S106" s="50" t="str">
+      <c r="R106" s="47"/>
+      <c r="S106" s="47" t="str">
         <f aca="false">IF(E106&gt;0,E106-Q106," ")</f>
         <v> </v>
       </c>
-      <c r="T106" s="50"/>
+      <c r="T106" s="47"/>
       <c r="U106" s="54"/>
       <c r="V106" s="57"/>
-      <c r="W106" s="53" t="str">
+      <c r="W106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,E106," ")</f>
         <v> </v>
       </c>
-      <c r="X106" s="53" t="str">
+      <c r="X106" s="50" t="str">
         <f aca="false">IF(V106&gt;0,J106," ")</f>
         <v> </v>
       </c>
-      <c r="Y106" s="50" t="str">
+      <c r="Y106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&lt;S106,(S106-V106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z106" s="50" t="str">
+      <c r="Z106" s="47" t="str">
         <f aca="false">IF((U106+V106)&gt;0,IF(V106&gt;S106,(V106-S106)*(1-M106)," ")," ")</f>
         <v> </v>
       </c>
@@ -7333,61 +7317,61 @@
       <c r="A107" s="42"/>
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
-      <c r="D107" s="84"/>
+      <c r="D107" s="83"/>
       <c r="E107" s="57"/>
-      <c r="F107" s="53"/>
-      <c r="G107" s="53"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50"/>
       <c r="H107" s="58" t="n">
         <f aca="false">H$96</f>
         <v>0.25</v>
       </c>
-      <c r="I107" s="53" t="str">
+      <c r="I107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,MIN(E107*H107,G107)," ")</f>
         <v> </v>
       </c>
-      <c r="J107" s="53" t="str">
+      <c r="J107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,F107+I107," ")</f>
         <v> </v>
       </c>
-      <c r="K107" s="53" t="str">
+      <c r="K107" s="50" t="str">
         <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
         <v> </v>
       </c>
-      <c r="L107" s="53"/>
-      <c r="M107" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="53"/>
-      <c r="O107" s="50"/>
-      <c r="P107" s="51" t="n">
+      <c r="L107" s="50"/>
+      <c r="M107" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="50"/>
+      <c r="O107" s="47"/>
+      <c r="P107" s="48" t="n">
         <f aca="false">IF(B107&gt;0,IF(B107&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q107" s="50" t="str">
+      <c r="Q107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107*P107/100," ")</f>
         <v> </v>
       </c>
-      <c r="R107" s="50"/>
-      <c r="S107" s="50" t="str">
+      <c r="R107" s="47"/>
+      <c r="S107" s="47" t="str">
         <f aca="false">IF(E107&gt;0,E107-Q107," ")</f>
         <v> </v>
       </c>
-      <c r="T107" s="50"/>
+      <c r="T107" s="47"/>
       <c r="U107" s="54"/>
       <c r="V107" s="57"/>
-      <c r="W107" s="53" t="str">
+      <c r="W107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,E107," ")</f>
         <v> </v>
       </c>
-      <c r="X107" s="53" t="str">
+      <c r="X107" s="50" t="str">
         <f aca="false">IF(V107&gt;0,J107," ")</f>
         <v> </v>
       </c>
-      <c r="Y107" s="50" t="str">
+      <c r="Y107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&lt;S107,(S107-V107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
-      <c r="Z107" s="50" t="str">
+      <c r="Z107" s="47" t="str">
         <f aca="false">IF((U107+V107)&gt;0,IF(V107&gt;S107,(V107-S107)*(1-M107)," ")," ")</f>
         <v> </v>
       </c>
@@ -7396,7 +7380,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7425,9 +7409,9 @@
         <f aca="false">SUM(K97:K107)</f>
         <v>0</v>
       </c>
-      <c r="L108" s="53"/>
+      <c r="L108" s="50"/>
       <c r="M108" s="58"/>
-      <c r="N108" s="53"/>
+      <c r="N108" s="50"/>
       <c r="O108" s="61" t="n">
         <f aca="false">SUM(O97:O107)</f>
         <v>0</v>
@@ -7445,8 +7429,8 @@
         <f aca="false">SUM(S97:S107)</f>
         <v>0</v>
       </c>
-      <c r="T108" s="50"/>
-      <c r="U108" s="52"/>
+      <c r="T108" s="47"/>
+      <c r="U108" s="49"/>
       <c r="V108" s="60" t="n">
         <f aca="false">SUM(V97:V107)</f>
         <v>0</v>
@@ -7471,140 +7455,140 @@
     </row>
     <row r="109" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="42"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="72"/>
-      <c r="D109" s="69"/>
-      <c r="E109" s="53"/>
-      <c r="F109" s="53"/>
-      <c r="G109" s="53"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="71"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="53"/>
-      <c r="J109" s="53"/>
-      <c r="K109" s="53"/>
-      <c r="L109" s="53"/>
+      <c r="I109" s="50"/>
+      <c r="J109" s="50"/>
+      <c r="K109" s="50"/>
+      <c r="L109" s="50"/>
       <c r="M109" s="58"/>
-      <c r="N109" s="53"/>
-      <c r="O109" s="50"/>
-      <c r="P109" s="51"/>
-      <c r="Q109" s="50"/>
-      <c r="R109" s="50"/>
-      <c r="S109" s="50"/>
-      <c r="T109" s="50"/>
-      <c r="U109" s="52"/>
-      <c r="V109" s="53"/>
-      <c r="W109" s="50"/>
-      <c r="X109" s="50"/>
-      <c r="Y109" s="50"/>
-      <c r="Z109" s="50"/>
+      <c r="N109" s="50"/>
+      <c r="O109" s="47"/>
+      <c r="P109" s="48"/>
+      <c r="Q109" s="47"/>
+      <c r="R109" s="47"/>
+      <c r="S109" s="47"/>
+      <c r="T109" s="47"/>
+      <c r="U109" s="49"/>
+      <c r="V109" s="50"/>
+      <c r="W109" s="47"/>
+      <c r="X109" s="47"/>
+      <c r="Y109" s="47"/>
+      <c r="Z109" s="47"/>
       <c r="AA109" s="25"/>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="42"/>
       <c r="B110" s="43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C110" s="43"/>
-      <c r="D110" s="87" t="n">
+      <c r="D110" s="86" t="n">
         <f aca="false">F59</f>
         <v>46477</v>
       </c>
-      <c r="E110" s="74" t="n">
+      <c r="E110" s="73" t="n">
         <f aca="false">E64+E75+E83+E94+E108</f>
         <v>0</v>
       </c>
-      <c r="F110" s="74" t="n">
+      <c r="F110" s="73" t="n">
         <f aca="false">F64+F75+F83+F94+F108</f>
         <v>0</v>
       </c>
-      <c r="G110" s="74" t="n">
+      <c r="G110" s="73" t="n">
         <f aca="false">G64+G75+G83+G94+G108</f>
         <v>0</v>
       </c>
       <c r="H110" s="58"/>
-      <c r="I110" s="74" t="n">
+      <c r="I110" s="73" t="n">
         <f aca="false">I64+I75+I83+I94+I108</f>
         <v>0</v>
       </c>
-      <c r="J110" s="74" t="n">
+      <c r="J110" s="73" t="n">
         <f aca="false">J64+J75+J83+J94+J108</f>
         <v>0</v>
       </c>
-      <c r="K110" s="74" t="n">
+      <c r="K110" s="73" t="n">
         <f aca="false">K64+K75+K83+K94+K108</f>
         <v>0</v>
       </c>
-      <c r="L110" s="53"/>
+      <c r="L110" s="50"/>
       <c r="M110" s="58"/>
-      <c r="N110" s="53"/>
-      <c r="O110" s="74" t="n">
+      <c r="N110" s="50"/>
+      <c r="O110" s="73" t="n">
         <f aca="false">O64+O75+O83+O94+O108</f>
         <v>0</v>
       </c>
       <c r="P110" s="62"/>
-      <c r="Q110" s="74" t="n">
+      <c r="Q110" s="73" t="n">
         <f aca="false">Q64+Q75+Q83+Q94+Q108</f>
         <v>0</v>
       </c>
-      <c r="R110" s="74" t="n">
+      <c r="R110" s="73" t="n">
         <f aca="false">R64+R75+R83+R94+R108</f>
         <v>0</v>
       </c>
-      <c r="S110" s="74" t="n">
+      <c r="S110" s="73" t="n">
         <f aca="false">S64+S75+S83+S94+S108</f>
         <v>0</v>
       </c>
-      <c r="T110" s="50"/>
-      <c r="U110" s="52"/>
-      <c r="V110" s="74" t="n">
+      <c r="T110" s="47"/>
+      <c r="U110" s="49"/>
+      <c r="V110" s="73" t="n">
         <f aca="false">V64+V75+V83+V94+V108</f>
         <v>0</v>
       </c>
-      <c r="W110" s="74" t="n">
+      <c r="W110" s="73" t="n">
         <f aca="false">W64+W75+W83+W94+W108</f>
         <v>0</v>
       </c>
-      <c r="X110" s="74" t="n">
+      <c r="X110" s="73" t="n">
         <f aca="false">X64+X75+X83+X94+X108</f>
         <v>0</v>
       </c>
-      <c r="Y110" s="74" t="n">
+      <c r="Y110" s="73" t="n">
         <f aca="false">Y64+Y75+Y83+Y94+Y108</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="74" t="n">
+      <c r="Z110" s="73" t="n">
         <f aca="false">Z64+Z75+Z83+Z94+Z108</f>
         <v>0</v>
       </c>
       <c r="AA110" s="25"/>
     </row>
     <row r="111" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="88"/>
-      <c r="B111" s="89"/>
-      <c r="C111" s="90"/>
-      <c r="D111" s="91"/>
-      <c r="E111" s="92"/>
-      <c r="F111" s="92"/>
-      <c r="G111" s="92"/>
-      <c r="H111" s="93"/>
-      <c r="I111" s="92"/>
-      <c r="J111" s="92"/>
-      <c r="K111" s="92"/>
-      <c r="L111" s="92"/>
-      <c r="M111" s="93"/>
-      <c r="N111" s="92"/>
-      <c r="O111" s="94"/>
-      <c r="P111" s="95"/>
-      <c r="Q111" s="94"/>
-      <c r="R111" s="94"/>
-      <c r="S111" s="94"/>
-      <c r="T111" s="94"/>
-      <c r="U111" s="89"/>
-      <c r="V111" s="92"/>
-      <c r="W111" s="92"/>
-      <c r="X111" s="92"/>
-      <c r="Y111" s="94"/>
-      <c r="Z111" s="94"/>
-      <c r="AA111" s="96"/>
+      <c r="A111" s="87"/>
+      <c r="B111" s="88"/>
+      <c r="C111" s="89"/>
+      <c r="D111" s="90"/>
+      <c r="E111" s="91"/>
+      <c r="F111" s="91"/>
+      <c r="G111" s="91"/>
+      <c r="H111" s="92"/>
+      <c r="I111" s="91"/>
+      <c r="J111" s="91"/>
+      <c r="K111" s="91"/>
+      <c r="L111" s="91"/>
+      <c r="M111" s="92"/>
+      <c r="N111" s="91"/>
+      <c r="O111" s="93"/>
+      <c r="P111" s="94"/>
+      <c r="Q111" s="93"/>
+      <c r="R111" s="93"/>
+      <c r="S111" s="93"/>
+      <c r="T111" s="93"/>
+      <c r="U111" s="88"/>
+      <c r="V111" s="91"/>
+      <c r="W111" s="91"/>
+      <c r="X111" s="91"/>
+      <c r="Y111" s="93"/>
+      <c r="Z111" s="93"/>
+      <c r="AA111" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="54">
@@ -7688,37 +7672,37 @@
   <dimension ref="A1:X16"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="97" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="97" width="27.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="97" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="97" width="3.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="97" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="97" width="5.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="97" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="97" width="6.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="97" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="97" width="2.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="97" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="97" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="97" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="96" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="96" width="27.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="96" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="96" width="3.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="96" width="5.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="7" style="96" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="96" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="96" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="96" width="2.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="96" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="96" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="96" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="98"/>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="99"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="98"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -7730,23 +7714,23 @@
       <c r="X1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="104" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="107"/>
+      <c r="A2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="106"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -7758,21 +7742,21 @@
       <c r="X2" s="7"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="100"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="107"/>
+      <c r="A3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="104"/>
+      <c r="O3" s="106"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -7784,31 +7768,31 @@
       <c r="X3" s="7"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="100"/>
-      <c r="B4" s="110" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="111" t="s">
+      <c r="A4" s="99"/>
+      <c r="B4" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="105"/>
-      <c r="G4" s="112" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="111" t="s">
+      <c r="F4" s="104"/>
+      <c r="G4" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="105"/>
-      <c r="M4" s="113" t="s">
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="113"/>
-      <c r="O4" s="107"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" s="112"/>
+      <c r="O4" s="106"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -7820,25 +7804,25 @@
       <c r="X4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="100"/>
-      <c r="B5" s="101" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="101" t="s">
+      <c r="A5" s="99"/>
+      <c r="B5" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="102"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="105"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="107"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="101"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="112"/>
+      <c r="N5" s="112"/>
+      <c r="O5" s="106"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -7850,31 +7834,31 @@
       <c r="X5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="100"/>
-      <c r="B6" s="114" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="115" t="n">
+      <c r="A6" s="99"/>
+      <c r="B6" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114" t="n">
         <f aca="false">Schedule!E64</f>
         <v>0</v>
       </c>
-      <c r="F6" s="105"/>
-      <c r="G6" s="114" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="114"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="115" t="n">
+      <c r="F6" s="104"/>
+      <c r="G6" s="113" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="114" t="n">
         <f aca="false">Schedule!V11+Schedule!V64</f>
         <v>0</v>
       </c>
-      <c r="L6" s="105"/>
-      <c r="M6" s="113"/>
-      <c r="N6" s="113"/>
-      <c r="O6" s="107"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="112"/>
+      <c r="N6" s="112"/>
+      <c r="O6" s="106"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -7886,31 +7870,31 @@
       <c r="X6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="100"/>
-      <c r="B7" s="114" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115" t="n">
+      <c r="A7" s="99"/>
+      <c r="B7" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="114" t="n">
         <f aca="false">Schedule!E75</f>
         <v>0</v>
       </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="114" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="114"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
-      <c r="K7" s="115" t="n">
+      <c r="F7" s="104"/>
+      <c r="G7" s="113" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="114" t="n">
         <f aca="false">Schedule!V22+Schedule!V75</f>
         <v>0</v>
       </c>
-      <c r="L7" s="105"/>
-      <c r="M7" s="113"/>
-      <c r="N7" s="113"/>
-      <c r="O7" s="107"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="112"/>
+      <c r="O7" s="106"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -7922,31 +7906,31 @@
       <c r="X7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="100"/>
-      <c r="B8" s="114" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="115" t="n">
+      <c r="A8" s="99"/>
+      <c r="B8" s="113" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="113"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="114" t="n">
         <f aca="false">Schedule!E83</f>
         <v>0</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="114" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="114"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="115" t="n">
+      <c r="F8" s="104"/>
+      <c r="G8" s="113" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="114" t="n">
         <f aca="false">Schedule!V30+Schedule!V83</f>
         <v>0</v>
       </c>
-      <c r="L8" s="105"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="113"/>
-      <c r="O8" s="107"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="106"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -7958,31 +7942,31 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="100"/>
-      <c r="B9" s="114" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="115" t="n">
+      <c r="A9" s="99"/>
+      <c r="B9" s="113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="114" t="n">
         <f aca="false">Schedule!E94</f>
         <v>0</v>
       </c>
-      <c r="F9" s="105"/>
-      <c r="G9" s="114" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="115" t="n">
+      <c r="F9" s="104"/>
+      <c r="G9" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="114" t="n">
         <f aca="false">Schedule!V41+Schedule!V94</f>
         <v>0</v>
       </c>
-      <c r="L9" s="105"/>
-      <c r="M9" s="113"/>
-      <c r="N9" s="113"/>
-      <c r="O9" s="107"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="106"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -7994,31 +7978,31 @@
       <c r="X9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="100"/>
-      <c r="B10" s="114" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="115" t="n">
+      <c r="A10" s="99"/>
+      <c r="B10" s="113" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="114" t="n">
         <f aca="false">Schedule!E108</f>
         <v>0</v>
       </c>
-      <c r="F10" s="105"/>
-      <c r="G10" s="114" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="114"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="115" t="n">
+      <c r="F10" s="104"/>
+      <c r="G10" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="114" t="n">
         <f aca="false">Schedule!V55+Schedule!V108</f>
         <v>0</v>
       </c>
-      <c r="L10" s="105"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="113"/>
-      <c r="O10" s="107"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="106"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -8030,31 +8014,31 @@
       <c r="X10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="100"/>
-      <c r="B11" s="116" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="117" t="n">
+      <c r="A11" s="99"/>
+      <c r="B11" s="115" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="116" t="n">
         <f aca="false">SUM(E6:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="105"/>
-      <c r="G11" s="118" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="118"/>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="117" t="n">
+      <c r="F11" s="104"/>
+      <c r="G11" s="117" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="116" t="n">
         <f aca="false">SUM(K6:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="105"/>
-      <c r="M11" s="113"/>
-      <c r="N11" s="113"/>
-      <c r="O11" s="107"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="106"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -8066,21 +8050,21 @@
       <c r="X11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="105"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="113"/>
-      <c r="O12" s="107"/>
+      <c r="A12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="106"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -8092,31 +8076,31 @@
       <c r="X12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="100"/>
-      <c r="B13" s="116" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="117" t="e">
+      <c r="A13" s="99"/>
+      <c r="B13" s="115" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="116" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="F13" s="105"/>
-      <c r="G13" s="118" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="117" t="e">
+      <c r="F13" s="104"/>
+      <c r="G13" s="117" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="116" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="L13" s="105"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="113"/>
-      <c r="O13" s="107"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="106"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -8128,21 +8112,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="100"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
-      <c r="O14" s="107"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="106"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -8154,33 +8138,33 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="100"/>
-      <c r="B15" s="119" t="e">
+      <c r="A15" s="99"/>
+      <c r="B15" s="118" t="e">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
         <v>#N/A</v>
       </c>
-      <c r="C15" s="119"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="120" t="e">
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="119" t="e">
         <f aca="false">E13-E11</f>
         <v>#N/A</v>
       </c>
-      <c r="F15" s="105"/>
-      <c r="G15" s="119" t="e">
+      <c r="F15" s="104"/>
+      <c r="G15" s="118" t="e">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
         <v>#N/A</v>
       </c>
-      <c r="H15" s="119"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
-      <c r="K15" s="120" t="e">
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="119" t="e">
         <f aca="false">K13-K11</f>
         <v>#N/A</v>
       </c>
-      <c r="L15" s="105"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
-      <c r="O15" s="107"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="106"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -8192,21 +8176,21 @@
       <c r="X15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="123"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="125"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="125"/>
-      <c r="K16" s="125"/>
-      <c r="L16" s="125"/>
-      <c r="M16" s="126"/>
-      <c r="N16" s="125"/>
-      <c r="O16" s="127"/>
+      <c r="A16" s="120"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="125"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="126"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -8258,122 +8242,122 @@
   <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="128" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="1.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="128" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="128" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="127" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="129" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="128" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="128" width="1.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="128" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="127" width="1.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="14" style="127" width="9.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="130"/>
-      <c r="B1" s="101"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="130"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="129"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="130"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="134" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="134"/>
-      <c r="E2" s="135" t="n">
+      <c r="A2" s="129"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="133" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="n">
         <f aca="false">SUM(E8:E26)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="136"/>
-      <c r="G2" s="137" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="130"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="136" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="129"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="130"/>
-      <c r="B3" s="138" t="s">
-        <v>53</v>
+      <c r="A3" s="129"/>
+      <c r="B3" s="137" t="s">
+        <v>54</v>
       </c>
       <c r="C3" s="62"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="130"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="129"/>
     </row>
     <row r="4" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="130"/>
-      <c r="B4" s="52"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="49"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="130"/>
-    </row>
-    <row r="5" s="143" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="141"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="129"/>
+    </row>
+    <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="142" t="s">
+      <c r="E5" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="142" t="s">
+      <c r="F5" s="141" t="s">
         <v>59</v>
       </c>
+      <c r="G5" s="141" t="s">
+        <v>60</v>
+      </c>
       <c r="H5" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
+      <c r="I5" s="141" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
       <c r="L5" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="M5" s="141"/>
-    </row>
-    <row r="6" s="143" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="141"/>
+        <v>63</v>
+      </c>
+      <c r="M5" s="140"/>
+    </row>
+    <row r="6" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="140"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -8381,507 +8365,507 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="142" t="s">
-        <v>63</v>
-      </c>
-      <c r="J6" s="142" t="s">
+      <c r="I6" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="142" t="s">
+      <c r="J6" s="141" t="s">
         <v>65</v>
       </c>
+      <c r="K6" s="141" t="s">
+        <v>66</v>
+      </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="141"/>
+      <c r="M6" s="140"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="130"/>
-      <c r="B7" s="52"/>
+      <c r="A7" s="129"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
       <c r="L7" s="62"/>
-      <c r="M7" s="130"/>
+      <c r="M7" s="129"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="130"/>
+      <c r="A8" s="129"/>
       <c r="B8" s="54"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="135"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="136" t="str">
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="135" t="str">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
         <v> </v>
       </c>
-      <c r="J8" s="136" t="str">
+      <c r="J8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
         <v> </v>
       </c>
-      <c r="K8" s="136" t="str">
+      <c r="K8" s="135" t="str">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="130"/>
+      <c r="M8" s="129"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="130"/>
-      <c r="B9" s="52"/>
+      <c r="A9" s="129"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="136"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
       <c r="L9" s="62"/>
-      <c r="M9" s="130"/>
+      <c r="M9" s="129"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="130"/>
+      <c r="A10" s="129"/>
       <c r="B10" s="54"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="136" t="e">
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J10" s="136" t="str">
+      <c r="J10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
         <v> </v>
       </c>
-      <c r="K10" s="136" t="str">
+      <c r="K10" s="135" t="str">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="130"/>
+      <c r="M10" s="129"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="130"/>
-      <c r="B11" s="52"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="62"/>
       <c r="D11" s="62"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="136"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="136"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="130"/>
+      <c r="M11" s="129"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="130"/>
+      <c r="A12" s="129"/>
       <c r="B12" s="54"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="136" t="e">
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J12" s="136" t="str">
+      <c r="J12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
         <v> </v>
       </c>
-      <c r="K12" s="136" t="str">
+      <c r="K12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,G12/H12," ")</f>
         <v> </v>
       </c>
       <c r="L12" s="56"/>
-      <c r="M12" s="130"/>
+      <c r="M12" s="129"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="130"/>
-      <c r="B13" s="52"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="136"/>
-      <c r="J13" s="136"/>
-      <c r="K13" s="136"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
       <c r="L13" s="62"/>
-      <c r="M13" s="130"/>
+      <c r="M13" s="129"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="130"/>
+      <c r="A14" s="129"/>
       <c r="B14" s="54"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="136" t="e">
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J14" s="136" t="str">
+      <c r="J14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
         <v> </v>
       </c>
-      <c r="K14" s="136" t="str">
+      <c r="K14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,G14/H14," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="56"/>
-      <c r="M14" s="130"/>
+      <c r="M14" s="129"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="130"/>
-      <c r="B15" s="52"/>
+      <c r="A15" s="129"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="62"/>
       <c r="D15" s="62"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="136"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="136"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
       <c r="L15" s="62"/>
-      <c r="M15" s="130"/>
+      <c r="M15" s="129"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="130"/>
+      <c r="A16" s="129"/>
       <c r="B16" s="54"/>
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="136" t="e">
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J16" s="136" t="str">
+      <c r="J16" s="135" t="str">
         <f aca="false">IF(H16&gt;0,I16-K16," ")</f>
         <v> </v>
       </c>
-      <c r="K16" s="136" t="str">
+      <c r="K16" s="135" t="str">
         <f aca="false">IF(H16&gt;0,G16/H16," ")</f>
         <v> </v>
       </c>
       <c r="L16" s="56"/>
-      <c r="M16" s="130"/>
+      <c r="M16" s="129"/>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="130"/>
-      <c r="B17" s="52"/>
+      <c r="A17" s="129"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="62"/>
       <c r="D17" s="62"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="135"/>
       <c r="L17" s="62"/>
-      <c r="M17" s="130"/>
+      <c r="M17" s="129"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="130"/>
+      <c r="A18" s="129"/>
       <c r="B18" s="54"/>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="144"/>
-      <c r="I18" s="136" t="e">
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="143"/>
+      <c r="I18" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J18" s="136" t="str">
+      <c r="J18" s="135" t="str">
         <f aca="false">IF(H18&gt;0,I18-K18," ")</f>
         <v> </v>
       </c>
-      <c r="K18" s="136" t="str">
+      <c r="K18" s="135" t="str">
         <f aca="false">IF(H18&gt;0,G18/H18," ")</f>
         <v> </v>
       </c>
       <c r="L18" s="56"/>
-      <c r="M18" s="130"/>
+      <c r="M18" s="129"/>
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="130"/>
-      <c r="B19" s="52"/>
+      <c r="A19" s="129"/>
+      <c r="B19" s="49"/>
       <c r="C19" s="62"/>
       <c r="D19" s="62"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="136"/>
-      <c r="K19" s="136"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="135"/>
       <c r="L19" s="62"/>
-      <c r="M19" s="130"/>
+      <c r="M19" s="129"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="130"/>
+      <c r="A20" s="129"/>
       <c r="B20" s="54"/>
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="144"/>
-      <c r="I20" s="136" t="e">
+      <c r="E20" s="134"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J20" s="136" t="str">
+      <c r="J20" s="135" t="str">
         <f aca="false">IF(H20&gt;0,I20-K20," ")</f>
         <v> </v>
       </c>
-      <c r="K20" s="136" t="str">
+      <c r="K20" s="135" t="str">
         <f aca="false">IF(H20&gt;0,G20/H20," ")</f>
         <v> </v>
       </c>
       <c r="L20" s="56"/>
-      <c r="M20" s="130"/>
+      <c r="M20" s="129"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="130"/>
-      <c r="B21" s="52"/>
+      <c r="A21" s="129"/>
+      <c r="B21" s="49"/>
       <c r="C21" s="62"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="136"/>
-      <c r="J21" s="136"/>
-      <c r="K21" s="136"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="135"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="135"/>
       <c r="L21" s="62"/>
-      <c r="M21" s="130"/>
+      <c r="M21" s="129"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="130"/>
+      <c r="A22" s="129"/>
       <c r="B22" s="54"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="135"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="144"/>
-      <c r="I22" s="136" t="e">
+      <c r="E22" s="134"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J22" s="136" t="str">
+      <c r="J22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
         <v> </v>
       </c>
-      <c r="K22" s="136" t="str">
+      <c r="K22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,G22/H22," ")</f>
         <v> </v>
       </c>
       <c r="L22" s="56"/>
-      <c r="M22" s="130"/>
+      <c r="M22" s="129"/>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="130"/>
-      <c r="B23" s="52"/>
+      <c r="A23" s="129"/>
+      <c r="B23" s="49"/>
       <c r="C23" s="62"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="136"/>
-      <c r="K23" s="136"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="130"/>
+      <c r="M23" s="129"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="130"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="54"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="136" t="e">
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J24" s="136" t="str">
+      <c r="J24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
         <v> </v>
       </c>
-      <c r="K24" s="136" t="str">
+      <c r="K24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,G24/H24," ")</f>
         <v> </v>
       </c>
       <c r="L24" s="56"/>
-      <c r="M24" s="130"/>
+      <c r="M24" s="129"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="130"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="129"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="62"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="136"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="136"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="135"/>
       <c r="L25" s="62"/>
-      <c r="M25" s="130"/>
+      <c r="M25" s="129"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="130"/>
+      <c r="A26" s="129"/>
       <c r="B26" s="54"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="135"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="136" t="e">
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J26" s="136" t="str">
+      <c r="J26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
         <v> </v>
       </c>
-      <c r="K26" s="136" t="str">
+      <c r="K26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,G26/H26," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="56"/>
-      <c r="M26" s="130"/>
+      <c r="M26" s="129"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="130"/>
-      <c r="B27" s="52"/>
+      <c r="A27" s="129"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="62"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="136"/>
-      <c r="J27" s="136"/>
-      <c r="K27" s="136"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
       <c r="L27" s="62"/>
-      <c r="M27" s="130"/>
+      <c r="M27" s="129"/>
     </row>
     <row r="28" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="130"/>
-      <c r="B28" s="101"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="132"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="132"/>
-      <c r="L28" s="103"/>
-      <c r="M28" s="130"/>
+      <c r="A28" s="129"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="102"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="131"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="129"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="130"/>
-      <c r="B29" s="138" t="s">
-        <v>66</v>
+      <c r="A29" s="129"/>
+      <c r="B29" s="137" t="s">
+        <v>67</v>
       </c>
       <c r="C29" s="62"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
       <c r="H29" s="62" t="s">
-        <v>67</v>
-      </c>
-      <c r="I29" s="133"/>
-      <c r="J29" s="133"/>
-      <c r="K29" s="133"/>
+        <v>68</v>
+      </c>
+      <c r="I29" s="132"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="132"/>
       <c r="L29" s="62"/>
-      <c r="M29" s="130"/>
+      <c r="M29" s="129"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="130"/>
-      <c r="B30" s="52"/>
+      <c r="A30" s="129"/>
+      <c r="B30" s="49"/>
       <c r="C30" s="62"/>
       <c r="D30" s="62"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="133"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="136"/>
-      <c r="J30" s="136"/>
-      <c r="K30" s="136"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
       <c r="L30" s="62"/>
-      <c r="M30" s="130"/>
-    </row>
-    <row r="31" s="143" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="141"/>
+      <c r="M30" s="129"/>
+    </row>
+    <row r="31" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="140"/>
       <c r="B31" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="142" t="s">
+      <c r="E31" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="142" t="s">
+      <c r="F31" s="141" t="s">
         <v>59</v>
       </c>
+      <c r="G31" s="141" t="s">
+        <v>60</v>
+      </c>
       <c r="H31" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I31" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="J31" s="142"/>
-      <c r="K31" s="142"/>
+      <c r="I31" s="141" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
       <c r="L31" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="M31" s="141"/>
-    </row>
-    <row r="32" s="143" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="141"/>
+        <v>63</v>
+      </c>
+      <c r="M31" s="140"/>
+    </row>
+    <row r="32" s="142" customFormat="true" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="140"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -8889,437 +8873,437 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
-      <c r="I32" s="142" t="s">
-        <v>63</v>
-      </c>
-      <c r="J32" s="142" t="s">
+      <c r="I32" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="K32" s="142" t="s">
+      <c r="J32" s="141" t="s">
         <v>65</v>
       </c>
+      <c r="K32" s="141" t="s">
+        <v>66</v>
+      </c>
       <c r="L32" s="21"/>
-      <c r="M32" s="141"/>
-    </row>
-    <row r="33" s="143" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="141"/>
-      <c r="B33" s="145"/>
-      <c r="C33" s="145"/>
-      <c r="D33" s="145"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="145"/>
-      <c r="H33" s="145"/>
-      <c r="I33" s="146"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="146"/>
-      <c r="L33" s="145"/>
-      <c r="M33" s="141"/>
+      <c r="M32" s="140"/>
+    </row>
+    <row r="33" s="142" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="140"/>
+      <c r="B33" s="144"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="144"/>
+      <c r="E33" s="144"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="144"/>
+      <c r="M33" s="140"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="130"/>
+      <c r="A34" s="129"/>
       <c r="B34" s="54"/>
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="144"/>
-      <c r="I34" s="136" t="str">
+      <c r="E34" s="134"/>
+      <c r="F34" s="134"/>
+      <c r="G34" s="134"/>
+      <c r="H34" s="143"/>
+      <c r="I34" s="135" t="str">
         <f aca="false">IF(E34&gt;0,(E34+F34+G34)/H34," ")</f>
         <v> </v>
       </c>
-      <c r="J34" s="136" t="str">
+      <c r="J34" s="135" t="str">
         <f aca="false">IF(H34&gt;0,I34-K34," ")</f>
         <v> </v>
       </c>
-      <c r="K34" s="136" t="str">
+      <c r="K34" s="135" t="str">
         <f aca="false">IF(H34&gt;0,G34/H34," ")</f>
         <v> </v>
       </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="130"/>
+      <c r="M34" s="129"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="130"/>
-      <c r="B35" s="52"/>
+      <c r="A35" s="129"/>
+      <c r="B35" s="49"/>
       <c r="C35" s="62"/>
       <c r="D35" s="62"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="133"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="136"/>
-      <c r="J35" s="136"/>
-      <c r="K35" s="136"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="135"/>
+      <c r="J35" s="135"/>
+      <c r="K35" s="135"/>
       <c r="L35" s="62"/>
-      <c r="M35" s="130"/>
+      <c r="M35" s="129"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="130"/>
+      <c r="A36" s="129"/>
       <c r="B36" s="54"/>
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
-      <c r="E36" s="135"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="135"/>
-      <c r="H36" s="144"/>
-      <c r="I36" s="136" t="e">
+      <c r="E36" s="134"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="134"/>
+      <c r="H36" s="143"/>
+      <c r="I36" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J36" s="136" t="str">
+      <c r="J36" s="135" t="str">
         <f aca="false">IF(H36&gt;0,I36-K36," ")</f>
         <v> </v>
       </c>
-      <c r="K36" s="136" t="str">
+      <c r="K36" s="135" t="str">
         <f aca="false">IF(H36&gt;0,G36/H36," ")</f>
         <v> </v>
       </c>
       <c r="L36" s="56"/>
-      <c r="M36" s="130"/>
+      <c r="M36" s="129"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="130"/>
-      <c r="B37" s="52"/>
+      <c r="A37" s="129"/>
+      <c r="B37" s="49"/>
       <c r="C37" s="62"/>
       <c r="D37" s="62"/>
-      <c r="E37" s="133"/>
-      <c r="F37" s="133"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="136"/>
-      <c r="J37" s="136"/>
-      <c r="K37" s="136"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="132"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="135"/>
+      <c r="J37" s="135"/>
+      <c r="K37" s="135"/>
       <c r="L37" s="62"/>
-      <c r="M37" s="130"/>
+      <c r="M37" s="129"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="130"/>
+      <c r="A38" s="129"/>
       <c r="B38" s="54"/>
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
-      <c r="E38" s="135"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="135"/>
-      <c r="H38" s="144"/>
-      <c r="I38" s="136" t="e">
+      <c r="E38" s="134"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="134"/>
+      <c r="H38" s="143"/>
+      <c r="I38" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J38" s="136" t="str">
+      <c r="J38" s="135" t="str">
         <f aca="false">IF(H38&gt;0,I38-K38," ")</f>
         <v> </v>
       </c>
-      <c r="K38" s="136" t="str">
+      <c r="K38" s="135" t="str">
         <f aca="false">IF(H38&gt;0,G38/H38," ")</f>
         <v> </v>
       </c>
       <c r="L38" s="56"/>
-      <c r="M38" s="130"/>
+      <c r="M38" s="129"/>
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="130"/>
-      <c r="B39" s="52"/>
+      <c r="A39" s="129"/>
+      <c r="B39" s="49"/>
       <c r="C39" s="62"/>
       <c r="D39" s="62"/>
-      <c r="E39" s="133"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="133"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="136"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="132"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="135"/>
+      <c r="J39" s="135"/>
+      <c r="K39" s="135"/>
       <c r="L39" s="62"/>
-      <c r="M39" s="130"/>
+      <c r="M39" s="129"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="130"/>
+      <c r="A40" s="129"/>
       <c r="B40" s="54"/>
       <c r="C40" s="56"/>
       <c r="D40" s="56"/>
-      <c r="E40" s="135"/>
-      <c r="F40" s="135"/>
-      <c r="G40" s="135"/>
-      <c r="H40" s="144"/>
-      <c r="I40" s="136" t="e">
+      <c r="E40" s="134"/>
+      <c r="F40" s="134"/>
+      <c r="G40" s="134"/>
+      <c r="H40" s="143"/>
+      <c r="I40" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J40" s="136" t="str">
+      <c r="J40" s="135" t="str">
         <f aca="false">IF(H40&gt;0,I40-K40," ")</f>
         <v> </v>
       </c>
-      <c r="K40" s="136" t="str">
+      <c r="K40" s="135" t="str">
         <f aca="false">IF(H40&gt;0,G40/H40," ")</f>
         <v> </v>
       </c>
       <c r="L40" s="56"/>
-      <c r="M40" s="130"/>
+      <c r="M40" s="129"/>
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="130"/>
-      <c r="B41" s="52"/>
+      <c r="A41" s="129"/>
+      <c r="B41" s="49"/>
       <c r="C41" s="62"/>
       <c r="D41" s="62"/>
-      <c r="E41" s="133"/>
-      <c r="F41" s="133"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="136"/>
-      <c r="J41" s="136"/>
-      <c r="K41" s="136"/>
+      <c r="E41" s="132"/>
+      <c r="F41" s="132"/>
+      <c r="G41" s="132"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="135"/>
+      <c r="J41" s="135"/>
+      <c r="K41" s="135"/>
       <c r="L41" s="62"/>
-      <c r="M41" s="130"/>
+      <c r="M41" s="129"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="130"/>
+      <c r="A42" s="129"/>
       <c r="B42" s="54"/>
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
-      <c r="E42" s="135"/>
-      <c r="F42" s="135"/>
-      <c r="G42" s="135"/>
-      <c r="H42" s="144"/>
-      <c r="I42" s="136" t="e">
+      <c r="E42" s="134"/>
+      <c r="F42" s="134"/>
+      <c r="G42" s="134"/>
+      <c r="H42" s="143"/>
+      <c r="I42" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J42" s="136" t="str">
+      <c r="J42" s="135" t="str">
         <f aca="false">IF(H42&gt;0,I42-K42," ")</f>
         <v> </v>
       </c>
-      <c r="K42" s="136" t="str">
+      <c r="K42" s="135" t="str">
         <f aca="false">IF(H42&gt;0,G42/H42," ")</f>
         <v> </v>
       </c>
       <c r="L42" s="56"/>
-      <c r="M42" s="130"/>
+      <c r="M42" s="129"/>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="130"/>
-      <c r="B43" s="52"/>
+      <c r="A43" s="129"/>
+      <c r="B43" s="49"/>
       <c r="C43" s="62"/>
       <c r="D43" s="62"/>
-      <c r="E43" s="133"/>
-      <c r="F43" s="133"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="136"/>
-      <c r="J43" s="136"/>
-      <c r="K43" s="136"/>
+      <c r="E43" s="132"/>
+      <c r="F43" s="132"/>
+      <c r="G43" s="132"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="135"/>
+      <c r="J43" s="135"/>
+      <c r="K43" s="135"/>
       <c r="L43" s="62"/>
-      <c r="M43" s="130"/>
+      <c r="M43" s="129"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="130"/>
+      <c r="A44" s="129"/>
       <c r="B44" s="54"/>
       <c r="C44" s="56"/>
       <c r="D44" s="56"/>
-      <c r="E44" s="135"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="135"/>
-      <c r="H44" s="144"/>
-      <c r="I44" s="136" t="e">
+      <c r="E44" s="134"/>
+      <c r="F44" s="134"/>
+      <c r="G44" s="134"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J44" s="136" t="str">
+      <c r="J44" s="135" t="str">
         <f aca="false">IF(H44&gt;0,I44-K44," ")</f>
         <v> </v>
       </c>
-      <c r="K44" s="136" t="str">
+      <c r="K44" s="135" t="str">
         <f aca="false">IF(H44&gt;0,G44/H44," ")</f>
         <v> </v>
       </c>
       <c r="L44" s="56"/>
-      <c r="M44" s="130"/>
+      <c r="M44" s="129"/>
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="130"/>
-      <c r="B45" s="52"/>
+      <c r="A45" s="129"/>
+      <c r="B45" s="49"/>
       <c r="C45" s="62"/>
       <c r="D45" s="62"/>
-      <c r="E45" s="133"/>
-      <c r="F45" s="133"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="136"/>
-      <c r="J45" s="136"/>
-      <c r="K45" s="136"/>
+      <c r="E45" s="132"/>
+      <c r="F45" s="132"/>
+      <c r="G45" s="132"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="135"/>
+      <c r="J45" s="135"/>
+      <c r="K45" s="135"/>
       <c r="L45" s="62"/>
-      <c r="M45" s="130"/>
+      <c r="M45" s="129"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="130"/>
+      <c r="A46" s="129"/>
       <c r="B46" s="54"/>
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
-      <c r="E46" s="135"/>
-      <c r="F46" s="135"/>
-      <c r="G46" s="135"/>
-      <c r="H46" s="144"/>
-      <c r="I46" s="136" t="e">
+      <c r="E46" s="134"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="134"/>
+      <c r="H46" s="143"/>
+      <c r="I46" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J46" s="136" t="str">
+      <c r="J46" s="135" t="str">
         <f aca="false">IF(H46&gt;0,I46-K46," ")</f>
         <v> </v>
       </c>
-      <c r="K46" s="136" t="str">
+      <c r="K46" s="135" t="str">
         <f aca="false">IF(H46&gt;0,G46/H46," ")</f>
         <v> </v>
       </c>
       <c r="L46" s="56"/>
-      <c r="M46" s="130"/>
+      <c r="M46" s="129"/>
     </row>
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="130"/>
-      <c r="B47" s="52"/>
+      <c r="A47" s="129"/>
+      <c r="B47" s="49"/>
       <c r="C47" s="62"/>
       <c r="D47" s="62"/>
-      <c r="E47" s="133"/>
-      <c r="F47" s="133"/>
-      <c r="G47" s="133"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="136"/>
-      <c r="J47" s="136"/>
-      <c r="K47" s="136"/>
+      <c r="E47" s="132"/>
+      <c r="F47" s="132"/>
+      <c r="G47" s="132"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="135"/>
+      <c r="J47" s="135"/>
+      <c r="K47" s="135"/>
       <c r="L47" s="62"/>
-      <c r="M47" s="130"/>
+      <c r="M47" s="129"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="130"/>
+      <c r="A48" s="129"/>
       <c r="B48" s="54"/>
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
-      <c r="E48" s="135"/>
-      <c r="F48" s="135"/>
-      <c r="G48" s="135"/>
-      <c r="H48" s="144"/>
-      <c r="I48" s="136" t="e">
+      <c r="E48" s="134"/>
+      <c r="F48" s="134"/>
+      <c r="G48" s="134"/>
+      <c r="H48" s="143"/>
+      <c r="I48" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J48" s="136" t="str">
+      <c r="J48" s="135" t="str">
         <f aca="false">IF(H48&gt;0,I48-K48," ")</f>
         <v> </v>
       </c>
-      <c r="K48" s="136" t="str">
+      <c r="K48" s="135" t="str">
         <f aca="false">IF(H48&gt;0,G48/H48," ")</f>
         <v> </v>
       </c>
       <c r="L48" s="56"/>
-      <c r="M48" s="130"/>
+      <c r="M48" s="129"/>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="130"/>
-      <c r="B49" s="52"/>
+      <c r="A49" s="129"/>
+      <c r="B49" s="49"/>
       <c r="C49" s="62"/>
       <c r="D49" s="62"/>
-      <c r="E49" s="133"/>
-      <c r="F49" s="133"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="136"/>
-      <c r="J49" s="136"/>
-      <c r="K49" s="136"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="135"/>
+      <c r="J49" s="135"/>
+      <c r="K49" s="135"/>
       <c r="L49" s="62"/>
-      <c r="M49" s="130"/>
+      <c r="M49" s="129"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="130"/>
+      <c r="A50" s="129"/>
       <c r="B50" s="54"/>
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
-      <c r="E50" s="135"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="135"/>
-      <c r="H50" s="144"/>
-      <c r="I50" s="136" t="e">
+      <c r="E50" s="134"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="134"/>
+      <c r="H50" s="143"/>
+      <c r="I50" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J50" s="136" t="str">
+      <c r="J50" s="135" t="str">
         <f aca="false">IF(H50&gt;0,I50-K50," ")</f>
         <v> </v>
       </c>
-      <c r="K50" s="136" t="str">
+      <c r="K50" s="135" t="str">
         <f aca="false">IF(H50&gt;0,G50/H50," ")</f>
         <v> </v>
       </c>
       <c r="L50" s="56"/>
-      <c r="M50" s="130"/>
+      <c r="M50" s="129"/>
     </row>
     <row r="51" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="130"/>
-      <c r="B51" s="52"/>
+      <c r="A51" s="129"/>
+      <c r="B51" s="49"/>
       <c r="C51" s="62"/>
       <c r="D51" s="62"/>
-      <c r="E51" s="133"/>
-      <c r="F51" s="133"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="136"/>
-      <c r="J51" s="136"/>
-      <c r="K51" s="136"/>
+      <c r="E51" s="132"/>
+      <c r="F51" s="132"/>
+      <c r="G51" s="132"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="135"/>
+      <c r="J51" s="135"/>
+      <c r="K51" s="135"/>
       <c r="L51" s="62"/>
-      <c r="M51" s="130"/>
+      <c r="M51" s="129"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="130"/>
+      <c r="A52" s="129"/>
       <c r="B52" s="54"/>
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
-      <c r="E52" s="135"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="135"/>
-      <c r="H52" s="144"/>
-      <c r="I52" s="136" t="e">
+      <c r="E52" s="134"/>
+      <c r="F52" s="134"/>
+      <c r="G52" s="134"/>
+      <c r="H52" s="143"/>
+      <c r="I52" s="135" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
-      <c r="J52" s="136" t="str">
+      <c r="J52" s="135" t="str">
         <f aca="false">IF(H52&gt;0,I52-K52," ")</f>
         <v> </v>
       </c>
-      <c r="K52" s="136" t="str">
+      <c r="K52" s="135" t="str">
         <f aca="false">IF(H52&gt;0,G52/H52," ")</f>
         <v> </v>
       </c>
       <c r="L52" s="56"/>
-      <c r="M52" s="130"/>
+      <c r="M52" s="129"/>
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="130"/>
-      <c r="B53" s="52"/>
+      <c r="A53" s="129"/>
+      <c r="B53" s="49"/>
       <c r="C53" s="62"/>
       <c r="D53" s="62"/>
-      <c r="E53" s="133"/>
-      <c r="F53" s="133"/>
-      <c r="G53" s="133"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="136"/>
-      <c r="J53" s="136"/>
-      <c r="K53" s="136"/>
+      <c r="E53" s="132"/>
+      <c r="F53" s="132"/>
+      <c r="G53" s="132"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="135"/>
+      <c r="J53" s="135"/>
+      <c r="K53" s="135"/>
       <c r="L53" s="62"/>
-      <c r="M53" s="130"/>
+      <c r="M53" s="129"/>
     </row>
     <row r="54" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="130"/>
-      <c r="B54" s="101"/>
-      <c r="C54" s="103"/>
-      <c r="D54" s="103"/>
-      <c r="E54" s="130"/>
-      <c r="F54" s="130"/>
-      <c r="G54" s="130"/>
-      <c r="H54" s="131"/>
-      <c r="I54" s="132"/>
-      <c r="J54" s="132"/>
-      <c r="K54" s="132"/>
-      <c r="L54" s="103"/>
-      <c r="M54" s="130"/>
+      <c r="A54" s="129"/>
+      <c r="B54" s="100"/>
+      <c r="C54" s="102"/>
+      <c r="D54" s="102"/>
+      <c r="E54" s="129"/>
+      <c r="F54" s="129"/>
+      <c r="G54" s="129"/>
+      <c r="H54" s="130"/>
+      <c r="I54" s="131"/>
+      <c r="J54" s="131"/>
+      <c r="K54" s="131"/>
+      <c r="L54" s="102"/>
+      <c r="M54" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/examples/ltd-latest/Fixedassets.xlsx
+++ b/examples/ltd-latest/Fixedassets.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -350,6 +350,18 @@
     <t xml:space="preserve">Monthly Interest</t>
   </si>
   <si>
+    <t xml:space="preserve">Close Brothers Asset Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP-2025-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precision Tooling Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP-2025-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hire Purchase Agreements existing at start of financial year</t>
   </si>
   <si>
@@ -1331,7 +1343,7 @@
         </row>
         <row r="7">
           <cell r="N7">
-            <v>47026</v>
+            <v>46660</v>
           </cell>
         </row>
         <row r="11">
@@ -1531,7 +1543,7 @@
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>43662</v>
+        <v>30990</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1693,11 +1705,11 @@
       <c r="I4" s="23"/>
       <c r="J4" s="26" t="n">
         <f aca="false">[1]Admin!$N$7</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="K4" s="26" t="n">
         <f aca="false">J4</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
@@ -1715,7 +1727,7 @@
       </c>
       <c r="S4" s="10" t="n">
         <f aca="false">J4</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="T4" s="16"/>
       <c r="U4" s="17"/>
@@ -1846,7 +1858,7 @@
         <v> </v>
       </c>
       <c r="K8" s="50" t="str">
-        <f aca="false">IF(E8&gt;0,E8-J8," ")</f>
+        <f aca="false">IF(E8&gt;0,IF(V8&gt;0,0,E8-J8)," ")</f>
         <v> </v>
       </c>
       <c r="L8" s="50"/>
@@ -1896,7 +1908,7 @@
         <v> </v>
       </c>
       <c r="K9" s="50" t="str">
-        <f aca="false">IF(E9&gt;0,E9-J9," ")</f>
+        <f aca="false">IF(E9&gt;0,IF(V9&gt;0,0,E9-J9)," ")</f>
         <v> </v>
       </c>
       <c r="L9" s="50"/>
@@ -1946,7 +1958,7 @@
         <v> </v>
       </c>
       <c r="K10" s="50" t="str">
-        <f aca="false">IF(E10&gt;0,E10-J10," ")</f>
+        <f aca="false">IF(E10&gt;0,IF(V10&gt;0,0,E10-J10)," ")</f>
         <v> </v>
       </c>
       <c r="L10" s="50"/>
@@ -2135,7 +2147,7 @@
         <v> </v>
       </c>
       <c r="K14" s="50" t="str">
-        <f aca="false">IF(E14&gt;0,E14-J14," ")</f>
+        <f aca="false">IF(E14&gt;0,IF(V14&gt;0,0,E14-J14)," ")</f>
         <v> </v>
       </c>
       <c r="L14" s="50"/>
@@ -2197,7 +2209,7 @@
         <v> </v>
       </c>
       <c r="K15" s="50" t="str">
-        <f aca="false">IF(E15&gt;0,E15-J15," ")</f>
+        <f aca="false">IF(E15&gt;0,IF(V15&gt;0,0,E15-J15)," ")</f>
         <v> </v>
       </c>
       <c r="L15" s="50"/>
@@ -2259,7 +2271,7 @@
         <v> </v>
       </c>
       <c r="K16" s="50" t="str">
-        <f aca="false">IF(E16&gt;0,E16-J16," ")</f>
+        <f aca="false">IF(E16&gt;0,IF(V16&gt;0,0,E16-J16)," ")</f>
         <v> </v>
       </c>
       <c r="L16" s="50"/>
@@ -2321,7 +2333,7 @@
         <v> </v>
       </c>
       <c r="K17" s="50" t="str">
-        <f aca="false">IF(E17&gt;0,E17-J17," ")</f>
+        <f aca="false">IF(E17&gt;0,IF(V17&gt;0,0,E17-J17)," ")</f>
         <v> </v>
       </c>
       <c r="L17" s="50"/>
@@ -2383,7 +2395,7 @@
         <v> </v>
       </c>
       <c r="K18" s="50" t="str">
-        <f aca="false">IF(E18&gt;0,E18-J18," ")</f>
+        <f aca="false">IF(E18&gt;0,IF(V18&gt;0,0,E18-J18)," ")</f>
         <v> </v>
       </c>
       <c r="L18" s="50"/>
@@ -2445,7 +2457,7 @@
         <v> </v>
       </c>
       <c r="K19" s="50" t="str">
-        <f aca="false">IF(E19&gt;0,E19-J19," ")</f>
+        <f aca="false">IF(E19&gt;0,IF(V19&gt;0,0,E19-J19)," ")</f>
         <v> </v>
       </c>
       <c r="L19" s="50"/>
@@ -2507,7 +2519,7 @@
         <v> </v>
       </c>
       <c r="K20" s="50" t="str">
-        <f aca="false">IF(E20&gt;0,E20-J20," ")</f>
+        <f aca="false">IF(E20&gt;0,IF(V20&gt;0,0,E20-J20)," ")</f>
         <v> </v>
       </c>
       <c r="L20" s="50"/>
@@ -2569,7 +2581,7 @@
         <v> </v>
       </c>
       <c r="K21" s="50" t="str">
-        <f aca="false">IF(E21&gt;0,E21-J21," ")</f>
+        <f aca="false">IF(E21&gt;0,IF(V21&gt;0,0,E21-J21)," ")</f>
         <v> </v>
       </c>
       <c r="L21" s="50"/>
@@ -2770,7 +2782,7 @@
         <v> </v>
       </c>
       <c r="K25" s="50" t="str">
-        <f aca="false">IF(E25&gt;0,E25-J25," ")</f>
+        <f aca="false">IF(E25&gt;0,IF(V25&gt;0,0,E25-J25)," ")</f>
         <v> </v>
       </c>
       <c r="L25" s="50"/>
@@ -2832,7 +2844,7 @@
         <v> </v>
       </c>
       <c r="K26" s="50" t="str">
-        <f aca="false">IF(E26&gt;0,E26-J26," ")</f>
+        <f aca="false">IF(E26&gt;0,IF(V26&gt;0,0,E26-J26)," ")</f>
         <v> </v>
       </c>
       <c r="L26" s="50"/>
@@ -2894,7 +2906,7 @@
         <v> </v>
       </c>
       <c r="K27" s="50" t="str">
-        <f aca="false">IF(E27&gt;0,E27-J27," ")</f>
+        <f aca="false">IF(E27&gt;0,IF(V27&gt;0,0,E27-J27)," ")</f>
         <v> </v>
       </c>
       <c r="L27" s="50"/>
@@ -2956,7 +2968,7 @@
         <v> </v>
       </c>
       <c r="K28" s="50" t="str">
-        <f aca="false">IF(E28&gt;0,E28-J28," ")</f>
+        <f aca="false">IF(E28&gt;0,IF(V28&gt;0,0,E28-J28)," ")</f>
         <v> </v>
       </c>
       <c r="L28" s="50"/>
@@ -3018,7 +3030,7 @@
         <v> </v>
       </c>
       <c r="K29" s="50" t="str">
-        <f aca="false">IF(E29&gt;0,E29-J29," ")</f>
+        <f aca="false">IF(E29&gt;0,IF(V29&gt;0,0,E29-J29)," ")</f>
         <v> </v>
       </c>
       <c r="L29" s="50"/>
@@ -3225,7 +3237,7 @@
         <v>1260</v>
       </c>
       <c r="K33" s="50" t="n">
-        <f aca="false">IF(E33&gt;0,E33-J33," ")</f>
+        <f aca="false">IF(E33&gt;0,IF(V33&gt;0,0,E33-J33)," ")</f>
         <v>1740</v>
       </c>
       <c r="L33" s="50"/>
@@ -3287,7 +3299,7 @@
         <v> </v>
       </c>
       <c r="K34" s="50" t="str">
-        <f aca="false">IF(E34&gt;0,E34-J34," ")</f>
+        <f aca="false">IF(E34&gt;0,IF(V34&gt;0,0,E34-J34)," ")</f>
         <v> </v>
       </c>
       <c r="L34" s="50"/>
@@ -3349,7 +3361,7 @@
         <v> </v>
       </c>
       <c r="K35" s="50" t="str">
-        <f aca="false">IF(E35&gt;0,E35-J35," ")</f>
+        <f aca="false">IF(E35&gt;0,IF(V35&gt;0,0,E35-J35)," ")</f>
         <v> </v>
       </c>
       <c r="L35" s="50"/>
@@ -3411,7 +3423,7 @@
         <v> </v>
       </c>
       <c r="K36" s="50" t="str">
-        <f aca="false">IF(E36&gt;0,E36-J36," ")</f>
+        <f aca="false">IF(E36&gt;0,IF(V36&gt;0,0,E36-J36)," ")</f>
         <v> </v>
       </c>
       <c r="L36" s="50"/>
@@ -3473,7 +3485,7 @@
         <v> </v>
       </c>
       <c r="K37" s="50" t="str">
-        <f aca="false">IF(E37&gt;0,E37-J37," ")</f>
+        <f aca="false">IF(E37&gt;0,IF(V37&gt;0,0,E37-J37)," ")</f>
         <v> </v>
       </c>
       <c r="L37" s="50"/>
@@ -3535,7 +3547,7 @@
         <v> </v>
       </c>
       <c r="K38" s="50" t="str">
-        <f aca="false">IF(E38&gt;0,E38-J38," ")</f>
+        <f aca="false">IF(E38&gt;0,IF(V38&gt;0,0,E38-J38)," ")</f>
         <v> </v>
       </c>
       <c r="L38" s="50"/>
@@ -3597,7 +3609,7 @@
         <v> </v>
       </c>
       <c r="K39" s="50" t="str">
-        <f aca="false">IF(E39&gt;0,E39-J39," ")</f>
+        <f aca="false">IF(E39&gt;0,IF(V39&gt;0,0,E39-J39)," ")</f>
         <v> </v>
       </c>
       <c r="L39" s="50"/>
@@ -3659,7 +3671,7 @@
         <v> </v>
       </c>
       <c r="K40" s="50" t="str">
-        <f aca="false">IF(E40&gt;0,E40-J40," ")</f>
+        <f aca="false">IF(E40&gt;0,IF(V40&gt;0,0,E40-J40)," ")</f>
         <v> </v>
       </c>
       <c r="L40" s="50"/>
@@ -3860,7 +3872,7 @@
         <v> </v>
       </c>
       <c r="K44" s="50" t="str">
-        <f aca="false">IF(E44&gt;0,E44-J44," ")</f>
+        <f aca="false">IF(E44&gt;0,IF(V44&gt;0,0,E44-J44)," ")</f>
         <v> </v>
       </c>
       <c r="L44" s="50"/>
@@ -3924,7 +3936,7 @@
         <v> </v>
       </c>
       <c r="K45" s="50" t="str">
-        <f aca="false">IF(E45&gt;0,E45-J45," ")</f>
+        <f aca="false">IF(E45&gt;0,IF(V45&gt;0,0,E45-J45)," ")</f>
         <v> </v>
       </c>
       <c r="L45" s="50"/>
@@ -3988,7 +4000,7 @@
         <v> </v>
       </c>
       <c r="K46" s="50" t="str">
-        <f aca="false">IF(E46&gt;0,E46-J46," ")</f>
+        <f aca="false">IF(E46&gt;0,IF(V46&gt;0,0,E46-J46)," ")</f>
         <v> </v>
       </c>
       <c r="L46" s="50"/>
@@ -4052,7 +4064,7 @@
         <v> </v>
       </c>
       <c r="K47" s="50" t="str">
-        <f aca="false">IF(E47&gt;0,E47-J47," ")</f>
+        <f aca="false">IF(E47&gt;0,IF(V47&gt;0,0,E47-J47)," ")</f>
         <v> </v>
       </c>
       <c r="L47" s="50"/>
@@ -4116,7 +4128,7 @@
         <v> </v>
       </c>
       <c r="K48" s="50" t="str">
-        <f aca="false">IF(E48&gt;0,E48-J48," ")</f>
+        <f aca="false">IF(E48&gt;0,IF(V48&gt;0,0,E48-J48)," ")</f>
         <v> </v>
       </c>
       <c r="L48" s="50"/>
@@ -4217,8 +4229,8 @@
         <v>17328</v>
       </c>
       <c r="K50" s="50" t="n">
-        <f aca="false">IF(E50&gt;0,E50-J50," ")</f>
-        <v>12672</v>
+        <f aca="false">IF(E50&gt;0,IF(V50&gt;0,0,E50-J50)," ")</f>
+        <v>0</v>
       </c>
       <c r="L50" s="50"/>
       <c r="M50" s="66" t="n">
@@ -4287,7 +4299,7 @@
         <v> </v>
       </c>
       <c r="K51" s="50" t="str">
-        <f aca="false">IF(E51&gt;0,E51-J51," ")</f>
+        <f aca="false">IF(E51&gt;0,IF(V51&gt;0,0,E51-J51)," ")</f>
         <v> </v>
       </c>
       <c r="L51" s="50"/>
@@ -4351,7 +4363,7 @@
         <v> </v>
       </c>
       <c r="K52" s="50" t="str">
-        <f aca="false">IF(E52&gt;0,E52-J52," ")</f>
+        <f aca="false">IF(E52&gt;0,IF(V52&gt;0,0,E52-J52)," ")</f>
         <v> </v>
       </c>
       <c r="L52" s="50"/>
@@ -4415,7 +4427,7 @@
         <v> </v>
       </c>
       <c r="K53" s="50" t="str">
-        <f aca="false">IF(E53&gt;0,E53-J53," ")</f>
+        <f aca="false">IF(E53&gt;0,IF(V53&gt;0,0,E53-J53)," ")</f>
         <v> </v>
       </c>
       <c r="L53" s="50"/>
@@ -4479,7 +4491,7 @@
         <v> </v>
       </c>
       <c r="K54" s="50" t="str">
-        <f aca="false">IF(E54&gt;0,E54-J54," ")</f>
+        <f aca="false">IF(E54&gt;0,IF(V54&gt;0,0,E54-J54)," ")</f>
         <v> </v>
       </c>
       <c r="L54" s="50"/>
@@ -4550,7 +4562,7 @@
       </c>
       <c r="K55" s="61" t="n">
         <f aca="false">SUM(K44:K54)</f>
-        <v>12672</v>
+        <v>0</v>
       </c>
       <c r="L55" s="50"/>
       <c r="M55" s="69"/>
@@ -4659,7 +4671,7 @@
       </c>
       <c r="K57" s="73" t="n">
         <f aca="false">K11+K22+K30+K41+K55</f>
-        <v>14412</v>
+        <v>1740</v>
       </c>
       <c r="L57" s="50"/>
       <c r="M57" s="58"/>
@@ -4749,7 +4761,7 @@
       </c>
       <c r="F59" s="80" t="n">
         <f aca="false">J4</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="G59" s="81"/>
       <c r="H59" s="58"/>
@@ -4828,7 +4840,7 @@
         <v> </v>
       </c>
       <c r="K61" s="50" t="str">
-        <f aca="false">IF(E61&gt;0,E61-J61," ")</f>
+        <f aca="false">IF(E61&gt;0,IF(V61&gt;0,0,E61-J61)," ")</f>
         <v> </v>
       </c>
       <c r="L61" s="50"/>
@@ -4875,7 +4887,7 @@
         <v> </v>
       </c>
       <c r="K62" s="50" t="str">
-        <f aca="false">IF(E62&gt;0,E62-J62," ")</f>
+        <f aca="false">IF(E62&gt;0,IF(V62&gt;0,0,E62-J62)," ")</f>
         <v> </v>
       </c>
       <c r="L62" s="50"/>
@@ -4922,7 +4934,7 @@
         <v> </v>
       </c>
       <c r="K63" s="50" t="str">
-        <f aca="false">IF(E63&gt;0,E63-J63," ")</f>
+        <f aca="false">IF(E63&gt;0,IF(V63&gt;0,0,E63-J63)," ")</f>
         <v> </v>
       </c>
       <c r="L63" s="50"/>
@@ -5114,7 +5126,7 @@
         <v>150</v>
       </c>
       <c r="K67" s="50" t="n">
-        <f aca="false">IF(E67&gt;0,E67-J67," ")</f>
+        <f aca="false">IF(E67&gt;0,IF(V67&gt;0,0,E67-J67)," ")</f>
         <v>1350</v>
       </c>
       <c r="L67" s="50"/>
@@ -5182,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="K68" s="50" t="n">
-        <f aca="false">IF(E68&gt;0,E68-J68," ")</f>
+        <f aca="false">IF(E68&gt;0,IF(V68&gt;0,0,E68-J68)," ")</f>
         <v>900</v>
       </c>
       <c r="L68" s="50"/>
@@ -5250,7 +5262,7 @@
         <v>3000</v>
       </c>
       <c r="K69" s="50" t="n">
-        <f aca="false">IF(E69&gt;0,E69-J69," ")</f>
+        <f aca="false">IF(E69&gt;0,IF(V69&gt;0,0,E69-J69)," ")</f>
         <v>27000</v>
       </c>
       <c r="L69" s="50"/>
@@ -5312,7 +5324,7 @@
         <v> </v>
       </c>
       <c r="K70" s="50" t="str">
-        <f aca="false">IF(E70&gt;0,E70-J70," ")</f>
+        <f aca="false">IF(E70&gt;0,IF(V70&gt;0,0,E70-J70)," ")</f>
         <v> </v>
       </c>
       <c r="L70" s="50"/>
@@ -5374,7 +5386,7 @@
         <v> </v>
       </c>
       <c r="K71" s="50" t="str">
-        <f aca="false">IF(E71&gt;0,E71-J71," ")</f>
+        <f aca="false">IF(E71&gt;0,IF(V71&gt;0,0,E71-J71)," ")</f>
         <v> </v>
       </c>
       <c r="L71" s="50"/>
@@ -5436,7 +5448,7 @@
         <v> </v>
       </c>
       <c r="K72" s="50" t="str">
-        <f aca="false">IF(E72&gt;0,E72-J72," ")</f>
+        <f aca="false">IF(E72&gt;0,IF(V72&gt;0,0,E72-J72)," ")</f>
         <v> </v>
       </c>
       <c r="L72" s="50"/>
@@ -5498,7 +5510,7 @@
         <v> </v>
       </c>
       <c r="K73" s="50" t="str">
-        <f aca="false">IF(E73&gt;0,E73-J73," ")</f>
+        <f aca="false">IF(E73&gt;0,IF(V73&gt;0,0,E73-J73)," ")</f>
         <v> </v>
       </c>
       <c r="L73" s="50"/>
@@ -5560,7 +5572,7 @@
         <v> </v>
       </c>
       <c r="K74" s="50" t="str">
-        <f aca="false">IF(E74&gt;0,E74-J74," ")</f>
+        <f aca="false">IF(E74&gt;0,IF(V74&gt;0,0,E74-J74)," ")</f>
         <v> </v>
       </c>
       <c r="L74" s="50"/>
@@ -5761,7 +5773,7 @@
         <v> </v>
       </c>
       <c r="K78" s="50" t="str">
-        <f aca="false">IF(E78&gt;0,E78-J78," ")</f>
+        <f aca="false">IF(E78&gt;0,IF(V78&gt;0,0,E78-J78)," ")</f>
         <v> </v>
       </c>
       <c r="L78" s="50"/>
@@ -5823,7 +5835,7 @@
         <v> </v>
       </c>
       <c r="K79" s="50" t="str">
-        <f aca="false">IF(E79&gt;0,E79-J79," ")</f>
+        <f aca="false">IF(E79&gt;0,IF(V79&gt;0,0,E79-J79)," ")</f>
         <v> </v>
       </c>
       <c r="L79" s="50"/>
@@ -5885,7 +5897,7 @@
         <v> </v>
       </c>
       <c r="K80" s="50" t="str">
-        <f aca="false">IF(E80&gt;0,E80-J80," ")</f>
+        <f aca="false">IF(E80&gt;0,IF(V80&gt;0,0,E80-J80)," ")</f>
         <v> </v>
       </c>
       <c r="L80" s="50"/>
@@ -5947,7 +5959,7 @@
         <v> </v>
       </c>
       <c r="K81" s="50" t="str">
-        <f aca="false">IF(E81&gt;0,E81-J81," ")</f>
+        <f aca="false">IF(E81&gt;0,IF(V81&gt;0,0,E81-J81)," ")</f>
         <v> </v>
       </c>
       <c r="L81" s="50"/>
@@ -6009,7 +6021,7 @@
         <v> </v>
       </c>
       <c r="K82" s="50" t="str">
-        <f aca="false">IF(E82&gt;0,E82-J82," ")</f>
+        <f aca="false">IF(E82&gt;0,IF(V82&gt;0,0,E82-J82)," ")</f>
         <v> </v>
       </c>
       <c r="L82" s="50"/>
@@ -6210,7 +6222,7 @@
         <v> </v>
       </c>
       <c r="K86" s="50" t="str">
-        <f aca="false">IF(E86&gt;0,E86-J86," ")</f>
+        <f aca="false">IF(E86&gt;0,IF(V86&gt;0,0,E86-J86)," ")</f>
         <v> </v>
       </c>
       <c r="L86" s="50"/>
@@ -6272,7 +6284,7 @@
         <v> </v>
       </c>
       <c r="K87" s="50" t="str">
-        <f aca="false">IF(E87&gt;0,E87-J87," ")</f>
+        <f aca="false">IF(E87&gt;0,IF(V87&gt;0,0,E87-J87)," ")</f>
         <v> </v>
       </c>
       <c r="L87" s="50"/>
@@ -6334,7 +6346,7 @@
         <v> </v>
       </c>
       <c r="K88" s="50" t="str">
-        <f aca="false">IF(E88&gt;0,E88-J88," ")</f>
+        <f aca="false">IF(E88&gt;0,IF(V88&gt;0,0,E88-J88)," ")</f>
         <v> </v>
       </c>
       <c r="L88" s="50"/>
@@ -6396,7 +6408,7 @@
         <v> </v>
       </c>
       <c r="K89" s="50" t="str">
-        <f aca="false">IF(E89&gt;0,E89-J89," ")</f>
+        <f aca="false">IF(E89&gt;0,IF(V89&gt;0,0,E89-J89)," ")</f>
         <v> </v>
       </c>
       <c r="L89" s="50"/>
@@ -6458,7 +6470,7 @@
         <v> </v>
       </c>
       <c r="K90" s="50" t="str">
-        <f aca="false">IF(E90&gt;0,E90-J90," ")</f>
+        <f aca="false">IF(E90&gt;0,IF(V90&gt;0,0,E90-J90)," ")</f>
         <v> </v>
       </c>
       <c r="L90" s="50"/>
@@ -6520,7 +6532,7 @@
         <v> </v>
       </c>
       <c r="K91" s="50" t="str">
-        <f aca="false">IF(E91&gt;0,E91-J91," ")</f>
+        <f aca="false">IF(E91&gt;0,IF(V91&gt;0,0,E91-J91)," ")</f>
         <v> </v>
       </c>
       <c r="L91" s="50"/>
@@ -6582,7 +6594,7 @@
         <v> </v>
       </c>
       <c r="K92" s="50" t="str">
-        <f aca="false">IF(E92&gt;0,E92-J92," ")</f>
+        <f aca="false">IF(E92&gt;0,IF(V92&gt;0,0,E92-J92)," ")</f>
         <v> </v>
       </c>
       <c r="L92" s="50"/>
@@ -6644,7 +6656,7 @@
         <v> </v>
       </c>
       <c r="K93" s="50" t="str">
-        <f aca="false">IF(E93&gt;0,E93-J93," ")</f>
+        <f aca="false">IF(E93&gt;0,IF(V93&gt;0,0,E93-J93)," ")</f>
         <v> </v>
       </c>
       <c r="L93" s="50"/>
@@ -6845,7 +6857,7 @@
         <v> </v>
       </c>
       <c r="K97" s="50" t="str">
-        <f aca="false">IF(E97&gt;0,E97-J97," ")</f>
+        <f aca="false">IF(E97&gt;0,IF(V97&gt;0,0,E97-J97)," ")</f>
         <v> </v>
       </c>
       <c r="L97" s="50"/>
@@ -6906,7 +6918,7 @@
         <v> </v>
       </c>
       <c r="K98" s="50" t="str">
-        <f aca="false">IF(E98&gt;0,E98-J98," ")</f>
+        <f aca="false">IF(E98&gt;0,IF(V98&gt;0,0,E98-J98)," ")</f>
         <v> </v>
       </c>
       <c r="L98" s="50"/>
@@ -6967,7 +6979,7 @@
         <v> </v>
       </c>
       <c r="K99" s="50" t="str">
-        <f aca="false">IF(E99&gt;0,E99-J99," ")</f>
+        <f aca="false">IF(E99&gt;0,IF(V99&gt;0,0,E99-J99)," ")</f>
         <v> </v>
       </c>
       <c r="L99" s="50"/>
@@ -7028,7 +7040,7 @@
         <v> </v>
       </c>
       <c r="K100" s="50" t="str">
-        <f aca="false">IF(E100&gt;0,E100-J100," ")</f>
+        <f aca="false">IF(E100&gt;0,IF(V100&gt;0,0,E100-J100)," ")</f>
         <v> </v>
       </c>
       <c r="L100" s="50"/>
@@ -7089,7 +7101,7 @@
         <v> </v>
       </c>
       <c r="K101" s="50" t="str">
-        <f aca="false">IF(E101&gt;0,E101-J101," ")</f>
+        <f aca="false">IF(E101&gt;0,IF(V101&gt;0,0,E101-J101)," ")</f>
         <v> </v>
       </c>
       <c r="L101" s="50"/>
@@ -7181,7 +7193,7 @@
         <v> </v>
       </c>
       <c r="K103" s="50" t="str">
-        <f aca="false">IF(E103&gt;0,E103-J103," ")</f>
+        <f aca="false">IF(E103&gt;0,IF(V103&gt;0,0,E103-J103)," ")</f>
         <v> </v>
       </c>
       <c r="L103" s="50"/>
@@ -7245,7 +7257,7 @@
         <v> </v>
       </c>
       <c r="K104" s="50" t="str">
-        <f aca="false">IF(E104&gt;0,E104-J104," ")</f>
+        <f aca="false">IF(E104&gt;0,IF(V104&gt;0,0,E104-J104)," ")</f>
         <v> </v>
       </c>
       <c r="L104" s="50"/>
@@ -7309,7 +7321,7 @@
         <v> </v>
       </c>
       <c r="K105" s="50" t="str">
-        <f aca="false">IF(E105&gt;0,E105-J105," ")</f>
+        <f aca="false">IF(E105&gt;0,IF(V105&gt;0,0,E105-J105)," ")</f>
         <v> </v>
       </c>
       <c r="L105" s="50"/>
@@ -7373,7 +7385,7 @@
         <v> </v>
       </c>
       <c r="K106" s="50" t="str">
-        <f aca="false">IF(E106&gt;0,E106-J106," ")</f>
+        <f aca="false">IF(E106&gt;0,IF(V106&gt;0,0,E106-J106)," ")</f>
         <v> </v>
       </c>
       <c r="L106" s="50"/>
@@ -7437,7 +7449,7 @@
         <v> </v>
       </c>
       <c r="K107" s="50" t="str">
-        <f aca="false">IF(E107&gt;0,E107-J107," ")</f>
+        <f aca="false">IF(E107&gt;0,IF(V107&gt;0,0,E107-J107)," ")</f>
         <v> </v>
       </c>
       <c r="L107" s="50"/>
@@ -7593,7 +7605,7 @@
       <c r="C110" s="43"/>
       <c r="D110" s="86" t="n">
         <f aca="false">F59</f>
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="E110" s="73" t="n">
         <f aca="false">E64+E75+E83+E94+E108</f>
@@ -8381,7 +8393,7 @@
       <c r="D2" s="133"/>
       <c r="E2" s="134" t="n">
         <f aca="false">SUM(E8:E26)</f>
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="136" t="s">
@@ -8497,26 +8509,42 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="129"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="135" t="str">
+      <c r="B8" s="54" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="134" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F8" s="134" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" s="134" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H8" s="143" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="135" t="n">
         <f aca="false">IF(E8&gt;0,(E8+F8+G8)/H8," ")</f>
-        <v> </v>
-      </c>
-      <c r="J8" s="135" t="str">
+        <v>750</v>
+      </c>
+      <c r="J8" s="135" t="n">
         <f aca="false">IF(H8&gt;0,I8-K8," ")</f>
-        <v> </v>
-      </c>
-      <c r="K8" s="135" t="str">
+        <v>660</v>
+      </c>
+      <c r="K8" s="135" t="n">
         <f aca="false">IF(H8&gt;0,G8/H8," ")</f>
-        <v> </v>
-      </c>
-      <c r="L8" s="56"/>
+        <v>90</v>
+      </c>
+      <c r="L8" s="56" t="s">
+        <v>72</v>
+      </c>
       <c r="M8" s="129"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8536,26 +8564,42 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="129"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="143"/>
-      <c r="I10" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J10" s="135" t="str">
+      <c r="B10" s="54" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="134" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F10" s="134" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" s="134" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" s="143" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="135" t="n">
+        <f aca="false">IF(E10&gt;0,(E10+F10+G10)/H10," ")</f>
+        <v>405</v>
+      </c>
+      <c r="J10" s="135" t="n">
         <f aca="false">IF(H10&gt;0,I10-K10," ")</f>
-        <v> </v>
-      </c>
-      <c r="K10" s="135" t="str">
+        <v>355</v>
+      </c>
+      <c r="K10" s="135" t="n">
         <f aca="false">IF(H10&gt;0,G10/H10," ")</f>
-        <v> </v>
-      </c>
-      <c r="L10" s="56"/>
+        <v>50</v>
+      </c>
+      <c r="L10" s="56" t="s">
+        <v>72</v>
+      </c>
       <c r="M10" s="129"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8582,9 +8626,9 @@
       <c r="F12" s="134"/>
       <c r="G12" s="134"/>
       <c r="H12" s="143"/>
-      <c r="I12" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I12" s="135" t="str">
+        <f aca="false">IF(E12&gt;0,(E12+F12+G12)/H12," ")</f>
+        <v> </v>
       </c>
       <c r="J12" s="135" t="str">
         <f aca="false">IF(H12&gt;0,I12-K12," ")</f>
@@ -8621,9 +8665,9 @@
       <c r="F14" s="134"/>
       <c r="G14" s="134"/>
       <c r="H14" s="143"/>
-      <c r="I14" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I14" s="135" t="str">
+        <f aca="false">IF(E14&gt;0,(E14+F14+G14)/H14," ")</f>
+        <v> </v>
       </c>
       <c r="J14" s="135" t="str">
         <f aca="false">IF(H14&gt;0,I14-K14," ")</f>
@@ -8660,9 +8704,9 @@
       <c r="F16" s="134"/>
       <c r="G16" s="134"/>
       <c r="H16" s="143"/>
-      <c r="I16" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I16" s="135" t="str">
+        <f aca="false">IF(E16&gt;0,(E16+F16+G16)/H16," ")</f>
+        <v> </v>
       </c>
       <c r="J16" s="135" t="str">
         <f aca="false">IF(H16&gt;0,I16-K16," ")</f>
@@ -8699,9 +8743,9 @@
       <c r="F18" s="134"/>
       <c r="G18" s="134"/>
       <c r="H18" s="143"/>
-      <c r="I18" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I18" s="135" t="str">
+        <f aca="false">IF(E18&gt;0,(E18+F18+G18)/H18," ")</f>
+        <v> </v>
       </c>
       <c r="J18" s="135" t="str">
         <f aca="false">IF(H18&gt;0,I18-K18," ")</f>
@@ -8738,9 +8782,9 @@
       <c r="F20" s="134"/>
       <c r="G20" s="134"/>
       <c r="H20" s="143"/>
-      <c r="I20" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I20" s="135" t="str">
+        <f aca="false">IF(E20&gt;0,(E20+F20+G20)/H20," ")</f>
+        <v> </v>
       </c>
       <c r="J20" s="135" t="str">
         <f aca="false">IF(H20&gt;0,I20-K20," ")</f>
@@ -8777,9 +8821,9 @@
       <c r="F22" s="134"/>
       <c r="G22" s="134"/>
       <c r="H22" s="143"/>
-      <c r="I22" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I22" s="135" t="str">
+        <f aca="false">IF(E22&gt;0,(E22+F22+G22)/H22," ")</f>
+        <v> </v>
       </c>
       <c r="J22" s="135" t="str">
         <f aca="false">IF(H22&gt;0,I22-K22," ")</f>
@@ -8816,9 +8860,9 @@
       <c r="F24" s="134"/>
       <c r="G24" s="134"/>
       <c r="H24" s="143"/>
-      <c r="I24" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I24" s="135" t="str">
+        <f aca="false">IF(E24&gt;0,(E24+F24+G24)/H24," ")</f>
+        <v> </v>
       </c>
       <c r="J24" s="135" t="str">
         <f aca="false">IF(H24&gt;0,I24-K24," ")</f>
@@ -8855,9 +8899,9 @@
       <c r="F26" s="134"/>
       <c r="G26" s="134"/>
       <c r="H26" s="143"/>
-      <c r="I26" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I26" s="135" t="str">
+        <f aca="false">IF(E26&gt;0,(E26+F26+G26)/H26," ")</f>
+        <v> </v>
       </c>
       <c r="J26" s="135" t="str">
         <f aca="false">IF(H26&gt;0,I26-K26," ")</f>
@@ -8903,7 +8947,7 @@
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="129"/>
       <c r="B29" s="137" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C29" s="62"/>
       <c r="D29" s="138"/>
@@ -8911,7 +8955,7 @@
       <c r="F29" s="132"/>
       <c r="G29" s="132"/>
       <c r="H29" s="62" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I29" s="132"/>
       <c r="J29" s="132"/>
@@ -9051,9 +9095,9 @@
       <c r="F36" s="134"/>
       <c r="G36" s="134"/>
       <c r="H36" s="143"/>
-      <c r="I36" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I36" s="135" t="str">
+        <f aca="false">IF(E36&gt;0,(E36+F36+G36)/H36," ")</f>
+        <v> </v>
       </c>
       <c r="J36" s="135" t="str">
         <f aca="false">IF(H36&gt;0,I36-K36," ")</f>
@@ -9090,9 +9134,9 @@
       <c r="F38" s="134"/>
       <c r="G38" s="134"/>
       <c r="H38" s="143"/>
-      <c r="I38" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I38" s="135" t="str">
+        <f aca="false">IF(E38&gt;0,(E38+F38+G38)/H38," ")</f>
+        <v> </v>
       </c>
       <c r="J38" s="135" t="str">
         <f aca="false">IF(H38&gt;0,I38-K38," ")</f>
@@ -9129,9 +9173,9 @@
       <c r="F40" s="134"/>
       <c r="G40" s="134"/>
       <c r="H40" s="143"/>
-      <c r="I40" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I40" s="135" t="str">
+        <f aca="false">IF(E40&gt;0,(E40+F40+G40)/H40," ")</f>
+        <v> </v>
       </c>
       <c r="J40" s="135" t="str">
         <f aca="false">IF(H40&gt;0,I40-K40," ")</f>
@@ -9168,9 +9212,9 @@
       <c r="F42" s="134"/>
       <c r="G42" s="134"/>
       <c r="H42" s="143"/>
-      <c r="I42" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I42" s="135" t="str">
+        <f aca="false">IF(E42&gt;0,(E42+F42+G42)/H42," ")</f>
+        <v> </v>
       </c>
       <c r="J42" s="135" t="str">
         <f aca="false">IF(H42&gt;0,I42-K42," ")</f>
@@ -9207,9 +9251,9 @@
       <c r="F44" s="134"/>
       <c r="G44" s="134"/>
       <c r="H44" s="143"/>
-      <c r="I44" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I44" s="135" t="str">
+        <f aca="false">IF(E44&gt;0,(E44+F44+G44)/H44," ")</f>
+        <v> </v>
       </c>
       <c r="J44" s="135" t="str">
         <f aca="false">IF(H44&gt;0,I44-K44," ")</f>
@@ -9246,9 +9290,9 @@
       <c r="F46" s="134"/>
       <c r="G46" s="134"/>
       <c r="H46" s="143"/>
-      <c r="I46" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I46" s="135" t="str">
+        <f aca="false">IF(E46&gt;0,(E46+F46+G46)/H46," ")</f>
+        <v> </v>
       </c>
       <c r="J46" s="135" t="str">
         <f aca="false">IF(H46&gt;0,I46-K46," ")</f>
@@ -9285,9 +9329,9 @@
       <c r="F48" s="134"/>
       <c r="G48" s="134"/>
       <c r="H48" s="143"/>
-      <c r="I48" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I48" s="135" t="str">
+        <f aca="false">IF(E48&gt;0,(E48+F48+G48)/H48," ")</f>
+        <v> </v>
       </c>
       <c r="J48" s="135" t="str">
         <f aca="false">IF(H48&gt;0,I48-K48," ")</f>
@@ -9324,9 +9368,9 @@
       <c r="F50" s="134"/>
       <c r="G50" s="134"/>
       <c r="H50" s="143"/>
-      <c r="I50" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I50" s="135" t="str">
+        <f aca="false">IF(E50&gt;0,(E50+F50+G50)/H50," ")</f>
+        <v> </v>
       </c>
       <c r="J50" s="135" t="str">
         <f aca="false">IF(H50&gt;0,I50-K50," ")</f>
@@ -9363,9 +9407,9 @@
       <c r="F52" s="134"/>
       <c r="G52" s="134"/>
       <c r="H52" s="143"/>
-      <c r="I52" s="135" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="I52" s="135" t="str">
+        <f aca="false">IF(E52&gt;0,(E52+F52+G52)/H52," ")</f>
+        <v> </v>
       </c>
       <c r="J52" s="135" t="str">
         <f aca="false">IF(H52&gt;0,I52-K52," ")</f>

--- a/examples/ltd-latest/Fixedassets.xlsx
+++ b/examples/ltd-latest/Fixedassets.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -239,6 +239,9 @@
     <t xml:space="preserve">Dell</t>
   </si>
   <si>
+    <t xml:space="preserve">Precision Tooling Supplies</t>
+  </si>
+  <si>
     <t xml:space="preserve">IKEA</t>
   </si>
   <si>
@@ -354,9 +357,6 @@
   </si>
   <si>
     <t xml:space="preserve">HP-2025-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precision Tooling Supplies</t>
   </si>
   <si>
     <t xml:space="preserve">HP-2025-02</t>
@@ -1520,7 +1520,7 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12" t="n">
         <f aca="false">E57+E110</f>
-        <v>65500</v>
+        <v>85500</v>
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
@@ -1535,15 +1535,15 @@
       </c>
       <c r="I1" s="13" t="n">
         <f aca="false">I57+I110</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="J1" s="13" t="n">
         <f aca="false">J57+J110</f>
-        <v>21838</v>
+        <v>23838</v>
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>30990</v>
+        <v>48990</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Q1" s="13" t="n">
         <f aca="false">Q57+Q110</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
@@ -5170,14 +5170,14 @@
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
       <c r="B68" s="54" t="n">
-        <v>46037</v>
+        <v>45992</v>
       </c>
       <c r="C68" s="55" t="s">
         <v>33</v>
       </c>
       <c r="D68" s="56"/>
       <c r="E68" s="57" t="n">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="F68" s="50"/>
       <c r="G68" s="50"/>
@@ -5187,15 +5187,15 @@
       </c>
       <c r="I68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,MIN(E68*H68,G68)," ")</f>
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="J68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,F68+I68," ")</f>
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="K68" s="50" t="n">
         <f aca="false">IF(E68&gt;0,IF(V68&gt;0,0,E68-J68)," ")</f>
-        <v>900</v>
+        <v>11700</v>
       </c>
       <c r="L68" s="50"/>
       <c r="M68" s="58"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Q68" s="47" t="n">
         <f aca="false">IF(E68&gt;0,E68*P68/100," ")</f>
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="R68" s="47"/>
       <c r="S68" s="47" t="n">
@@ -5238,14 +5238,14 @@
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
       <c r="B69" s="54" t="n">
-        <v>46137</v>
+        <v>46037</v>
       </c>
       <c r="C69" s="55" t="s">
         <v>34</v>
       </c>
       <c r="D69" s="56"/>
       <c r="E69" s="57" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="F69" s="50"/>
       <c r="G69" s="50"/>
@@ -5255,15 +5255,15 @@
       </c>
       <c r="I69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,MIN(E69*H69,G69)," ")</f>
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="J69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,F69+I69," ")</f>
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="K69" s="50" t="n">
         <f aca="false">IF(E69&gt;0,IF(V69&gt;0,0,E69-J69)," ")</f>
-        <v>27000</v>
+        <v>900</v>
       </c>
       <c r="L69" s="50"/>
       <c r="M69" s="58"/>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="Q69" s="47" t="n">
         <f aca="false">IF(E69&gt;0,E69*P69/100," ")</f>
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="R69" s="47"/>
       <c r="S69" s="47" t="n">
@@ -5305,27 +5305,33 @@
     </row>
     <row r="70" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="42"/>
-      <c r="B70" s="54"/>
-      <c r="C70" s="55"/>
+      <c r="B70" s="54" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C70" s="55" t="s">
+        <v>33</v>
+      </c>
       <c r="D70" s="56"/>
-      <c r="E70" s="57"/>
+      <c r="E70" s="57" t="n">
+        <v>7000</v>
+      </c>
       <c r="F70" s="50"/>
       <c r="G70" s="50"/>
       <c r="H70" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I70" s="50" t="str">
+      <c r="I70" s="50" t="n">
         <f aca="false">IF(E70&gt;0,MIN(E70*H70,G70)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J70" s="50" t="str">
+        <v>700</v>
+      </c>
+      <c r="J70" s="50" t="n">
         <f aca="false">IF(E70&gt;0,F70+I70," ")</f>
-        <v> </v>
-      </c>
-      <c r="K70" s="50" t="str">
+        <v>700</v>
+      </c>
+      <c r="K70" s="50" t="n">
         <f aca="false">IF(E70&gt;0,IF(V70&gt;0,0,E70-J70)," ")</f>
-        <v> </v>
+        <v>6300</v>
       </c>
       <c r="L70" s="50"/>
       <c r="M70" s="58"/>
@@ -5335,14 +5341,14 @@
         <f aca="false">IF(B70&gt;0,IF(B70&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q70" s="47" t="str">
+      <c r="Q70" s="47" t="n">
         <f aca="false">IF(E70&gt;0,E70*P70/100," ")</f>
-        <v> </v>
+        <v>7000</v>
       </c>
       <c r="R70" s="47"/>
-      <c r="S70" s="47" t="str">
+      <c r="S70" s="47" t="n">
         <f aca="false">IF(E70&gt;0,E70-Q70," ")</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="T70" s="47"/>
       <c r="U70" s="54"/>
@@ -5367,27 +5373,33 @@
     </row>
     <row r="71" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="42"/>
-      <c r="B71" s="54"/>
-      <c r="C71" s="55"/>
+      <c r="B71" s="54" t="n">
+        <v>46137</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>35</v>
+      </c>
       <c r="D71" s="56"/>
-      <c r="E71" s="57"/>
+      <c r="E71" s="57" t="n">
+        <v>30000</v>
+      </c>
       <c r="F71" s="50"/>
       <c r="G71" s="50"/>
       <c r="H71" s="58" t="n">
         <f aca="false">H$66</f>
         <v>0.1</v>
       </c>
-      <c r="I71" s="50" t="str">
+      <c r="I71" s="50" t="n">
         <f aca="false">IF(E71&gt;0,MIN(E71*H71,G71)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J71" s="50" t="str">
+        <v>3000</v>
+      </c>
+      <c r="J71" s="50" t="n">
         <f aca="false">IF(E71&gt;0,F71+I71," ")</f>
-        <v> </v>
-      </c>
-      <c r="K71" s="50" t="str">
+        <v>3000</v>
+      </c>
+      <c r="K71" s="50" t="n">
         <f aca="false">IF(E71&gt;0,IF(V71&gt;0,0,E71-J71)," ")</f>
-        <v> </v>
+        <v>27000</v>
       </c>
       <c r="L71" s="50"/>
       <c r="M71" s="58"/>
@@ -5397,14 +5409,14 @@
         <f aca="false">IF(B71&gt;0,IF(B71&gt;[1]Admin!$N$11,[1]Admin!$G$7,[1]Admin!$G$5),[1]Admin!$G$5)</f>
         <v>100</v>
       </c>
-      <c r="Q71" s="47" t="str">
+      <c r="Q71" s="47" t="n">
         <f aca="false">IF(E71&gt;0,E71*P71/100," ")</f>
-        <v> </v>
+        <v>30000</v>
       </c>
       <c r="R71" s="47"/>
-      <c r="S71" s="47" t="str">
+      <c r="S71" s="47" t="n">
         <f aca="false">IF(E71&gt;0,E71-Q71," ")</f>
-        <v> </v>
+        <v>0</v>
       </c>
       <c r="T71" s="47"/>
       <c r="U71" s="54"/>
@@ -5616,13 +5628,13 @@
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C75" s="59"/>
       <c r="D75" s="59"/>
       <c r="E75" s="60" t="n">
         <f aca="false">SUM(E67:E74)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F75" s="61" t="n">
         <f aca="false">SUM(F67:F74)</f>
@@ -5635,15 +5647,15 @@
       <c r="H75" s="58"/>
       <c r="I75" s="61" t="n">
         <f aca="false">SUM(I67:I74)</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="J75" s="61" t="n">
         <f aca="false">SUM(J67:J74)</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="K75" s="61" t="n">
         <f aca="false">SUM(K67:K74)</f>
-        <v>29250</v>
+        <v>47250</v>
       </c>
       <c r="L75" s="50"/>
       <c r="M75" s="58"/>
@@ -5655,7 +5667,7 @@
       <c r="P75" s="62"/>
       <c r="Q75" s="61" t="n">
         <f aca="false">SUM(Q67:Q74)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="R75" s="61" t="n">
         <f aca="false">SUM(R67:R74)</f>
@@ -6065,7 +6077,7 @@
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C83" s="59"/>
       <c r="D83" s="59"/>
@@ -6700,7 +6712,7 @@
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="42"/>
       <c r="B94" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="59"/>
@@ -7495,7 +7507,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7600,7 +7612,7 @@
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="42"/>
       <c r="B110" s="43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C110" s="43"/>
       <c r="D110" s="86" t="n">
@@ -7609,7 +7621,7 @@
       </c>
       <c r="E110" s="73" t="n">
         <f aca="false">E64+E75+E83+E94+E108</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F110" s="73" t="n">
         <f aca="false">F64+F75+F83+F94+F108</f>
@@ -7622,15 +7634,15 @@
       <c r="H110" s="58"/>
       <c r="I110" s="73" t="n">
         <f aca="false">I64+I75+I83+I94+I108</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="J110" s="73" t="n">
         <f aca="false">J64+J75+J83+J94+J108</f>
-        <v>3250</v>
+        <v>5250</v>
       </c>
       <c r="K110" s="73" t="n">
         <f aca="false">K64+K75+K83+K94+K108</f>
-        <v>29250</v>
+        <v>47250</v>
       </c>
       <c r="L110" s="50"/>
       <c r="M110" s="58"/>
@@ -7642,7 +7654,7 @@
       <c r="P110" s="62"/>
       <c r="Q110" s="73" t="n">
         <f aca="false">Q64+Q75+Q83+Q94+Q108</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="R110" s="73" t="n">
         <f aca="false">R64+R75+R83+R94+R108</f>
@@ -7834,7 +7846,7 @@
       <c r="C2" s="101"/>
       <c r="D2" s="102"/>
       <c r="E2" s="103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2" s="103"/>
       <c r="G2" s="103"/>
@@ -7885,7 +7897,7 @@
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="99"/>
       <c r="B4" s="109" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="101"/>
       <c r="D4" s="102"/>
@@ -7894,17 +7906,17 @@
       </c>
       <c r="F4" s="104"/>
       <c r="G4" s="111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
       <c r="J4" s="104"/>
       <c r="K4" s="110" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L4" s="104"/>
       <c r="M4" s="112" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N4" s="112"/>
       <c r="O4" s="106"/>
@@ -7921,14 +7933,14 @@
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="99"/>
       <c r="B5" s="100" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="101"/>
       <c r="D5" s="102"/>
       <c r="E5" s="104"/>
       <c r="F5" s="104"/>
       <c r="G5" s="100" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" s="101"/>
       <c r="I5" s="102"/>
@@ -7961,7 +7973,7 @@
       </c>
       <c r="F6" s="104"/>
       <c r="G6" s="113" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" s="113"/>
       <c r="I6" s="113"/>
@@ -7987,17 +7999,17 @@
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="99"/>
       <c r="B7" s="113" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="113"/>
       <c r="D7" s="113"/>
       <c r="E7" s="114" t="n">
         <f aca="false">Schedule!E75</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F7" s="104"/>
       <c r="G7" s="113" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7" s="113"/>
       <c r="I7" s="113"/>
@@ -8023,7 +8035,7 @@
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="99"/>
       <c r="B8" s="113" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="113"/>
       <c r="D8" s="113"/>
@@ -8033,7 +8045,7 @@
       </c>
       <c r="F8" s="104"/>
       <c r="G8" s="113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" s="113"/>
       <c r="I8" s="113"/>
@@ -8059,7 +8071,7 @@
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="99"/>
       <c r="B9" s="113" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="113"/>
       <c r="D9" s="113"/>
@@ -8069,7 +8081,7 @@
       </c>
       <c r="F9" s="104"/>
       <c r="G9" s="113" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H9" s="113"/>
       <c r="I9" s="113"/>
@@ -8095,7 +8107,7 @@
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="99"/>
       <c r="B10" s="113" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="113"/>
       <c r="D10" s="113"/>
@@ -8105,7 +8117,7 @@
       </c>
       <c r="F10" s="104"/>
       <c r="G10" s="113" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" s="113"/>
       <c r="I10" s="113"/>
@@ -8131,17 +8143,17 @@
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="99"/>
       <c r="B11" s="115" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="115"/>
       <c r="D11" s="115"/>
       <c r="E11" s="116" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="F11" s="104"/>
       <c r="G11" s="117" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="117"/>
@@ -8193,7 +8205,7 @@
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="99"/>
       <c r="B13" s="115" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="115"/>
       <c r="D13" s="115"/>
@@ -8203,7 +8215,7 @@
       </c>
       <c r="F13" s="104"/>
       <c r="G13" s="117" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="117"/>
@@ -8388,7 +8400,7 @@
       <c r="A2" s="129"/>
       <c r="B2" s="132"/>
       <c r="C2" s="133" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="133"/>
       <c r="E2" s="134" t="n">
@@ -8397,7 +8409,7 @@
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="136" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" s="136"/>
       <c r="I2" s="136"/>
@@ -8409,7 +8421,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="129"/>
       <c r="B3" s="137" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="138"/>
@@ -8441,33 +8453,33 @@
     <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" s="141" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F5" s="141" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I5" s="141" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="141"/>
       <c r="K5" s="141"/>
       <c r="L5" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M5" s="140"/>
     </row>
@@ -8481,13 +8493,13 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6" s="141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K6" s="141" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="140"/>
@@ -8513,10 +8525,10 @@
         <v>45992</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="134" t="n">
         <v>13000</v>
@@ -8543,7 +8555,7 @@
         <v>90</v>
       </c>
       <c r="L8" s="56" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="M8" s="129"/>
     </row>
@@ -8568,7 +8580,7 @@
         <v>46082</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" s="56" t="s">
         <v>73</v>
@@ -8598,7 +8610,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="56" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="M10" s="129"/>
     </row>
@@ -8981,33 +8993,33 @@
     <row r="31" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="140"/>
       <c r="B31" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E31" s="141" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F31" s="141" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G31" s="141" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I31" s="141" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J31" s="141"/>
       <c r="K31" s="141"/>
       <c r="L31" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M31" s="140"/>
     </row>
@@ -9021,13 +9033,13 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J32" s="141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K32" s="141" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L32" s="21"/>
       <c r="M32" s="140"/>

--- a/examples/ltd-latest/Fixedassets.xlsx
+++ b/examples/ltd-latest/Fixedassets.xlsx
@@ -1332,6 +1332,11 @@
           </cell>
         </row>
         <row r="6">
+          <cell r="G6">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="6">
           <cell r="L6">
             <v>46296</v>
           </cell>
@@ -1344,16 +1349,6 @@
         <row r="7">
           <cell r="N7">
             <v>46660</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11">
-            <v>12000</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="G11">
-            <v>3000</v>
           </cell>
         </row>
         <row r="11">
@@ -1563,11 +1558,11 @@
       </c>
       <c r="R1" s="13" t="n">
         <f aca="false">R57+R110</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="S1" s="13" t="n">
         <f aca="false">S57+S110</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T1" s="16"/>
       <c r="U1" s="17" t="s">
@@ -1587,7 +1582,7 @@
       </c>
       <c r="Y1" s="13" t="n">
         <f aca="false">Y57+Y110</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z1" s="13" t="n">
         <f aca="false">Z57+Z110</f>
@@ -1723,7 +1718,8 @@
       </c>
       <c r="Q4" s="22"/>
       <c r="R4" s="28" t="n">
-        <v>20</v>
+        <f aca="false">[1]Admin!$G$6</f>
+        <v>14</v>
       </c>
       <c r="S4" s="10" t="n">
         <f aca="false">J4</f>
@@ -3884,7 +3880,7 @@
       <c r="P44" s="48"/>
       <c r="Q44" s="47"/>
       <c r="R44" s="47" t="str">
-        <f aca="false">IF(O44&gt;0,MIN(O44*R$4/100*(1-M44),3000*(1-M44))," ")</f>
+        <f aca="false">IF(O44&gt;0,O44*R$4/100*(1-M44)," ")</f>
         <v> </v>
       </c>
       <c r="S44" s="47" t="str">
@@ -3948,7 +3944,7 @@
       <c r="P45" s="48"/>
       <c r="Q45" s="47"/>
       <c r="R45" s="47" t="str">
-        <f aca="false">IF(O45&gt;0,MIN(O45*R$4/100*(1-M45),3000*(1-M45))," ")</f>
+        <f aca="false">IF(O45&gt;0,O45*R$4/100*(1-M45)," ")</f>
         <v> </v>
       </c>
       <c r="S45" s="47" t="str">
@@ -4012,7 +4008,7 @@
       <c r="P46" s="48"/>
       <c r="Q46" s="47"/>
       <c r="R46" s="47" t="str">
-        <f aca="false">IF(O46&gt;0,MIN(O46*R$4/100*(1-M46),3000*(1-M46))," ")</f>
+        <f aca="false">IF(O46&gt;0,O46*R$4/100*(1-M46)," ")</f>
         <v> </v>
       </c>
       <c r="S46" s="47" t="str">
@@ -4076,7 +4072,7 @@
       <c r="P47" s="48"/>
       <c r="Q47" s="47"/>
       <c r="R47" s="47" t="str">
-        <f aca="false">IF(O47&gt;0,MIN(O47*R$4/100*(1-M47),3000*(1-M47))," ")</f>
+        <f aca="false">IF(O47&gt;0,O47*R$4/100*(1-M47)," ")</f>
         <v> </v>
       </c>
       <c r="S47" s="47" t="str">
@@ -4140,7 +4136,7 @@
       <c r="P48" s="48"/>
       <c r="Q48" s="47"/>
       <c r="R48" s="47" t="str">
-        <f aca="false">IF(O48&gt;0,MIN(O48*R$4/100*(1-M48),3000*(1-M48))," ")</f>
+        <f aca="false">IF(O48&gt;0,O48*R$4/100*(1-M48)," ")</f>
         <v> </v>
       </c>
       <c r="S48" s="47" t="str">
@@ -4243,12 +4239,12 @@
       <c r="P50" s="48"/>
       <c r="Q50" s="47"/>
       <c r="R50" s="47" t="n">
-        <f aca="false">IF(O50&gt;0,IF(O50&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M50),O50*R$4/100)*(1-M50)," ")</f>
-        <v>3000</v>
+        <f aca="false">IF(O50&gt;0,O50*R$4/100*(1-M50)," ")</f>
+        <v>3360</v>
       </c>
       <c r="S50" s="47" t="n">
         <f aca="false">IF(O50&gt;0,O50-R50," ")</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T50" s="47"/>
       <c r="U50" s="54" t="n">
@@ -4267,7 +4263,7 @@
       </c>
       <c r="Y50" s="47" t="n">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&lt;S50,(S50-V50)*(1-M50)," ")," ")</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z50" s="47" t="str">
         <f aca="false">IF((U50+V50)&gt;0,IF(V50&gt;S50,(V50-S50)*(1-M50)," ")," ")</f>
@@ -4311,7 +4307,7 @@
       <c r="P51" s="48"/>
       <c r="Q51" s="47"/>
       <c r="R51" s="47" t="str">
-        <f aca="false">IF(O51&gt;0,IF(O51&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M51),O51*R$4/100)*(1-M51)," ")</f>
+        <f aca="false">IF(O51&gt;0,O51*R$4/100*(1-M51)," ")</f>
         <v> </v>
       </c>
       <c r="S51" s="47" t="str">
@@ -4375,7 +4371,7 @@
       <c r="P52" s="48"/>
       <c r="Q52" s="47"/>
       <c r="R52" s="47" t="str">
-        <f aca="false">IF(O52&gt;0,IF(O52&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M52),O52*R$4/100)*(1-M52)," ")</f>
+        <f aca="false">IF(O52&gt;0,O52*R$4/100*(1-M52)," ")</f>
         <v> </v>
       </c>
       <c r="S52" s="47" t="str">
@@ -4439,7 +4435,7 @@
       <c r="P53" s="48"/>
       <c r="Q53" s="47"/>
       <c r="R53" s="47" t="str">
-        <f aca="false">IF(O53&gt;0,IF(O53&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M53),O53*R$4/100)*(1-M53)," ")</f>
+        <f aca="false">IF(O53&gt;0,O53*R$4/100*(1-M53)," ")</f>
         <v> </v>
       </c>
       <c r="S53" s="47" t="str">
@@ -4503,7 +4499,7 @@
       <c r="P54" s="48"/>
       <c r="Q54" s="47"/>
       <c r="R54" s="47" t="str">
-        <f aca="false">IF(O54&gt;0,IF(O54&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M54),O54*R$4/100)*(1-M54)," ")</f>
+        <f aca="false">IF(O54&gt;0,O54*R$4/100*(1-M54)," ")</f>
         <v> </v>
       </c>
       <c r="S54" s="47" t="str">
@@ -4578,11 +4574,11 @@
       </c>
       <c r="R55" s="61" t="n">
         <f aca="false">SUM(R44:R54)</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="S55" s="61" t="n">
         <f aca="false">SUM(S44:S54)</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T55" s="50"/>
       <c r="U55" s="49"/>
@@ -4600,7 +4596,7 @@
       </c>
       <c r="Y55" s="61" t="n">
         <f aca="false">SUM(Y44:Y54)</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z55" s="61" t="n">
         <f aca="false">SUM(Z44:Z54)</f>
@@ -4687,11 +4683,11 @@
       </c>
       <c r="R57" s="73" t="n">
         <f aca="false">R11+R22+R30+R41+R55</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="S57" s="73" t="n">
         <f aca="false">S11+S22+S30+S41+S55</f>
-        <v>21000</v>
+        <v>20640</v>
       </c>
       <c r="T57" s="47"/>
       <c r="U57" s="49"/>
@@ -4709,7 +4705,7 @@
       </c>
       <c r="Y57" s="73" t="n">
         <f aca="false">Y11+Y22+Y30+Y41+Y55</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="Z57" s="73" t="n">
         <f aca="false">Z11+Z22+Z30+Z41+Z55</f>
@@ -6881,7 +6877,7 @@
       <c r="P97" s="48"/>
       <c r="Q97" s="47"/>
       <c r="R97" s="47" t="str">
-        <f aca="false">IF(E97&gt;0,IF(E97&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M97),E97*R$4/100)*(1-M97)," ")</f>
+        <f aca="false">IF(E97&gt;0,E97*R$4/100*(1-M97)," ")</f>
         <v> </v>
       </c>
       <c r="S97" s="47" t="str">
@@ -6942,7 +6938,7 @@
       <c r="P98" s="48"/>
       <c r="Q98" s="47"/>
       <c r="R98" s="47" t="str">
-        <f aca="false">IF(E98&gt;0,IF(E98&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M98),E98*R$4/100)*(1-M98)," ")</f>
+        <f aca="false">IF(E98&gt;0,E98*R$4/100*(1-M98)," ")</f>
         <v> </v>
       </c>
       <c r="S98" s="47" t="str">
@@ -7003,7 +6999,7 @@
       <c r="P99" s="48"/>
       <c r="Q99" s="47"/>
       <c r="R99" s="47" t="str">
-        <f aca="false">IF(E99&gt;0,IF(E99&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M99),E99*R$4/100)*(1-M99)," ")</f>
+        <f aca="false">IF(E99&gt;0,E99*R$4/100*(1-M99)," ")</f>
         <v> </v>
       </c>
       <c r="S99" s="47" t="str">
@@ -7064,7 +7060,7 @@
       <c r="P100" s="48"/>
       <c r="Q100" s="47"/>
       <c r="R100" s="47" t="str">
-        <f aca="false">IF(E100&gt;0,IF(E100&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M100),E100*R$4/100)*(1-M100)," ")</f>
+        <f aca="false">IF(E100&gt;0,E100*R$4/100*(1-M100)," ")</f>
         <v> </v>
       </c>
       <c r="S100" s="47" t="str">
@@ -7125,7 +7121,7 @@
       <c r="P101" s="48"/>
       <c r="Q101" s="47"/>
       <c r="R101" s="47" t="str">
-        <f aca="false">IF(E101&gt;0,IF(E101&gt;[1]Admin!$E$11,[1]Admin!$G$11*(1-M101),E101*R$4/100)*(1-M101)," ")</f>
+        <f aca="false">IF(E101&gt;0,E101*R$4/100*(1-M101)," ")</f>
         <v> </v>
       </c>
       <c r="S101" s="47" t="str">

--- a/examples/ltd-latest/Fixedassets.xlsx
+++ b/examples/ltd-latest/Fixedassets.xlsx
@@ -14,6 +14,8 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Schedule!$A:$G,Schedule!$1:$4</definedName>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
   <si>
     <t xml:space="preserve">Date Asset Purchased</t>
   </si>
@@ -204,6 +206,9 @@
   </si>
   <si>
     <t xml:space="preserve">Land &amp; Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office premises</t>
   </si>
   <si>
     <t xml:space="preserve">Plant &amp; Machinery</t>
@@ -1299,11 +1304,21 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="13">
+          <cell r="G13">
+            <v>200000</v>
+          </cell>
+        </row>
+        <row r="13">
           <cell r="J13">
             <v>3000</v>
           </cell>
           <cell r="K13">
             <v>30000</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="M13">
+            <v>40000</v>
           </cell>
         </row>
         <row r="13">
@@ -1338,7 +1353,7 @@
         </row>
         <row r="6">
           <cell r="L6">
-            <v>46296</v>
+            <v>46327</v>
           </cell>
         </row>
         <row r="7">
@@ -1348,15 +1363,105 @@
         </row>
         <row r="7">
           <cell r="N7">
-            <v>46660</v>
+            <v>46691</v>
           </cell>
         </row>
         <row r="11">
           <cell r="N11">
-            <v>46660</v>
+            <v>46691</v>
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="OpeningCreditors"/>
+      <sheetName val="Nov"/>
+      <sheetName val="Dec"/>
+      <sheetName val="Jan"/>
+      <sheetName val="Feb"/>
+      <sheetName val="Mar"/>
+      <sheetName val="Apr"/>
+      <sheetName val="May"/>
+      <sheetName val="Jun"/>
+      <sheetName val="Jul"/>
+      <sheetName val="Aug"/>
+      <sheetName val="Sep"/>
+      <sheetName val="Oct"/>
+      <sheetName val="ClosingCreditors"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
+        <row r="2">
+          <cell r="AI2">
+            <v>52500</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="OpeningDebtors"/>
+      <sheetName val="Nov"/>
+      <sheetName val="Dec"/>
+      <sheetName val="Jan"/>
+      <sheetName val="Feb"/>
+      <sheetName val="Mar"/>
+      <sheetName val="Apr"/>
+      <sheetName val="May"/>
+      <sheetName val="Jun"/>
+      <sheetName val="Jul"/>
+      <sheetName val="Aug"/>
+      <sheetName val="Sep"/>
+      <sheetName val="Oct"/>
+      <sheetName val="ClosingDebtors"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
+        <row r="2">
+          <cell r="U2">
+            <v>12500</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1515,15 +1620,15 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12" t="n">
         <f aca="false">E57+E110</f>
-        <v>85500</v>
+        <v>285500</v>
       </c>
       <c r="F1" s="13" t="n">
         <f aca="false">F57+F110</f>
-        <v>10098</v>
+        <v>50098</v>
       </c>
       <c r="G1" s="13" t="n">
         <f aca="false">G57+G110</f>
-        <v>22902</v>
+        <v>182902</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>2</v>
@@ -1534,11 +1639,11 @@
       </c>
       <c r="J1" s="13" t="n">
         <f aca="false">J57+J110</f>
-        <v>23838</v>
+        <v>63838</v>
       </c>
       <c r="K1" s="13" t="n">
         <f aca="false">K57+K110</f>
-        <v>48990</v>
+        <v>208990</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="14" t="s">
@@ -1690,28 +1795,28 @@
       <c r="E4" s="22"/>
       <c r="F4" s="26" t="n">
         <f aca="false">D6</f>
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="G4" s="26" t="n">
         <f aca="false">D6</f>
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="23"/>
       <c r="J4" s="26" t="n">
         <f aca="false">[1]Admin!$N$7</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="K4" s="26" t="n">
         <f aca="false">J4</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
       <c r="N4" s="13"/>
       <c r="O4" s="10" t="n">
         <f aca="false">D6</f>
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="P4" s="27" t="n">
         <v>100</v>
@@ -1723,7 +1828,7 @@
       </c>
       <c r="S4" s="10" t="n">
         <f aca="false">J4</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="T4" s="16"/>
       <c r="U4" s="17"/>
@@ -1771,7 +1876,7 @@
       <c r="C6" s="43"/>
       <c r="D6" s="44" t="n">
         <f aca="false">[1]Admin!$L$6</f>
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="E6" s="44"/>
       <c r="F6" s="45"/>
@@ -1833,29 +1938,35 @@
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42"/>
       <c r="B8" s="54"/>
-      <c r="C8" s="55"/>
+      <c r="C8" s="55" t="s">
+        <v>22</v>
+      </c>
       <c r="D8" s="56"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="50" t="str">
+      <c r="E8" s="57" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F8" s="57" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G8" s="50" t="n">
         <f aca="false">IF(E8&gt;0,E8-F8," ")</f>
-        <v> </v>
+        <v>160000</v>
       </c>
       <c r="H8" s="58" t="n">
         <f aca="false">H$7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="50" t="str">
+      <c r="I8" s="50" t="n">
         <f aca="false">IF(E8&gt;0,MIN(E8*H8,G8)," ")</f>
-        <v> </v>
-      </c>
-      <c r="J8" s="50" t="str">
+        <v>0</v>
+      </c>
+      <c r="J8" s="50" t="n">
         <f aca="false">IF(E8&gt;0,F8+I8," ")</f>
-        <v> </v>
-      </c>
-      <c r="K8" s="50" t="str">
+        <v>40000</v>
+      </c>
+      <c r="K8" s="50" t="n">
         <f aca="false">IF(E8&gt;0,IF(V8&gt;0,0,E8-J8)," ")</f>
-        <v> </v>
+        <v>160000</v>
       </c>
       <c r="L8" s="50"/>
       <c r="M8" s="58"/>
@@ -1990,15 +2101,15 @@
       <c r="D11" s="59"/>
       <c r="E11" s="60" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F11" s="60" t="n">
         <f aca="false">SUM(F8:F10)</f>
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="G11" s="61" t="n">
         <f aca="false">SUM(G8:G10)</f>
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="H11" s="58"/>
       <c r="I11" s="61" t="n">
@@ -2007,11 +2118,11 @@
       </c>
       <c r="J11" s="61" t="n">
         <f aca="false">SUM(J8:J10)</f>
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="K11" s="61" t="n">
         <f aca="false">SUM(K8:K10)</f>
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="L11" s="50"/>
       <c r="M11" s="58"/>
@@ -2089,7 +2200,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="42"/>
       <c r="B13" s="51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="51"/>
       <c r="D13" s="62"/>
@@ -2724,7 +2835,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="42"/>
       <c r="B24" s="51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="62"/>
@@ -3173,7 +3284,7 @@
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="42"/>
       <c r="B32" s="51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="68"/>
@@ -3207,7 +3318,7 @@
       <c r="A33" s="42"/>
       <c r="B33" s="54"/>
       <c r="C33" s="55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" s="56"/>
       <c r="E33" s="57" t="n">
@@ -3814,7 +3925,7 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="42"/>
       <c r="B43" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="68"/>
@@ -4167,7 +4278,7 @@
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="42"/>
       <c r="B49" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C49" s="51"/>
       <c r="D49" s="62"/>
@@ -4199,7 +4310,7 @@
       <c r="A50" s="42"/>
       <c r="B50" s="54"/>
       <c r="C50" s="55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D50" s="56"/>
       <c r="E50" s="57" t="n">
@@ -4248,7 +4359,7 @@
       </c>
       <c r="T50" s="47"/>
       <c r="U50" s="54" t="n">
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="V50" s="57" t="n">
         <v>12500</v>
@@ -4642,19 +4753,19 @@
       <c r="C57" s="43"/>
       <c r="D57" s="72" t="n">
         <f aca="false">D6</f>
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="E57" s="73" t="n">
         <f aca="false">E11+E22+E30+E41+E55</f>
-        <v>33000</v>
+        <v>233000</v>
       </c>
       <c r="F57" s="73" t="n">
         <f aca="false">F11+F22+F30+F41+F55</f>
-        <v>10098</v>
+        <v>50098</v>
       </c>
       <c r="G57" s="73" t="n">
         <f aca="false">G11+G22+G30+G41+G55</f>
-        <v>22902</v>
+        <v>182902</v>
       </c>
       <c r="H57" s="58"/>
       <c r="I57" s="73" t="n">
@@ -4663,11 +4774,11 @@
       </c>
       <c r="J57" s="73" t="n">
         <f aca="false">J11+J22+J30+J41+J55</f>
-        <v>18588</v>
+        <v>58588</v>
       </c>
       <c r="K57" s="73" t="n">
         <f aca="false">K11+K22+K30+K41+K55</f>
-        <v>1740</v>
+        <v>161740</v>
       </c>
       <c r="L57" s="50"/>
       <c r="M57" s="58"/>
@@ -4745,19 +4856,19 @@
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="42"/>
       <c r="B59" s="77" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C59" s="77"/>
       <c r="D59" s="78" t="n">
         <f aca="false">D57</f>
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="E59" s="79" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F59" s="80" t="n">
         <f aca="false">J4</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="G59" s="81"/>
       <c r="H59" s="58"/>
@@ -4959,7 +5070,7 @@
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="42"/>
       <c r="B64" s="59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
@@ -5064,7 +5175,7 @@
     <row r="66" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="42"/>
       <c r="B66" s="51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C66" s="51"/>
       <c r="D66" s="62"/>
@@ -5098,10 +5209,10 @@
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42"/>
       <c r="B67" s="54" t="n">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D67" s="56"/>
       <c r="E67" s="57" t="n">
@@ -5166,10 +5277,10 @@
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
       <c r="B68" s="54" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="C68" s="55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D68" s="56"/>
       <c r="E68" s="57" t="n">
@@ -5234,10 +5345,10 @@
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
       <c r="B69" s="54" t="n">
-        <v>46037</v>
+        <v>46068</v>
       </c>
       <c r="C69" s="55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D69" s="56"/>
       <c r="E69" s="57" t="n">
@@ -5302,10 +5413,10 @@
     <row r="70" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="42"/>
       <c r="B70" s="54" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D70" s="56"/>
       <c r="E70" s="57" t="n">
@@ -5370,10 +5481,10 @@
     <row r="71" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="42"/>
       <c r="B71" s="54" t="n">
-        <v>46137</v>
+        <v>46167</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D71" s="56"/>
       <c r="E71" s="57" t="n">
@@ -5624,7 +5735,7 @@
     <row r="75" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="42"/>
       <c r="B75" s="59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C75" s="59"/>
       <c r="D75" s="59"/>
@@ -5729,7 +5840,7 @@
     <row r="77" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="42"/>
       <c r="B77" s="51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C77" s="51"/>
       <c r="D77" s="62"/>
@@ -6073,7 +6184,7 @@
     <row r="83" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="42"/>
       <c r="B83" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C83" s="59"/>
       <c r="D83" s="59"/>
@@ -6178,7 +6289,7 @@
     <row r="85" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="42"/>
       <c r="B85" s="51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C85" s="51"/>
       <c r="D85" s="68"/>
@@ -6708,7 +6819,7 @@
     <row r="94" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="42"/>
       <c r="B94" s="59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="59"/>
@@ -6813,7 +6924,7 @@
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="42"/>
       <c r="B96" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C96" s="51"/>
       <c r="D96" s="68"/>
@@ -7152,7 +7263,7 @@
     <row r="102" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="42"/>
       <c r="B102" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C102" s="51"/>
       <c r="D102" s="68"/>
@@ -7503,7 +7614,7 @@
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="42"/>
       <c r="B108" s="59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C108" s="59"/>
       <c r="D108" s="59"/>
@@ -7608,12 +7719,12 @@
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="42"/>
       <c r="B110" s="43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C110" s="43"/>
       <c r="D110" s="86" t="n">
         <f aca="false">F59</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="E110" s="73" t="n">
         <f aca="false">E64+E75+E83+E94+E108</f>
@@ -7842,7 +7953,7 @@
       <c r="C2" s="101"/>
       <c r="D2" s="102"/>
       <c r="E2" s="103" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" s="103"/>
       <c r="G2" s="103"/>
@@ -7893,7 +8004,7 @@
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="99"/>
       <c r="B4" s="109" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="101"/>
       <c r="D4" s="102"/>
@@ -7902,17 +8013,17 @@
       </c>
       <c r="F4" s="104"/>
       <c r="G4" s="111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
       <c r="J4" s="104"/>
       <c r="K4" s="110" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L4" s="104"/>
       <c r="M4" s="112" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N4" s="112"/>
       <c r="O4" s="106"/>
@@ -7929,14 +8040,14 @@
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="99"/>
       <c r="B5" s="100" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="101"/>
       <c r="D5" s="102"/>
       <c r="E5" s="104"/>
       <c r="F5" s="104"/>
       <c r="G5" s="100" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="101"/>
       <c r="I5" s="102"/>
@@ -7959,7 +8070,7 @@
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="99"/>
       <c r="B6" s="113" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="113"/>
       <c r="D6" s="113"/>
@@ -7969,7 +8080,7 @@
       </c>
       <c r="F6" s="104"/>
       <c r="G6" s="113" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="113"/>
       <c r="I6" s="113"/>
@@ -7995,7 +8106,7 @@
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="99"/>
       <c r="B7" s="113" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="113"/>
       <c r="D7" s="113"/>
@@ -8005,7 +8116,7 @@
       </c>
       <c r="F7" s="104"/>
       <c r="G7" s="113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7" s="113"/>
       <c r="I7" s="113"/>
@@ -8031,7 +8142,7 @@
     <row r="8" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="99"/>
       <c r="B8" s="113" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="113"/>
       <c r="D8" s="113"/>
@@ -8041,7 +8152,7 @@
       </c>
       <c r="F8" s="104"/>
       <c r="G8" s="113" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8" s="113"/>
       <c r="I8" s="113"/>
@@ -8067,7 +8178,7 @@
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="99"/>
       <c r="B9" s="113" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="113"/>
       <c r="D9" s="113"/>
@@ -8077,7 +8188,7 @@
       </c>
       <c r="F9" s="104"/>
       <c r="G9" s="113" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="113"/>
       <c r="I9" s="113"/>
@@ -8103,7 +8214,7 @@
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="99"/>
       <c r="B10" s="113" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="113"/>
       <c r="D10" s="113"/>
@@ -8113,7 +8224,7 @@
       </c>
       <c r="F10" s="104"/>
       <c r="G10" s="113" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="113"/>
       <c r="I10" s="113"/>
@@ -8139,7 +8250,7 @@
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="99"/>
       <c r="B11" s="115" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="115"/>
       <c r="D11" s="115"/>
@@ -8149,7 +8260,7 @@
       </c>
       <c r="F11" s="104"/>
       <c r="G11" s="117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="117"/>
@@ -8201,24 +8312,24 @@
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="99"/>
       <c r="B13" s="115" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="115"/>
       <c r="D13" s="115"/>
-      <c r="E13" s="116" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="E13" s="116" t="n">
+        <f aca="false">[2]Oct!$AI$2</f>
+        <v>52500</v>
       </c>
       <c r="F13" s="104"/>
       <c r="G13" s="117" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="117"/>
       <c r="J13" s="117"/>
-      <c r="K13" s="116" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="K13" s="116" t="n">
+        <f aca="false">[3]Oct!$U$2</f>
+        <v>12500</v>
       </c>
       <c r="L13" s="104"/>
       <c r="M13" s="112"/>
@@ -8262,27 +8373,27 @@
     </row>
     <row r="15" s="1" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="99"/>
-      <c r="B15" s="118" t="e">
+      <c r="B15" s="118" t="str">
         <f aca="false">IF(E15&gt;0,"Purchases exceed Assets listed on Schedule",IF(E15&lt;0,"Assets listed on Schedule exceed Purchase values","Purchases reconcile with Fixed asset Schedule"))</f>
-        <v>#N/A</v>
+        <v>Purchases reconcile with Fixed asset Schedule</v>
       </c>
       <c r="C15" s="118"/>
       <c r="D15" s="118"/>
-      <c r="E15" s="119" t="e">
+      <c r="E15" s="119" t="n">
         <f aca="false">E13-E11</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="F15" s="104"/>
-      <c r="G15" s="118" t="e">
+      <c r="G15" s="118" t="str">
         <f aca="false">IF(K15&gt;0,"Sales exceed Assets listed on Schedule",IF(K15&lt;0,"Assets listed on Schedule exceed Sales values","Sales reconcile with Fixed asset Schedule"))</f>
-        <v>#N/A</v>
+        <v>Sales reconcile with Fixed asset Schedule</v>
       </c>
       <c r="H15" s="118"/>
       <c r="I15" s="118"/>
       <c r="J15" s="118"/>
-      <c r="K15" s="119" t="e">
+      <c r="K15" s="119" t="n">
         <f aca="false">K13-K11</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="L15" s="104"/>
       <c r="M15" s="112"/>
@@ -8396,7 +8507,7 @@
       <c r="A2" s="129"/>
       <c r="B2" s="132"/>
       <c r="C2" s="133" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" s="133"/>
       <c r="E2" s="134" t="n">
@@ -8405,7 +8516,7 @@
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="136" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H2" s="136"/>
       <c r="I2" s="136"/>
@@ -8417,7 +8528,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="129"/>
       <c r="B3" s="137" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="138"/>
@@ -8449,33 +8560,33 @@
     <row r="5" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="140"/>
       <c r="B5" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" s="141" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" s="141" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="141" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I5" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="141"/>
       <c r="K5" s="141"/>
       <c r="L5" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M5" s="140"/>
     </row>
@@ -8489,13 +8600,13 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="141" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K6" s="141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="140"/>
@@ -8518,13 +8629,13 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="129"/>
       <c r="B8" s="54" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" s="134" t="n">
         <v>13000</v>
@@ -8551,7 +8662,7 @@
         <v>90</v>
       </c>
       <c r="L8" s="56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M8" s="129"/>
     </row>
@@ -8573,13 +8684,13 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="129"/>
       <c r="B10" s="54" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" s="134" t="n">
         <v>7000</v>
@@ -8606,7 +8717,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M10" s="129"/>
     </row>
@@ -8955,7 +9066,7 @@
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="129"/>
       <c r="B29" s="137" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" s="62"/>
       <c r="D29" s="138"/>
@@ -8963,7 +9074,7 @@
       <c r="F29" s="132"/>
       <c r="G29" s="132"/>
       <c r="H29" s="62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I29" s="132"/>
       <c r="J29" s="132"/>
@@ -8989,33 +9100,33 @@
     <row r="31" s="142" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="140"/>
       <c r="B31" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" s="141" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" s="141" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G31" s="141" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I31" s="141" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J31" s="141"/>
       <c r="K31" s="141"/>
       <c r="L31" s="21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M31" s="140"/>
     </row>
@@ -9029,13 +9140,13 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J32" s="141" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K32" s="141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L32" s="21"/>
       <c r="M32" s="140"/>

--- a/examples/ltd-latest/Fixedassets.xlsx
+++ b/examples/ltd-latest/Fixedassets.xlsx
@@ -4359,7 +4359,7 @@
       </c>
       <c r="T50" s="47"/>
       <c r="U50" s="54" t="n">
-        <v>46152</v>
+        <v>46517</v>
       </c>
       <c r="V50" s="57" t="n">
         <v>12500</v>
@@ -5209,7 +5209,7 @@
     <row r="67" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42"/>
       <c r="B67" s="54" t="n">
-        <v>46006</v>
+        <v>46371</v>
       </c>
       <c r="C67" s="55" t="s">
         <v>33</v>
@@ -5277,7 +5277,7 @@
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42"/>
       <c r="B68" s="54" t="n">
-        <v>46023</v>
+        <v>46388</v>
       </c>
       <c r="C68" s="55" t="s">
         <v>34</v>
@@ -5345,7 +5345,7 @@
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="42"/>
       <c r="B69" s="54" t="n">
-        <v>46068</v>
+        <v>46433</v>
       </c>
       <c r="C69" s="55" t="s">
         <v>35</v>
@@ -5413,7 +5413,7 @@
     <row r="70" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="42"/>
       <c r="B70" s="54" t="n">
-        <v>46113</v>
+        <v>46478</v>
       </c>
       <c r="C70" s="55" t="s">
         <v>34</v>
@@ -5481,7 +5481,7 @@
     <row r="71" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="42"/>
       <c r="B71" s="54" t="n">
-        <v>46167</v>
+        <v>46532</v>
       </c>
       <c r="C71" s="55" t="s">
         <v>36</v>
@@ -8629,7 +8629,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="129"/>
       <c r="B8" s="54" t="n">
-        <v>46023</v>
+        <v>46388</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>72</v>
@@ -8684,7 +8684,7 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="129"/>
       <c r="B10" s="54" t="n">
-        <v>46113</v>
+        <v>46478</v>
       </c>
       <c r="C10" s="56" t="s">
         <v>72</v>
